--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -978,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>978조 7665억 8728만</t>
+    <t>1112조 8677억 9360만</t>
   </si>
   <si>
     <t>빌런투킬</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>933조 5078억 2755만</t>
+    <t>960조 7702억 374만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -1026,6 +1026,15 @@
     <t>147조 7288억 7111만</t>
   </si>
   <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>143조 1307억 9972만</t>
+  </si>
+  <si>
     <t>부엉이없다</t>
   </si>
   <si>
@@ -1035,15 +1044,6 @@
     <t>137조 9189억 5210만</t>
   </si>
   <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>133조 9835억 1204만</t>
-  </si>
-  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>71조 5763억 8505만</t>
+    <t>73조 9039억 3442만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -1095,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>56조 1022억 3684만</t>
+    <t>56조 9226억 6343만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>36조 6013억 1317만</t>
+    <t>36조 7009억 4629만</t>
   </si>
   <si>
     <t>두근푸근연근</t>
@@ -1200,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=junoflo</t>
   </si>
   <si>
-    <t>9조 8206억 4671만</t>
+    <t>10조 5344억 1386만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -5413,7 +5413,7 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>333</v>
@@ -5445,7 +5445,7 @@
         <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>336</v>
@@ -5733,7 +5733,7 @@
         <v>85</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>363</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -1224,7 +1224,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1307조 3651억 6640만</t>
+    <t>1442조 8556억 7433만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
   </si>
   <si>
-    <t>608조 7932억 5418만</t>
+    <t>650조 9376억 9597만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>272조 1241억 8322만</t>
+    <t>311조 8644억 9662만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1278,7 +1278,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
   </si>
   <si>
-    <t>222조 1071억 7012만</t>
+    <t>267조 4873억 4322만</t>
+  </si>
+  <si>
+    <t>26밍밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>146조 2366억 2351만</t>
   </si>
   <si>
     <t>임승민</t>
@@ -1287,7 +1296,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>142조 5227억 3133만</t>
+    <t>146조 1368억 9777만</t>
   </si>
   <si>
     <t>몬함</t>
@@ -1299,22 +1308,13 @@
     <t>124조 7535억 8679만</t>
   </si>
   <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>119조 856억 3291만</t>
-  </si>
-  <si>
     <t>뻔수니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>70조 1185억 192만</t>
+    <t>70조 3138억 1542만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1332,7 +1332,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 2242억 936만</t>
+    <t>37조 4761억 287만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1368,7 +1368,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>17조 8709억 3446만</t>
+    <t>18조 1110억 6972만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1410,7 +1410,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>12조 6004억 5926만</t>
+    <t>12조 8151억 908만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1428,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>9조 5687억 8045만</t>
+    <t>11조 3435억 1205만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1437,7 +1437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>8조 9447억 626만</t>
+    <t>9조 3250억 4217만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1473,7 +1473,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>1경 5137조 5318억 6677만</t>
+    <t>1경 5982조 1294억 8442만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1491,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1477조 4447억 9081만</t>
+    <t>1539조 7438억 6316만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>691조 3520억 132만</t>
+    <t>698조 9405억 1129만</t>
   </si>
   <si>
     <t>송곧</t>
@@ -1572,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>39조 2155억 5761만</t>
+    <t>39조 2931억 101만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1599,7 +1599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
   </si>
   <si>
-    <t>13조 226억 8271만</t>
+    <t>13조 4225억 797만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1608,7 +1608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
   </si>
   <si>
-    <t>11조 9560억 3534만</t>
+    <t>12조 5841억 5205만</t>
   </si>
   <si>
     <t>박미쯔</t>
@@ -1665,7 +1665,16 @@
     <t>99</t>
   </si>
   <si>
-    <t>6조 1297억 4182만</t>
+    <t>6조 2410억 1159만</t>
+  </si>
+  <si>
+    <t>SingA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+  </si>
+  <si>
+    <t>6조 326억 8572만</t>
   </si>
   <si>
     <t>햄쓱이</t>
@@ -1677,559 +1686,550 @@
     <t>5조 4672억 9243만</t>
   </si>
   <si>
-    <t>SingA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+    <t>술취한호랑이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 9474억 7543만</t>
+  </si>
+  <si>
+    <t>수년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
+  </si>
+  <si>
+    <t>4조 3429억 3876만</t>
+  </si>
+  <si>
+    <t>한Poll</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
+  </si>
+  <si>
+    <t>4조 3050억 8452만</t>
+  </si>
+  <si>
+    <t>김치왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>3조 8849억 2658만</t>
+  </si>
+  <si>
+    <t>쿠쏘야로로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>2조 7321억 5062만</t>
+  </si>
+  <si>
+    <t>치즈왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>2조 1846억 5297만</t>
+  </si>
+  <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>9288조 7988억 1546만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>8668조 7855억 1234만</t>
+  </si>
+  <si>
+    <t>실민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>1232조 428억 1327만</t>
+  </si>
+  <si>
+    <t>민실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>760조 7667억 2010만</t>
+  </si>
+  <si>
+    <t>약한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>732조 9186억 8857만</t>
+  </si>
+  <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>317조 9218억 327만</t>
+  </si>
+  <si>
+    <t>문디르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>209조 3802억 6873만</t>
+  </si>
+  <si>
+    <t>항상밝은하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>198조 5777억 2328만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>160조 5093억 7580만</t>
+  </si>
+  <si>
+    <t>봉튜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
+  </si>
+  <si>
+    <t>101조 5005억 6045만</t>
+  </si>
+  <si>
+    <t>월광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>88조 8232억 3579만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>66조 6160억 1431만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>45조 2828억 2447만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>38조 9416억 5281만</t>
+  </si>
+  <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>25조 6837억 4377만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>24조 1275억 9609만</t>
+  </si>
+  <si>
+    <t>김대협</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
+  </si>
+  <si>
+    <t>24조 343억 8478만</t>
+  </si>
+  <si>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>13조 6686억 9958만</t>
+  </si>
+  <si>
+    <t>낭만만듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
+  </si>
+  <si>
+    <t>11조 4930억 9873만</t>
+  </si>
+  <si>
+    <t>봄녘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
+  </si>
+  <si>
+    <t>9조 3942억 2359만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8조 6843억 7977만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>7조 1372억 9919만</t>
+  </si>
+  <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>7조 541억 2250만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>3조 9612억 7314만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>2조 4727억 9722만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>1조 449억 856만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>6424억 6751만</t>
+  </si>
+  <si>
+    <t>용광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>6354억 2182만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>4074억 222만</t>
+  </si>
+  <si>
+    <t>코로드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
+  </si>
+  <si>
+    <t>1경 3094조 6438억 3447만</t>
+  </si>
+  <si>
+    <t>맠스맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A0%EC%8A%A4%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>4719조 300억 9804만</t>
+  </si>
+  <si>
+    <t>슨녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
+  </si>
+  <si>
+    <t>3330조 8692억 9686만</t>
+  </si>
+  <si>
+    <t>Bit숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
+  </si>
+  <si>
+    <t>178조 8088억 5238만</t>
+  </si>
+  <si>
+    <t>김해님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>171조 7664억 5190만</t>
+  </si>
+  <si>
+    <t>빌린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>139조 6154억 5307만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>123조 5425억 2061만</t>
+  </si>
+  <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>56조 5338억 7127만</t>
+  </si>
+  <si>
+    <t>산타선물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>55조 5068억 8947만</t>
+  </si>
+  <si>
+    <t>도령3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
+  </si>
+  <si>
+    <t>52조 2523억 7048만</t>
+  </si>
+  <si>
+    <t>조콩나무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%BD%A9%EB%82%98%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>47조 3657억 4221만</t>
+  </si>
+  <si>
+    <t>이러는거아냐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
+  </si>
+  <si>
+    <t>28조 236억 7493만</t>
+  </si>
+  <si>
+    <t>백엄경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>26조 5534억 6019만</t>
+  </si>
+  <si>
+    <t>숮2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
+  </si>
+  <si>
+    <t>26조 4226억 4497만</t>
+  </si>
+  <si>
+    <t>키움맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%80%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>21조 2617억 8155만</t>
+  </si>
+  <si>
+    <t>천칸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%B8</t>
+  </si>
+  <si>
+    <t>17조 8681억 7133만</t>
+  </si>
+  <si>
+    <t>한유화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>14조 4540억 460만</t>
+  </si>
+  <si>
+    <t>95도도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
+  </si>
+  <si>
+    <t>14조 1726억 7817만</t>
+  </si>
+  <si>
+    <t>최소뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
+  </si>
+  <si>
+    <t>13조 6106억 2682만</t>
+  </si>
+  <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>13조 3904억 8124만</t>
+  </si>
+  <si>
+    <t>혈마신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>8조 4071억 2262만</t>
+  </si>
+  <si>
+    <t>숑당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>7조 1457억 4077만</t>
+  </si>
+  <si>
+    <t>리얼크크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%96%BC%ED%81%AC%ED%81%AC</t>
+  </si>
+  <si>
+    <t>5조 3354억 6934만</t>
+  </si>
+  <si>
+    <t>현즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
+  </si>
+  <si>
+    <t>4조 8579억 3603만</t>
+  </si>
+  <si>
+    <t>박하민린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
   </si>
   <si>
     <t>98</t>
-  </si>
-  <si>
-    <t>5조 4430억 3652만</t>
-  </si>
-  <si>
-    <t>술취한호랑이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 8734억 8870만</t>
-  </si>
-  <si>
-    <t>수년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
-  </si>
-  <si>
-    <t>4조 3429억 3876만</t>
-  </si>
-  <si>
-    <t>한Poll</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
-  </si>
-  <si>
-    <t>4조 3050억 8452만</t>
-  </si>
-  <si>
-    <t>김치왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>3조 8849억 2658만</t>
-  </si>
-  <si>
-    <t>쿠쏘야로로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>2조 6663억 6952만</t>
-  </si>
-  <si>
-    <t>치즈왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>2조 1846억 5297만</t>
-  </si>
-  <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>9288조 7988억 1546만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>8668조 7855억 1234만</t>
-  </si>
-  <si>
-    <t>실민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>1232조 428억 1327만</t>
-  </si>
-  <si>
-    <t>민실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>760조 7667억 2010만</t>
-  </si>
-  <si>
-    <t>약한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>732조 9186억 8857만</t>
-  </si>
-  <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>317조 9218억 327만</t>
-  </si>
-  <si>
-    <t>문디르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>209조 3802억 6873만</t>
-  </si>
-  <si>
-    <t>항상밝은하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>198조 5777억 2328만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>160조 5093억 7580만</t>
-  </si>
-  <si>
-    <t>봉튜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
-  </si>
-  <si>
-    <t>101조 5005억 6045만</t>
-  </si>
-  <si>
-    <t>월광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
-  </si>
-  <si>
-    <t>88조 8232억 3579만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>66조 6160억 1431만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>45조 2828억 2447만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>38조 9416억 5281만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>25조 6837억 4377만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>24조 1275억 9609만</t>
-  </si>
-  <si>
-    <t>김대협</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
-  </si>
-  <si>
-    <t>24조 343억 8478만</t>
-  </si>
-  <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>13조 6686억 9958만</t>
-  </si>
-  <si>
-    <t>낭만만듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
-  </si>
-  <si>
-    <t>11조 4930억 9873만</t>
-  </si>
-  <si>
-    <t>봄녘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
-  </si>
-  <si>
-    <t>9조 3942억 2359만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8조 6843억 7977만</t>
-  </si>
-  <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>7조 1372억 9919만</t>
-  </si>
-  <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>7조 541억 2250만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>3조 9612억 7314만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>2조 4727억 9722만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>1조 449억 856만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>6424억 6751만</t>
-  </si>
-  <si>
-    <t>용광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>6354억 2182만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>4074억 222만</t>
-  </si>
-  <si>
-    <t>코로드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1경 3094조 6438억 3447만</t>
-  </si>
-  <si>
-    <t>맠스맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A0%EC%8A%A4%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>4719조 300억 9804만</t>
-  </si>
-  <si>
-    <t>슨녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
-  </si>
-  <si>
-    <t>3330조 8692억 9686만</t>
-  </si>
-  <si>
-    <t>Bit숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
-  </si>
-  <si>
-    <t>178조 8088억 5238만</t>
-  </si>
-  <si>
-    <t>김해님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>171조 7664억 5190만</t>
-  </si>
-  <si>
-    <t>빌린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>139조 6154억 5307만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>123조 5425억 2061만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>56조 5338억 7127만</t>
-  </si>
-  <si>
-    <t>산타선물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>55조 5068억 8947만</t>
-  </si>
-  <si>
-    <t>도령3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
-  </si>
-  <si>
-    <t>52조 2523억 7048만</t>
-  </si>
-  <si>
-    <t>조콩나무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%BD%A9%EB%82%98%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>47조 3657억 4221만</t>
-  </si>
-  <si>
-    <t>이러는거아냐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
-  </si>
-  <si>
-    <t>28조 236억 7493만</t>
-  </si>
-  <si>
-    <t>백엄경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>26조 5534억 6019만</t>
-  </si>
-  <si>
-    <t>숮2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
-  </si>
-  <si>
-    <t>26조 4226억 4497만</t>
-  </si>
-  <si>
-    <t>키움맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%80%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>21조 2617억 8155만</t>
-  </si>
-  <si>
-    <t>천칸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%B8</t>
-  </si>
-  <si>
-    <t>17조 8681억 7133만</t>
-  </si>
-  <si>
-    <t>한유화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>14조 4540억 460만</t>
-  </si>
-  <si>
-    <t>95도도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
-  </si>
-  <si>
-    <t>14조 1726억 7817만</t>
-  </si>
-  <si>
-    <t>최소뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
-  </si>
-  <si>
-    <t>13조 6106억 2682만</t>
-  </si>
-  <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>13조 3904억 8124만</t>
-  </si>
-  <si>
-    <t>혈마신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>8조 4071억 2262만</t>
-  </si>
-  <si>
-    <t>숑당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>7조 1457억 4077만</t>
-  </si>
-  <si>
-    <t>리얼크크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%96%BC%ED%81%AC%ED%81%AC</t>
-  </si>
-  <si>
-    <t>5조 3354억 6934만</t>
-  </si>
-  <si>
-    <t>현즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
-  </si>
-  <si>
-    <t>4조 8579억 3603만</t>
-  </si>
-  <si>
-    <t>박하민린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
   </si>
   <si>
     <t>3조 8168억 3272만</t>
@@ -6423,10 +6423,10 @@
         <v>84</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>418</v>
@@ -6455,10 +6455,10 @@
         <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>421</v>
@@ -6487,7 +6487,7 @@
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>158</v>
@@ -7851,10 +7851,10 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>543</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>547</v>
@@ -7883,13 +7883,13 @@
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7903,13 +7903,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -7921,7 +7921,7 @@
         <v>454</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7935,13 +7935,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -7953,7 +7953,7 @@
         <v>285</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7967,13 +7967,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -7985,7 +7985,7 @@
         <v>543</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7999,13 +7999,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -8017,7 +8017,7 @@
         <v>285</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8031,13 +8031,13 @@
         <v>293</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -8049,7 +8049,7 @@
         <v>543</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8063,13 +8063,13 @@
         <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -8081,7 +8081,7 @@
         <v>543</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8180,13 +8180,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -8198,7 +8198,7 @@
         <v>479</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8212,13 +8212,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -8230,7 +8230,7 @@
         <v>479</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8244,13 +8244,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -8262,7 +8262,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8276,13 +8276,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -8294,7 +8294,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8308,13 +8308,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -8326,7 +8326,7 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8340,13 +8340,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -8358,7 +8358,7 @@
         <v>98</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8372,13 +8372,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -8390,7 +8390,7 @@
         <v>129</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8404,13 +8404,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -8422,7 +8422,7 @@
         <v>158</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8436,13 +8436,13 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -8454,7 +8454,7 @@
         <v>129</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8468,13 +8468,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -8486,7 +8486,7 @@
         <v>129</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8500,13 +8500,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -8518,7 +8518,7 @@
         <v>200</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8532,13 +8532,13 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -8550,7 +8550,7 @@
         <v>200</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8564,13 +8564,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -8582,7 +8582,7 @@
         <v>200</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8596,13 +8596,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -8614,7 +8614,7 @@
         <v>200</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8628,13 +8628,13 @@
         <v>151</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -8646,7 +8646,7 @@
         <v>266</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8660,13 +8660,13 @@
         <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -8678,7 +8678,7 @@
         <v>285</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8692,13 +8692,13 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -8710,7 +8710,7 @@
         <v>200</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8724,13 +8724,13 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -8742,7 +8742,7 @@
         <v>454</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8756,13 +8756,13 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -8774,7 +8774,7 @@
         <v>285</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8788,13 +8788,13 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -8806,7 +8806,7 @@
         <v>285</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8820,13 +8820,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -8838,7 +8838,7 @@
         <v>454</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8852,13 +8852,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -8870,7 +8870,7 @@
         <v>454</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8884,13 +8884,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -8902,7 +8902,7 @@
         <v>454</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8916,13 +8916,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -8931,10 +8931,10 @@
         <v>85</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8948,13 +8948,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -8966,7 +8966,7 @@
         <v>543</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8980,13 +8980,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -8995,10 +8995,10 @@
         <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9018,7 +9018,7 @@
         <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>153</v>
@@ -9027,10 +9027,10 @@
         <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9044,13 +9044,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -9059,10 +9059,10 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9076,13 +9076,13 @@
         <v>293</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -9091,10 +9091,10 @@
         <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9192,13 +9192,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -9210,7 +9210,7 @@
         <v>479</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9224,13 +9224,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -9242,7 +9242,7 @@
         <v>210</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9256,13 +9256,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -9274,7 +9274,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9288,13 +9288,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -9306,7 +9306,7 @@
         <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9320,13 +9320,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -9338,7 +9338,7 @@
         <v>129</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9352,13 +9352,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -9370,7 +9370,7 @@
         <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9390,7 +9390,7 @@
         <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>153</v>
@@ -9402,7 +9402,7 @@
         <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9416,13 +9416,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -9434,7 +9434,7 @@
         <v>200</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9448,13 +9448,13 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -9466,7 +9466,7 @@
         <v>200</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9480,13 +9480,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -9498,7 +9498,7 @@
         <v>200</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9512,13 +9512,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -9530,7 +9530,7 @@
         <v>285</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9544,13 +9544,13 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -9562,7 +9562,7 @@
         <v>285</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9576,13 +9576,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -9594,7 +9594,7 @@
         <v>454</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9608,13 +9608,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -9626,7 +9626,7 @@
         <v>285</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9640,13 +9640,13 @@
         <v>151</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -9658,7 +9658,7 @@
         <v>266</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9672,13 +9672,13 @@
         <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -9690,7 +9690,7 @@
         <v>285</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9704,13 +9704,13 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -9722,7 +9722,7 @@
         <v>454</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9736,13 +9736,13 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -9754,7 +9754,7 @@
         <v>285</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9768,13 +9768,13 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -9786,7 +9786,7 @@
         <v>454</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9800,13 +9800,13 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -9818,7 +9818,7 @@
         <v>285</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9832,13 +9832,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -9850,7 +9850,7 @@
         <v>285</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9864,13 +9864,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -9882,7 +9882,7 @@
         <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9896,13 +9896,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -9914,7 +9914,7 @@
         <v>543</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9928,13 +9928,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -9946,7 +9946,7 @@
         <v>543</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9960,13 +9960,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -9975,7 +9975,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>550</v>
+        <v>732</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>733</v>
@@ -10007,7 +10007,7 @@
         <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>736</v>
@@ -10039,7 +10039,7 @@
         <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>550</v>
+        <v>732</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>739</v>
@@ -10071,7 +10071,7 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>550</v>
+        <v>732</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>742</v>
@@ -10103,7 +10103,7 @@
         <v>120</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>745</v>
@@ -10135,7 +10135,7 @@
         <v>85</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>748</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="748">
   <si>
     <t>guild_name</t>
   </si>
@@ -312,7 +312,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>3437조 1196억 91만</t>
+    <t>3689조 5713억 1370만</t>
   </si>
   <si>
     <t>3</t>
@@ -396,7 +396,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>497조 5158억 82만</t>
+    <t>504조 5421억 5481만</t>
   </si>
   <si>
     <t>8</t>
@@ -408,7 +408,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%9A%B0</t>
   </si>
   <si>
-    <t>463조 5092억 1105만</t>
+    <t>473조 1842억 5800만</t>
   </si>
   <si>
     <t>9</t>
@@ -423,7 +423,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>414조 9938억 1988만</t>
+    <t>415조 6134억 8369만</t>
   </si>
   <si>
     <t>10</t>
@@ -540,6 +540,21 @@
     <t>19</t>
   </si>
   <si>
+    <t>샾프란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>148조 3247억 919만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>츠키티</t>
   </si>
   <si>
@@ -549,24 +564,21 @@
     <t>145조 5718억 6431만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>샾프란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>142조 502억 2146만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
+    <t>샾번뜩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
+  </si>
+  <si>
+    <t>128조 1007억 7352만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>반맥아범</t>
   </si>
   <si>
@@ -576,7 +588,7 @@
     <t>128조 541억 9730만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>샾허브</t>
@@ -588,16 +600,13 @@
     <t>127조 5666억 1411만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>샾번뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>122조 2296억 160만</t>
+    <t>샾얍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
+  </si>
+  <si>
+    <t>122조 7798억 8343만</t>
   </si>
   <si>
     <t>샾테리</t>
@@ -609,22 +618,13 @@
     <t>101조 9434억 8356만</t>
   </si>
   <si>
-    <t>샾얍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
-  </si>
-  <si>
-    <t>100조 2606억 5508만</t>
-  </si>
-  <si>
     <t>샾76세현수</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE76%EC%84%B8%ED%98%84%EC%88%98</t>
   </si>
   <si>
-    <t>99조 2033억 883만</t>
+    <t>100조 2476억 8988만</t>
   </si>
   <si>
     <t>샾6</t>
@@ -678,7 +678,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>2793조 6494억 320만</t>
+    <t>2818조 5909억 2748만</t>
   </si>
   <si>
     <t>쥬정뱅이</t>
@@ -732,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%8D%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>498조 3363억 3430만</t>
+    <t>533조 6710억 627만</t>
   </si>
   <si>
     <t>구픽</t>
@@ -762,6 +762,15 @@
     <t>152조 3758억 2126만</t>
   </si>
   <si>
+    <t>응누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
+  </si>
+  <si>
+    <t>141조 7209억 5097만</t>
+  </si>
+  <si>
     <t>노득</t>
   </si>
   <si>
@@ -777,7 +786,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
   </si>
   <si>
-    <t>117조 6780억 1499만</t>
+    <t>117조 8718억 427만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -786,7 +795,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
   </si>
   <si>
-    <t>103조 6848억 3526만</t>
+    <t>112조 7208억 226만</t>
   </si>
   <si>
     <t>겸찰</t>
@@ -798,15 +807,6 @@
     <t>93조 8421억 3607만</t>
   </si>
   <si>
-    <t>응누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
-  </si>
-  <si>
-    <t>85조 9801억 803만</t>
-  </si>
-  <si>
     <t>핫장</t>
   </si>
   <si>
@@ -822,7 +822,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
   </si>
   <si>
-    <t>76조 5107억 3164만</t>
+    <t>79조 1018억 174만</t>
   </si>
   <si>
     <t>앨리스빌</t>
@@ -852,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>43조 2491억 5531만</t>
+    <t>43조 3445억 280만</t>
   </si>
   <si>
     <t>연지임당</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>35조 8863억 2843만</t>
+    <t>36조 776억 8808만</t>
   </si>
   <si>
     <t>쵸꼬님</t>
@@ -909,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>16조 9184억 6689만</t>
+    <t>18조 520억 4268만</t>
   </si>
   <si>
     <t>29</t>
@@ -933,7 +933,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%82%A8</t>
   </si>
   <si>
-    <t>13조 2761억 8847만</t>
+    <t>13조 2800억 1577만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -1764,16 +1764,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1232조 428억 1327만</t>
-  </si>
-  <si>
-    <t>민실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>760조 7667억 2010만</t>
+    <t>1243조 1722억 9668만</t>
+  </si>
+  <si>
+    <t>설즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>921조 3238억 6430만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1800,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>209조 3802억 6873만</t>
+    <t>212조 4834억 8037만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1845,7 +1845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>66조 6160억 1431만</t>
+    <t>75조 662억 2801만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1872,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>25조 6837억 4377만</t>
+    <t>25조 6977억 6223만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>24조 1275억 9609만</t>
+    <t>24조 6417억 7062만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1917,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>9조 3942억 2359만</t>
+    <t>9조 7577억 4333만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>8조 6843억 7977만</t>
+    <t>9조 5098억 7158만</t>
   </si>
   <si>
     <t>봉합불가</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>7조 1372억 9919만</t>
+    <t>7조 2028억 4048만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
   </si>
   <si>
-    <t>7조 541억 2250만</t>
+    <t>7조 1388억 6222만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1965,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>2조 4727억 9722만</t>
+    <t>2조 5899억 6994만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1977,34 +1977,31 @@
     <t>1조 449억 856만</t>
   </si>
   <si>
+    <t>용광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>7680억 9109만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>96</t>
-  </si>
-  <si>
     <t>6424억 6751만</t>
   </si>
   <si>
-    <t>용광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
   </si>
   <si>
     <t>95</t>
-  </si>
-  <si>
-    <t>6354억 2182만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>94</t>
   </si>
   <si>
     <t>4074억 222만</t>
@@ -3642,13 +3639,13 @@
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3659,22 +3656,22 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>129</v>
@@ -3706,10 +3703,10 @@
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>180</v>
@@ -3738,10 +3735,10 @@
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>184</v>
@@ -3770,10 +3767,10 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>188</v>
@@ -3802,7 +3799,7 @@
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>158</v>
@@ -3834,7 +3831,7 @@
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>158</v>
@@ -4429,10 +4426,10 @@
         <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
@@ -4461,7 +4458,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>158</v>
@@ -4493,10 +4490,10 @@
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>251</v>
@@ -4525,7 +4522,7 @@
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>129</v>
@@ -4560,7 +4557,7 @@
         <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>257</v>
@@ -4621,7 +4618,7 @@
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>200</v>
@@ -4638,7 +4635,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>264</v>
@@ -4813,7 +4810,7 @@
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>200</v>
@@ -5683,7 +5680,7 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>358</v>
@@ -5922,7 +5919,7 @@
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>200</v>
@@ -6487,7 +6484,7 @@
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>158</v>
@@ -6728,7 +6725,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>446</v>
@@ -7740,7 +7737,7 @@
         <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>535</v>
@@ -7979,7 +7976,7 @@
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>543</v>
@@ -8785,7 +8782,7 @@
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>626</v>
@@ -8835,7 +8832,7 @@
         <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>454</v>
+        <v>285</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>631</v>
@@ -9012,25 +9009,25 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>648</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>648</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9044,25 +9041,25 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>651</v>
+        <v>65</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>651</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>652</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9076,13 +9073,13 @@
         <v>293</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -9091,10 +9088,10 @@
         <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9192,13 +9189,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -9210,7 +9207,7 @@
         <v>479</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9224,13 +9221,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -9242,7 +9239,7 @@
         <v>210</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9256,13 +9253,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -9274,7 +9271,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9288,13 +9285,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -9306,7 +9303,7 @@
         <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9320,13 +9317,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -9338,7 +9335,7 @@
         <v>129</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9352,13 +9349,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -9370,7 +9367,7 @@
         <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9390,7 +9387,7 @@
         <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>153</v>
@@ -9402,7 +9399,7 @@
         <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9416,13 +9413,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -9434,7 +9431,7 @@
         <v>200</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9448,13 +9445,13 @@
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -9466,7 +9463,7 @@
         <v>200</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9480,13 +9477,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -9498,7 +9495,7 @@
         <v>200</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9512,13 +9509,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -9530,7 +9527,7 @@
         <v>285</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9544,13 +9541,13 @@
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -9562,7 +9559,7 @@
         <v>285</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9576,13 +9573,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -9594,7 +9591,7 @@
         <v>454</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9608,13 +9605,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -9626,7 +9623,7 @@
         <v>285</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9640,13 +9637,13 @@
         <v>151</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>701</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -9658,7 +9655,7 @@
         <v>266</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9672,13 +9669,13 @@
         <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -9690,7 +9687,7 @@
         <v>285</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9704,13 +9701,13 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -9722,7 +9719,7 @@
         <v>454</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9736,13 +9733,13 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -9754,7 +9751,7 @@
         <v>285</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9768,13 +9765,13 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -9786,7 +9783,7 @@
         <v>454</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9797,16 +9794,16 @@
         <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -9818,7 +9815,7 @@
         <v>285</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9832,13 +9829,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -9850,7 +9847,7 @@
         <v>285</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9864,13 +9861,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -9882,7 +9879,7 @@
         <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9896,13 +9893,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -9914,7 +9911,7 @@
         <v>543</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9928,13 +9925,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -9946,7 +9943,7 @@
         <v>543</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9960,13 +9957,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -9975,10 +9972,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9992,13 +9989,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -10010,7 +10007,7 @@
         <v>640</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10024,13 +10021,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -10039,10 +10036,10 @@
         <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10056,13 +10053,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -10071,10 +10068,10 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10088,13 +10085,13 @@
         <v>293</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -10106,7 +10103,7 @@
         <v>640</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10120,13 +10117,13 @@
         <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>747</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -10135,10 +10132,10 @@
         <v>85</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
   </si>
   <si>
-    <t>139조 6154억 5307만</t>
+    <t>155조 3946억 5358만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -2067,6 +2067,15 @@
     <t>123조 5425억 2061만</t>
   </si>
   <si>
+    <t>산타선물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>56조 7307억 1694만</t>
+  </si>
+  <si>
     <t>아마날</t>
   </si>
   <si>
@@ -2076,15 +2085,6 @@
     <t>56조 5338억 7127만</t>
   </si>
   <si>
-    <t>산타선물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>55조 5068억 8947만</t>
-  </si>
-  <si>
     <t>도령3</t>
   </si>
   <si>
@@ -2112,6 +2112,15 @@
     <t>28조 236억 7493만</t>
   </si>
   <si>
+    <t>숮2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
+  </si>
+  <si>
+    <t>27조 3095억 4161만</t>
+  </si>
+  <si>
     <t>백엄경</t>
   </si>
   <si>
@@ -2121,15 +2130,6 @@
     <t>26조 5534억 6019만</t>
   </si>
   <si>
-    <t>숮2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
-  </si>
-  <si>
-    <t>26조 4226억 4497만</t>
-  </si>
-  <si>
     <t>키움맨</t>
   </si>
   <si>
@@ -2148,6 +2148,15 @@
     <t>17조 8681억 7133만</t>
   </si>
   <si>
+    <t>최소뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
+  </si>
+  <si>
+    <t>15조 3071억 7112만</t>
+  </si>
+  <si>
     <t>한유화</t>
   </si>
   <si>
@@ -2166,15 +2175,6 @@
     <t>14조 1726억 7817만</t>
   </si>
   <si>
-    <t>최소뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
-  </si>
-  <si>
-    <t>13조 6106억 2682만</t>
-  </si>
-  <si>
     <t>시프님</t>
   </si>
   <si>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>4조 8579억 3603만</t>
+    <t>4조 8754억 6914만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -2229,7 +2229,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 8168억 3272만</t>
+    <t>4조 106억 6369만</t>
   </si>
   <si>
     <t>군명</t>
@@ -2238,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
   </si>
   <si>
-    <t>3조 4778억 1911만</t>
+    <t>3조 5609억 3444만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -2256,7 +2256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>2조 5940억 3610만</t>
+    <t>2조 7138억 2376만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -2265,7 +2265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
   </si>
   <si>
-    <t>2조 43억 7919만</t>
+    <t>2조 417억 6202만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -9396,7 +9396,7 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>677</v>
@@ -9425,7 +9425,7 @@
         <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>200</v>
@@ -9457,7 +9457,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>200</v>
@@ -9524,7 +9524,7 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>689</v>
@@ -9585,10 +9585,10 @@
         <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>454</v>
+        <v>285</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>695</v>
@@ -9617,10 +9617,10 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>698</v>
@@ -9713,7 +9713,7 @@
         <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>454</v>
@@ -9745,10 +9745,10 @@
         <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>710</v>
@@ -9780,7 +9780,7 @@
         <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>454</v>
+        <v>285</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>713</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">item!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">더샾!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">더샾!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">딸기키우기!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">이콩!$A$1:$J$30</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="742">
   <si>
     <t>guild_name</t>
   </si>
@@ -312,7 +312,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>3689조 5713억 1370만</t>
+    <t>3701조 4597억 936만</t>
   </si>
   <si>
     <t>3</t>
@@ -363,7 +363,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>778조 5996억 3427만</t>
+    <t>783조 4862억 7966만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>567조 487억 3333만</t>
+    <t>592조 9763억 6242만</t>
   </si>
   <si>
     <t>7</t>
@@ -408,6 +408,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%9A%B0</t>
   </si>
   <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
     <t>473조 1842억 5800만</t>
   </si>
   <si>
@@ -423,7 +426,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>415조 6134억 8369만</t>
+    <t>453조 8682억 9723만</t>
   </si>
   <si>
     <t>10</t>
@@ -435,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>413조 4724억 8993만</t>
+    <t>414조 2213억 9191만</t>
   </si>
   <si>
     <t>11</t>
@@ -495,7 +498,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>216조 2528억 2552만</t>
+    <t>219조 2806억 4866만</t>
   </si>
   <si>
     <t>16</t>
@@ -510,7 +513,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>185조 2875억 7751만</t>
+    <t>187조 9164억 8111만</t>
   </si>
   <si>
     <t>17</t>
@@ -522,19 +525,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%B6%9C</t>
   </si>
   <si>
-    <t>161조 6440억 1887만</t>
+    <t>173조 4222억 4909만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>샾섚솊샢셒셮</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%84%9A%EC%86%8A%EC%83%A2%EC%85%92%EC%85%AE</t>
-  </si>
-  <si>
-    <t>152조 9487억 8767만</t>
+    <t>츠키티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>151조 3634억 801만</t>
   </si>
   <si>
     <t>19</t>
@@ -546,67 +549,67 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
   </si>
   <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>148조 3247억 919만</t>
+    <t>148조 3645억 9495만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>츠키티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>145조 5718억 6431만</t>
+    <t>샾번뜩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
+  </si>
+  <si>
+    <t>128조 1007억 7352만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>샾번뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>128조 1007억 7352만</t>
+    <t>반맥아범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%A7%A5%EC%95%84%EB%B2%94</t>
+  </si>
+  <si>
+    <t>128조 541억 9730만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>반맥아범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%A7%A5%EC%95%84%EB%B2%94</t>
-  </si>
-  <si>
-    <t>128조 541억 9730만</t>
+    <t>샾허브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%97%88%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>127조 5666억 1411만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>샾허브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%97%88%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>127조 5666억 1411만</t>
-  </si>
-  <si>
     <t>샾얍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
   </si>
   <si>
-    <t>122조 7798억 8343만</t>
+    <t>124조 5314억 9252만</t>
+  </si>
+  <si>
+    <t>샾6</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE6</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>102조 8055억 313만</t>
   </si>
   <si>
     <t>샾테리</t>
@@ -624,28 +627,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE76%EC%84%B8%ED%98%84%EC%88%98</t>
   </si>
   <si>
-    <t>100조 2476억 8988만</t>
-  </si>
-  <si>
-    <t>샾6</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE6</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>90조 3063억 8765만</t>
-  </si>
-  <si>
-    <t>샾스핀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%8A%A4%ED%95%80</t>
-  </si>
-  <si>
-    <t>89조 2611억 4815만</t>
+    <t>100조 3312억 1001만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
@@ -714,7 +696,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
   </si>
   <si>
-    <t>676조 2117억 1642만</t>
+    <t>677조 3632억 3790만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -759,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>152조 3758억 2126만</t>
+    <t>152조 6388억 8303만</t>
   </si>
   <si>
     <t>응누</t>
@@ -795,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
   </si>
   <si>
-    <t>112조 7208억 226만</t>
+    <t>112조 7437억 2449만</t>
   </si>
   <si>
     <t>겸찰</t>
@@ -813,7 +795,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
   </si>
   <si>
-    <t>84조 9568억 9192만</t>
+    <t>92조 8402억 3471만</t>
   </si>
   <si>
     <t>약해진쭌석</t>
@@ -843,7 +825,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
   </si>
   <si>
-    <t>49조 2187억 3466만</t>
+    <t>53조 8171억 9044만</t>
   </si>
   <si>
     <t>핫딜만삼</t>
@@ -861,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>36조 776억 8808만</t>
+    <t>39조 1534억 9400만</t>
   </si>
   <si>
     <t>쵸꼬님</t>
@@ -921,7 +903,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%82%ACPC</t>
   </si>
   <si>
-    <t>16조 4818억 5749만</t>
+    <t>17조 2207억 761만</t>
   </si>
   <si>
     <t>30</t>
@@ -960,7 +942,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>2077조 7738억 8253만</t>
+    <t>2202조 8792억 6515만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -987,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>960조 7702억 374만</t>
+    <t>968조 805억 7034만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -996,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>314조 5879억 8957만</t>
+    <t>314조 7554억 6013만</t>
   </si>
   <si>
     <t>여사</t>
@@ -1014,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
   </si>
   <si>
-    <t>165조 4170억 907만</t>
+    <t>165조 5055억 7507만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1041,7 +1023,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>137조 9189억 5210만</t>
+    <t>140조 8180억 9133만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -1059,7 +1041,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>85조 1744억 8515만</t>
+    <t>86조 6580억 5183만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>74조 5245억 2328만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1071,15 +1062,6 @@
     <t>73조 9039억 3442만</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>70조 3961억 1459만</t>
-  </si>
-  <si>
     <t>POSCO</t>
   </si>
   <si>
@@ -1107,6 +1089,15 @@
     <t>37조 1057억 885만</t>
   </si>
   <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>36조 8989억 4048만</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
@@ -1116,15 +1107,6 @@
     <t>36조 8904억 6796만</t>
   </si>
   <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>36조 7009억 4629만</t>
-  </si>
-  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
@@ -1155,7 +1137,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>26조 3529억 5204만</t>
+    <t>27조 7168억 210만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>25조 7875억 6068만</t>
   </si>
   <si>
     <t>포뇨야</t>
@@ -1167,15 +1158,6 @@
     <t>25조 4912억 9969만</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>23조 3910억 228만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -1200,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=junoflo</t>
   </si>
   <si>
-    <t>10조 5344억 1386만</t>
+    <t>10조 7228억 5142만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -1296,7 +1278,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>146조 1368억 9777만</t>
+    <t>146조 2127억 6389만</t>
   </si>
   <si>
     <t>몬함</t>
@@ -1314,7 +1296,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>70조 3138억 1542만</t>
+    <t>70조 3640억 3678만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1332,7 +1314,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 4761억 287만</t>
+    <t>37조 4899억 9572만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1350,7 +1332,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
   </si>
   <si>
-    <t>20조 6247억 8310만</t>
+    <t>20조 9225억 7053만</t>
   </si>
   <si>
     <t>26퐝바</t>
@@ -1359,7 +1341,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>19조 7244억 2353만</t>
+    <t>19조 9013억 2453만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1377,7 +1359,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>16조 5068억 5050만</t>
+    <t>16조 6522억 3012만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1428,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>11조 3435억 1205만</t>
+    <t>11조 5309억 6647만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1491,7 +1473,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1539조 7438억 6316만</t>
+    <t>1571조 3639억 2129만</t>
+  </si>
+  <si>
+    <t>누짜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
+  </si>
+  <si>
+    <t>825조 9972억 7840만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1503,15 +1494,6 @@
     <t>790조 4923억 9555만</t>
   </si>
   <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>698조 9405억 1129만</t>
-  </si>
-  <si>
     <t>송곧</t>
   </si>
   <si>
@@ -1536,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>183조 1156억 7543만</t>
+    <t>189조 9296억 2994만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1635,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>8조 5741억 4400만</t>
+    <t>9조 1327억 7557만</t>
   </si>
   <si>
     <t>키우는건질색</t>
@@ -1695,6 +1677,15 @@
     <t>4조 9474억 7543만</t>
   </si>
   <si>
+    <t>한Poll</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
+  </si>
+  <si>
+    <t>4조 5387억 17만</t>
+  </si>
+  <si>
     <t>수년</t>
   </si>
   <si>
@@ -1704,15 +1695,6 @@
     <t>4조 3429억 3876만</t>
   </si>
   <si>
-    <t>한Poll</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
-  </si>
-  <si>
-    <t>4조 3050억 8452만</t>
-  </si>
-  <si>
     <t>김치왕뚜껑</t>
   </si>
   <si>
@@ -1728,7 +1710,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 7321억 5062만</t>
+    <t>2조 7419억 3854만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1746,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>9288조 7988억 1546만</t>
+    <t>1경 412조 578억 8642만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1881,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>24조 6417억 7062만</t>
+    <t>25조 2107억 5095만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -2031,7 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>3330조 8692억 9686만</t>
+    <t>3358조 2280억 7710만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -2040,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>178조 8088억 5238만</t>
+    <t>178조 9018억 5514만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -2163,7 +2145,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>14조 4540억 460만</t>
+    <t>14조 8065억 8136만</t>
+  </si>
+  <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>14조 1905억 9943만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -2175,15 +2166,6 @@
     <t>14조 1726억 7817만</t>
   </si>
   <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>13조 3904억 8124만</t>
-  </si>
-  <si>
     <t>혈마신</t>
   </si>
   <si>
@@ -2229,7 +2211,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 106억 6369만</t>
+    <t>4조 1421억 9067만</t>
   </si>
   <si>
     <t>군명</t>
@@ -2265,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
   </si>
   <si>
-    <t>2조 417억 6202만</t>
+    <t>2조 613억 190만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -2998,7 +2980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3287,13 +3269,13 @@
         <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3304,16 +3286,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -3322,10 +3304,10 @@
         <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3336,16 +3318,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -3354,10 +3336,10 @@
         <v>85</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3368,16 +3350,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -3389,7 +3371,7 @@
         <v>115</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3400,16 +3382,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -3418,10 +3400,10 @@
         <v>85</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3432,16 +3414,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -3450,10 +3432,10 @@
         <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3464,16 +3446,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -3482,10 +3464,10 @@
         <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3496,7 +3478,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>23</v>
@@ -3505,19 +3487,19 @@
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3528,16 +3510,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -3546,10 +3528,10 @@
         <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3560,16 +3542,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -3578,10 +3560,10 @@
         <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3592,28 +3574,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3624,25 +3606,25 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>172</v>
@@ -3671,10 +3653,10 @@
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>176</v>
@@ -3703,10 +3685,10 @@
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>180</v>
@@ -3735,10 +3717,10 @@
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>184</v>
@@ -3767,10 +3749,10 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>188</v>
@@ -3799,13 +3781,13 @@
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3819,13 +3801,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -3834,10 +3816,10 @@
         <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3851,13 +3833,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -3866,81 +3848,17 @@
         <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J27"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3968,8 +3886,6 @@
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4036,19 +3952,19 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4062,13 +3978,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -4077,10 +3993,10 @@
         <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4094,25 +4010,25 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4126,13 +4042,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -4144,7 +4060,7 @@
         <v>92</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4158,13 +4074,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -4176,7 +4092,7 @@
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4190,13 +4106,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -4208,7 +4124,7 @@
         <v>98</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4222,13 +4138,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -4240,7 +4156,7 @@
         <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4254,13 +4170,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -4269,10 +4185,10 @@
         <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4283,16 +4199,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -4304,7 +4220,7 @@
         <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4315,16 +4231,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -4333,10 +4249,10 @@
         <v>109</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4347,16 +4263,16 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -4365,10 +4281,10 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4379,16 +4295,16 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -4397,10 +4313,10 @@
         <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4411,16 +4327,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -4429,10 +4345,10 @@
         <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4443,16 +4359,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -4461,10 +4377,10 @@
         <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4475,28 +4391,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4507,16 +4423,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -4525,10 +4441,10 @@
         <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4539,16 +4455,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -4557,10 +4473,10 @@
         <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4571,16 +4487,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -4589,10 +4505,10 @@
         <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4603,28 +4519,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4638,13 +4554,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -4653,10 +4569,10 @@
         <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4670,13 +4586,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -4685,10 +4601,10 @@
         <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4702,13 +4618,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -4717,10 +4633,10 @@
         <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4734,13 +4650,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -4749,10 +4665,10 @@
         <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4766,13 +4682,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -4781,10 +4697,10 @@
         <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4798,25 +4714,25 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4830,13 +4746,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -4845,10 +4761,10 @@
         <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4862,13 +4778,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -4877,10 +4793,10 @@
         <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4894,13 +4810,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -4909,10 +4825,10 @@
         <v>109</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4923,16 +4839,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -4941,10 +4857,10 @@
         <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4955,16 +4871,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -4973,10 +4889,10 @@
         <v>103</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5075,13 +4991,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -5093,7 +5009,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>42</v>
@@ -5107,13 +5023,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -5125,7 +5041,7 @@
         <v>92</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>42</v>
@@ -5139,13 +5055,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -5157,7 +5073,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>42</v>
@@ -5171,13 +5087,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -5189,7 +5105,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>42</v>
@@ -5203,13 +5119,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -5221,7 +5137,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>42</v>
@@ -5235,25 +5151,25 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>42</v>
@@ -5267,13 +5183,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -5285,7 +5201,7 @@
         <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>42</v>
@@ -5299,13 +5215,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -5317,7 +5233,7 @@
         <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>42</v>
@@ -5328,16 +5244,16 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -5346,10 +5262,10 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>42</v>
@@ -5360,16 +5276,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -5378,10 +5294,10 @@
         <v>114</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>42</v>
@@ -5392,16 +5308,16 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -5410,10 +5326,10 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>42</v>
@@ -5424,16 +5340,16 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -5442,10 +5358,10 @@
         <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
@@ -5456,16 +5372,16 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -5474,10 +5390,10 @@
         <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>42</v>
@@ -5488,16 +5404,16 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -5506,10 +5422,10 @@
         <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>42</v>
@@ -5520,28 +5436,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>42</v>
@@ -5552,28 +5468,28 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>42</v>
@@ -5584,16 +5500,16 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -5602,10 +5518,10 @@
         <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>42</v>
@@ -5616,16 +5532,16 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -5634,10 +5550,10 @@
         <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>42</v>
@@ -5648,16 +5564,16 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -5666,10 +5582,10 @@
         <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>42</v>
@@ -5683,25 +5599,25 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>42</v>
@@ -5715,25 +5631,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>42</v>
@@ -5747,13 +5663,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -5762,10 +5678,10 @@
         <v>85</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>42</v>
@@ -5779,13 +5695,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -5794,10 +5710,10 @@
         <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>42</v>
@@ -5817,19 +5733,19 @@
         <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>42</v>
@@ -5843,13 +5759,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -5858,10 +5774,10 @@
         <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>42</v>
@@ -5875,25 +5791,25 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>42</v>
@@ -5907,25 +5823,25 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>42</v>
@@ -5939,13 +5855,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -5954,10 +5870,10 @@
         <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>42</v>
@@ -5968,16 +5884,16 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -5986,10 +5902,10 @@
         <v>109</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>42</v>
@@ -6000,16 +5916,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -6018,10 +5934,10 @@
         <v>97</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>42</v>
@@ -6120,13 +6036,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -6135,10 +6051,10 @@
         <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6158,19 +6074,19 @@
         <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6184,13 +6100,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -6202,7 +6118,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6216,13 +6132,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -6234,7 +6150,7 @@
         <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6248,25 +6164,25 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6280,13 +6196,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -6298,7 +6214,7 @@
         <v>98</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6312,13 +6228,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -6330,7 +6246,7 @@
         <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6344,13 +6260,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -6362,7 +6278,7 @@
         <v>98</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6373,16 +6289,16 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -6394,7 +6310,7 @@
         <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6405,16 +6321,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -6423,10 +6339,10 @@
         <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6437,16 +6353,16 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -6458,7 +6374,7 @@
         <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6469,28 +6385,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6501,16 +6417,16 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -6519,10 +6435,10 @@
         <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6533,16 +6449,16 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -6551,10 +6467,10 @@
         <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6565,16 +6481,16 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -6583,10 +6499,10 @@
         <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6597,16 +6513,16 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -6615,10 +6531,10 @@
         <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6629,16 +6545,16 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6647,10 +6563,10 @@
         <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6661,16 +6577,16 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -6679,10 +6595,10 @@
         <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6693,16 +6609,16 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -6711,10 +6627,10 @@
         <v>120</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6728,13 +6644,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -6743,10 +6659,10 @@
         <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6760,13 +6676,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -6775,10 +6691,10 @@
         <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6792,25 +6708,25 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6824,25 +6740,25 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6856,13 +6772,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -6871,10 +6787,10 @@
         <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6888,13 +6804,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -6903,10 +6819,10 @@
         <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6920,13 +6836,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -6935,10 +6851,10 @@
         <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6952,13 +6868,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -6967,10 +6883,10 @@
         <v>120</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6984,13 +6900,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -6999,10 +6915,10 @@
         <v>120</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7013,16 +6929,16 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -7031,10 +6947,10 @@
         <v>85</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7138,19 +7054,19 @@
         <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7164,13 +7080,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -7179,10 +7095,10 @@
         <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7196,13 +7112,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -7214,7 +7130,7 @@
         <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7228,25 +7144,25 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7260,25 +7176,25 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7292,13 +7208,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -7310,7 +7226,7 @@
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7324,13 +7240,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -7342,7 +7258,7 @@
         <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7356,13 +7272,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -7374,7 +7290,7 @@
         <v>98</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7385,16 +7301,16 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -7403,10 +7319,10 @@
         <v>109</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7417,16 +7333,16 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -7435,10 +7351,10 @@
         <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7449,16 +7365,16 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -7467,10 +7383,10 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7481,16 +7397,16 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -7499,10 +7415,10 @@
         <v>109</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7513,16 +7429,16 @@
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -7531,10 +7447,10 @@
         <v>109</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7545,16 +7461,16 @@
         <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -7563,10 +7479,10 @@
         <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7577,16 +7493,16 @@
         <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -7595,10 +7511,10 @@
         <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7609,16 +7525,16 @@
         <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -7627,10 +7543,10 @@
         <v>85</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7641,16 +7557,16 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -7659,10 +7575,10 @@
         <v>120</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7673,16 +7589,16 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -7691,10 +7607,10 @@
         <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7705,16 +7621,16 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -7723,10 +7639,10 @@
         <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7740,13 +7656,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -7755,10 +7671,10 @@
         <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7772,13 +7688,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -7787,10 +7703,10 @@
         <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7804,13 +7720,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -7819,10 +7735,10 @@
         <v>114</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7836,13 +7752,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -7851,10 +7767,10 @@
         <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7868,13 +7784,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -7883,10 +7799,10 @@
         <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7900,13 +7816,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -7915,10 +7831,10 @@
         <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7932,25 +7848,25 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>285</v>
+        <v>537</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7964,25 +7880,25 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>543</v>
+        <v>279</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7996,13 +7912,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -8011,10 +7927,10 @@
         <v>97</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8025,16 +7941,16 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -8043,10 +7959,10 @@
         <v>120</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8057,16 +7973,16 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -8075,10 +7991,10 @@
         <v>97</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8133,7 +8049,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8177,13 +8093,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -8192,10 +8108,10 @@
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8209,13 +8125,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -8224,10 +8140,10 @@
         <v>109</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8241,13 +8157,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -8259,7 +8175,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8273,13 +8189,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -8291,7 +8207,7 @@
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8305,13 +8221,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -8323,7 +8239,7 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8337,13 +8253,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -8355,7 +8271,7 @@
         <v>98</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8369,13 +8285,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -8384,10 +8300,10 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8401,13 +8317,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -8416,10 +8332,10 @@
         <v>103</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8430,16 +8346,16 @@
         <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -8448,10 +8364,10 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8462,16 +8378,16 @@
         <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -8480,10 +8396,10 @@
         <v>97</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8494,16 +8410,16 @@
         <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -8512,10 +8428,10 @@
         <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8526,16 +8442,16 @@
         <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -8544,10 +8460,10 @@
         <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8558,16 +8474,16 @@
         <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -8576,10 +8492,10 @@
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8590,16 +8506,16 @@
         <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -8608,10 +8524,10 @@
         <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8622,16 +8538,16 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -8640,10 +8556,10 @@
         <v>120</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8654,16 +8570,16 @@
         <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -8672,10 +8588,10 @@
         <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8686,16 +8602,16 @@
         <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -8704,10 +8620,10 @@
         <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8718,16 +8634,16 @@
         <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -8736,10 +8652,10 @@
         <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8750,16 +8666,16 @@
         <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -8768,10 +8684,10 @@
         <v>120</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8785,13 +8701,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -8800,10 +8716,10 @@
         <v>114</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8817,13 +8733,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -8832,10 +8748,10 @@
         <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8849,13 +8765,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -8864,10 +8780,10 @@
         <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8881,13 +8797,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -8896,10 +8812,10 @@
         <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8913,13 +8829,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -8928,10 +8844,10 @@
         <v>85</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8945,13 +8861,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -8960,10 +8876,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8977,13 +8893,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -8992,10 +8908,10 @@
         <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9009,13 +8925,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -9024,10 +8940,10 @@
         <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9047,19 +8963,19 @@
         <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9070,16 +8986,16 @@
         <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -9088,10 +9004,10 @@
         <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9189,13 +9105,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -9204,10 +9120,10 @@
         <v>120</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9221,13 +9137,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -9236,10 +9152,10 @@
         <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9253,13 +9169,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -9268,10 +9184,10 @@
         <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9285,13 +9201,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -9303,7 +9219,7 @@
         <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9317,13 +9233,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -9332,10 +9248,10 @@
         <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9349,13 +9265,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -9364,10 +9280,10 @@
         <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9387,19 +9303,19 @@
         <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9413,13 +9329,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -9428,10 +9344,10 @@
         <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9442,16 +9358,16 @@
         <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -9460,10 +9376,10 @@
         <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9474,16 +9390,16 @@
         <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -9492,10 +9408,10 @@
         <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9506,16 +9422,16 @@
         <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -9524,10 +9440,10 @@
         <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9538,16 +9454,16 @@
         <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -9556,10 +9472,10 @@
         <v>109</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9570,16 +9486,16 @@
         <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -9588,10 +9504,10 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9602,16 +9518,16 @@
         <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -9620,10 +9536,10 @@
         <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9634,16 +9550,16 @@
         <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -9652,10 +9568,10 @@
         <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9666,16 +9582,16 @@
         <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -9684,10 +9600,10 @@
         <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9698,16 +9614,16 @@
         <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -9716,10 +9632,10 @@
         <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9730,16 +9646,16 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -9748,10 +9664,10 @@
         <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9762,28 +9678,28 @@
         <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9797,25 +9713,25 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9829,13 +9745,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -9844,10 +9760,10 @@
         <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9861,13 +9777,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -9876,10 +9792,10 @@
         <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9893,13 +9809,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -9908,10 +9824,10 @@
         <v>85</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9925,13 +9841,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
@@ -9940,10 +9856,10 @@
         <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9957,13 +9873,13 @@
         <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -9972,10 +9888,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9989,13 +9905,13 @@
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -10004,10 +9920,10 @@
         <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10021,13 +9937,13 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -10036,10 +9952,10 @@
         <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10053,13 +9969,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
@@ -10068,10 +9984,10 @@
         <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10082,16 +9998,16 @@
         <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
@@ -10100,10 +10016,10 @@
         <v>120</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10114,16 +10030,16 @@
         <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
@@ -10132,10 +10048,10 @@
         <v>85</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -672,13 +672,13 @@
     <t>2626조 826억 4063만</t>
   </si>
   <si>
-    <t>봉사원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%82%AC%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1119조 5054억 4040만</t>
+    <t>가정교육필수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%A0%95%EA%B5%90%EC%9C%A1%ED%95%84%EC%88%98</t>
+  </si>
+  <si>
+    <t>1230조 3132억 570만</t>
   </si>
   <si>
     <t>밀프푸씨</t>
@@ -723,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%94%BD</t>
   </si>
   <si>
-    <t>310조 1495억 2527만</t>
+    <t>317조 9264억 4759만</t>
   </si>
   <si>
     <t>냉도</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
   </si>
   <si>
-    <t>141조 7209억 5097만</t>
+    <t>146조 366억 5215만</t>
   </si>
   <si>
     <t>노득</t>
@@ -768,7 +768,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
   </si>
   <si>
-    <t>117조 8718억 427만</t>
+    <t>119조 8239억 1659만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
   </si>
   <si>
-    <t>112조 7437억 2449만</t>
+    <t>113조 3371억 8583만</t>
   </si>
   <si>
     <t>겸찰</t>
@@ -786,7 +786,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
   </si>
   <si>
-    <t>93조 8421억 3607만</t>
+    <t>94조 7654억 7153만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -804,7 +804,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
   </si>
   <si>
-    <t>79조 1018억 174만</t>
+    <t>79조 3003억 6948만</t>
   </si>
   <si>
     <t>앨리스빌</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>39조 1534억 9400만</t>
+    <t>39조 9658억 2069만</t>
   </si>
   <si>
     <t>쵸꼬님</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
   </si>
   <si>
-    <t>34조 5616억 9441만</t>
+    <t>34조 8051억 5406만</t>
   </si>
   <si>
     <t>81학찬</t>
@@ -915,7 +915,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%82%A8</t>
   </si>
   <si>
-    <t>13조 2800억 1577만</t>
+    <t>13조 2835억 7827만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -1755,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>921조 3238억 6430만</t>
+    <t>932조 4522억 4629만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1836,7 +1836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>45조 2828억 2447만</t>
+    <t>45조 5262억 6458만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1848,6 +1848,15 @@
     <t>38조 9416억 5281만</t>
   </si>
   <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>26조 659억 4024만</t>
+  </si>
+  <si>
     <t>땩콩</t>
   </si>
   <si>
@@ -1857,15 +1866,6 @@
     <t>25조 6977억 6223만</t>
   </si>
   <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>25조 2107억 5095만</t>
-  </si>
-  <si>
     <t>김대협</t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>13조 6686억 9958만</t>
+    <t>13조 7228억 2986만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
   </si>
   <si>
-    <t>7조 1388억 6222만</t>
+    <t>7조 1828억 2777만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1956,7 +1956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>1조 449억 856만</t>
+    <t>1조 456억 4386만</t>
   </si>
   <si>
     <t>용광사</t>
@@ -1968,13 +1968,13 @@
     <t>96</t>
   </si>
   <si>
-    <t>7680억 9109만</t>
+    <t>7711억 3776만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>6424억 6751만</t>
+    <t>6570억 1540만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>56조 7307억 1694만</t>
+    <t>58조 4263억 1230만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -2085,6 +2085,15 @@
     <t>47조 3657억 4221만</t>
   </si>
   <si>
+    <t>백엄경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>28조 5463억 612만</t>
+  </si>
+  <si>
     <t>이러는거아냐</t>
   </si>
   <si>
@@ -2103,15 +2112,6 @@
     <t>27조 3095억 4161만</t>
   </si>
   <si>
-    <t>백엄경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>26조 5534억 6019만</t>
-  </si>
-  <si>
     <t>키움맨</t>
   </si>
   <si>
@@ -2154,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>14조 1905억 9943만</t>
+    <t>14조 2969억 3551만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -2220,7 +2220,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
   </si>
   <si>
-    <t>3조 5609억 3444만</t>
+    <t>3조 6021억 7591만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -8556,7 +8556,7 @@
         <v>120</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>607</v>
@@ -8588,7 +8588,7 @@
         <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>610</v>
@@ -9469,10 +9469,10 @@
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>279</v>
+        <v>448</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>686</v>
@@ -9501,7 +9501,7 @@
         <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>279</v>
@@ -9533,10 +9533,10 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>448</v>
+        <v>279</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>692</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -207,7 +207,7 @@
     <t>오래 하실분들 환영입니다</t>
   </si>
   <si>
-    <t>애기요밋</t>
+    <t>기요밋</t>
   </si>
   <si>
     <t>이콩</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%ED%8B%B0</t>
   </si>
   <si>
-    <t>151조 3634억 801만</t>
+    <t>151조 9822억 4583만</t>
   </si>
   <si>
     <t>19</t>
@@ -597,7 +597,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
   </si>
   <si>
-    <t>124조 5314억 9252만</t>
+    <t>124조 8616억 7198만</t>
   </si>
   <si>
     <t>샾6</t>
@@ -660,7 +660,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>2818조 5909억 2748만</t>
+    <t>2831조 5974억 1891만</t>
   </si>
   <si>
     <t>쥬정뱅이</t>
@@ -741,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>152조 6388억 8303만</t>
+    <t>158조 3705억 7457만</t>
   </si>
   <si>
     <t>응누</t>
@@ -804,7 +804,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
   </si>
   <si>
-    <t>79조 3003억 6948만</t>
+    <t>79조 4720억 3769만</t>
   </si>
   <si>
     <t>앨리스빌</t>
@@ -828,6 +828,15 @@
     <t>53조 8171억 9044만</t>
   </si>
   <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>47조 3804억 5999만</t>
+  </si>
+  <si>
     <t>핫딜만삼</t>
   </si>
   <si>
@@ -837,15 +846,6 @@
     <t>43조 3445억 280만</t>
   </si>
   <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>39조 9658억 2069만</t>
-  </si>
-  <si>
     <t>쵸꼬님</t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>18조 520억 4268만</t>
+    <t>18조 9839억 406만</t>
   </si>
   <si>
     <t>29</t>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>968조 805억 7034만</t>
+    <t>1021조 5073억 9566만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -978,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>314조 7554억 6013만</t>
+    <t>315조 3104억 9477만</t>
   </si>
   <si>
     <t>여사</t>
@@ -996,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
   </si>
   <si>
-    <t>165조 5055억 7507만</t>
+    <t>176조 573억 7249만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1032,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>117조 2807억 9343만</t>
+    <t>123조 7397억 6038만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>73조 9039억 3442만</t>
+    <t>74조 2195억 2686만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -1080,6 +1080,15 @@
     <t>56조 9226억 6343만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>37조 7902억 3547만</t>
+  </si>
+  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -1098,15 +1107,6 @@
     <t>36조 8989억 4048만</t>
   </si>
   <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>36조 8904억 6796만</t>
-  </si>
-  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1442조 8556억 7433만</t>
+    <t>1448조 1213억 6213만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1224,7 +1224,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>462조 3946억 8834만</t>
+    <t>473조 935억 9830만</t>
   </si>
   <si>
     <t>26길초</t>
@@ -1236,6 +1236,15 @@
     <t>423조 609억 3629만</t>
   </si>
   <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>355조 4228억 3360만</t>
+  </si>
+  <si>
     <t>26들박</t>
   </si>
   <si>
@@ -1245,15 +1254,6 @@
     <t>329조 7132억 4310만</t>
   </si>
   <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>311조 8644억 9662만</t>
-  </si>
-  <si>
     <t>옴짝</t>
   </si>
   <si>
@@ -1263,6 +1263,15 @@
     <t>267조 4873억 4322만</t>
   </si>
   <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>148조 5059억 7662만</t>
+  </si>
+  <si>
     <t>26밍밍</t>
   </si>
   <si>
@@ -1281,15 +1290,6 @@
     <t>146조 2127억 6389만</t>
   </si>
   <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>124조 7535억 8679만</t>
-  </si>
-  <si>
     <t>뻔수니</t>
   </si>
   <si>
@@ -1314,7 +1314,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 4899억 9572만</t>
+    <t>37조 7539억 6445만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1326,15 +1335,6 @@
     <t>28조 3019억 2162만</t>
   </si>
   <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>20조 9225억 7053만</t>
-  </si>
-  <si>
     <t>26퐝바</t>
   </si>
   <si>
@@ -1395,6 +1395,15 @@
     <t>12조 8151억 908만</t>
   </si>
   <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>12조 5345억 9009만</t>
+  </si>
+  <si>
     <t>최씨용</t>
   </si>
   <si>
@@ -1413,15 +1422,6 @@
     <t>11조 5309억 6647만</t>
   </si>
   <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>9조 3250억 4217만</t>
-  </si>
-  <si>
     <t>귬스파파</t>
   </si>
   <si>
@@ -1449,13 +1449,13 @@
     <t>5조 8558억 8323만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>1경 5982조 1294억 8442만</t>
+    <t>1경 6018조 9292억 8956만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1571조 3639억 2129만</t>
+    <t>2064조 9957억 9090만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -1482,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>825조 9972억 7840만</t>
+    <t>826조 6872억 1556만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>189조 9296억 2994만</t>
+    <t>202조 3173억 1129만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>172조 2611억 5897만</t>
+    <t>180조 3813억 983만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1554,7 +1554,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>39조 2931억 101만</t>
+    <t>39조 3817억 8922만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1563,7 +1563,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
   </si>
   <si>
-    <t>19조 5492억 8560만</t>
+    <t>19조 8609억 6211만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1572,7 +1572,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
   </si>
   <si>
-    <t>19조 3549억 5667만</t>
+    <t>19조 3653억 8609만</t>
+  </si>
+  <si>
+    <t>유디티기찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>14조 952억 8021만</t>
   </si>
   <si>
     <t>왓쳐</t>
@@ -1584,22 +1593,13 @@
     <t>13조 4225억 797만</t>
   </si>
   <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>12조 5841억 5205만</t>
-  </si>
-  <si>
     <t>박미쯔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
   </si>
   <si>
-    <t>11조 396억 3541만</t>
+    <t>11조 1492억 1717만</t>
   </si>
   <si>
     <t>끽코</t>
@@ -1617,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>9조 1327억 7557만</t>
+    <t>9조 1576억 3503만</t>
   </si>
   <si>
     <t>키우는건질색</t>
@@ -1635,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
   </si>
   <si>
-    <t>6조 9563억 9212만</t>
+    <t>7조 5150억 8566만</t>
   </si>
   <si>
     <t>후아멀로하냐</t>
@@ -1674,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 9474억 7543만</t>
+    <t>5조 518억 7354만</t>
   </si>
   <si>
     <t>한Poll</t>
@@ -1683,7 +1683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
   </si>
   <si>
-    <t>4조 5387억 17만</t>
+    <t>4조 5474억 2305만</t>
   </si>
   <si>
     <t>수년</t>
@@ -1719,7 +1719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 1846억 5297만</t>
+    <t>2조 4200억 4456만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -1728,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>1경 412조 578억 8642만</t>
+    <t>1경 425조 3870억 640만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1746,7 +1746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1243조 1722억 9668만</t>
+    <t>1248조 757억 8818만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -1782,7 +1782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>212조 4834억 8037만</t>
+    <t>218조 1202억 7446만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1809,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
   </si>
   <si>
-    <t>101조 5005억 6045만</t>
+    <t>103조 906억 2823만</t>
   </si>
   <si>
     <t>월광사</t>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>13조 7228억 2986만</t>
+    <t>13조 7847억 942만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1890,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
   </si>
   <si>
-    <t>11조 4930억 9873만</t>
+    <t>12조 429억 4007만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1911,6 +1911,15 @@
     <t>9조 5098억 7158만</t>
   </si>
   <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>7조 3040억 619만</t>
+  </si>
+  <si>
     <t>봉합불가</t>
   </si>
   <si>
@@ -1920,15 +1929,6 @@
     <t>7조 2028억 4048만</t>
   </si>
   <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>7조 1828억 2777만</t>
-  </si>
-  <si>
     <t>양카오너</t>
   </si>
   <si>
@@ -1938,7 +1938,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 9612억 7314만</t>
+    <t>4조 641억 9689만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1956,7 +1956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>1조 456억 4386만</t>
+    <t>1조 461억 2138만</t>
   </si>
   <si>
     <t>용광사</t>
@@ -1974,7 +1974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>6570억 1540만</t>
+    <t>6617억 4476만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1986,7 +1986,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>4074억 222만</t>
+    <t>4591억 8954만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -2022,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>178조 9018억 5514만</t>
+    <t>179조 2835억 250만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
   </si>
   <si>
-    <t>155조 3946억 5358만</t>
+    <t>171조 2175억 7720만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>58조 4263억 1230만</t>
+    <t>58조 6344억 9259만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -2091,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
-    <t>28조 5463억 612만</t>
+    <t>28조 7492억 3376만</t>
   </si>
   <si>
     <t>이러는거아냐</t>
@@ -2145,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>14조 8065억 8136만</t>
+    <t>14조 9711억 9031만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -2172,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>8조 4071억 2262만</t>
+    <t>8조 5641억 1682만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -2181,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
   </si>
   <si>
-    <t>7조 1457억 4077만</t>
+    <t>7조 4312억 8094만</t>
   </si>
   <si>
     <t>리얼크크</t>
@@ -2199,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>4조 8754억 6914만</t>
+    <t>4조 8774억 3308만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -2238,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>2조 7138억 2376만</t>
+    <t>2조 7337억 3836만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -4633,7 +4633,7 @@
         <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>267</v>
@@ -4665,7 +4665,7 @@
         <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>270</v>
@@ -5579,7 +5579,7 @@
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>159</v>
@@ -5611,10 +5611,10 @@
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>354</v>
@@ -5643,10 +5643,10 @@
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>357</v>
@@ -6179,7 +6179,7 @@
         <v>208</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>397</v>
@@ -6240,10 +6240,10 @@
         <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>403</v>
@@ -6272,7 +6272,7 @@
         <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>98</v>
@@ -6336,10 +6336,10 @@
         <v>84</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>412</v>
@@ -6368,10 +6368,10 @@
         <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>415</v>
@@ -6400,10 +6400,10 @@
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>418</v>
@@ -6528,7 +6528,7 @@
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>260</v>
@@ -6560,7 +6560,7 @@
         <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>260</v>
@@ -6784,7 +6784,7 @@
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>279</v>
@@ -6816,7 +6816,7 @@
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>279</v>
@@ -6848,10 +6848,10 @@
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>448</v>
+        <v>279</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>462</v>
@@ -7508,10 +7508,10 @@
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>516</v>
@@ -7540,10 +7540,10 @@
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>519</v>
@@ -7991,7 +7991,7 @@
         <v>97</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>537</v>
+        <v>448</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>562</v>
@@ -8233,7 +8233,7 @@
         <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>114</v>
+        <v>452</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>92</v>
@@ -8300,7 +8300,7 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>583</v>
@@ -9280,7 +9280,7 @@
         <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>669</v>
@@ -9632,7 +9632,7 @@
         <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>448</v>
+        <v>279</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>701</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>1021조 5073억 9566만</t>
+    <t>1022조 1463억 7965만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>74조 2195억 2686만</t>
+    <t>74조 2546억 7807만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -1086,7 +1086,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>37조 7902억 3547만</t>
+    <t>38조 3694억 6015만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 568억 6620만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1098,15 +1107,6 @@
     <t>37조 1057억 885만</t>
   </si>
   <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>36조 8989억 4048만</t>
-  </si>
-  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>423조 609억 3629만</t>
+    <t>427조 2003억 2087만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
   </si>
   <si>
-    <t>329조 7132억 4310만</t>
+    <t>330조 3801억 9081만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>2064조 9957억 9090만</t>
+    <t>2066조 6901억 7240만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -1647,7 +1647,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>6조 2410억 1159만</t>
+    <t>6조 6518억 9389만</t>
   </si>
   <si>
     <t>SingA</t>
@@ -1755,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>932조 4522억 4629만</t>
+    <t>932조 7496억 7919만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -2148,6 +2148,15 @@
     <t>14조 9711억 9031만</t>
   </si>
   <si>
+    <t>95도도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
+  </si>
+  <si>
+    <t>14조 6429억 438만</t>
+  </si>
+  <si>
     <t>시프님</t>
   </si>
   <si>
@@ -2157,15 +2166,6 @@
     <t>14조 2969억 3551만</t>
   </si>
   <si>
-    <t>95도도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
-  </si>
-  <si>
-    <t>14조 1726억 7817만</t>
-  </si>
-  <si>
     <t>혈마신</t>
   </si>
   <si>
@@ -2238,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>2조 7337억 3836만</t>
+    <t>2조 8362억 3551만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -5611,10 +5611,10 @@
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>354</v>
@@ -5643,10 +5643,10 @@
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>357</v>
@@ -9536,7 +9536,7 @@
         <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>692</v>
@@ -9693,7 +9693,7 @@
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>279</v>
@@ -9725,7 +9725,7 @@
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>279</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 26</t>
   </si>
   <si>
-    <t>32</t>
+    <t>27</t>
   </si>
   <si>
     <t>4위</t>
@@ -93,10 +93,10 @@
     <t>Lv.8</t>
   </si>
   <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1경 9131조 4168억 2075만</t>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>2경 4467조 804억 2890만</t>
   </si>
   <si>
     <t>해시태그 샾 닉변 디코 톡방 친화력 필수요</t>
@@ -105,7 +105,7 @@
     <t>샾로로</t>
   </si>
   <si>
-    <t>2026.04.10</t>
+    <t>2026.04.15</t>
   </si>
   <si>
     <t>딸기키우기</t>
@@ -117,784 +117,787 @@
     <t>Scania 28</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 7426조 7944억 583만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 20조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>2경 2301조 6004억 1090만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.14</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 4536조 7164억 1513만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>호러</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
+  </si>
+  <si>
+    <t>Scania 10</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
+    <t>2경 5706조 9974억 6737만</t>
+  </si>
+  <si>
+    <t>오래 하실분들 환영입니다</t>
+  </si>
+  <si>
+    <t>기요밋</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>3위</t>
   </si>
   <si>
-    <t>2경 3364조 1843억 9134만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 20조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 302조 8354억 4885만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.11</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>2경 3611조 9079억 5482만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2경 3115조 6655억 9653만</t>
+  </si>
+  <si>
+    <t>We Go Together !</t>
+  </si>
+  <si>
+    <t>템이</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>샾둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 2292조 295억 855만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>애갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>3706조 8730억 838만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>샾값</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%92</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1082조 7018억 22만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>샾패트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%8C%A8%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>1018조 5785억 5602만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>샾오리미야옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EB%A6%AC%EB%AF%B8%EC%95%BC%EC%98%B9</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>784조 2987억 8025만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>샾하연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%98%EC%97%B0</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>603조 7869억 1914만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>샾도도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%8F%84%EB%8F%84</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>504조 5421억 5481만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>쉬운이름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EC%9A%B4%EC%9D%B4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>478조 3935억 3103만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>샾우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>473조 1842억 5800만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>샾32별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE32%EB%B3%84</t>
+  </si>
+  <si>
+    <t>467조 9374억 8608만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>샾둘기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>442조 6317억 8947만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>샾매트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%A7%A4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>387조 5253억 3282만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>보샤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%83%A4</t>
+  </si>
+  <si>
+    <t>319조 9722억 3623만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>샾뽀니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%BD%80%EB%8B%88</t>
+  </si>
+  <si>
+    <t>261조 6921억 9875만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%A1%9C%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>223조 3830억 8607만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>샾구름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B5%AC%EB%A6%84</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>192조 6506억 8667만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>샾프란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
+  </si>
+  <si>
+    <t>188조 2531억 366만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>샾출</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%B6%9C</t>
+  </si>
+  <si>
+    <t>177조 2660억 6204만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>츠키티</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%ED%8B%B0</t>
+  </si>
+  <si>
+    <t>160조 2728억 5698만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>샾허브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%97%88%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>143조 8939억 9900만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>샾번뜩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
+  </si>
+  <si>
+    <t>128조 9772억 7703만</t>
+  </si>
+  <si>
+    <t>반맥아범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%A7%A5%EC%95%84%EB%B2%94</t>
+  </si>
+  <si>
+    <t>128조 541억 9730만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>샾얍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
+  </si>
+  <si>
+    <t>127조 4391억 30만</t>
+  </si>
+  <si>
+    <t>샾76세현수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE76%EC%84%B8%ED%98%84%EC%88%98</t>
+  </si>
+  <si>
+    <t>103조 5999억 4228만</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 2185조 8183억 1617만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>호러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>2경 1593조 2154억 9496만</t>
-  </si>
-  <si>
-    <t>오래 하실분들 환영입니다</t>
-  </si>
-  <si>
-    <t>기요밋</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>1경 9137조 3448억 6787만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
+    <t>샾6</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE6</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>102조 8055억 313만</t>
+  </si>
+  <si>
+    <t>샾테리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%85%8C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>101조 9434억 8356만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 2747조 9927억 4574만</t>
+  </si>
+  <si>
+    <t>카뚝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EB%9A%9D</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3126조 9530억 3038만</t>
+  </si>
+  <si>
+    <t>디올핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EC%98%AC%ED%95%91</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>3094조 6038억 7206만</t>
+  </si>
+  <si>
+    <t>쥬정뱅이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2637조 2629억 5630만</t>
+  </si>
+  <si>
+    <t>가정교육필수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%A0%95%EA%B5%90%EC%9C%A1%ED%95%84%EC%88%98</t>
+  </si>
+  <si>
+    <t>1234조 1231억 743만</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>782조 4730억 812만</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>727조 2185억 8964만</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>702조 7403억 8419만</t>
+  </si>
+  <si>
+    <t>피데기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%8D%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>614조 3767억 8359만</t>
+  </si>
+  <si>
+    <t>구픽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%94%BD</t>
+  </si>
+  <si>
+    <t>317조 9264억 4759만</t>
+  </si>
+  <si>
+    <t>냉도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
+  </si>
+  <si>
+    <t>190조 4719억 9661만</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>171조 2873억 8460만</t>
+  </si>
+  <si>
+    <t>엔젤가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>164조 9218억 9723만</t>
+  </si>
+  <si>
+    <t>응누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
+  </si>
+  <si>
+    <t>146조 366억 5215만</t>
+  </si>
+  <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>121조 1997억 6214만</t>
+  </si>
+  <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>118조 4831억 452만</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>116조 4052억 3123만</t>
+  </si>
+  <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>103조 3419억 69만</t>
+  </si>
+  <si>
+    <t>핫장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>92조 8402억 3471만</t>
+  </si>
+  <si>
+    <t>앨리스빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>81조 2714억 2819만</t>
+  </si>
+  <si>
+    <t>키은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>53조 9416억 2444만</t>
+  </si>
+  <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>48조 6465억 1640만</t>
+  </si>
+  <si>
+    <t>핫딜만삼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
+  </si>
+  <si>
+    <t>46조 7324억 2599만</t>
+  </si>
+  <si>
+    <t>머쓰윽타드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
+  </si>
+  <si>
+    <t>36조 9865억 7770만</t>
+  </si>
+  <si>
+    <t>쵸꼬님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>35조 5852억 6210만</t>
+  </si>
+  <si>
+    <t>81학찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>29조 8531억 436만</t>
+  </si>
+  <si>
+    <t>핫두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
+  </si>
+  <si>
+    <t>29조 66억 4936만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>2경 148조 6982억 7060만</t>
-  </si>
-  <si>
-    <t>We Go Together !</t>
-  </si>
-  <si>
-    <t>템이</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>샾둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 2292조 295억 855만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>애갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>3701조 4597억 936만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>샾패트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%8C%A8%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>1018조 5785억 5602만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>샾값</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%92</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>938조 4514억 4043만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>샾오리미야옹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EB%A6%AC%EB%AF%B8%EC%95%BC%EC%98%B9</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>783조 4862억 7966만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>샾하연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%98%EC%97%B0</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>592조 9763억 6242만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>샾도도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%8F%84%EB%8F%84</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>504조 5421억 5481만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>샾우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>473조 1842억 5800만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>쉬운이름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EC%9A%B4%EC%9D%B4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>453조 8682억 9723만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>샾둘기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%91%98%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>414조 2213억 9191만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>샾매트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%A7%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>387조 5253억 3282만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>샾32별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE32%EB%B3%84</t>
-  </si>
-  <si>
-    <t>341조 4530억 8309만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>보샤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%83%A4</t>
-  </si>
-  <si>
-    <t>294조 7348억 2117만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>샾뽀니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%BD%80%EB%8B%88</t>
-  </si>
-  <si>
-    <t>255조 7억 252만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%A1%9C%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>219조 2806억 4866만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>샾구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>187조 9164억 8111만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>샾출</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%B6%9C</t>
-  </si>
-  <si>
-    <t>173조 4222억 4909만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>츠키티</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%ED%8B%B0</t>
-  </si>
-  <si>
-    <t>151조 9822억 4583만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>샾프란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
-  </si>
-  <si>
-    <t>148조 3645억 9495만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>샾번뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B2%88%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>128조 1007억 7352만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>반맥아범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%A7%A5%EC%95%84%EB%B2%94</t>
-  </si>
-  <si>
-    <t>128조 541억 9730만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>샾허브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%97%88%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>127조 5666억 1411만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>샾얍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%96%8D</t>
-  </si>
-  <si>
-    <t>124조 8616억 7198만</t>
-  </si>
-  <si>
-    <t>샾6</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE6</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>102조 8055억 313만</t>
-  </si>
-  <si>
-    <t>샾테리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%85%8C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>101조 9434억 8356만</t>
-  </si>
-  <si>
-    <t>샾76세현수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE76%EC%84%B8%ED%98%84%EC%88%98</t>
-  </si>
-  <si>
-    <t>100조 3312억 1001만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 2747조 9927억 4574만</t>
-  </si>
-  <si>
-    <t>카뚝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EB%9A%9D</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>3024조 1380억 4377만</t>
-  </si>
-  <si>
-    <t>디올핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EC%98%AC%ED%95%91</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>2831조 5974억 1891만</t>
-  </si>
-  <si>
-    <t>쥬정뱅이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2626조 826억 4063만</t>
-  </si>
-  <si>
-    <t>가정교육필수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%A0%95%EA%B5%90%EC%9C%A1%ED%95%84%EC%88%98</t>
-  </si>
-  <si>
-    <t>1230조 3132억 570만</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>702조 7403억 8419만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>677조 3632억 3790만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>638조 6825억 9826만</t>
-  </si>
-  <si>
-    <t>피데기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%8D%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>533조 6710억 627만</t>
-  </si>
-  <si>
-    <t>구픽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%94%BD</t>
-  </si>
-  <si>
-    <t>317조 9264억 4759만</t>
-  </si>
-  <si>
-    <t>냉도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
-  </si>
-  <si>
-    <t>190조 4719억 9661만</t>
-  </si>
-  <si>
-    <t>엔젤가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>158조 3705억 7457만</t>
-  </si>
-  <si>
-    <t>응누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
-  </si>
-  <si>
-    <t>146조 366억 5215만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>120조 671억 411만</t>
-  </si>
-  <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>119조 8239억 1659만</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>113조 3371억 8583만</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>94조 7654억 7153만</t>
-  </si>
-  <si>
-    <t>핫장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>92조 8402억 3471만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>79조 4720억 3769만</t>
-  </si>
-  <si>
-    <t>앨리스빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>63조 6749억 4416만</t>
-  </si>
-  <si>
-    <t>키은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>53조 8171억 9044만</t>
-  </si>
-  <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>47조 3804억 5999만</t>
-  </si>
-  <si>
-    <t>핫딜만삼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
-  </si>
-  <si>
-    <t>43조 3445억 280만</t>
-  </si>
-  <si>
-    <t>쵸꼬님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>35조 1146억 6347만</t>
-  </si>
-  <si>
-    <t>머쓰윽타드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
-  </si>
-  <si>
-    <t>34조 8051억 5406만</t>
-  </si>
-  <si>
-    <t>81학찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>28조 6304억 3515만</t>
-  </si>
-  <si>
-    <t>핫두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
-  </si>
-  <si>
-    <t>23조 7790억 405만</t>
-  </si>
-  <si>
     <t>챠재범</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>18조 9839억 406만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>20조 29억 3881만</t>
   </si>
   <si>
     <t>까사PC</t>
@@ -906,9 +909,6 @@
     <t>17조 2207억 761만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>환불남</t>
   </si>
   <si>
@@ -942,7 +942,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>2202조 8792억 6515만</t>
+    <t>2283조 7142억 7674만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -951,7 +951,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>1182조 6684억 3913만</t>
+    <t>1394조 1932억 8825만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -963,22 +972,13 @@
     <t>1112조 8677억 9360만</t>
   </si>
   <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1022조 1463억 7965만</t>
-  </si>
-  <si>
     <t>스타뎀</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>315조 3104억 9477만</t>
+    <t>475조 5893억 7767만</t>
   </si>
   <si>
     <t>여사</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
   </si>
   <si>
-    <t>305조 8357억 2579만</t>
+    <t>400조 1307억 6796만</t>
   </si>
   <si>
     <t>단풍노비</t>
@@ -999,13 +999,22 @@
     <t>176조 573억 7249만</t>
   </si>
   <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>153조 4242억 2362만</t>
+  </si>
+  <si>
     <t>약어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>147조 7288억 7111만</t>
+    <t>152조 6744억 2175만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1017,15 +1026,6 @@
     <t>143조 1307억 9972만</t>
   </si>
   <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>140조 8180억 9133만</t>
-  </si>
-  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
@@ -1041,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>86조 6580억 5183만</t>
+    <t>89조 2869억 199만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -1050,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>74조 5245억 2328만</t>
+    <t>83조 3411억 4487만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>74조 2546억 7807만</t>
+    <t>75조 5035억 6634만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=POSCO</t>
   </si>
   <si>
-    <t>59조 1651억 31만</t>
+    <t>65조 7697억 3285만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -1077,7 +1077,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>56조 9226억 6343만</t>
+    <t>64조 3897억 2993만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>42조 7569억 3167만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -1095,16 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>38조 568억 6620만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>37조 1057억 885만</t>
+    <t>38조 1459억 7981만</t>
   </si>
   <si>
     <t>두근푸근연근</t>
@@ -1113,7 +1113,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>33조 7492억 4506만</t>
+    <t>37조 4329억 7511만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>35조 3962억 1100만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1122,13 +1131,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>31조 4997억 1522만</t>
+    <t>32조 3503억 166만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>28조 2054억 3268만</t>
+    <t>28조 5128억 7466만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>28조 3422억 4602만</t>
   </si>
   <si>
     <t>울힝</t>
@@ -1140,31 +1158,13 @@
     <t>27조 7168억 210만</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>25조 7875억 6068만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>25조 4912억 9969만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
   </si>
   <si>
-    <t>23조 3285억 9707만</t>
+    <t>25조 817억 1488만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>21조 327억 3756만</t>
+    <t>22조 9589억 8035만</t>
   </si>
   <si>
     <t>junoflo</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=junoflo</t>
   </si>
   <si>
-    <t>10조 7228억 5142만</t>
+    <t>10조 9422억 5450만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -1197,7 +1197,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
   </si>
   <si>
-    <t>2516조 4761억 566만</t>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2604조 1519억 6474만</t>
   </si>
   <si>
     <t>26상탗</t>
@@ -1206,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1448조 1213억 6213만</t>
+    <t>1601조 7815억 6566만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1215,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
   </si>
   <si>
-    <t>650조 9376억 9597만</t>
+    <t>651조 4386억 2995만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1233,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>427조 2003억 2087만</t>
+    <t>437조 2061억 5293만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1251,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
   </si>
   <si>
-    <t>330조 3801억 9081만</t>
+    <t>342조 5420억 8712만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1269,34 +1272,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>148조 5059억 7662만</t>
-  </si>
-  <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+    <t>177조 5670억 5779만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>161조 2593억 1562만</t>
+  </si>
+  <si>
+    <t>중타치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%80%EC%B9%98</t>
   </si>
   <si>
     <t>146조 2366억 2351만</t>
   </si>
   <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>146조 2127억 6389만</t>
-  </si>
-  <si>
     <t>뻔수니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>70조 3640억 3678만</t>
+    <t>83조 6254억 8539만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1305,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
   </si>
   <si>
-    <t>54조 757억 7660만</t>
+    <t>59조 6571억 7041만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1314,7 +1317,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 7539억 6445만</t>
+    <t>38조 8453억 6606만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>30조 6445억 1264만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1326,22 +1338,13 @@
     <t>29조 4752억 2082만</t>
   </si>
   <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>28조 3019억 2162만</t>
-  </si>
-  <si>
     <t>26퐝바</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>19조 9013억 2453만</t>
+    <t>21조 2028억 7543만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1350,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>18조 1110억 6972만</t>
+    <t>20조 3738억 8689만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1359,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>16조 6522억 3012만</t>
+    <t>17조 6676억 1993만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1392,7 +1395,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>12조 8151억 908만</t>
+    <t>13조 8329억 6602만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1404,6 +1407,15 @@
     <t>12조 5345억 9009만</t>
   </si>
   <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>12조 3514억 8343만</t>
+  </si>
+  <si>
     <t>최씨용</t>
   </si>
   <si>
@@ -1413,13 +1425,13 @@
     <t>12조 1214억 5182만</t>
   </si>
   <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>11조 5309억 6647만</t>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>7조 8227억 8591만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1431,15 +1443,6 @@
     <t>6조 8903억 4281만</t>
   </si>
   <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 6146억 1716만</t>
-  </si>
-  <si>
     <t>고영희멈뭄미</t>
   </si>
   <si>
@@ -1452,10 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1경 6018조 9292억 8956만</t>
+    <t>1경 6497조 902억 5584만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>2066조 6901억 7240만</t>
+    <t>2098조 2328억 5174만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -1482,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>826조 6872억 1556만</t>
+    <t>831조 6038억 4515만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1500,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>581조 5500억 3401만</t>
+    <t>585조 4268억 1881만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>266조 8506억 6360만</t>
+    <t>285조 322억 2842만</t>
   </si>
   <si>
     <t>다이사</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>202조 3173억 1129만</t>
+    <t>210조 9912억 9752만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>180조 3813억 983만</t>
+    <t>197조 3967억 6859만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1536,7 +1536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
   </si>
   <si>
-    <t>116조 5809억 6591만</t>
+    <t>121조 6230억 5539만</t>
   </si>
   <si>
     <t>원순철</t>
@@ -1545,7 +1545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
   </si>
   <si>
-    <t>47조 2419억 4473만</t>
+    <t>47조 7024억 8512만</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -1554,7 +1554,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>39조 3817억 8922만</t>
+    <t>42조 5691억 8437만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1563,7 +1563,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
   </si>
   <si>
-    <t>19조 8609억 6211만</t>
+    <t>20조 94억 66만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1572,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
   </si>
   <si>
-    <t>19조 3653억 8609만</t>
+    <t>19조 3948억 273만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1584,6 +1584,15 @@
     <t>14조 952억 8021만</t>
   </si>
   <si>
+    <t>끽코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
+  </si>
+  <si>
+    <t>13조 7773억 9953만</t>
+  </si>
+  <si>
     <t>왓쳐</t>
   </si>
   <si>
@@ -1599,16 +1608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
   </si>
   <si>
-    <t>11조 1492억 1717만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>10조 5748억 5807만</t>
+    <t>12조 8265억 5390만</t>
   </si>
   <si>
     <t>강띵띵</t>
@@ -1617,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>9조 1576억 3503만</t>
+    <t>9조 1785억 5900만</t>
   </si>
   <si>
     <t>키우는건질색</t>
@@ -1644,19 +1644,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
   </si>
   <si>
+    <t>7조 3244억 896만</t>
+  </si>
+  <si>
+    <t>SingA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+  </si>
+  <si>
     <t>99</t>
   </si>
   <si>
-    <t>6조 6518억 9389만</t>
-  </si>
-  <si>
-    <t>SingA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SingA</t>
-  </si>
-  <si>
-    <t>6조 326억 8572만</t>
+    <t>6조 4585억 5406만</t>
   </si>
   <si>
     <t>햄쓱이</t>
@@ -1665,7 +1665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 4672억 9243만</t>
+    <t>6조 829억 6294만</t>
   </si>
   <si>
     <t>술취한호랑이</t>
@@ -1674,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 518억 7354만</t>
+    <t>5조 4573억 8251만</t>
   </si>
   <si>
     <t>한Poll</t>
@@ -1683,7 +1683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
   </si>
   <si>
-    <t>4조 5474억 2305만</t>
+    <t>4조 8436억 9982만</t>
   </si>
   <si>
     <t>수년</t>
@@ -1692,7 +1692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
   </si>
   <si>
-    <t>4조 3429억 3876만</t>
+    <t>4조 5839억 3632만</t>
   </si>
   <si>
     <t>김치왕뚜껑</t>
@@ -1710,7 +1710,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 7419억 3854만</t>
+    <t>2조 9861억 6830만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1719,7 +1719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 4200억 4456만</t>
+    <t>2조 5913억 7317만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -1728,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>1경 425조 3870억 640만</t>
+    <t>1경 466조 380억 5867만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1746,7 +1746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1248조 757억 8818만</t>
+    <t>1316조 9476억 443만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -1755,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>932조 7496억 7919만</t>
+    <t>1057조 1778억 3358만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1773,7 +1773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
   </si>
   <si>
-    <t>317조 9218억 327만</t>
+    <t>321조 7864억 5930만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -1782,7 +1782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>218조 1202억 7446만</t>
+    <t>236조 6736억 2515만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1800,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>160조 5093억 7580만</t>
+    <t>191조 5397억 6335만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -1845,7 +1845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
   </si>
   <si>
-    <t>38조 9416억 5281만</t>
+    <t>39조 6191억 375만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1854,7 +1854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>26조 659억 4024만</t>
+    <t>28조 9920억 907만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -1863,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>25조 6977억 6223만</t>
+    <t>27조 6839억 965만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1872,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>24조 343억 8478만</t>
+    <t>25조 4755억 1503만</t>
   </si>
   <si>
     <t>에망</t>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>13조 7847억 942만</t>
+    <t>14조 1637억 9802만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1890,7 +1890,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
   </si>
   <si>
-    <t>12조 429억 4007만</t>
+    <t>12조 923억 4440만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>10조 2967억 9982만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1899,16 +1908,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>9조 7577억 4333만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>9조 5098억 7158만</t>
+    <t>10조 129억 2470만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>7조 4531억 2484만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1920,15 +1929,6 @@
     <t>7조 3040억 619만</t>
   </si>
   <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>7조 2028억 4048만</t>
-  </si>
-  <si>
     <t>양카오너</t>
   </si>
   <si>
@@ -1938,7 +1938,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>4조 641억 9689만</t>
+    <t>4조 1168억 1838만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1947,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>2조 5899억 6994만</t>
+    <t>2조 7268억 3352만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1968,13 +1968,13 @@
     <t>96</t>
   </si>
   <si>
-    <t>7711억 3776만</t>
+    <t>8361억 7612만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>6617억 4476만</t>
+    <t>7146억 2017만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1986,7 +1986,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>4591억 8954만</t>
+    <t>5016억 6902만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -2013,7 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>3358조 2280억 7710만</t>
+    <t>4125조 6229억 6967만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -2022,7 +2022,16 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>179조 2835억 250만</t>
+    <t>205조 2045억 9051만</t>
+  </si>
+  <si>
+    <t>빌린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>200조 2123억 7040만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -2031,16 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>171조 7664억 5190만</t>
-  </si>
-  <si>
-    <t>빌린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>171조 2175억 7720만</t>
+    <t>180조 1593억 4007만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -2055,7 +2055,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>58조 6344억 9259만</t>
+    <t>65조 8687억 6713만</t>
+  </si>
+  <si>
+    <t>도령3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
+  </si>
+  <si>
+    <t>62조 5165억 8158만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -2067,22 +2076,13 @@
     <t>56조 5338억 7127만</t>
   </si>
   <si>
-    <t>도령3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
-  </si>
-  <si>
-    <t>52조 2523억 7048만</t>
-  </si>
-  <si>
     <t>조콩나무</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%BD%A9%EB%82%98%EB%AC%B4</t>
   </si>
   <si>
-    <t>47조 3657억 4221만</t>
+    <t>49조 1424억 1837만</t>
   </si>
   <si>
     <t>백엄경</t>
@@ -2091,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
-    <t>28조 7492억 3376만</t>
+    <t>29조 6826억 8222만</t>
   </si>
   <si>
     <t>이러는거아냐</t>
@@ -2109,7 +2109,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
   </si>
   <si>
-    <t>27조 3095억 4161만</t>
+    <t>27조 8183억 6459만</t>
   </si>
   <si>
     <t>키움맨</t>
@@ -2136,7 +2136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
   </si>
   <si>
-    <t>15조 3071억 7112만</t>
+    <t>17조 5039억 9837만</t>
   </si>
   <si>
     <t>한유화</t>
@@ -2145,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>14조 9711억 9031만</t>
+    <t>16조 3190억 3028만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -2154,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
   </si>
   <si>
-    <t>14조 6429억 438만</t>
+    <t>15조 1277억 9749만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -2163,7 +2163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>14조 2969억 3551만</t>
+    <t>14조 8844억 1964만</t>
   </si>
   <si>
     <t>혈마신</t>
@@ -2172,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>8조 5641억 1682만</t>
+    <t>8조 8287억 706만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -2181,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
   </si>
   <si>
-    <t>7조 4312억 8094만</t>
+    <t>7조 8817억 1470만</t>
   </si>
   <si>
     <t>리얼크크</t>
@@ -2190,7 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%96%BC%ED%81%AC%ED%81%AC</t>
   </si>
   <si>
-    <t>5조 3354억 6934만</t>
+    <t>6조 5556억 9102만</t>
   </si>
   <si>
     <t>현즈</t>
@@ -2199,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>4조 8774억 3308만</t>
+    <t>5조 5442억 6289만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -2208,19 +2208,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
   </si>
   <si>
+    <t>4조 3533억 199만</t>
+  </si>
+  <si>
+    <t>군명</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
+  </si>
+  <si>
     <t>98</t>
   </si>
   <si>
-    <t>4조 1421억 9067만</t>
-  </si>
-  <si>
-    <t>군명</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
-  </si>
-  <si>
-    <t>3조 6021억 7591만</t>
+    <t>3조 7757억 6176만</t>
+  </si>
+  <si>
+    <t>김똔똔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
+  </si>
+  <si>
+    <t>3조 1248억 2860만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -2232,22 +2241,13 @@
     <t>3조 620억 6174만</t>
   </si>
   <si>
-    <t>김똔똔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
-  </si>
-  <si>
-    <t>2조 8362억 3551만</t>
-  </si>
-  <si>
     <t>니코짱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
   </si>
   <si>
-    <t>2조 613억 190만</t>
+    <t>2조 2135억 3487만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -2256,7 +2256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%A7%B9%EC%9A%B0</t>
   </si>
   <si>
-    <t>9774억 5685만</t>
+    <t>1조 1323억 8185만</t>
   </si>
 </sst>
 </file>
@@ -2743,16 +2743,16 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2760,31 +2760,31 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>39</v>
@@ -2819,7 +2819,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>47</v>
@@ -2860,13 +2860,13 @@
         <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>56</v>
@@ -2901,22 +2901,22 @@
         <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2924,40 +2924,40 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>24</v>
@@ -2998,28 +2998,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3030,28 +3030,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3062,28 +3062,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3094,28 +3094,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3126,28 +3126,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3158,28 +3158,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3190,28 +3190,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3222,28 +3222,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3254,28 +3254,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3286,28 +3286,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3318,28 +3318,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3350,28 +3350,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3382,28 +3382,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3414,28 +3414,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3446,28 +3446,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3478,7 +3478,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>23</v>
@@ -3487,19 +3487,19 @@
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3510,28 +3510,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3542,28 +3542,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3574,28 +3574,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3606,28 +3606,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3638,28 +3638,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3670,28 +3670,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3702,7 +3702,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>182</v>
@@ -3714,13 +3714,13 @@
         <v>183</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>184</v>
@@ -3746,13 +3746,13 @@
         <v>187</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>188</v>
@@ -3766,7 +3766,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>189</v>
@@ -3778,16 +3778,16 @@
         <v>190</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3798,7 +3798,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>193</v>
@@ -3810,16 +3810,16 @@
         <v>194</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3830,28 +3830,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3911,28 +3911,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3943,28 +3943,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3975,28 +3975,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4007,28 +4007,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4039,28 +4039,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4071,28 +4071,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4103,28 +4103,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4135,28 +4135,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4167,28 +4167,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4199,28 +4199,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4231,28 +4231,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4263,28 +4263,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4295,28 +4295,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4327,28 +4327,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4359,28 +4359,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4391,28 +4391,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4423,28 +4423,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4455,28 +4455,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4487,28 +4487,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4519,28 +4519,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4551,28 +4551,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4583,28 +4583,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4615,28 +4615,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4650,25 +4650,25 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4679,28 +4679,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4711,28 +4711,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4743,28 +4743,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4775,28 +4775,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4807,28 +4807,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4839,28 +4839,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4871,7 +4871,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>292</v>
@@ -4883,13 +4883,13 @@
         <v>293</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>294</v>
@@ -4956,28 +4956,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>295</v>
@@ -5000,13 +5000,13 @@
         <v>296</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>297</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>298</v>
@@ -5032,13 +5032,13 @@
         <v>299</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>300</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>301</v>
@@ -5064,13 +5064,13 @@
         <v>302</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>303</v>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>304</v>
@@ -5096,13 +5096,13 @@
         <v>305</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>306</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>307</v>
@@ -5128,13 +5128,13 @@
         <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>309</v>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>310</v>
@@ -5160,13 +5160,13 @@
         <v>311</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>312</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>313</v>
@@ -5192,13 +5192,13 @@
         <v>314</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>315</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>316</v>
@@ -5224,13 +5224,13 @@
         <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>318</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>319</v>
@@ -5256,13 +5256,13 @@
         <v>320</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>321</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>322</v>
@@ -5288,13 +5288,13 @@
         <v>323</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>324</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>325</v>
@@ -5320,13 +5320,13 @@
         <v>326</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>327</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>328</v>
@@ -5352,13 +5352,13 @@
         <v>329</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>330</v>
@@ -5369,10 +5369,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>331</v>
@@ -5384,13 +5384,13 @@
         <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>333</v>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>334</v>
@@ -5416,13 +5416,13 @@
         <v>335</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>336</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>337</v>
@@ -5448,13 +5448,13 @@
         <v>338</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>339</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>340</v>
@@ -5480,13 +5480,13 @@
         <v>341</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>342</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>343</v>
@@ -5512,13 +5512,13 @@
         <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>345</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>346</v>
@@ -5544,13 +5544,13 @@
         <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>348</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>349</v>
@@ -5576,13 +5576,13 @@
         <v>350</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>351</v>
@@ -5593,10 +5593,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>352</v>
@@ -5608,13 +5608,13 @@
         <v>353</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>354</v>
@@ -5625,10 +5625,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>355</v>
@@ -5640,13 +5640,13 @@
         <v>356</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>357</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>358</v>
@@ -5672,13 +5672,13 @@
         <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>360</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
@@ -5704,13 +5704,13 @@
         <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>363</v>
@@ -5721,31 +5721,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>42</v>
@@ -5753,28 +5753,28 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>368</v>
@@ -5785,10 +5785,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>369</v>
@@ -5800,13 +5800,13 @@
         <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>371</v>
@@ -5817,10 +5817,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>372</v>
@@ -5832,13 +5832,13 @@
         <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>374</v>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>375</v>
@@ -5864,13 +5864,13 @@
         <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>377</v>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>378</v>
@@ -5896,13 +5896,13 @@
         <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>380</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>381</v>
@@ -5928,13 +5928,13 @@
         <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>383</v>
@@ -6001,28 +6001,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6033,7 +6033,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>384</v>
@@ -6045,13 +6045,13 @@
         <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>386</v>
@@ -6065,7 +6065,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -6077,16 +6077,16 @@
         <v>387</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>204</v>
+        <v>388</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6097,28 +6097,28 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6129,28 +6129,28 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6161,28 +6161,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6193,28 +6193,28 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6225,28 +6225,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6257,28 +6257,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6289,28 +6289,28 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6321,28 +6321,28 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6353,28 +6353,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6385,28 +6385,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6417,28 +6417,28 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6449,28 +6449,28 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6481,28 +6481,28 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6513,28 +6513,28 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6545,28 +6545,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6577,28 +6577,28 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6609,28 +6609,28 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6641,28 +6641,28 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6673,28 +6673,28 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6705,28 +6705,28 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6740,25 +6740,25 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6769,28 +6769,28 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6801,28 +6801,28 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6833,28 +6833,28 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6865,28 +6865,28 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6897,28 +6897,28 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6929,28 +6929,28 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7004,7 +7004,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7013,28 +7013,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -7045,7 +7045,7 @@
         <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>58</v>
@@ -7054,16 +7054,16 @@
         <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>474</v>
@@ -7077,7 +7077,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>475</v>
@@ -7089,13 +7089,13 @@
         <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>477</v>
@@ -7109,7 +7109,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>478</v>
@@ -7121,13 +7121,13 @@
         <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>480</v>
@@ -7141,7 +7141,7 @@
         <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>481</v>
@@ -7153,13 +7153,13 @@
         <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>483</v>
@@ -7173,7 +7173,7 @@
         <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>484</v>
@@ -7185,13 +7185,13 @@
         <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>486</v>
@@ -7205,7 +7205,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>487</v>
@@ -7217,13 +7217,13 @@
         <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>489</v>
@@ -7237,7 +7237,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>490</v>
@@ -7249,13 +7249,13 @@
         <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>492</v>
@@ -7269,7 +7269,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>493</v>
@@ -7281,13 +7281,13 @@
         <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>495</v>
@@ -7301,7 +7301,7 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>496</v>
@@ -7313,13 +7313,13 @@
         <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>498</v>
@@ -7333,7 +7333,7 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>499</v>
@@ -7345,13 +7345,13 @@
         <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>501</v>
@@ -7365,7 +7365,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>502</v>
@@ -7377,13 +7377,13 @@
         <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>504</v>
@@ -7397,7 +7397,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>505</v>
@@ -7409,13 +7409,13 @@
         <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>507</v>
@@ -7429,7 +7429,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>508</v>
@@ -7441,13 +7441,13 @@
         <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>510</v>
@@ -7461,7 +7461,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>511</v>
@@ -7473,13 +7473,13 @@
         <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>513</v>
@@ -7493,7 +7493,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>514</v>
@@ -7505,13 +7505,13 @@
         <v>515</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>516</v>
@@ -7525,7 +7525,7 @@
         <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>517</v>
@@ -7537,13 +7537,13 @@
         <v>518</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>519</v>
@@ -7557,7 +7557,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>520</v>
@@ -7569,13 +7569,13 @@
         <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>522</v>
@@ -7589,7 +7589,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>523</v>
@@ -7601,13 +7601,13 @@
         <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>525</v>
@@ -7621,7 +7621,7 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>526</v>
@@ -7633,13 +7633,13 @@
         <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>528</v>
@@ -7653,7 +7653,7 @@
         <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>529</v>
@@ -7665,13 +7665,13 @@
         <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>531</v>
@@ -7685,7 +7685,7 @@
         <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>532</v>
@@ -7697,13 +7697,13 @@
         <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>534</v>
@@ -7717,7 +7717,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>535</v>
@@ -7729,16 +7729,16 @@
         <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7752,22 +7752,22 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>541</v>
@@ -7781,7 +7781,7 @@
         <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>542</v>
@@ -7793,13 +7793,13 @@
         <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>544</v>
@@ -7813,7 +7813,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>545</v>
@@ -7825,13 +7825,13 @@
         <v>546</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>547</v>
@@ -7845,7 +7845,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>548</v>
@@ -7857,13 +7857,13 @@
         <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>550</v>
@@ -7877,7 +7877,7 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>551</v>
@@ -7889,13 +7889,13 @@
         <v>552</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>553</v>
@@ -7909,7 +7909,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>554</v>
@@ -7921,13 +7921,13 @@
         <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>556</v>
@@ -7941,7 +7941,7 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>557</v>
@@ -7953,13 +7953,13 @@
         <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>559</v>
@@ -7973,7 +7973,7 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>560</v>
@@ -7985,13 +7985,13 @@
         <v>561</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>562</v>
@@ -8058,28 +8058,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -8090,7 +8090,7 @@
         <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>563</v>
@@ -8102,13 +8102,13 @@
         <v>564</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>565</v>
@@ -8122,7 +8122,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>566</v>
@@ -8134,13 +8134,13 @@
         <v>567</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>568</v>
@@ -8154,7 +8154,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>569</v>
@@ -8166,13 +8166,13 @@
         <v>570</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>571</v>
@@ -8186,7 +8186,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>572</v>
@@ -8198,13 +8198,13 @@
         <v>573</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>574</v>
@@ -8218,7 +8218,7 @@
         <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>575</v>
@@ -8230,13 +8230,13 @@
         <v>576</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>577</v>
@@ -8250,7 +8250,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>578</v>
@@ -8262,13 +8262,13 @@
         <v>579</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>580</v>
@@ -8282,7 +8282,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>581</v>
@@ -8294,13 +8294,13 @@
         <v>582</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>583</v>
@@ -8314,7 +8314,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>584</v>
@@ -8326,13 +8326,13 @@
         <v>585</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>586</v>
@@ -8346,7 +8346,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>587</v>
@@ -8358,13 +8358,13 @@
         <v>588</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>589</v>
@@ -8378,7 +8378,7 @@
         <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>590</v>
@@ -8390,13 +8390,13 @@
         <v>591</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>592</v>
@@ -8410,7 +8410,7 @@
         <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>593</v>
@@ -8422,13 +8422,13 @@
         <v>594</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>595</v>
@@ -8442,7 +8442,7 @@
         <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>596</v>
@@ -8454,13 +8454,13 @@
         <v>597</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>598</v>
@@ -8474,7 +8474,7 @@
         <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>599</v>
@@ -8486,13 +8486,13 @@
         <v>600</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>601</v>
@@ -8506,7 +8506,7 @@
         <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>602</v>
@@ -8518,13 +8518,13 @@
         <v>603</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>604</v>
@@ -8538,7 +8538,7 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>605</v>
@@ -8550,13 +8550,13 @@
         <v>606</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>607</v>
@@ -8570,7 +8570,7 @@
         <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>608</v>
@@ -8582,13 +8582,13 @@
         <v>609</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>610</v>
@@ -8602,7 +8602,7 @@
         <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>611</v>
@@ -8614,13 +8614,13 @@
         <v>612</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>613</v>
@@ -8634,7 +8634,7 @@
         <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>614</v>
@@ -8646,13 +8646,13 @@
         <v>615</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>616</v>
@@ -8666,7 +8666,7 @@
         <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>617</v>
@@ -8678,13 +8678,13 @@
         <v>618</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>619</v>
@@ -8698,7 +8698,7 @@
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>620</v>
@@ -8710,13 +8710,13 @@
         <v>621</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>622</v>
@@ -8730,7 +8730,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>623</v>
@@ -8742,13 +8742,13 @@
         <v>624</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>625</v>
@@ -8762,7 +8762,7 @@
         <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>626</v>
@@ -8774,13 +8774,13 @@
         <v>627</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>628</v>
@@ -8806,13 +8806,13 @@
         <v>630</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>631</v>
@@ -8826,7 +8826,7 @@
         <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>632</v>
@@ -8838,10 +8838,10 @@
         <v>633</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>634</v>
@@ -8858,7 +8858,7 @@
         <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>636</v>
@@ -8870,13 +8870,13 @@
         <v>637</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>638</v>
@@ -8890,7 +8890,7 @@
         <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>639</v>
@@ -8902,10 +8902,10 @@
         <v>640</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>634</v>
@@ -8922,7 +8922,7 @@
         <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>642</v>
@@ -8934,10 +8934,10 @@
         <v>643</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>644</v>
@@ -8954,22 +8954,22 @@
         <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>646</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>644</v>
@@ -8986,7 +8986,7 @@
         <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>648</v>
@@ -8998,10 +8998,10 @@
         <v>649</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>650</v>
@@ -9070,28 +9070,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>652</v>
@@ -9114,13 +9114,13 @@
         <v>653</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>654</v>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>655</v>
@@ -9146,13 +9146,13 @@
         <v>656</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>657</v>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>658</v>
@@ -9178,13 +9178,13 @@
         <v>659</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>660</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>661</v>
@@ -9210,13 +9210,13 @@
         <v>662</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>663</v>
@@ -9227,10 +9227,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>664</v>
@@ -9242,13 +9242,13 @@
         <v>665</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>666</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>667</v>
@@ -9274,13 +9274,13 @@
         <v>668</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>669</v>
@@ -9291,28 +9291,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>670</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>671</v>
@@ -9323,10 +9323,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>672</v>
@@ -9338,13 +9338,13 @@
         <v>673</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>674</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>675</v>
@@ -9370,13 +9370,13 @@
         <v>676</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>677</v>
@@ -9387,10 +9387,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>678</v>
@@ -9402,13 +9402,13 @@
         <v>679</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>680</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>681</v>
@@ -9434,13 +9434,13 @@
         <v>682</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>683</v>
@@ -9451,10 +9451,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>684</v>
@@ -9466,13 +9466,13 @@
         <v>685</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>686</v>
@@ -9483,10 +9483,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>687</v>
@@ -9498,13 +9498,13 @@
         <v>688</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>689</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>690</v>
@@ -9530,13 +9530,13 @@
         <v>691</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>692</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>693</v>
@@ -9562,13 +9562,13 @@
         <v>694</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>695</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>696</v>
@@ -9594,13 +9594,13 @@
         <v>697</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>698</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>699</v>
@@ -9626,13 +9626,13 @@
         <v>700</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>701</v>
@@ -9643,10 +9643,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>702</v>
@@ -9658,13 +9658,13 @@
         <v>703</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>704</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>705</v>
@@ -9690,13 +9690,13 @@
         <v>706</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>707</v>
@@ -9707,10 +9707,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>708</v>
@@ -9722,13 +9722,13 @@
         <v>709</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>710</v>
@@ -9739,10 +9739,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>711</v>
@@ -9754,13 +9754,13 @@
         <v>712</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>713</v>
@@ -9771,10 +9771,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>714</v>
@@ -9786,13 +9786,13 @@
         <v>715</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>716</v>
@@ -9803,7 +9803,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
@@ -9818,13 +9818,13 @@
         <v>718</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>537</v>
+        <v>449</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>719</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>720</v>
@@ -9850,13 +9850,13 @@
         <v>721</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>537</v>
+        <v>449</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>722</v>
@@ -9867,10 +9867,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>723</v>
@@ -9882,16 +9882,16 @@
         <v>724</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9899,28 +9899,28 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>729</v>
@@ -9931,10 +9931,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>730</v>
@@ -9946,13 +9946,13 @@
         <v>731</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>732</v>
@@ -9963,10 +9963,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>733</v>
@@ -9978,13 +9978,13 @@
         <v>734</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>735</v>
@@ -9995,10 +9995,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>736</v>
@@ -10010,10 +10010,10 @@
         <v>737</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>634</v>
@@ -10027,10 +10027,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>739</v>
@@ -10042,10 +10042,10 @@
         <v>740</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>644</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -642,6 +642,18 @@
     <t>1경 2747조 9927억 4574만</t>
   </si>
   <si>
+    <t>디올핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EC%98%AC%ED%95%91</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>3199조 1193억 6158만</t>
+  </si>
+  <si>
     <t>카뚝</t>
   </si>
   <si>
@@ -654,18 +666,6 @@
     <t>3126조 9530억 3038만</t>
   </si>
   <si>
-    <t>디올핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EC%98%AC%ED%95%91</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>3094조 6038억 7206만</t>
-  </si>
-  <si>
     <t>쥬정뱅이</t>
   </si>
   <si>
@@ -846,7 +846,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>46조 7324억 2599만</t>
+    <t>47조 527억 3992만</t>
   </si>
   <si>
     <t>머쓰윽타드</t>
@@ -1200,7 +1200,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>2604조 1519억 6474만</t>
+    <t>2783조 7486억 5197만</t>
   </si>
   <si>
     <t>26상탗</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1601조 7815억 6566만</t>
+    <t>1602조 4421억 8043만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1365,6 +1365,18 @@
     <t>17조 6676억 1993만</t>
   </si>
   <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>16조 4521억 4228만</t>
+  </si>
+  <si>
     <t>26조선</t>
   </si>
   <si>
@@ -1386,18 +1398,6 @@
     <t>15조 637억 960만</t>
   </si>
   <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>13조 8329억 6602만</t>
-  </si>
-  <si>
     <t>뿜삐</t>
   </si>
   <si>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>180조 1593억 4007만</t>
+    <t>180조 2187억 3061만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -3990,10 +3990,10 @@
         <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>206</v>
@@ -4022,10 +4022,10 @@
         <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>210</v>
@@ -4665,7 +4665,7 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>271</v>
@@ -5070,7 +5070,7 @@
         <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>303</v>
@@ -5131,7 +5131,7 @@
         <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>93</v>
@@ -6176,7 +6176,7 @@
         <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>116</v>
@@ -6688,13 +6688,13 @@
         <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>446</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>261</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6708,22 +6708,22 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>449</v>
+        <v>261</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>450</v>
@@ -6752,10 +6752,10 @@
         <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>454</v>
@@ -7735,7 +7735,7 @@
         <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>537</v>
@@ -7831,7 +7831,7 @@
         <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>547</v>
@@ -7991,7 +7991,7 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>562</v>
@@ -8233,7 +8233,7 @@
         <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>93</v>
@@ -8652,7 +8652,7 @@
         <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>616</v>
@@ -8780,7 +8780,7 @@
         <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>628</v>
@@ -8812,7 +8812,7 @@
         <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>631</v>
@@ -9152,7 +9152,7 @@
         <v>115</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>657</v>
@@ -9184,7 +9184,7 @@
         <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>660</v>
@@ -9472,7 +9472,7 @@
         <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>686</v>
@@ -9664,7 +9664,7 @@
         <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>704</v>
@@ -9824,7 +9824,7 @@
         <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>719</v>
@@ -9856,7 +9856,7 @@
         <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>722</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -1491,6 +1491,15 @@
     <t>2291조 1697억 43만</t>
   </si>
   <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1407조 6499억 5640만</t>
+  </si>
+  <si>
     <t>말레이히어로</t>
   </si>
   <si>
@@ -1500,15 +1509,6 @@
     <t>1394조 1932억 8825만</t>
   </si>
   <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1351조 3377억 9806만</t>
-  </si>
-  <si>
     <t>빌런투킬</t>
   </si>
   <si>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>162조 1649억 2915만</t>
+    <t>162조 5886억 9598만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>42조 7791억 4344만</t>
+    <t>43조 9302억 789만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1671,6 +1671,15 @@
     <t>35조 3962억 1100만</t>
   </si>
   <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>32조 6412억 5256만</t>
+  </si>
+  <si>
     <t>대방어조아</t>
   </si>
   <si>
@@ -1702,15 +1711,6 @@
   </si>
   <si>
     <t>29조 2978억 7327만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>28조 3643억 3420만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -7153,7 +7153,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>92</v>
@@ -7185,7 +7185,7 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>92</v>
@@ -7793,10 +7793,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>548</v>
@@ -7825,10 +7825,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>551</v>
@@ -7857,10 +7857,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>554</v>
@@ -7877,25 +7877,25 @@
         <v>47</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>555</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>555</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7909,22 +7909,22 @@
         <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>557</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>559</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -9,11 +9,11 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="딸기키우기" sheetId="2" r:id="rId2"/>
-    <sheet name="이콩" sheetId="3" r:id="rId3"/>
+    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
     <sheet name="LUXURY" sheetId="4" r:id="rId4"/>
     <sheet name="고점" sheetId="5" r:id="rId5"/>
-    <sheet name="셀린느" sheetId="6" r:id="rId6"/>
-    <sheet name="싸이월드" sheetId="7" r:id="rId7"/>
+    <sheet name="싸이월드" sheetId="6" r:id="rId6"/>
+    <sheet name="이콩" sheetId="7" r:id="rId7"/>
     <sheet name="라때는말이야" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">딸기키우기!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">셀린느!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">이콩!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">싸이월드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">이콩!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,6 +108,105 @@
     <t>2026.04.17</t>
   </si>
   <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 4688조 3717억 8454만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 5624조 8913억 5301만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2경 4932조 7746억 8196만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>2경 4565조 7950억 589만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
     <t>이콩</t>
   </si>
   <si>
@@ -123,9 +222,6 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>29명</t>
-  </si>
-  <si>
     <t>2경 4637조 8545억 7188만</t>
   </si>
   <si>
@@ -135,102 +231,6 @@
     <t>요쯔</t>
   </si>
   <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 5624조 8913억 5301만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>2경 4932조 7746억 8196만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2경 4659조 4565억 6859만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>2경 4565조 7950억 589만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
     <t>라때는말이야</t>
   </si>
   <si>
@@ -654,15 +654,1083 @@
     <t>18조 6610억 3103만</t>
   </si>
   <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2291조 1697억 43만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1407조 6499억 5640만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>1394조 1932억 8825만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>278조 3832억 696만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>174조 1025억 3447만</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>162조 5886억 9598만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>150조 7025억 6128만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>135조 4527억 1903만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>101조 3300억 3895만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>84조 4353억 6632만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>83조 4958억 6972만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>79조 606억 7880만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>46조 4973억 6304만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>43조 9302억 789만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>40조 6065억 2233만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>40조 3193억 9244만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1459억 7981만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>33조 1885억 3176만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>32조 2430억 2723만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>31조 4662억 190만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>29조 5789억 1997만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>24조 3071억 135만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>1경 6991조 8873억 8940만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2831조 1506억 5892만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1676조 5414억 1837만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>708조 1355억 7402만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>516조 9172억 9058만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>473조 935억 9830만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>457조 7446억 1398만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>381조 6871억 2231만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>353조 4051억 6458만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>267조 4873억 4322만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>216조 5819억 7929만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>196조 911억 5708만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>181조 4736억 2563만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>88조 5232억 4641만</t>
+  </si>
+  <si>
+    <t>하탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>73조 6589억 4898만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>43조 5788억 651만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>37조 4179억 3701만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>23조 1264억 4895만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>21조 9533억 9367만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>21조 3943억 1549만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>19조 728억 950만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>18조 7407억 6984만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>18조 1871억 4713만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>17조 1535억 3231만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>14조 623억 4943만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>13조 7002억 6087만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>8조 6489억 2060만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>7조 905억 306만</t>
+  </si>
+  <si>
+    <t>고영희멈뭄미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 9661억 9494만</t>
+  </si>
+  <si>
+    <t>THE끌림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>9185조 2104억 1214만</t>
+  </si>
+  <si>
+    <t>멸국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>7637조 5387억 5123만</t>
+  </si>
+  <si>
+    <t>NUKE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
+  </si>
+  <si>
+    <t>3443조 8915억 676만</t>
+  </si>
+  <si>
+    <t>쌔주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>1712조 8787억 1372만</t>
+  </si>
+  <si>
+    <t>픠즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>521조 9925억 2987만</t>
+  </si>
+  <si>
+    <t>똔똔잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
+  </si>
+  <si>
+    <t>460조 1447억 9911만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
+  </si>
+  <si>
+    <t>414조 6451억 1146만</t>
+  </si>
+  <si>
+    <t>S2베코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
+  </si>
+  <si>
+    <t>397조 6333억 9949만</t>
+  </si>
+  <si>
+    <t>환불한너잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
+  </si>
+  <si>
+    <t>292조 5925억 4808만</t>
+  </si>
+  <si>
+    <t>아투피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
+  </si>
+  <si>
+    <t>284조 4707억 2132만</t>
+  </si>
+  <si>
+    <t>뷰질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
+  </si>
+  <si>
+    <t>239조 9115억 8111만</t>
+  </si>
+  <si>
+    <t>근접맞나이거</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
+  </si>
+  <si>
+    <t>125조 4174억 3407만</t>
+  </si>
+  <si>
+    <t>순서교체</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
+  </si>
+  <si>
+    <t>83조 1135억 1769만</t>
+  </si>
+  <si>
+    <t>김천아재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>60조 4489억 1441만</t>
+  </si>
+  <si>
+    <t>약할뻔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
+  </si>
+  <si>
+    <t>54조 1677억 7881만</t>
+  </si>
+  <si>
+    <t>맥맥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
+  </si>
+  <si>
+    <t>48조 2417억 2969만</t>
+  </si>
+  <si>
+    <t>무썬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
+  </si>
+  <si>
+    <t>45조 6533억 6659만</t>
+  </si>
+  <si>
+    <t>성칙이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>40조 589억 5183만</t>
+  </si>
+  <si>
+    <t>안재똥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
+  </si>
+  <si>
+    <t>34조 6364억 9517만</t>
+  </si>
+  <si>
+    <t>숔숔숔숔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
+  </si>
+  <si>
+    <t>23조 6226억 513만</t>
+  </si>
+  <si>
+    <t>돌아온홍굴이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19조 3844억 5289만</t>
+  </si>
+  <si>
+    <t>kiaer</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
+  </si>
+  <si>
+    <t>18조 168억 7310만</t>
+  </si>
+  <si>
+    <t>순샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
+  </si>
+  <si>
+    <t>14조 327억 2590만</t>
+  </si>
+  <si>
+    <t>보마가될인재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>12조 6829억 6156만</t>
+  </si>
+  <si>
+    <t>구뺑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
+  </si>
+  <si>
+    <t>9조 5413억 4809만</t>
+  </si>
+  <si>
+    <t>탱탱볼탱탱볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>9조 3091억 8659만</t>
+  </si>
+  <si>
+    <t>기차아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>8조 1174억 664만</t>
+  </si>
+  <si>
+    <t>이서지용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>7조 8263억 6165만</t>
+  </si>
+  <si>
+    <t>힐줄까</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
+  </si>
+  <si>
+    <t>1경 2826조 9385억 9729만</t>
+  </si>
+  <si>
+    <t>키노눙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
+  </si>
+  <si>
+    <t>5492조 4561억 7507만</t>
+  </si>
+  <si>
+    <t>닉네임미정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EB%84%A4%EC%9E%84%EB%AF%B8%EC%A0%95</t>
+  </si>
+  <si>
+    <t>2815조 1492억 7249만</t>
+  </si>
+  <si>
+    <t>한마드릴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
+  </si>
+  <si>
+    <t>926조 3779억 3028만</t>
+  </si>
+  <si>
+    <t>윤돌이굴돌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>810조 5247억 4427만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>632조 6627억 5610만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>382조 3117억 4486만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>334조 3891억 2620만</t>
+  </si>
+  <si>
+    <t>쏘세용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>110조 8680억 6765만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>64조 9984억 1728만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>58조 7829억 7512만</t>
+  </si>
+  <si>
+    <t>다끝남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>49조 3791억 2239만</t>
+  </si>
+  <si>
+    <t>갓쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>49조 3515억 8411만</t>
+  </si>
+  <si>
+    <t>퀸돈대통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
+  </si>
+  <si>
+    <t>49조 3143억 9658만</t>
+  </si>
+  <si>
+    <t>킴술하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
+  </si>
+  <si>
+    <t>44조 4619억 465만</t>
+  </si>
+  <si>
+    <t>우당탕탼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
+  </si>
+  <si>
+    <t>44조 1836억 7409만</t>
+  </si>
+  <si>
+    <t>김컁구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>39조 7023억 7022만</t>
+  </si>
+  <si>
+    <t>표창빌런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
+  </si>
+  <si>
+    <t>29조 3826억 9245만</t>
+  </si>
+  <si>
+    <t>사철화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>19조 9280억 6163만</t>
+  </si>
+  <si>
+    <t>얼음조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>12조 5977억 6174만</t>
+  </si>
+  <si>
+    <t>잼이유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>12조 4975억 2049만</t>
+  </si>
+  <si>
+    <t>시네루최</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 6838억 6523만</t>
+  </si>
+  <si>
+    <t>메린이이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 3450억 781만</t>
+  </si>
+  <si>
+    <t>57년김춘배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>4조 6941억 6162만</t>
+  </si>
+  <si>
+    <t>붕붕월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>4조 303억 7359만</t>
+  </si>
+  <si>
+    <t>아신아이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%8B%A0%EC%95%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 8312억 9235만</t>
+  </si>
+  <si>
+    <t>킴밍끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 5579억 1535만</t>
+  </si>
+  <si>
+    <t>박살곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%82%B4%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>3조 4189억 5339만</t>
+  </si>
+  <si>
+    <t>최시네루친구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B9%9C%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>2조 9747억 5658만</t>
+  </si>
+  <si>
+    <t>카찍스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%B0%8D%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>1조 4746억 872만</t>
+  </si>
+  <si>
     <t>싸뤽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>1경 944조 8907억 2718만</t>
   </si>
   <si>
@@ -699,9 +1767,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>신궁</t>
-  </si>
-  <si>
     <t>747조 987억 1716만</t>
   </si>
   <si>
@@ -783,9 +1848,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
     <t>39조 6191억 375만</t>
   </si>
   <si>
@@ -867,9 +1929,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>8조 6164억 1816만</t>
   </si>
   <si>
@@ -879,9 +1938,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>4조 3833억 4067만</t>
   </si>
   <si>
@@ -891,9 +1947,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>99</t>
-  </si>
-  <si>
     <t>3조 3517억 255만</t>
   </si>
   <si>
@@ -903,9 +1956,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>97</t>
-  </si>
-  <si>
     <t>1조 2182억 5558만</t>
   </si>
   <si>
@@ -937,1056 +1987,6 @@
   </si>
   <si>
     <t>6722억 4026만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>1경 6991조 8873억 8940만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>2783조 7486억 5197만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1675조 2080억 6401만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>651조 4386억 2995만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>516조 9172억 9058만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>473조 935억 9830만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>457조 7446억 1398만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>380조 3833억 3836만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>345조 6593억 1885만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>267조 4873억 4322만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>216조 5819억 7929만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>196조 911억 5708만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>181조 4736억 2563만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>85조 7125억 8889만</t>
-  </si>
-  <si>
-    <t>하탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>59조 6571억 7041만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>41조 4388억 7692만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>34조 7192억 7265만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>29조 4752억 2082만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>23조 1264억 4895만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>21조 9533억 9367만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>21조 3943억 1549만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>19조 728억 950만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>18조 7407억 6984만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>15조 1898억 2101만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>13조 2695억 2748만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>12조 4978억 3574만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>12조 1214억 5182만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>8조 6161억 9253만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>7조 905억 306만</t>
-  </si>
-  <si>
-    <t>고영희멈뭄미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5조 9125억 826만</t>
-  </si>
-  <si>
-    <t>THE끌림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>8950조 9043억 971만</t>
-  </si>
-  <si>
-    <t>멸국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>7560조 9966억 6082만</t>
-  </si>
-  <si>
-    <t>NUKE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>3255조 5975억 1585만</t>
-  </si>
-  <si>
-    <t>쌔주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>1618조 1246억 1650만</t>
-  </si>
-  <si>
-    <t>픠즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>502조 1892억 3063만</t>
-  </si>
-  <si>
-    <t>똔똔잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
-  </si>
-  <si>
-    <t>454조 8360억 8001만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
-  </si>
-  <si>
-    <t>414조 6451억 1146만</t>
-  </si>
-  <si>
-    <t>S2베코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
-  </si>
-  <si>
-    <t>353조 7250억 6762만</t>
-  </si>
-  <si>
-    <t>환불한너잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
-  </si>
-  <si>
-    <t>291조 2275억 8457만</t>
-  </si>
-  <si>
-    <t>아투피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
-  </si>
-  <si>
-    <t>284조 4707억 2132만</t>
-  </si>
-  <si>
-    <t>뷰질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
-  </si>
-  <si>
-    <t>239조 9115억 8111만</t>
-  </si>
-  <si>
-    <t>근접맞나이거</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
-  </si>
-  <si>
-    <t>125조 4174억 3407만</t>
-  </si>
-  <si>
-    <t>순서교체</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
-  </si>
-  <si>
-    <t>82조 9458억 9343만</t>
-  </si>
-  <si>
-    <t>약할뻔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
-  </si>
-  <si>
-    <t>54조 1677억 7881만</t>
-  </si>
-  <si>
-    <t>김천아재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>53조 3569억 7504만</t>
-  </si>
-  <si>
-    <t>맥맥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
-  </si>
-  <si>
-    <t>48조 2417억 2969만</t>
-  </si>
-  <si>
-    <t>무썬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
-  </si>
-  <si>
-    <t>45조 6315억 7091만</t>
-  </si>
-  <si>
-    <t>성칙이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>37조 2950억 4962만</t>
-  </si>
-  <si>
-    <t>안재똥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
-  </si>
-  <si>
-    <t>26조 8700억 5850만</t>
-  </si>
-  <si>
-    <t>숔숔숔숔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
-  </si>
-  <si>
-    <t>23조 5448억 5268만</t>
-  </si>
-  <si>
-    <t>kiaer</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
-  </si>
-  <si>
-    <t>18조 168억 7310만</t>
-  </si>
-  <si>
-    <t>돌아온홍굴이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>17조 6905억 3591만</t>
-  </si>
-  <si>
-    <t>순샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
-  </si>
-  <si>
-    <t>13조 3280억 2823만</t>
-  </si>
-  <si>
-    <t>보마가될인재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>11조 7105억 9506만</t>
-  </si>
-  <si>
-    <t>탱탱볼탱탱볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>9조 293억 623만</t>
-  </si>
-  <si>
-    <t>기차아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>8조 1174억 664만</t>
-  </si>
-  <si>
-    <t>구뺑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
-  </si>
-  <si>
-    <t>8조 609억 9947만</t>
-  </si>
-  <si>
-    <t>이서지용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>7조 8263억 6165만</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2291조 1697억 43만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1407조 6499억 5640만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1394조 1932억 8825만</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1120조 9927억 5165만</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>278조 3832억 696만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>174조 1025억 3447만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>162조 5886억 9598만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>150조 7025억 6128만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>135조 4527억 1903만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>89조 2869억 199만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>84조 776억 5946만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>83조 3411억 4487만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>77조 1302억 5026만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>43조 9302억 789만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>42조 7569억 3167만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>37조 5548억 7023만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>35조 3962억 1100만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>32조 6412억 5256만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>32조 3503억 166만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>30조 2709억 4719만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>29조 9578억 9214만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>29조 2978억 7327만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>24조 3071억 135만</t>
-  </si>
-  <si>
-    <t>힐줄까</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
-  </si>
-  <si>
-    <t>1경 2526조 7922억 3122만</t>
-  </si>
-  <si>
-    <t>키노눙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
-  </si>
-  <si>
-    <t>4639조 5492억 2684만</t>
-  </si>
-  <si>
-    <t>닉네임미정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EB%84%A4%EC%9E%84%EB%AF%B8%EC%A0%95</t>
-  </si>
-  <si>
-    <t>2815조 1492억 7249만</t>
-  </si>
-  <si>
-    <t>한마드릴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
-  </si>
-  <si>
-    <t>926조 3779억 3028만</t>
-  </si>
-  <si>
-    <t>윤돌이굴돌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>810조 5247억 4427만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>581조 1475억 4080만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>382조 3117억 4486만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>334조 3891억 2620만</t>
-  </si>
-  <si>
-    <t>쏘세용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>103조 9154억 4061만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>64조 9984억 1728만</t>
-  </si>
-  <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>54조 3822억 5318만</t>
-  </si>
-  <si>
-    <t>다끝남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>49조 3791억 2239만</t>
-  </si>
-  <si>
-    <t>갓쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>45조 8639억 797만</t>
-  </si>
-  <si>
-    <t>우당탕탼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
-  </si>
-  <si>
-    <t>42조 3919억 6973만</t>
-  </si>
-  <si>
-    <t>킴술하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
-  </si>
-  <si>
-    <t>41조 4063억 7022만</t>
-  </si>
-  <si>
-    <t>김컁구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>37조 4250억 223만</t>
-  </si>
-  <si>
-    <t>퀸돈대통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
-  </si>
-  <si>
-    <t>32조 6324억 2658만</t>
-  </si>
-  <si>
-    <t>표창빌런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>26조 5626억 8530만</t>
-  </si>
-  <si>
-    <t>사철화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>19조 9280억 6163만</t>
-  </si>
-  <si>
-    <t>얼음조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>12조 5977억 6174만</t>
-  </si>
-  <si>
-    <t>잼이유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>10조 7748억 9824만</t>
-  </si>
-  <si>
-    <t>시네루최</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
-  </si>
-  <si>
-    <t>6조 6249억 814만</t>
-  </si>
-  <si>
-    <t>메린이이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 2541억 9319만</t>
-  </si>
-  <si>
-    <t>57년김춘배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>4조 6900억 460만</t>
-  </si>
-  <si>
-    <t>붕붕월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>4조 100억 4859만</t>
-  </si>
-  <si>
-    <t>아신아이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%8B%A0%EC%95%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 8312억 9235만</t>
-  </si>
-  <si>
-    <t>킴밍끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
-  </si>
-  <si>
-    <t>3조 5579억 1535만</t>
-  </si>
-  <si>
-    <t>박살곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%82%B4%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>3조 4189억 5339만</t>
-  </si>
-  <si>
-    <t>최시네루친구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B9%9C%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>2조 8293억 9751만</t>
-  </si>
-  <si>
-    <t>카찍스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%B0%8D%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 4746억 872만</t>
   </si>
   <si>
     <t>김도움</t>
@@ -2728,16 +2728,16 @@
         <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>30</v>
@@ -2775,22 +2775,22 @@
         <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2798,25 +2798,25 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2825,13 +2825,13 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2839,31 +2839,31 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -2892,19 +2892,19 @@
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>63</v>
@@ -2939,13 +2939,13 @@
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>70</v>
@@ -3859,7 +3859,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>201</v>
@@ -3891,7 +3891,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>204</v>
@@ -4021,13 +4021,13 @@
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4041,25 +4041,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4073,25 +4073,25 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4105,25 +4105,25 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4137,25 +4137,25 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4169,25 +4169,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4201,25 +4201,25 @@
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4233,25 +4233,25 @@
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4265,13 +4265,13 @@
         <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -4280,10 +4280,10 @@
         <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4297,25 +4297,25 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4329,25 +4329,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4361,25 +4361,25 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4393,25 +4393,25 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4425,22 +4425,22 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>251</v>
@@ -4472,7 +4472,7 @@
         <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>254</v>
@@ -4501,10 +4501,10 @@
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>257</v>
@@ -4533,7 +4533,7 @@
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>150</v>
@@ -4565,10 +4565,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>263</v>
@@ -4597,10 +4597,10 @@
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>266</v>
@@ -4629,10 +4629,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>269</v>
@@ -4661,10 +4661,10 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>272</v>
@@ -4693,10 +4693,10 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>275</v>
@@ -4725,13 +4725,13 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4745,25 +4745,25 @@
         <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4777,25 +4777,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4809,25 +4809,25 @@
         <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4838,28 +4838,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>294</v>
+        <v>155</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4870,7 +4870,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>33</v>
@@ -4879,19 +4879,19 @@
         <v>33</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4902,28 +4902,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5021,13 +5021,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -5039,7 +5039,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5053,13 +5053,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -5068,10 +5068,10 @@
         <v>119</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5085,13 +5085,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -5103,7 +5103,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5117,13 +5117,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -5135,7 +5135,7 @@
         <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5149,25 +5149,25 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5181,13 +5181,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -5199,7 +5199,7 @@
         <v>114</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5213,13 +5213,13 @@
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -5231,7 +5231,7 @@
         <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5245,13 +5245,13 @@
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -5263,7 +5263,7 @@
         <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5277,13 +5277,13 @@
         <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -5292,10 +5292,10 @@
         <v>107</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5309,13 +5309,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -5327,7 +5327,7 @@
         <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5341,13 +5341,13 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -5359,7 +5359,7 @@
         <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5373,13 +5373,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -5391,7 +5391,7 @@
         <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5405,13 +5405,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -5423,7 +5423,7 @@
         <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5437,13 +5437,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -5455,7 +5455,7 @@
         <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5469,13 +5469,13 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -5487,7 +5487,7 @@
         <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5501,13 +5501,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -5519,7 +5519,7 @@
         <v>155</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5533,25 +5533,25 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5565,25 +5565,25 @@
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5597,13 +5597,13 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -5615,7 +5615,7 @@
         <v>150</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5629,25 +5629,25 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>195</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5661,13 +5661,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -5679,7 +5679,7 @@
         <v>150</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5693,13 +5693,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -5711,7 +5711,7 @@
         <v>150</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5725,13 +5725,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -5740,10 +5740,10 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5757,13 +5757,13 @@
         <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -5775,7 +5775,7 @@
         <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5789,13 +5789,13 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -5807,7 +5807,7 @@
         <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5821,25 +5821,25 @@
         <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5850,28 +5850,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5882,16 +5882,16 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -5903,7 +5903,7 @@
         <v>199</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5914,16 +5914,16 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -5935,7 +5935,7 @@
         <v>199</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5946,16 +5946,16 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -5967,7 +5967,7 @@
         <v>199</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6060,19 +6060,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -6081,10 +6081,10 @@
         <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6092,19 +6092,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -6116,7 +6116,7 @@
         <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6124,19 +6124,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -6145,10 +6145,10 @@
         <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>400</v>
+        <v>214</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6156,19 +6156,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -6180,7 +6180,7 @@
         <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6188,31 +6188,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6220,19 +6220,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -6244,7 +6244,7 @@
         <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6252,31 +6252,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6284,19 +6284,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -6308,7 +6308,7 @@
         <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6316,19 +6316,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -6340,7 +6340,7 @@
         <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6348,19 +6348,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -6372,7 +6372,7 @@
         <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6380,19 +6380,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -6404,7 +6404,7 @@
         <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6412,19 +6412,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -6436,7 +6436,7 @@
         <v>155</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6444,19 +6444,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -6468,7 +6468,7 @@
         <v>150</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6476,31 +6476,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6508,31 +6508,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6540,31 +6540,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6572,19 +6572,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -6596,7 +6596,7 @@
         <v>150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6604,19 +6604,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -6628,7 +6628,7 @@
         <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6636,19 +6636,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -6660,7 +6660,7 @@
         <v>195</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6668,31 +6668,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6700,31 +6700,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6732,31 +6732,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6764,19 +6764,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -6788,7 +6788,7 @@
         <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6796,31 +6796,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6828,31 +6828,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6860,31 +6860,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6892,31 +6892,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6924,19 +6924,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -6948,7 +6948,7 @@
         <v>195</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6992,1018 +6992,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8051,19 +7039,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>563</v>
+        <v>471</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>563</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>564</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8075,7 +7063,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>565</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8083,19 +7071,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>566</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>566</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>567</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -8104,10 +7092,10 @@
         <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>568</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8115,19 +7103,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>569</v>
+        <v>477</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>569</v>
+        <v>477</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>570</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -8136,10 +7124,10 @@
         <v>107</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>571</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8147,19 +7135,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>573</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -8171,7 +7159,7 @@
         <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>574</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8179,19 +7167,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>576</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -8203,7 +7191,7 @@
         <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>577</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8211,19 +7199,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>579</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -8235,7 +7223,7 @@
         <v>114</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>580</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8243,19 +7231,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -8267,7 +7255,7 @@
         <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>583</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8275,19 +7263,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>584</v>
+        <v>492</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -8299,7 +7287,7 @@
         <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>585</v>
+        <v>493</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8307,19 +7295,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>586</v>
+        <v>494</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>586</v>
+        <v>494</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>587</v>
+        <v>495</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -8328,10 +7316,10 @@
         <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>588</v>
+        <v>496</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8339,19 +7327,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>589</v>
+        <v>497</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>589</v>
+        <v>497</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>590</v>
+        <v>498</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8363,7 +7351,7 @@
         <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>591</v>
+        <v>499</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8371,19 +7359,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>592</v>
+        <v>500</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>592</v>
+        <v>500</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>593</v>
+        <v>501</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
@@ -8395,7 +7383,7 @@
         <v>155</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>594</v>
+        <v>502</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8403,19 +7391,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>595</v>
+        <v>503</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>595</v>
+        <v>503</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>596</v>
+        <v>504</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8427,7 +7415,7 @@
         <v>155</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>597</v>
+        <v>505</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8435,31 +7423,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>598</v>
+        <v>506</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>598</v>
+        <v>506</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>599</v>
+        <v>507</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8467,31 +7455,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>601</v>
+        <v>509</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>601</v>
+        <v>509</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>602</v>
+        <v>510</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>603</v>
+        <v>511</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8499,19 +7487,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>604</v>
+        <v>512</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>604</v>
+        <v>512</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>605</v>
+        <v>513</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -8523,7 +7511,7 @@
         <v>150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>606</v>
+        <v>514</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8531,31 +7519,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>607</v>
+        <v>515</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>607</v>
+        <v>515</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>608</v>
+        <v>516</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>609</v>
+        <v>517</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8563,31 +7551,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>610</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>610</v>
+        <v>518</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>611</v>
+        <v>519</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>612</v>
+        <v>520</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8595,31 +7583,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>613</v>
+        <v>521</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>613</v>
+        <v>521</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>614</v>
+        <v>522</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>615</v>
+        <v>523</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8627,19 +7615,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>616</v>
+        <v>524</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>616</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>617</v>
+        <v>525</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -8651,7 +7639,7 @@
         <v>195</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>618</v>
+        <v>526</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8659,19 +7647,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>619</v>
+        <v>527</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>619</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>620</v>
+        <v>528</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -8683,7 +7671,7 @@
         <v>195</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>621</v>
+        <v>529</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8691,19 +7679,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>622</v>
+        <v>530</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>622</v>
+        <v>530</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>623</v>
+        <v>531</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -8712,10 +7700,10 @@
         <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>624</v>
+        <v>532</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8723,19 +7711,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>625</v>
+        <v>533</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>625</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>626</v>
+        <v>534</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -8744,10 +7732,10 @@
         <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>627</v>
+        <v>536</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8755,31 +7743,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>628</v>
+        <v>537</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>628</v>
+        <v>537</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>629</v>
+        <v>538</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>630</v>
+        <v>539</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8787,31 +7775,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>631</v>
+        <v>540</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>631</v>
+        <v>540</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>632</v>
+        <v>541</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>633</v>
+        <v>542</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8819,19 +7807,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>634</v>
+        <v>543</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>634</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>635</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -8840,10 +7828,10 @@
         <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>636</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8851,19 +7839,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>637</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>637</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>638</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -8872,10 +7860,10 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>639</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8883,19 +7871,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>640</v>
+        <v>550</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>640</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>641</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -8904,10 +7892,10 @@
         <v>119</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>642</v>
+        <v>553</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8915,19 +7903,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>643</v>
+        <v>554</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>643</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>644</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -8936,10 +7924,10 @@
         <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>645</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8947,19 +7935,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>646</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>646</v>
+        <v>557</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>647</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -8968,10 +7956,10 @@
         <v>113</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>286</v>
+        <v>535</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>648</v>
+        <v>559</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8979,19 +7967,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>649</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>649</v>
+        <v>560</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>650</v>
+        <v>561</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -9000,10 +7988,10 @@
         <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>290</v>
+        <v>562</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>651</v>
+        <v>563</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -9047,6 +8035,1018 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -9117,7 +9117,7 @@
         <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>654</v>
@@ -9149,7 +9149,7 @@
         <v>97</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>657</v>
@@ -9210,7 +9210,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>155</v>
@@ -9565,7 +9565,7 @@
         <v>107</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>696</v>
@@ -9661,7 +9661,7 @@
         <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>705</v>
@@ -9722,10 +9722,10 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>711</v>
@@ -9757,7 +9757,7 @@
         <v>141</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>714</v>
@@ -9789,7 +9789,7 @@
         <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>717</v>
@@ -9821,7 +9821,7 @@
         <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>720</v>
@@ -9850,10 +9850,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>723</v>
@@ -9885,7 +9885,7 @@
         <v>119</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>726</v>
@@ -9914,10 +9914,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>729</v>
@@ -9931,7 +9931,7 @@
         <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>730</v>
@@ -9949,7 +9949,7 @@
         <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>732</v>
@@ -9963,7 +9963,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>733</v>
@@ -9981,7 +9981,7 @@
         <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>735</v>
@@ -9995,7 +9995,7 @@
         <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>736</v>
@@ -10013,7 +10013,7 @@
         <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>294</v>
+        <v>644</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>738</v>
@@ -10027,7 +10027,7 @@
         <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>72</v>
@@ -10045,7 +10045,7 @@
         <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>290</v>
+        <v>562</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>740</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>163조 5754억 4231만</t>
+    <t>179조 9670억 2979만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -846,6 +846,15 @@
     <t>65조 7697억 3285만</t>
   </si>
   <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>52조 9036억 6306만</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
@@ -855,15 +864,6 @@
     <t>51조 5399억 1217만</t>
   </si>
   <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>49조 4912억 6649만</t>
-  </si>
-  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9B%80</t>
   </si>
   <si>
-    <t>1경 2209조 228억 1145만</t>
+    <t>1경 2224조 6171억 7285만</t>
   </si>
   <si>
     <t>용려니</t>
@@ -2061,7 +2061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
   </si>
   <si>
-    <t>448조 5004억 6769만</t>
+    <t>460조 5135억 3348만</t>
   </si>
   <si>
     <t>참달</t>
@@ -4704,7 +4704,7 @@
         <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>148</v>
@@ -4736,7 +4736,7 @@
         <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>148</v>
@@ -9232,7 +9232,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -11,27 +11,27 @@
     <sheet name="딸기키우기" sheetId="2" r:id="rId2"/>
     <sheet name="셀린느" sheetId="3" r:id="rId3"/>
     <sheet name="LUXURY" sheetId="4" r:id="rId4"/>
-    <sheet name="고점" sheetId="5" r:id="rId5"/>
-    <sheet name="이콩" sheetId="6" r:id="rId6"/>
+    <sheet name="이콩" sheetId="5" r:id="rId5"/>
+    <sheet name="고점" sheetId="6" r:id="rId6"/>
     <sheet name="싸이월드" sheetId="7" r:id="rId7"/>
     <sheet name="라때는말이야" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">고점!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">딸기키우기!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이콩!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="756">
   <si>
     <t>guild_name</t>
   </si>
@@ -162,6 +162,33 @@
     <t>살뽀시</t>
   </si>
   <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>27명</t>
+  </si>
+  <si>
+    <t>2경 7734조 6358억 5468만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
     <t>고점</t>
   </si>
   <si>
@@ -186,33 +213,6 @@
     <t>루팡잉</t>
   </si>
   <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>27명</t>
-  </si>
-  <si>
-    <t>2경 7734조 6358억 5468만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
     <t>싸이월드</t>
   </si>
   <si>
@@ -297,7 +297,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>1경 3736조 3708억 4126만</t>
+    <t>1경 3975조 3702억 544만</t>
   </si>
   <si>
     <t>2</t>
@@ -318,7 +318,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>3647조 3345억 9699만</t>
+    <t>3653조 9132억 8396만</t>
   </si>
   <si>
     <t>3</t>
@@ -351,7 +351,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>1306조 1350억 3612만</t>
+    <t>1383조 3577억 1491만</t>
   </si>
   <si>
     <t>5</t>
@@ -366,66 +366,66 @@
     <t>다크나이트</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>988조 3652억 3006만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>859조 6628억 706만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>806조 6582억 9627만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>쑥국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>678조 354억 2031만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>구픽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%94%BD</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
-    <t>923조 704억 4552만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>859조 6628억 706만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>806조 6582억 9627만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>쑥국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>674조 7911억 7183만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>구픽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%94%BD</t>
-  </si>
-  <si>
     <t>389조 358억 8583만</t>
   </si>
   <si>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
   </si>
   <si>
-    <t>235조 988억 6307만</t>
+    <t>235조 1809억 5476만</t>
   </si>
   <si>
     <t>11</t>
@@ -450,7 +450,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>224조 1627억 2959만</t>
+    <t>224조 6463억 731만</t>
   </si>
   <si>
     <t>12</t>
@@ -471,6 +471,33 @@
     <t>13</t>
   </si>
   <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>160조 5194억 1638만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>158조 579억 7454만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>약해진쭌석</t>
   </si>
   <si>
@@ -483,7 +510,7 @@
     <t>156조 5823억 551만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>응누</t>
@@ -492,58 +519,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EB%88%84</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>155조 1943억 7917만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>155조 475억 745만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>150조 3247억 986만</t>
+    <t>155조 4070억 9366만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>118조 1446억 5755만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>핫장</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
   </si>
   <si>
-    <t>113조 6983억 4562만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>112조 1099억 3002만</t>
+    <t>114조 957억 2396만</t>
   </si>
   <si>
     <t>19</t>
@@ -570,7 +570,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>81조 7814억 6307만</t>
+    <t>82조 9137억 2549만</t>
   </si>
   <si>
     <t>21</t>
@@ -594,7 +594,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
   </si>
   <si>
-    <t>63조 5940억 3675만</t>
+    <t>64조 6321억 2721만</t>
   </si>
   <si>
     <t>머쓰윽타드</t>
@@ -612,7 +612,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>54조 9339억 682만</t>
+    <t>55조 5675억 2416만</t>
   </si>
   <si>
     <t>핫딜만삼</t>
@@ -666,459 +666,462 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
+    <t>23조 18억 6428만</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>1744조 8442억 4005만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1549조 1560억 6234만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>1123조 3986억 1263만</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>348조 1289억 3205만</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>257조 1107억 752만</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>228조 665억 3930만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>213조 2895억 1154만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>179조 9670억 2979만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>144조 1150억 6923만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>114조 4296억 9140만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>102조 7914억 2403만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>96조 8446억 9775만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>89조 3419억 3056만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>87조 8872억 604만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>53조 5004억 3815만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>53조 4067억 7706만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>39조 6669억 6476만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1924억 9359만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>36조 474억 2125만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>35조 5257억 7876만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>34조 8711억 1818만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>25조 8550억 2155만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 8086조 9055억 5923만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2831조 1506억 5892만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1980조 6362억 7930만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>809조 5985억 7097만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>610조 7151억 5119만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>555조 8163억 1781만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>537조 9392억 417만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>484조 8510억 4884만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>481조 1298억 3265만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>477조 6715억 7462만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>373조 2967억 3028만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>241조 7005억 7985만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>225조 7671억 6693만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>109조 531억 9126만</t>
+  </si>
+  <si>
+    <t>하탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>82조 2996억 4164만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>52조 5398억 4286만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>48조 3657억 8560만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>21조 7890억 6212만</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4143조 7347억 1708만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1744조 8442억 4005만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1540조 3596억 8447만</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1123조 3986억 1263만</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>348조 1289억 3205만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>228조 665억 3930만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>225조 316억 7503만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>213조 2895억 1154만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>179조 9670억 2979만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>143조 6668억 6475만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>114조 2396억 3369만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>101조 6267억 648만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>88조 9672억 2946만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>88조 6379억 49만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>52조 9036억 6306만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>51조 5399억 1217만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>46조 8231억 8034만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>39조 1111억 1972만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>36조 474억 2125만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>34조 8711억 1818만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>33조 231억 7698만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>25조 8550억 2155만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 8086조 9055억 5923만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2831조 1506억 5892만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1974조 233억 937만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>809조 5985억 7097만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>525조 431억 8929만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>519조 4897억 3481만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>484조 5861억 9002만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>477조 6715억 7462만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>404조 9826억 7892만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>373조 2967억 3028만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>370조 6979억 9727만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>241조 7005억 7985만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>225조 7671억 6693만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>92조 27억 6340만</t>
-  </si>
-  <si>
-    <t>하탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>82조 2996억 4164만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>48조 129억 4261만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>41조 3143억 1479만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>29조 4752억 2082만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
     <t>23조 1931억 726만</t>
   </si>
   <si>
@@ -1131,6 +1134,15 @@
     <t>23조 1264억 4895만</t>
   </si>
   <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>22조 8461억 2869만</t>
+  </si>
+  <si>
     <t>브깃</t>
   </si>
   <si>
@@ -1143,13 +1155,13 @@
     <t>21조 9533억 9367만</t>
   </si>
   <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>21조 4013억 3703만</t>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>20조 5223억 8240만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1170,15 +1182,6 @@
     <t>18조 1871억 4713만</t>
   </si>
   <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>18조 734억 9249만</t>
-  </si>
-  <si>
     <t>크앙레몬</t>
   </si>
   <si>
@@ -1203,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>9조 832억 341만</t>
+    <t>9조 2773억 9881만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1221,7 +1224,283 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>6조 754억 4971만</t>
+    <t>6조 1706억 6032만</t>
+  </si>
+  <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>1경 3979조 9625억 2654만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>1경 1031조 8760억 3683만</t>
+  </si>
+  <si>
+    <t>실민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>1654조 9079억 6485만</t>
+  </si>
+  <si>
+    <t>설즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1421조 9727억 8555만</t>
+  </si>
+  <si>
+    <t>약한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>747조 987억 1716만</t>
+  </si>
+  <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>392조 8881억 4109만</t>
+  </si>
+  <si>
+    <t>항상밝은하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>374조 3925억 7841만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>311조 1188억 9724만</t>
+  </si>
+  <si>
+    <t>문디르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>303조 1045억 6485만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>149조 5967억 3844만</t>
+  </si>
+  <si>
+    <t>봉튜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
+  </si>
+  <si>
+    <t>112조 6152억 2505만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>53조 5931억 5875만</t>
+  </si>
+  <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>53조 1756억 2497만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>42조 4184억 2975만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>33조 9792억 8744만</t>
+  </si>
+  <si>
+    <t>벨히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
+  </si>
+  <si>
+    <t>33조 1316억 3693만</t>
+  </si>
+  <si>
+    <t>김대협</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
+  </si>
+  <si>
+    <t>29조 6399억 2474만</t>
+  </si>
+  <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>29조 781억 7508만</t>
+  </si>
+  <si>
+    <t>낭만탕슉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%83%95%EC%8A%89</t>
+  </si>
+  <si>
+    <t>22조 2041억 3782만</t>
+  </si>
+  <si>
+    <t>낭만만듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
+  </si>
+  <si>
+    <t>17조 1140억 8451만</t>
+  </si>
+  <si>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>15조 9945억 9723만</t>
+  </si>
+  <si>
+    <t>봄녘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
+  </si>
+  <si>
+    <t>12조 5419억 7711만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>11조 9096억 8122만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>10조 4545억 7849만</t>
+  </si>
+  <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>10조 1480억 1330만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 3901억 5879만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>4조 403억 5588만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>1조 4664억 7441만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 384억 8666만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>8249억 8565만</t>
   </si>
   <si>
     <t>THE끌림</t>
@@ -1239,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
   </si>
   <si>
-    <t>8403조 9181억 4364만</t>
+    <t>8427조 8129억 8839만</t>
   </si>
   <si>
     <t>NUKE</t>
@@ -1248,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>3565조 7552억 8356만</t>
+    <t>3573조 3337억 9930만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -1266,13 +1545,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>533조 5019억 4465만</t>
+    <t>552조 2324억 5008만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
   </si>
   <si>
-    <t>515조 1552억 4756만</t>
+    <t>516조 3149억 8933만</t>
   </si>
   <si>
     <t>똔똔잉</t>
@@ -1281,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>468조 1673억 7188만</t>
+    <t>475조 5715억 8482만</t>
   </si>
   <si>
     <t>S2베코</t>
@@ -1290,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
   </si>
   <si>
-    <t>435조 5380억 3504만</t>
+    <t>435조 6447억 7970만</t>
   </si>
   <si>
     <t>환불한너잉</t>
@@ -1326,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
   </si>
   <si>
-    <t>255조 9670억 7267만</t>
+    <t>257조 5088억 8989만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1344,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
   </si>
   <si>
-    <t>90조 8509억 3252만</t>
+    <t>91조 7090억 9345만</t>
   </si>
   <si>
     <t>김천아재</t>
@@ -1353,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>62조 6528억 426만</t>
+    <t>63조 2824억 9042만</t>
   </si>
   <si>
     <t>성칙이</t>
@@ -1407,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>25조 7522억 268만</t>
+    <t>25조 7835억 7777만</t>
   </si>
   <si>
     <t>돌아온홍굴이</t>
@@ -1425,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>18조 8382억 7299만</t>
+    <t>21조 2923억 2793만</t>
   </si>
   <si>
     <t>순샷</t>
@@ -1434,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
   </si>
   <si>
-    <t>15조 5589억 4978만</t>
+    <t>16조 350억 635만</t>
   </si>
   <si>
     <t>보마가될인재</t>
@@ -1446,22 +1725,22 @@
     <t>13조 3213억 1854만</t>
   </si>
   <si>
+    <t>기차아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>11조 7077억 5472만</t>
+  </si>
+  <si>
     <t>탱탱볼탱탱볼</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
   </si>
   <si>
-    <t>11조 9억 7823만</t>
-  </si>
-  <si>
-    <t>기차아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>10조 2529억 9631만</t>
+    <t>11조 760억 5746만</t>
   </si>
   <si>
     <t>구뺑</t>
@@ -1470,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>9조 7265억 6262만</t>
+    <t>9조 8061억 2014만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1482,811 +1761,535 @@
     <t>7조 8263억 6165만</t>
   </si>
   <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>1경 1110조 7753억 6584만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>1경 1031조 8760억 3683만</t>
-  </si>
-  <si>
-    <t>실민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>1643조 7987억 790만</t>
-  </si>
-  <si>
-    <t>설즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1413조 7831억 7127만</t>
-  </si>
-  <si>
-    <t>약한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>747조 987억 1716만</t>
-  </si>
-  <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>391조 7205억 504만</t>
-  </si>
-  <si>
-    <t>항상밝은하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>370조 5616억 584만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>311조 1188억 9724만</t>
-  </si>
-  <si>
-    <t>문디르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>302조 3832억 9318만</t>
-  </si>
-  <si>
-    <t>봉튜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
-  </si>
-  <si>
-    <t>112조 2721억 455만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>91조 6043억 9480만</t>
-  </si>
-  <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>51조 8782억 219만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>51조 3598억 746만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>42조 4184억 2975만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>33조 9792억 8744만</t>
-  </si>
-  <si>
-    <t>벨히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
-  </si>
-  <si>
-    <t>33조 1316억 3693만</t>
-  </si>
-  <si>
-    <t>김대협</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
-  </si>
-  <si>
-    <t>29조 2558억 3517만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>29조 781억 7508만</t>
-  </si>
-  <si>
-    <t>낭만탕슉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%83%95%EC%8A%89</t>
-  </si>
-  <si>
-    <t>17조 4858억 1298만</t>
-  </si>
-  <si>
-    <t>낭만만듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
-  </si>
-  <si>
-    <t>16조 7106억 2207만</t>
-  </si>
-  <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>15조 9945억 9723만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>11조 6442억 2705만</t>
-  </si>
-  <si>
-    <t>봄녘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
-  </si>
-  <si>
-    <t>11조 4804억 4653만</t>
-  </si>
-  <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>10조 4545억 7849만</t>
-  </si>
-  <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>9조 4050억 356만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 3833억 4067만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>4조 403억 5588만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>1조 4284억 6262만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>9316억 9387만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+    <t>힐줄까</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
+  </si>
+  <si>
+    <t>1경 3426조 7539억 7298만</t>
+  </si>
+  <si>
+    <t>키노눙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
+  </si>
+  <si>
+    <t>6566조 5986억 4257만</t>
+  </si>
+  <si>
+    <t>닉네임미정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EB%84%A4%EC%9E%84%EB%AF%B8%EC%A0%95</t>
+  </si>
+  <si>
+    <t>3015조 4136억 1233만</t>
+  </si>
+  <si>
+    <t>한마드릴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
+  </si>
+  <si>
+    <t>1034조 5311억 8092만</t>
+  </si>
+  <si>
+    <t>윤돌이굴돌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>827조 8614억 9375만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>823조 3603억 4315만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>431조 5200억 7259만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>345조 7906억 4526만</t>
+  </si>
+  <si>
+    <t>쏘세용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>110조 8680억 6765만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>72조 8162억 9562만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>70조 7550억 3869만</t>
+  </si>
+  <si>
+    <t>퀸돈대통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
+  </si>
+  <si>
+    <t>58조 8644억 9982만</t>
+  </si>
+  <si>
+    <t>갓쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>56조 9358억 7110만</t>
+  </si>
+  <si>
+    <t>다끝남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>56조 8889억 5853만</t>
+  </si>
+  <si>
+    <t>우당탕탼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
+  </si>
+  <si>
+    <t>53조 9042억 4902만</t>
+  </si>
+  <si>
+    <t>킴술하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
+  </si>
+  <si>
+    <t>53조 7664억 3605만</t>
+  </si>
+  <si>
+    <t>김컁구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>42조 9280억 9940만</t>
+  </si>
+  <si>
+    <t>표창빌런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
+  </si>
+  <si>
+    <t>30조 4763억 8710만</t>
+  </si>
+  <si>
+    <t>사철화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>21조 6118억 6523만</t>
+  </si>
+  <si>
+    <t>얼음조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>15조 2657억 7496만</t>
+  </si>
+  <si>
+    <t>잼이유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>13조 8570억 801만</t>
+  </si>
+  <si>
+    <t>커피숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
+  </si>
+  <si>
+    <t>7조 6734억 9408만</t>
+  </si>
+  <si>
+    <t>시네루최</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
+  </si>
+  <si>
+    <t>7조 609억 8718만</t>
+  </si>
+  <si>
+    <t>메린이이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6조 8900억 25만</t>
+  </si>
+  <si>
+    <t>킴밍끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
+  </si>
+  <si>
+    <t>6조 3213억 4459만</t>
+  </si>
+  <si>
+    <t>아신아이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%8B%A0%EC%95%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 8001억 5133만</t>
+  </si>
+  <si>
+    <t>57년김춘배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>5조 1881억 3828만</t>
+  </si>
+  <si>
+    <t>붕붕월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>4조 5826억 895만</t>
+  </si>
+  <si>
+    <t>최시네루친구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B9%9C%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>3조 1960억 7125만</t>
+  </si>
+  <si>
+    <t>카찍스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%B0%8D%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1조 9495억 5789만</t>
+  </si>
+  <si>
+    <t>김도움</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9B%80</t>
+  </si>
+  <si>
+    <t>1경 2281조 3450억 4477만</t>
+  </si>
+  <si>
+    <t>용려니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>8335조 7249억 3275만</t>
+  </si>
+  <si>
+    <t>켘켘3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
+  </si>
+  <si>
+    <t>512조 8192억 3258만</t>
+  </si>
+  <si>
+    <t>메키멍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
+  </si>
+  <si>
+    <t>460조 5135억 3348만</t>
+  </si>
+  <si>
+    <t>참달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>146조 1420억 5518만</t>
+  </si>
+  <si>
+    <t>샤프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>140조 3516억 2247만</t>
+  </si>
+  <si>
+    <t>소잦ol</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
+  </si>
+  <si>
+    <t>94조 5505억 333만</t>
+  </si>
+  <si>
+    <t>아빠의기운</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%9D%98%EA%B8%B0%EC%9A%B4</t>
+  </si>
+  <si>
+    <t>86조 1292억 8032만</t>
+  </si>
+  <si>
+    <t>랏해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
+  </si>
+  <si>
+    <t>78조 3581억 6736만</t>
+  </si>
+  <si>
+    <t>마리아네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
+  </si>
+  <si>
+    <t>54조 9933억 4380만</t>
+  </si>
+  <si>
+    <t>포근한소리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>48조 9742억 1934만</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>30조 1279억 9295만</t>
+  </si>
+  <si>
+    <t>못스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>27조 3504억 743만</t>
+  </si>
+  <si>
+    <t>스파륑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%EB%A5%91</t>
+  </si>
+  <si>
+    <t>20조 313억 2338만</t>
+  </si>
+  <si>
+    <t>머수킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%88%98%ED%82%B9</t>
+  </si>
+  <si>
+    <t>14조 5919억 5170만</t>
+  </si>
+  <si>
+    <t>본분</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%B6%84</t>
+  </si>
+  <si>
+    <t>13조 9505억 4891만</t>
+  </si>
+  <si>
+    <t>로넌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
+  </si>
+  <si>
+    <t>11조 7665억 7906만</t>
+  </si>
+  <si>
+    <t>하이요하임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%EC%9A%94%ED%95%98%EC%9E%84</t>
+  </si>
+  <si>
+    <t>11조 6543억 1380만</t>
+  </si>
+  <si>
+    <t>개도둑놈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
+  </si>
+  <si>
+    <t>7조 7996억 5509만</t>
+  </si>
+  <si>
+    <t>외단</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
+  </si>
+  <si>
+    <t>7조 6880억 3448만</t>
+  </si>
+  <si>
+    <t>잘스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>7조 2244억 7227만</t>
+  </si>
+  <si>
+    <t>1조투력찍었던</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
+  </si>
+  <si>
+    <t>6조 9720억 7486만</t>
+  </si>
+  <si>
+    <t>콩새우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%A9%EC%83%88%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>5조 104억 5635만</t>
+  </si>
+  <si>
+    <t>겁재이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%81%EC%9E%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 2915억 9088만</t>
+  </si>
+  <si>
+    <t>BudriQ</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
+  </si>
+  <si>
+    <t>3조 8654억 4168만</t>
+  </si>
+  <si>
+    <t>가겠네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
+  </si>
+  <si>
+    <t>3조 6771억 3311만</t>
+  </si>
+  <si>
+    <t>킴카</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
+  </si>
+  <si>
+    <t>3조 3723억 5670만</t>
+  </si>
+  <si>
+    <t>탕화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
+  </si>
+  <si>
+    <t>3조 955억 1988만</t>
+  </si>
+  <si>
+    <t>군곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EA%B3%A4</t>
   </si>
   <si>
     <t>97</t>
-  </si>
-  <si>
-    <t>8249억 8565만</t>
-  </si>
-  <si>
-    <t>힐줄까</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
-  </si>
-  <si>
-    <t>1경 3426조 7539억 7298만</t>
-  </si>
-  <si>
-    <t>키노눙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
-  </si>
-  <si>
-    <t>6536조 9847억 8532만</t>
-  </si>
-  <si>
-    <t>닉네임미정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EB%84%A4%EC%9E%84%EB%AF%B8%EC%A0%95</t>
-  </si>
-  <si>
-    <t>3015조 4136억 1233만</t>
-  </si>
-  <si>
-    <t>한마드릴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
-  </si>
-  <si>
-    <t>1001조 2946억 4803만</t>
-  </si>
-  <si>
-    <t>윤돌이굴돌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>817조 207억 2377만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>721조 1541억 2117만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>431조 3786억 7691만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>345조 7906억 4526만</t>
-  </si>
-  <si>
-    <t>쏘세용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>110조 8680억 6765만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>72조 5725억 6649만</t>
-  </si>
-  <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>70조 7550억 3869만</t>
-  </si>
-  <si>
-    <t>퀸돈대통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
-  </si>
-  <si>
-    <t>58조 8644억 9982만</t>
-  </si>
-  <si>
-    <t>갓쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>56조 9358억 7110만</t>
-  </si>
-  <si>
-    <t>다끝남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>56조 8889억 5853만</t>
-  </si>
-  <si>
-    <t>우당탕탼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
-  </si>
-  <si>
-    <t>53조 6554억 3216만</t>
-  </si>
-  <si>
-    <t>킴술하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
-  </si>
-  <si>
-    <t>52조 4425억 9574만</t>
-  </si>
-  <si>
-    <t>김컁구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>42조 6170억 840만</t>
-  </si>
-  <si>
-    <t>표창빌런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>29조 8582억 3067만</t>
-  </si>
-  <si>
-    <t>사철화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>21조 6118억 6523만</t>
-  </si>
-  <si>
-    <t>얼음조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>14조 7887억 6026만</t>
-  </si>
-  <si>
-    <t>잼이유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>13조 8570억 801만</t>
-  </si>
-  <si>
-    <t>커피숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
-  </si>
-  <si>
-    <t>7조 5246억 3432만</t>
-  </si>
-  <si>
-    <t>시네루최</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
-  </si>
-  <si>
-    <t>7조 609억 8718만</t>
-  </si>
-  <si>
-    <t>킴밍끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
-  </si>
-  <si>
-    <t>6조 144억 824만</t>
-  </si>
-  <si>
-    <t>메린이이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 9423억 8404만</t>
-  </si>
-  <si>
-    <t>아신아이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%8B%A0%EC%95%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 8001억 5133만</t>
-  </si>
-  <si>
-    <t>57년김춘배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>5조 734억 355만</t>
-  </si>
-  <si>
-    <t>붕붕월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>4조 4900억 2286만</t>
-  </si>
-  <si>
-    <t>최시네루친구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B9%9C%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>3조 1960억 7125만</t>
-  </si>
-  <si>
-    <t>카찍스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%B0%8D%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 6623억 5864만</t>
-  </si>
-  <si>
-    <t>김도움</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9B%80</t>
-  </si>
-  <si>
-    <t>1경 2224조 6171억 7285만</t>
-  </si>
-  <si>
-    <t>용려니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>8335조 7249억 3275만</t>
-  </si>
-  <si>
-    <t>켘켘3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
-  </si>
-  <si>
-    <t>512조 8192억 3258만</t>
-  </si>
-  <si>
-    <t>메키멍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
-  </si>
-  <si>
-    <t>460조 5135억 3348만</t>
-  </si>
-  <si>
-    <t>참달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>145조 9586억 3095만</t>
-  </si>
-  <si>
-    <t>샤프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>137조 9505억 5043만</t>
-  </si>
-  <si>
-    <t>소잦ol</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
-  </si>
-  <si>
-    <t>94조 5505억 333만</t>
-  </si>
-  <si>
-    <t>아빠의기운</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%9D%98%EA%B8%B0%EC%9A%B4</t>
-  </si>
-  <si>
-    <t>86조 1292억 8032만</t>
-  </si>
-  <si>
-    <t>랏해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
-  </si>
-  <si>
-    <t>73조 6155억 7494만</t>
-  </si>
-  <si>
-    <t>마리아네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
-  </si>
-  <si>
-    <t>54조 9933억 4380만</t>
-  </si>
-  <si>
-    <t>포근한소리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>48조 9742억 1934만</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>30조 1279억 9295만</t>
-  </si>
-  <si>
-    <t>못스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>27조 3504억 743만</t>
-  </si>
-  <si>
-    <t>본분</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%B6%84</t>
-  </si>
-  <si>
-    <t>13조 9505억 4891만</t>
-  </si>
-  <si>
-    <t>스파륑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%EB%A5%91</t>
-  </si>
-  <si>
-    <t>12조 9454억 3295만</t>
-  </si>
-  <si>
-    <t>머수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>12조 5909억 5016만</t>
-  </si>
-  <si>
-    <t>로넌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
-  </si>
-  <si>
-    <t>11조 7447억 3608만</t>
-  </si>
-  <si>
-    <t>하이요하임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%EC%9A%94%ED%95%98%EC%9E%84</t>
-  </si>
-  <si>
-    <t>11조 6167억 1602만</t>
-  </si>
-  <si>
-    <t>외단</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
-  </si>
-  <si>
-    <t>7조 6880억 3448만</t>
-  </si>
-  <si>
-    <t>개도둑놈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
-  </si>
-  <si>
-    <t>7조 6600억 7299만</t>
-  </si>
-  <si>
-    <t>잘스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>7조 2244억 7227만</t>
-  </si>
-  <si>
-    <t>1조투력찍었던</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
-  </si>
-  <si>
-    <t>6조 9720억 7486만</t>
-  </si>
-  <si>
-    <t>콩새우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%A9%EC%83%88%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>5조 104억 5635만</t>
-  </si>
-  <si>
-    <t>겁재이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%81%EC%9E%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 1983억 2077만</t>
-  </si>
-  <si>
-    <t>BudriQ</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
-  </si>
-  <si>
-    <t>3조 8654억 4168만</t>
-  </si>
-  <si>
-    <t>킴카</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
-  </si>
-  <si>
-    <t>3조 3672억 9000만</t>
-  </si>
-  <si>
-    <t>가겠네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
-  </si>
-  <si>
-    <t>3조 81억 4460만</t>
-  </si>
-  <si>
-    <t>탕화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
-  </si>
-  <si>
-    <t>2조 9016억 9499만</t>
-  </si>
-  <si>
-    <t>군곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EA%B3%A4</t>
   </si>
   <si>
     <t>2조 4539억 9225만</t>
@@ -2852,28 +2855,28 @@
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2881,28 +2884,28 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>56</v>
@@ -2984,7 +2987,7 @@
         <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>30</v>
@@ -3028,7 +3031,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3279,10 +3282,10 @@
         <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3293,16 +3296,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -3311,10 +3314,10 @@
         <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3325,16 +3328,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -3343,7 +3346,7 @@
         <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>131</v>
@@ -3375,7 +3378,7 @@
         <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>135</v>
@@ -3407,7 +3410,7 @@
         <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -3439,7 +3442,7 @@
         <v>143</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>144</v>
@@ -3468,7 +3471,7 @@
         <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>148</v>
@@ -3500,13 +3503,13 @@
         <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3517,25 +3520,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>158</v>
@@ -3564,10 +3567,10 @@
         <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>162</v>
@@ -3596,10 +3599,10 @@
         <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>166</v>
@@ -3628,10 +3631,10 @@
         <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>170</v>
@@ -3663,7 +3666,7 @@
         <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>174</v>
@@ -3727,7 +3730,7 @@
         <v>116</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>183</v>
@@ -3773,7 +3776,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>188</v>
@@ -3791,7 +3794,7 @@
         <v>143</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>190</v>
@@ -3823,7 +3826,7 @@
         <v>116</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>193</v>
@@ -3855,7 +3858,7 @@
         <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>196</v>
@@ -3965,7 +3968,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>209</v>
@@ -3983,10 +3986,10 @@
         <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4084,22 +4087,22 @@
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>216</v>
@@ -4305,7 +4308,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>235</v>
@@ -4337,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>238</v>
@@ -4384,10 +4387,10 @@
         <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>243</v>
@@ -4416,10 +4419,10 @@
         <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>246</v>
@@ -4448,10 +4451,10 @@
         <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>249</v>
@@ -4483,7 +4486,7 @@
         <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>252</v>
@@ -4515,7 +4518,7 @@
         <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>255</v>
@@ -4529,7 +4532,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>256</v>
@@ -4547,7 +4550,7 @@
         <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>258</v>
@@ -4579,7 +4582,7 @@
         <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>261</v>
@@ -4608,10 +4611,10 @@
         <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>264</v>
@@ -4640,10 +4643,10 @@
         <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>267</v>
@@ -4672,10 +4675,10 @@
         <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>270</v>
@@ -4704,7 +4707,7 @@
         <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>148</v>
@@ -4736,7 +4739,7 @@
         <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>148</v>
@@ -4768,10 +4771,10 @@
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>279</v>
@@ -4785,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>280</v>
@@ -4803,7 +4806,7 @@
         <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>282</v>
@@ -4896,7 +4899,7 @@
         <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>200</v>
@@ -4960,10 +4963,10 @@
         <v>92</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>296</v>
@@ -4977,7 +4980,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>297</v>
@@ -4992,10 +4995,10 @@
         <v>92</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
@@ -5240,7 +5243,7 @@
         <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>316</v>
@@ -5269,10 +5272,10 @@
         <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>319</v>
@@ -5304,7 +5307,7 @@
         <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>322</v>
@@ -5333,10 +5336,10 @@
         <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>325</v>
@@ -5350,7 +5353,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>326</v>
@@ -5365,10 +5368,10 @@
         <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>328</v>
@@ -5382,7 +5385,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>329</v>
@@ -5400,7 +5403,7 @@
         <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>331</v>
@@ -5429,10 +5432,10 @@
         <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>334</v>
@@ -5461,7 +5464,7 @@
         <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>111</v>
@@ -5496,7 +5499,7 @@
         <v>143</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>340</v>
@@ -5528,7 +5531,7 @@
         <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>343</v>
@@ -5560,7 +5563,7 @@
         <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>346</v>
@@ -5574,7 +5577,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>347</v>
@@ -5592,7 +5595,7 @@
         <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>349</v>
@@ -5621,13 +5624,13 @@
         <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
+        <v>352</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5641,22 +5644,22 @@
         <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>355</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>356</v>
@@ -5685,7 +5688,7 @@
         <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>178</v>
@@ -5720,10 +5723,10 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5737,13 +5740,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -5752,10 +5755,10 @@
         <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5769,22 +5772,22 @@
         <v>180</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>368</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>369</v>
@@ -5813,13 +5816,13 @@
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
+        <v>372</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5830,28 +5833,28 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5865,25 +5868,25 @@
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5897,25 +5900,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5929,13 +5932,13 @@
         <v>197</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -5947,7 +5950,7 @@
         <v>200</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5961,13 +5964,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
@@ -5979,7 +5982,7 @@
         <v>200</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5993,13 +5996,13 @@
         <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>92</v>
@@ -6008,10 +6011,10 @@
         <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6022,16 +6025,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>92</v>
@@ -6040,10 +6043,10 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6057,13 +6060,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>92</v>
@@ -6072,10 +6075,10 @@
         <v>99</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6121,1018 +6124,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7180,19 +6171,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>483</v>
+        <v>398</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>483</v>
+        <v>398</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>92</v>
@@ -7204,7 +6195,7 @@
         <v>306</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7212,19 +6203,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
@@ -7236,7 +6227,7 @@
         <v>306</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>488</v>
+        <v>403</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7244,19 +6235,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>489</v>
+        <v>404</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>489</v>
+        <v>404</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>490</v>
+        <v>405</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -7268,7 +6259,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>491</v>
+        <v>406</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7276,19 +6267,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>492</v>
+        <v>407</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>492</v>
+        <v>407</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
@@ -7300,7 +6291,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>494</v>
+        <v>409</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7308,31 +6299,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7340,19 +6331,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>499</v>
+        <v>414</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -7361,10 +6352,10 @@
         <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7372,19 +6363,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>502</v>
+        <v>417</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -7393,10 +6384,10 @@
         <v>116</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7404,19 +6395,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -7425,10 +6416,10 @@
         <v>116</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7436,19 +6427,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>508</v>
+        <v>423</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -7457,10 +6448,10 @@
         <v>116</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>509</v>
+        <v>424</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7468,31 +6459,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>512</v>
+        <v>427</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7500,31 +6491,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>515</v>
+        <v>430</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7532,31 +6523,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>516</v>
+        <v>431</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>516</v>
+        <v>431</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>518</v>
+        <v>433</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7564,31 +6555,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>519</v>
+        <v>434</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>519</v>
+        <v>434</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>521</v>
+        <v>436</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7596,31 +6587,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>523</v>
+        <v>438</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7628,19 +6619,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>525</v>
+        <v>440</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>525</v>
+        <v>440</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>526</v>
+        <v>441</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -7649,10 +6640,10 @@
         <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>527</v>
+        <v>442</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7660,19 +6651,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>528</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>528</v>
+        <v>443</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>529</v>
+        <v>444</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -7684,7 +6675,7 @@
         <v>200</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>530</v>
+        <v>445</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7692,19 +6683,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>531</v>
+        <v>446</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>531</v>
+        <v>446</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>532</v>
+        <v>447</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
@@ -7713,10 +6704,10 @@
         <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>533</v>
+        <v>448</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7724,19 +6715,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>534</v>
+        <v>449</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>534</v>
+        <v>449</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>535</v>
+        <v>450</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
@@ -7748,7 +6739,7 @@
         <v>178</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>536</v>
+        <v>451</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7756,19 +6747,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>537</v>
+        <v>452</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>537</v>
+        <v>452</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
@@ -7777,10 +6768,10 @@
         <v>143</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7788,19 +6779,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>540</v>
+        <v>455</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>540</v>
+        <v>455</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>541</v>
+        <v>456</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -7812,7 +6803,7 @@
         <v>200</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7820,19 +6811,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>544</v>
+        <v>459</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -7841,10 +6832,10 @@
         <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>545</v>
+        <v>460</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7852,31 +6843,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>546</v>
+        <v>461</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>546</v>
+        <v>461</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>547</v>
+        <v>462</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>548</v>
+        <v>463</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7884,31 +6875,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>549</v>
+        <v>464</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>549</v>
+        <v>464</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
+        <v>362</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>551</v>
+        <v>466</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7916,19 +6907,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>553</v>
+        <v>468</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
@@ -7937,10 +6928,10 @@
         <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>470</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7948,19 +6939,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>471</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>471</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>472</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
@@ -7969,10 +6960,10 @@
         <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>558</v>
+        <v>473</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7980,19 +6971,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>559</v>
+        <v>474</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>559</v>
+        <v>474</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>560</v>
+        <v>475</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -8001,10 +6992,10 @@
         <v>99</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>561</v>
+        <v>476</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>562</v>
+        <v>477</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8012,31 +7003,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>563</v>
+        <v>478</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>563</v>
+        <v>478</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>564</v>
+        <v>479</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>565</v>
+        <v>480</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8044,19 +7035,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>566</v>
+        <v>481</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>566</v>
+        <v>481</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>567</v>
+        <v>482</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>92</v>
@@ -8065,10 +7056,10 @@
         <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>561</v>
+        <v>476</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>568</v>
+        <v>483</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8076,19 +7067,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>569</v>
+        <v>484</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>569</v>
+        <v>484</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>570</v>
+        <v>485</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>92</v>
@@ -8097,10 +7088,10 @@
         <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>571</v>
+        <v>486</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>572</v>
+        <v>487</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8108,19 +7099,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>573</v>
+        <v>488</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>85</v>
@@ -8129,10 +7120,10 @@
         <v>116</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>574</v>
+        <v>476</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>575</v>
+        <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8176,6 +7167,1018 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -8342,7 +8345,7 @@
         <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>587</v>
@@ -8374,7 +8377,7 @@
         <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>590</v>
@@ -8406,7 +8409,7 @@
         <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>593</v>
@@ -8438,7 +8441,7 @@
         <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>596</v>
@@ -8452,7 +8455,7 @@
         <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>67</v>
@@ -8470,7 +8473,7 @@
         <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>598</v>
@@ -8484,7 +8487,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>599</v>
@@ -8502,7 +8505,7 @@
         <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>601</v>
@@ -8534,7 +8537,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>604</v>
@@ -8566,7 +8569,7 @@
         <v>143</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>607</v>
@@ -8627,10 +8630,10 @@
         <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>613</v>
@@ -8662,7 +8665,7 @@
         <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>616</v>
@@ -8676,7 +8679,7 @@
         <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>617</v>
@@ -8758,7 +8761,7 @@
         <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>625</v>
@@ -8787,7 +8790,7 @@
         <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>178</v>
@@ -8915,10 +8918,10 @@
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>640</v>
@@ -8932,7 +8935,7 @@
         <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>641</v>
@@ -8950,7 +8953,7 @@
         <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>643</v>
@@ -8979,10 +8982,10 @@
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>554</v>
+        <v>200</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>646</v>
@@ -9011,10 +9014,10 @@
         <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>215</v>
+        <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>469</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>649</v>
@@ -9046,7 +9049,7 @@
         <v>86</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>652</v>
@@ -9075,10 +9078,10 @@
         <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>655</v>
@@ -9110,7 +9113,7 @@
         <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>658</v>
@@ -9124,7 +9127,7 @@
         <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>659</v>
@@ -9142,7 +9145,7 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>661</v>
@@ -9174,7 +9177,7 @@
         <v>86</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>561</v>
+        <v>476</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>664</v>
@@ -9291,7 +9294,7 @@
         <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>667</v>
@@ -9355,7 +9358,7 @@
         <v>99</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>673</v>
@@ -9384,10 +9387,10 @@
         <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>676</v>
@@ -9419,7 +9422,7 @@
         <v>116</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>679</v>
@@ -9451,7 +9454,7 @@
         <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>682</v>
@@ -9483,7 +9486,7 @@
         <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>685</v>
@@ -9497,7 +9500,7 @@
         <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>686</v>
@@ -9515,7 +9518,7 @@
         <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>688</v>
@@ -9529,7 +9532,7 @@
         <v>68</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>689</v>
@@ -9704,10 +9707,10 @@
         <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>211</v>
+        <v>476</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>706</v>
@@ -9721,7 +9724,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>707</v>
@@ -9736,10 +9739,10 @@
         <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>574</v>
+        <v>362</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>709</v>
@@ -9768,10 +9771,10 @@
         <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>712</v>
@@ -9835,7 +9838,7 @@
         <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>718</v>
@@ -9864,10 +9867,10 @@
         <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>554</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>721</v>
@@ -9896,10 +9899,10 @@
         <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>469</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>724</v>
@@ -9931,7 +9934,7 @@
         <v>143</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>554</v>
+        <v>362</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>727</v>
@@ -9960,10 +9963,10 @@
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>730</v>
@@ -9977,7 +9980,7 @@
         <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>731</v>
@@ -10024,10 +10027,10 @@
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>737</v>
@@ -10059,7 +10062,7 @@
         <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>740</v>
@@ -10088,7 +10091,7 @@
         <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>733</v>
@@ -10120,7 +10123,7 @@
         <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>733</v>
@@ -10169,7 +10172,7 @@
         <v>68</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>750</v>
@@ -10187,10 +10190,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>574</v>
+        <v>752</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10210,7 +10213,7 @@
         <v>74</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>85</v>
@@ -10222,7 +10225,7 @@
         <v>733</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -10,17 +10,17 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
     <sheet name="이콩" sheetId="3" r:id="rId3"/>
-    <sheet name="LUXURY" sheetId="4" r:id="rId4"/>
-    <sheet name="딸기키우기" sheetId="5" r:id="rId5"/>
+    <sheet name="딸기키우기" sheetId="4" r:id="rId4"/>
+    <sheet name="LUXURY" sheetId="5" r:id="rId5"/>
     <sheet name="고점" sheetId="6" r:id="rId6"/>
     <sheet name="싸이월드" sheetId="7" r:id="rId7"/>
     <sheet name="라때는말이야" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">고점!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">딸기키우기!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">딸기키우기!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$30</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="745">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,561 +84,561 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 795조 530억 3667만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.06</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>11경 8671조 7327억 4990만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>5경 2795조 5043억 6030만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.05</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>5경 8284조 3756억 5532만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>7경 706조 9369억 6313만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>7경 2193조 1516억 9085만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>6경 8981조 9859억 3906만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>6경 7552조 6685억 2486만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 6417조 5007억 3060만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6442조 4590억 4780만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>4200조 912억 9692만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>2876조 6035억 1029만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2011조 4544억 3476만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1007조 3178억 5658만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>872조 522억 4681만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>827조 8255억 4449만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>615조 966억 3132만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>480조 4284억 4041만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>366조 6787억 5438만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>333조 9657억 1895만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>321조 5291억 6983만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>11경 8302조 9293억 1250만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>6경 9971조 3646억 188만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 5317조 9772억 6235만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>7경 908조 1299억 2761만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>6경 7827조 3588억 841만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>267조 5583억 8727만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>263조 2828억 1813만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>252조 9962억 8450만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>247조 8297억 5839만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>239조 5598억 9073만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>181조 6612억 1265만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>143조 3408억 6701만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>91조 2927억 8263만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>68조 2761억 4360만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>61조 8207억 5987만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>59조 7773억 9141만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>55조 7049억 3694만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>5경 9370조 249억 3234만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2경 2416조 5600억 7829만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>7035조 2326억 1084만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5919조 4226억 5562만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>4140조 1288억 2038만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>2876조 6035억 1029만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2011조 4544억 3476만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>869조 7089억 4153만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>818조 9238억 3029만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>799조 1207억 1777만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>598조 8908억 4660만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>456조 3820억 3239만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>339조 1017억 5902만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>303조 3719억 9248만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>252조 9962억 8450만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>249조 9305억 6636만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>245조 1557억 471만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>236조 8642억 5619만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>233조 8269억 1796만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>224조 5276억 7418만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>174조 3878억 3501만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>143조 3408억 6701만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>90조 9979억 5431만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>67조 8929억 150만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>61조 8207억 5987만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>55조 6070억 4691만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>54조 863억 2345만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -666,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>40조 1094억 7484만</t>
+    <t>42조 8377억 6291만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -675,7 +675,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>8경 4595조 5871억 5134만</t>
+    <t>8경 4605조 5179억 3801만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -687,7 +687,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>2경 2003조 2347억 3439만</t>
+    <t>2경 2100조 9597억 1931만</t>
   </si>
   <si>
     <t>실민</t>
@@ -696,7 +696,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>2552조 7883억 9435만</t>
+    <t>2557조 517억 7197만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -708,7 +708,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>2348조 7811억 6584만</t>
+    <t>2522조 3017억 1179만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -729,6 +729,15 @@
     <t>759조 7355억 439만</t>
   </si>
   <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>733조 6203억 8517만</t>
+  </si>
+  <si>
     <t>비트츄</t>
   </si>
   <si>
@@ -738,22 +747,13 @@
     <t>721조 6837억 3333만</t>
   </si>
   <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>713조 2234억 4272만</t>
-  </si>
-  <si>
     <t>문디르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>657조 3806억 9640만</t>
+    <t>676조 3860억 485만</t>
   </si>
   <si>
     <t>공포의오함마</t>
@@ -762,7 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>594조 6224억 2681만</t>
+    <t>595조 3193억 1491만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -771,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
   </si>
   <si>
-    <t>229조 3990억 6694만</t>
+    <t>231조 2571억 7985만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -780,7 +780,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>164조 3927억 2066만</t>
+    <t>180조 1511억 6313만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>103조 7256억 5191만</t>
   </si>
   <si>
     <t>낭만탕슉</t>
@@ -789,19 +801,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%83%95%EC%8A%89</t>
   </si>
   <si>
-    <t>102조 2508억 2268만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>97조 9336억 2806만</t>
+    <t>102조 8045억 7118만</t>
+  </si>
+  <si>
+    <t>봄녘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
+  </si>
+  <si>
+    <t>97조 7761억 4970만</t>
   </si>
   <si>
     <t>경특</t>
@@ -810,16 +819,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
   </si>
   <si>
-    <t>94조 4925억 9689만</t>
-  </si>
-  <si>
-    <t>봄녘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
-  </si>
-  <si>
-    <t>91조 5124억 8855만</t>
+    <t>95조 9087억 8563만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -828,7 +828,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>88조 7589억 2370만</t>
+    <t>93조 9222억 9452만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -855,7 +855,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
   </si>
   <si>
-    <t>64조 8901억 5662만</t>
+    <t>66조 5091억 2720만</t>
+  </si>
+  <si>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>54조 2197억 8399만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -867,1111 +876,1120 @@
     <t>48조 6128억 1055만</t>
   </si>
   <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>43조 6924억 1314만</t>
-  </si>
-  <si>
     <t>봉합불가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
+    <t>35조 7282억 8133만</t>
+  </si>
+  <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>30조 3332억 8831만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>30조 1377억 9123만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>32조 2444억 8450만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>29조 477억 8364만</t>
-  </si>
-  <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>26조 7583억 70만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+    <t>13조 9027억 593만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>7조 1441억 2224만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>4조 9121억 1951만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>1조 3833억 9331만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
+  </si>
+  <si>
+    <t>3경 8288조 8596억 2121만</t>
+  </si>
+  <si>
+    <t>쥬정뱅이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5401조 1775억 9579만</t>
+  </si>
+  <si>
+    <t>서넬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%84%AC</t>
+  </si>
+  <si>
+    <t>2368조 2326억 1555만</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2164조 6361억 9806만</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>2040조 2096억 9819만</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>1768조 6189억 4009만</t>
+  </si>
+  <si>
+    <t>쑥국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>1433조 1240억 8623만</t>
+  </si>
+  <si>
+    <t>냉도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
+  </si>
+  <si>
+    <t>590조 9541억 2714만</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>506조 4480억 7633만</t>
+  </si>
+  <si>
+    <t>엔젤가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>450조 8886억 9927만</t>
+  </si>
+  <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>357조 3874억 6906만</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>351조 8492억 1580만</t>
+  </si>
+  <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>348조 712억 4764만</t>
+  </si>
+  <si>
+    <t>핫장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>254조 3992억 7562만</t>
+  </si>
+  <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>215조 5822억 7965만</t>
+  </si>
+  <si>
+    <t>쵸꼬님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>198조 2897억 5440만</t>
+  </si>
+  <si>
+    <t>키은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>187조 7068억 1178만</t>
+  </si>
+  <si>
+    <t>개점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
+  </si>
+  <si>
+    <t>184조 8328억 9468만</t>
+  </si>
+  <si>
+    <t>헛점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
+  </si>
+  <si>
+    <t>182조 1231억 889만</t>
+  </si>
+  <si>
+    <t>사마련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>169조 6095억 1023만</t>
+  </si>
+  <si>
+    <t>앨리스빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>135조 9349억 5864만</t>
+  </si>
+  <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>123조 3182억 1974만</t>
+  </si>
+  <si>
+    <t>81학찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>122조 3620억 6338만</t>
+  </si>
+  <si>
+    <t>머쓰윽타드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
+  </si>
+  <si>
+    <t>100조 4428억 3022만</t>
+  </si>
+  <si>
+    <t>핫딜만삼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
+  </si>
+  <si>
+    <t>83조 9600억 7589만</t>
+  </si>
+  <si>
+    <t>샤갈츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
+  </si>
+  <si>
+    <t>79조 7546억 4080만</t>
+  </si>
+  <si>
+    <t>챠재범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
+  </si>
+  <si>
+    <t>66조 3220억 6577만</t>
+  </si>
+  <si>
+    <t>핫두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
+  </si>
+  <si>
+    <t>57조 1080억 8059만</t>
+  </si>
+  <si>
+    <t>까사PC</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%82%ACPC</t>
+  </si>
+  <si>
+    <t>35조 6114억 3084만</t>
+  </si>
+  <si>
+    <t>딸기비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>16조 5600억 6366만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>4경 3707조 2620억 9240만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 51조 1568억 2849만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>4411조 1890억 4667만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>1910조 6530억 8185만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1785조 9877억 5238만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1516조 4618억 7308만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>1179조 3435억 8759만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>1165조 48억 3022만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>912조 2420억 8820만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>908조 9061억 9527만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>701조 5176억 4278만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>676조 3856억 4619만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>491조 9049억 1230만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>373조 8415억 2368만</t>
+  </si>
+  <si>
+    <t>하탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>180조 8692억 9594만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>142조 427억 623만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>91조 5258억 8878만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>64조 1021억 6596만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>64조 615억 4022만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>61조 7138억 9820만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>61조 6600억 8872만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>42조 7545억 8140만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>34조 6175억 5949만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>33조 3361억 4093만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>30조 6216억 8106만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>28조 5477억 2207만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>25조 6546억 6954만</t>
+  </si>
+  <si>
+    <t>라흐S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
+  </si>
+  <si>
+    <t>21조 5556억 5967만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>17조 3788억 1099만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>14조 6374억 5269만</t>
+  </si>
+  <si>
+    <t>THE끌림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>2경 7603조 4170억 1597만</t>
+  </si>
+  <si>
+    <t>멸국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>2경 1019조 5891억 2946만</t>
+  </si>
+  <si>
+    <t>NUKE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
+  </si>
+  <si>
+    <t>1경 729조 2871억 9338만</t>
+  </si>
+  <si>
+    <t>쌔주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>4536조 29억 3617만</t>
+  </si>
+  <si>
+    <t>S2베코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
+  </si>
+  <si>
+    <t>1122조 5711억 445만</t>
+  </si>
+  <si>
+    <t>픠즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1101조 7618억 8922만</t>
+  </si>
+  <si>
+    <t>환불한너잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
+  </si>
+  <si>
+    <t>994조 1109억 7955만</t>
+  </si>
+  <si>
+    <t>똔똔잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
+  </si>
+  <si>
+    <t>897조 9270억 5416만</t>
+  </si>
+  <si>
+    <t>아투피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
+  </si>
+  <si>
+    <t>817조 5160억 1169만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
+  </si>
+  <si>
+    <t>754조 7329억 996만</t>
+  </si>
+  <si>
+    <t>널비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
+  </si>
+  <si>
+    <t>740조 2648억 1193만</t>
+  </si>
+  <si>
+    <t>뷰질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
+  </si>
+  <si>
+    <t>363조 4035억 3744만</t>
+  </si>
+  <si>
+    <t>근접맞나이거</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
+  </si>
+  <si>
+    <t>292조 3059억 2299만</t>
+  </si>
+  <si>
+    <t>순서교체</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
+  </si>
+  <si>
+    <t>279조 4615억 8250만</t>
+  </si>
+  <si>
+    <t>김천아재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>143조 1750억 8158만</t>
+  </si>
+  <si>
+    <t>무썬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
+  </si>
+  <si>
+    <t>133조 1855억 4352만</t>
+  </si>
+  <si>
+    <t>약할뻔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
+  </si>
+  <si>
+    <t>118조 9378억 4192만</t>
+  </si>
+  <si>
+    <t>맥맥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
+  </si>
+  <si>
+    <t>102조 3828억 5629만</t>
+  </si>
+  <si>
+    <t>성칙이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>99조 2930억 183만</t>
+  </si>
+  <si>
+    <t>돌아온홍굴이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>63조 1174억 4254만</t>
+  </si>
+  <si>
+    <t>kiaer</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
+  </si>
+  <si>
+    <t>55조 5203억 2746만</t>
+  </si>
+  <si>
+    <t>안재똥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
+  </si>
+  <si>
+    <t>53조 316억 6109만</t>
+  </si>
+  <si>
+    <t>숔숔숔숔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
+  </si>
+  <si>
+    <t>50조 2478억 3457만</t>
+  </si>
+  <si>
+    <t>순샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
+  </si>
+  <si>
+    <t>28조 1538억 8950만</t>
+  </si>
+  <si>
+    <t>탱탱볼탱탱볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>22조 2876억 1489만</t>
+  </si>
+  <si>
+    <t>기차아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>21조 5370억 1579만</t>
+  </si>
+  <si>
+    <t>보마가될인재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>20조 7031억 8531만</t>
+  </si>
+  <si>
+    <t>이서지용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>14조 7080억 4787만</t>
+  </si>
+  <si>
+    <t>구뺑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
+  </si>
+  <si>
+    <t>14조 5182억 6768만</t>
+  </si>
+  <si>
+    <t>힐줄까</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
+  </si>
+  <si>
+    <t>3경 8920조 1864억 1544만</t>
+  </si>
+  <si>
+    <t>키노눙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
+  </si>
+  <si>
+    <t>1경 6707조 9046억 3656만</t>
+  </si>
+  <si>
+    <t>Rahee</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
+  </si>
+  <si>
+    <t>4481조 7441억 4928만</t>
+  </si>
+  <si>
+    <t>한마드릴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
+  </si>
+  <si>
+    <t>2372조 8225억 1874만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1593조 2425억 1661만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1173조 2300억 690만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>1049조 6039억 2329만</t>
+  </si>
+  <si>
+    <t>윤돌이굴돌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>882조 8717억 7904만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>308조 1656억 8294만</t>
+  </si>
+  <si>
+    <t>쏘세용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>264조 7186억 3340만</t>
+  </si>
+  <si>
+    <t>갓쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>208조 4588억 4458만</t>
+  </si>
+  <si>
+    <t>퀸돈대통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
+  </si>
+  <si>
+    <t>192조 6574억 726만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>130조 5809억 799만</t>
+  </si>
+  <si>
+    <t>김컁구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>112조 8623억 7315만</t>
+  </si>
+  <si>
+    <t>킴술하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
+  </si>
+  <si>
+    <t>107조 4309억 5168만</t>
+  </si>
+  <si>
+    <t>우당탕탼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
+  </si>
+  <si>
+    <t>94조 6162억 350만</t>
+  </si>
+  <si>
+    <t>표창빌런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
+  </si>
+  <si>
+    <t>75조 9369억 9337만</t>
+  </si>
+  <si>
+    <t>잼이유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>51조 3598억 1393만</t>
+  </si>
+  <si>
+    <t>붕붕월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>38조 2956억 4793만</t>
+  </si>
+  <si>
+    <t>사철화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>35조 6128억 8346만</t>
+  </si>
+  <si>
+    <t>얼음조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>29조 9650억 2208만</t>
+  </si>
+  <si>
+    <t>커피숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
+  </si>
+  <si>
+    <t>20조 7109억 6991만</t>
+  </si>
+  <si>
+    <t>뵤으</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
+  </si>
+  <si>
+    <t>20조 4451억 8915만</t>
+  </si>
+  <si>
+    <t>Subaru</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
+  </si>
+  <si>
+    <t>18조 3365억 7780만</t>
+  </si>
+  <si>
+    <t>도시리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>17조 8938억 4460만</t>
+  </si>
+  <si>
+    <t>57년김춘배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>14조 1113억 6643만</t>
+  </si>
+  <si>
+    <t>킴밍끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
-    <t>10조 2683억 1587만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>7조 934억 6936만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4조 5836억 4371만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>1조 3833억 9331만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>4경 3707조 2620억 9240만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 51조 1568억 2849만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>4007조 8575억 5248만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>1910조 6530억 8185만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1767조 737억 1782만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1513조 7964억 6793만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>1148조 5347억 7192만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>1068조 8537억 3569만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>908조 9061억 9527만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>877조 4282억 9838만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>701조 5176억 4278만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>586조 4551억 6225만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>466조 6381억 9052만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>368조 7877억 5663만</t>
-  </si>
-  <si>
-    <t>하탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>180조 8692억 9594만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>140조 4378억 3728만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>85조 4596억 3842만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>64조 1021억 6596만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>63조 8853억 9315만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>57조 8752억 3608만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>57조 8522억 5684만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>41조 2461억 4444만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>33조 3361억 4093만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>31조 9571억 9631만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>29조 7833억 9317만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>28조 5477억 2207만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>23조 404억 1383만</t>
-  </si>
-  <si>
-    <t>라흐S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
-  </si>
-  <si>
-    <t>19조 1716억 2008만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>16조 7271억 9915만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>12조 1514억 5369만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
-  </si>
-  <si>
-    <t>3경 5424조 639억 9269만</t>
-  </si>
-  <si>
-    <t>쥬정뱅이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5398조 661억 4262만</t>
-  </si>
-  <si>
-    <t>서넬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%84%AC</t>
-  </si>
-  <si>
-    <t>2292조 5278억 8310만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2126조 5861억 2177만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>1888조 1764억 1915만</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>1768조 6189억 4009만</t>
-  </si>
-  <si>
-    <t>쑥국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>1433조 1240억 8623만</t>
-  </si>
-  <si>
-    <t>냉도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
-  </si>
-  <si>
-    <t>590조 3억 2729만</t>
-  </si>
-  <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>496조 4871억 4602만</t>
-  </si>
-  <si>
-    <t>엔젤가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>445조 5440억 8143만</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>347조 5255억 8309만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>347조 3347억 5470만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>343조 7926억 643만</t>
-  </si>
-  <si>
-    <t>핫장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>254조 3992억 7562만</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>215조 3695억 4535만</t>
-  </si>
-  <si>
-    <t>쵸꼬님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>185조 2512억 2204만</t>
-  </si>
-  <si>
-    <t>개점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
-  </si>
-  <si>
-    <t>184조 8328억 9468만</t>
-  </si>
-  <si>
-    <t>키은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>184조 2845억 2767만</t>
-  </si>
-  <si>
-    <t>헛점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
-  </si>
-  <si>
-    <t>182조 1231억 889만</t>
-  </si>
-  <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>123조 3182억 1974만</t>
-  </si>
-  <si>
-    <t>81학찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>122조 3620억 6338만</t>
-  </si>
-  <si>
-    <t>앨리스빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>104조 5489억 7913만</t>
-  </si>
-  <si>
-    <t>머쓰윽타드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
-  </si>
-  <si>
-    <t>83조 6843억 2364만</t>
-  </si>
-  <si>
-    <t>샤갈츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
-  </si>
-  <si>
-    <t>79조 7546억 4080만</t>
-  </si>
-  <si>
-    <t>핫딜만삼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
-  </si>
-  <si>
-    <t>76조 4069억 2391만</t>
-  </si>
-  <si>
-    <t>챠재범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
-  </si>
-  <si>
-    <t>64조 9708억 6347만</t>
-  </si>
-  <si>
-    <t>핫두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
-  </si>
-  <si>
-    <t>56조 3514억 196만</t>
-  </si>
-  <si>
-    <t>까사PC</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%82%ACPC</t>
-  </si>
-  <si>
-    <t>35조 6114억 3084만</t>
-  </si>
-  <si>
-    <t>딸기비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>16조 2236억 3081만</t>
-  </si>
-  <si>
-    <t>THE끌림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>2경 7603조 4170억 1597만</t>
-  </si>
-  <si>
-    <t>멸국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>2경 1019조 5891억 2946만</t>
-  </si>
-  <si>
-    <t>NUKE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
-  </si>
-  <si>
-    <t>9783조 4222억 1342만</t>
-  </si>
-  <si>
-    <t>쌔주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>4348조 4550억 8883만</t>
-  </si>
-  <si>
-    <t>픠즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1100조 5552억 1049만</t>
-  </si>
-  <si>
-    <t>S2베코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
-  </si>
-  <si>
-    <t>1042조 8266억 6390만</t>
-  </si>
-  <si>
-    <t>환불한너잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
-  </si>
-  <si>
-    <t>994조 1109억 7955만</t>
-  </si>
-  <si>
-    <t>똔똔잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
-  </si>
-  <si>
-    <t>897조 9270억 5416만</t>
-  </si>
-  <si>
-    <t>아투피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
-  </si>
-  <si>
-    <t>817조 5160억 1169만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
-  </si>
-  <si>
-    <t>754조 7329억 996만</t>
-  </si>
-  <si>
-    <t>널비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
-  </si>
-  <si>
-    <t>719조 4892억 5173만</t>
-  </si>
-  <si>
-    <t>뷰질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
-  </si>
-  <si>
-    <t>350조 6784억 240만</t>
-  </si>
-  <si>
-    <t>근접맞나이거</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
-  </si>
-  <si>
-    <t>292조 1350억 3660만</t>
-  </si>
-  <si>
-    <t>순서교체</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
-  </si>
-  <si>
-    <t>278조 5066억 693만</t>
-  </si>
-  <si>
-    <t>김천아재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>143조 1750억 8158만</t>
-  </si>
-  <si>
-    <t>무썬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
-  </si>
-  <si>
-    <t>130조 6203억 1435만</t>
-  </si>
-  <si>
-    <t>약할뻔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
-  </si>
-  <si>
-    <t>118조 3506억 2317만</t>
-  </si>
-  <si>
-    <t>맥맥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
-  </si>
-  <si>
-    <t>102조 3828억 5629만</t>
-  </si>
-  <si>
-    <t>성칙이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>92조 7018억 9649만</t>
-  </si>
-  <si>
-    <t>돌아온홍굴이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>63조 1174억 4254만</t>
-  </si>
-  <si>
-    <t>kiaer</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
-  </si>
-  <si>
-    <t>53조 5603억 1732만</t>
-  </si>
-  <si>
-    <t>숔숔숔숔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
-  </si>
-  <si>
-    <t>48조 6700억 5252만</t>
-  </si>
-  <si>
-    <t>안재똥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
-  </si>
-  <si>
-    <t>37조 9124억 1610만</t>
-  </si>
-  <si>
-    <t>순샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
-  </si>
-  <si>
-    <t>26조 501억 4266만</t>
-  </si>
-  <si>
-    <t>탱탱볼탱탱볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>22조 2876억 1489만</t>
-  </si>
-  <si>
-    <t>보마가될인재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>20조 5831억 949만</t>
-  </si>
-  <si>
-    <t>기차아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>17조 5271억 8599만</t>
-  </si>
-  <si>
-    <t>이서지용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>14조 7080억 4787만</t>
-  </si>
-  <si>
-    <t>구뺑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
-  </si>
-  <si>
-    <t>13조 9987억 3324만</t>
-  </si>
-  <si>
-    <t>힐줄까</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
-  </si>
-  <si>
-    <t>3경 8272조 3824억 4049만</t>
-  </si>
-  <si>
-    <t>키노눙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
-  </si>
-  <si>
-    <t>1경 6657조 3780억 7165만</t>
-  </si>
-  <si>
-    <t>Rahee</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
-  </si>
-  <si>
-    <t>4481조 7441억 4928만</t>
-  </si>
-  <si>
-    <t>한마드릴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
-  </si>
-  <si>
-    <t>2058조 5932억 9761만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1593조 2425억 1661만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1173조 2300억 690만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>1049조 6039억 2329만</t>
-  </si>
-  <si>
-    <t>윤돌이굴돌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>881조 3206억 2637만</t>
-  </si>
-  <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>260조 198억 4376만</t>
-  </si>
-  <si>
-    <t>쏘세용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>245조 8043억 8995만</t>
-  </si>
-  <si>
-    <t>갓쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>206조 150억 3382만</t>
-  </si>
-  <si>
-    <t>퀸돈대통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
-  </si>
-  <si>
-    <t>192조 6574억 726만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>118조 6948억 9392만</t>
-  </si>
-  <si>
-    <t>킴술하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
-  </si>
-  <si>
-    <t>105조 6500억 3631만</t>
-  </si>
-  <si>
-    <t>김컁구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>103조 1676억 1535만</t>
-  </si>
-  <si>
-    <t>우당탕탼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
-  </si>
-  <si>
-    <t>87조 7171억 7168만</t>
-  </si>
-  <si>
-    <t>표창빌런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>75조 3969억 2577만</t>
-  </si>
-  <si>
-    <t>잼이유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>46조 6347억 1648만</t>
-  </si>
-  <si>
-    <t>붕붕월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>35조 6148억 8400만</t>
-  </si>
-  <si>
-    <t>사철화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>35조 6128억 8346만</t>
-  </si>
-  <si>
-    <t>얼음조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>27조 852억 4351만</t>
-  </si>
-  <si>
-    <t>뵤으</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
-  </si>
-  <si>
-    <t>19조 6482억 6303만</t>
-  </si>
-  <si>
-    <t>커피숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
-  </si>
-  <si>
-    <t>18조 9950억 3607만</t>
-  </si>
-  <si>
-    <t>Subaru</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
-  </si>
-  <si>
-    <t>18조 3365억 7780만</t>
-  </si>
-  <si>
-    <t>도시리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>17조 8938억 4460만</t>
-  </si>
-  <si>
-    <t>57년김춘배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>13조 122억 3756만</t>
-  </si>
-  <si>
-    <t>킴밍끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
-  </si>
-  <si>
-    <t>12조 9444억 3083만</t>
+    <t>13조 5330억 3869만</t>
+  </si>
+  <si>
+    <t>시네루최</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
+  </si>
+  <si>
+    <t>11조 52억 3281만</t>
   </si>
   <si>
     <t>메린이이</t>
@@ -1983,22 +2001,13 @@
     <t>9조 8298억 4972만</t>
   </si>
   <si>
-    <t>시네루최</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
-  </si>
-  <si>
-    <t>8조 3997억 9352만</t>
-  </si>
-  <si>
     <t>먕겜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%95%EA%B2%9C</t>
   </si>
   <si>
-    <t>3경 6241조 1854억 2489만</t>
+    <t>4경 993조 8187억 6351만</t>
   </si>
   <si>
     <t>용려니</t>
@@ -2007,7 +2016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
   </si>
   <si>
-    <t>1경 7172조 9206억 9638만</t>
+    <t>2경 341조 2395억 3889만</t>
   </si>
   <si>
     <t>메키멍</t>
@@ -2025,7 +2034,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>1415조 2321억 8007만</t>
+    <t>1461조 8726억 7625만</t>
+  </si>
+  <si>
+    <t>샤프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>634조 4715억 6984만</t>
   </si>
   <si>
     <t>참달</t>
@@ -2034,16 +2052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
   </si>
   <si>
-    <t>544조 169억 8454만</t>
-  </si>
-  <si>
-    <t>샤프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>534조 3569억 9976만</t>
+    <t>595조 2826억 5325만</t>
   </si>
   <si>
     <t>인두겁</t>
@@ -2052,7 +2061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>294조 1230억 8091만</t>
+    <t>308조 5022억 7425만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2061,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>161조 8971억 8732만</t>
+    <t>169조 2665억 763만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2079,13 +2088,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>127조 4259억 2958만</t>
+    <t>135조 3185억 3067만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>60조 8548억 1831만</t>
+    <t>63조 4078억 7837만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2103,16 +2112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
   </si>
   <si>
-    <t>52조 6404억 3193만</t>
-  </si>
-  <si>
-    <t>스파륑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%EB%A5%91</t>
-  </si>
-  <si>
-    <t>40조 7581억 7641만</t>
+    <t>54조 9966억 3279만</t>
   </si>
   <si>
     <t>본분</t>
@@ -2130,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>31조 1018억 6733만</t>
+    <t>31조 1829억 1115만</t>
   </si>
   <si>
     <t>못스제</t>
@@ -2157,7 +2157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
   </si>
   <si>
-    <t>20조 8970억 1069만</t>
+    <t>22조 9580억 1744만</t>
   </si>
   <si>
     <t>하이요하임</t>
@@ -2175,7 +2175,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>15조 1591억 8028만</t>
+    <t>15조 8287억 2821만</t>
+  </si>
+  <si>
+    <t>1조투력찍었던</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
+  </si>
+  <si>
+    <t>15조 1689억 1238만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2187,13 +2196,13 @@
     <t>14조 4673억 6555만</t>
   </si>
   <si>
-    <t>1조투력찍었던</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
-  </si>
-  <si>
-    <t>14조 4216억 5233만</t>
+    <t>훈이ing</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EC%9D%B4ing</t>
+  </si>
+  <si>
+    <t>14조 2938억 3283만</t>
   </si>
   <si>
     <t>탕화</t>
@@ -2229,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>7조 2446억 9551만</t>
+    <t>7조 5107억 5140만</t>
   </si>
   <si>
     <t>BudriQ</t>
@@ -2238,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
   </si>
   <si>
-    <t>6조 4566억 7313만</t>
+    <t>6조 7907억 4297만</t>
   </si>
   <si>
     <t>가겠네</t>
@@ -2256,7 +2265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
   </si>
   <si>
-    <t>4조 6474억 3713만</t>
+    <t>4조 7892억 8086만</t>
   </si>
 </sst>
 </file>
@@ -2772,16 +2781,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
@@ -2813,16 +2822,16 @@
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -3301,13 +3310,13 @@
         <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3318,25 +3327,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>131</v>
@@ -3368,7 +3377,7 @@
         <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>136</v>
@@ -3400,7 +3409,7 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>140</v>
@@ -3432,7 +3441,7 @@
         <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>144</v>
@@ -3493,13 +3502,13 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3510,28 +3519,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3542,16 +3551,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
@@ -3560,10 +3569,10 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3574,28 +3583,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3606,25 +3615,25 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3653,10 +3662,10 @@
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>174</v>
@@ -3688,7 +3697,7 @@
         <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>178</v>
@@ -3720,7 +3729,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>182</v>
@@ -3752,7 +3761,7 @@
         <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>185</v>
@@ -3766,7 +3775,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>186</v>
@@ -3784,7 +3793,7 @@
         <v>188</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>189</v>
@@ -3816,7 +3825,7 @@
         <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>192</v>
@@ -3830,7 +3839,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>23</v>
@@ -3839,19 +3848,19 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3862,16 +3871,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -3880,10 +3889,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3894,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>202</v>
@@ -3926,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>206</v>
@@ -3941,10 +3950,10 @@
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>208</v>
@@ -3958,7 +3967,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>209</v>
@@ -3976,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>211</v>
@@ -4282,7 +4291,7 @@
         <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>116</v>
@@ -4314,7 +4323,7 @@
         <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>116</v>
@@ -4349,7 +4358,7 @@
         <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>240</v>
@@ -4363,7 +4372,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>241</v>
@@ -4381,7 +4390,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>243</v>
@@ -4445,7 +4454,7 @@
         <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>249</v>
@@ -4474,13 +4483,13 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4494,22 +4503,22 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>256</v>
@@ -4538,10 +4547,10 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>259</v>
@@ -4555,7 +4564,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>260</v>
@@ -4570,10 +4579,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>262</v>
@@ -4587,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>263</v>
@@ -4602,10 +4611,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>265</v>
@@ -4619,7 +4628,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>266</v>
@@ -4637,7 +4646,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>268</v>
@@ -4651,7 +4660,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>269</v>
@@ -4666,10 +4675,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>271</v>
@@ -4701,7 +4710,7 @@
         <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>274</v>
@@ -4730,10 +4739,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>277</v>
@@ -4762,10 +4771,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>280</v>
@@ -4797,10 +4806,10 @@
         <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4811,28 +4820,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4846,25 +4855,25 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4875,28 +4884,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4907,16 +4916,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -4925,10 +4934,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4939,16 +4948,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
@@ -4957,10 +4966,10 @@
         <v>100</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4971,7 +4980,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>33</v>
@@ -4980,19 +4989,19 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5090,25 +5099,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5122,25 +5131,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>305</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>305</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5154,25 +5163,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5186,25 +5195,25 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5218,13 +5227,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -5233,10 +5242,10 @@
         <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5250,25 +5259,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5282,25 +5291,25 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5314,25 +5323,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5346,13 +5355,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -5364,7 +5373,7 @@
         <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5375,28 +5384,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5410,25 +5419,25 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5442,13 +5451,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -5460,7 +5469,7 @@
         <v>116</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5474,25 +5483,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5506,25 +5515,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5538,13 +5547,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -5553,10 +5562,10 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5567,16 +5576,16 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -5585,10 +5594,10 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5599,28 +5608,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5631,28 +5640,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5663,28 +5672,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5698,25 +5707,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5730,25 +5739,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5762,25 +5771,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5794,25 +5803,25 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5823,16 +5832,16 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -5841,10 +5850,10 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5858,25 +5867,25 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5887,28 +5896,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5919,28 +5928,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5951,28 +5960,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5983,28 +5992,28 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6015,28 +6024,28 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6082,7 +6091,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6091,7 +6100,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6135,25 +6144,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>217</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6167,25 +6176,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6199,25 +6208,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6231,25 +6240,25 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6263,13 +6272,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -6278,10 +6287,10 @@
         <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6295,25 +6304,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6327,25 +6336,25 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6359,25 +6368,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6391,25 +6400,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6420,28 +6429,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6455,25 +6464,25 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6487,25 +6496,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6519,25 +6528,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6551,25 +6560,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6583,13 +6592,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -6598,10 +6607,10 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6612,16 +6621,16 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -6630,10 +6639,10 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6644,28 +6653,28 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6676,28 +6685,28 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6708,28 +6717,28 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6743,13 +6752,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
@@ -6758,10 +6767,10 @@
         <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6775,25 +6784,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6807,25 +6816,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6839,13 +6848,13 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -6854,10 +6863,10 @@
         <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6868,28 +6877,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6903,25 +6912,25 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6932,28 +6941,28 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>470</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6964,28 +6973,28 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>473</v>
-      </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6996,16 +7005,16 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
@@ -7014,10 +7023,10 @@
         <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>204</v>
+        <v>296</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7028,35 +7037,67 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7087,6 +7128,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7147,13 +7189,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>83</v>
@@ -7165,7 +7207,7 @@
         <v>217</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7179,13 +7221,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -7197,7 +7239,7 @@
         <v>217</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7211,13 +7253,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -7229,7 +7271,7 @@
         <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7243,13 +7285,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -7261,7 +7303,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7275,25 +7317,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7307,25 +7349,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7339,13 +7381,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -7357,7 +7399,7 @@
         <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7371,13 +7413,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -7389,7 +7431,7 @@
         <v>121</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7403,13 +7445,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -7418,10 +7460,10 @@
         <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7432,7 +7474,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>55</v>
@@ -7441,10 +7483,10 @@
         <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>84</v>
@@ -7453,7 +7495,7 @@
         <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7467,13 +7509,13 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -7482,10 +7524,10 @@
         <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7499,13 +7541,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -7517,7 +7559,7 @@
         <v>116</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7531,13 +7573,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -7546,10 +7588,10 @@
         <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7563,25 +7605,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7595,13 +7637,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -7610,10 +7652,10 @@
         <v>188</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7624,16 +7666,16 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -7642,10 +7684,10 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7656,16 +7698,16 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
@@ -7674,10 +7716,10 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7688,16 +7730,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
@@ -7706,10 +7748,10 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7720,16 +7762,16 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
@@ -7738,10 +7780,10 @@
         <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7755,13 +7797,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
@@ -7770,10 +7812,10 @@
         <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7787,13 +7829,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
@@ -7805,7 +7847,7 @@
         <v>204</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7819,25 +7861,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>157</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7851,25 +7893,25 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7880,16 +7922,16 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -7898,10 +7940,10 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7915,13 +7957,13 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
@@ -7933,7 +7975,7 @@
         <v>204</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7944,28 +7986,28 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7976,28 +8018,28 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8008,28 +8050,28 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8040,16 +8082,16 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
@@ -8061,7 +8103,7 @@
         <v>204</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8159,13 +8201,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>83</v>
@@ -8177,7 +8219,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8191,13 +8233,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -8206,10 +8248,10 @@
         <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8223,13 +8265,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -8241,7 +8283,7 @@
         <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8255,25 +8297,25 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8287,13 +8329,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -8305,7 +8347,7 @@
         <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8325,10 +8367,10 @@
         <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>106</v>
@@ -8337,7 +8379,7 @@
         <v>121</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8351,13 +8393,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -8369,7 +8411,7 @@
         <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8383,13 +8425,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -8401,7 +8443,7 @@
         <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8415,13 +8457,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -8430,10 +8472,10 @@
         <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8444,28 +8486,28 @@
         <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8479,13 +8521,13 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -8494,10 +8536,10 @@
         <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8511,13 +8553,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -8526,10 +8568,10 @@
         <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8543,25 +8585,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8575,25 +8617,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8607,25 +8649,25 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8636,16 +8678,16 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -8654,10 +8696,10 @@
         <v>188</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8668,28 +8710,28 @@
         <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8700,16 +8742,16 @@
         <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
@@ -8718,10 +8760,10 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8732,16 +8774,16 @@
         <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
@@ -8750,10 +8792,10 @@
         <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8767,25 +8809,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8799,25 +8841,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8831,25 +8873,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8863,25 +8905,25 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>255</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8892,16 +8934,16 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -8913,7 +8955,7 @@
         <v>204</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8927,13 +8969,13 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
@@ -8942,10 +8984,10 @@
         <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8956,16 +8998,16 @@
         <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
@@ -8974,10 +9016,10 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8988,16 +9030,16 @@
         <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -9006,10 +9048,10 @@
         <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>293</v>
+        <v>648</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9020,28 +9062,28 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9052,28 +9094,28 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9127,7 +9169,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9171,25 +9213,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>308</v>
+        <v>217</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9203,13 +9245,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -9218,10 +9260,10 @@
         <v>111</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>91</v>
+        <v>396</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9235,13 +9277,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -9253,7 +9295,7 @@
         <v>116</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9267,13 +9309,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -9282,10 +9324,10 @@
         <v>111</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9299,25 +9341,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9331,25 +9373,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9363,13 +9405,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -9378,10 +9420,10 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9395,13 +9437,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -9410,10 +9452,10 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9427,25 +9469,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9456,16 +9498,16 @@
         <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
@@ -9474,10 +9516,10 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9497,19 +9539,19 @@
         <v>71</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9523,13 +9565,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -9538,10 +9580,10 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9555,13 +9597,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -9570,10 +9612,10 @@
         <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9587,25 +9629,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9619,25 +9661,25 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9648,28 +9690,28 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9680,28 +9722,28 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>204</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9712,16 +9754,16 @@
         <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
@@ -9730,10 +9772,10 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9744,28 +9786,28 @@
         <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9779,25 +9821,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9811,25 +9853,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9843,25 +9885,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>293</v>
+        <v>648</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9875,25 +9917,25 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9904,16 +9946,16 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -9922,10 +9964,10 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>293</v>
+        <v>648</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9939,25 +9981,25 @@
         <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9968,16 +10010,16 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
@@ -9986,10 +10028,10 @@
         <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10000,16 +10042,16 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -10018,10 +10060,10 @@
         <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10032,16 +10074,16 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
@@ -10050,10 +10092,10 @@
         <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>293</v>
+        <v>648</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10064,16 +10106,16 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
@@ -10082,10 +10124,10 @@
         <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10096,16 +10138,16 @@
         <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>83</v>
@@ -10114,10 +10156,10 @@
         <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>297</v>
+        <v>648</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -84,580 +84,580 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 6578조 3092억 4574만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>11경 9267조 3727억 8819만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>5경 8868조 2988억 6543만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>7경 895조 6692억 2510만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>7경 5026조 3174억 3719만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>6경 9162조 9519억 932만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>6경 9232조 7667억 1784만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3경 27조 8635억 7445만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6493조 5045억 7772만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5860조 1812억 2503만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3106조 9258억 9914만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2011조 4544억 3476만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1007조 3178억 5658만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>874조 5211억 9379만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>869조 5677억 141만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>684조 4401억 9646만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>481조 5847억 7403만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>379조 5440억 9162만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>366조 6787억 5438만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>334조 4614억 9803만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>275조 8357억 446만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>273조 8981억 703만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>266조 8078억 6673만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>254조 2629억 9000만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>239조 5598억 9073만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>186조 7933억 7887만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>143조 3408억 6701만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>92조 4870억 8016만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>70조 9879억 8078만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>70조 9613억 4646만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>59조 7773억 9141만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>55조 7049억 3694만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>53조 811억 6540만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>6경 795조 530억 3667만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.06</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>11경 8671조 7327억 4990만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 8284조 3756억 5532만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>7경 706조 9369억 6313만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>7경 2193조 1516억 9085만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>6경 8981조 9859억 3906만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>6경 7552조 6685억 2486만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2경 6417조 5007억 3060만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6442조 4590억 4780만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>4200조 912억 9692만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>2876조 6035억 1029만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2011조 4544억 3476만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1007조 3178억 5658만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>872조 522억 4681만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>827조 8255억 4449만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>615조 966억 3132만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>480조 4284억 4041만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>366조 6787억 5438만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>333조 9657억 1895만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>321조 5291억 6983만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>267조 5583억 8727만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>263조 2828억 1813만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>252조 9962억 8450만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>247조 8297억 5839만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>239조 5598억 9073만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>181조 6612억 1265만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>143조 3408억 6701만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>91조 2927억 8263만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>68조 2761억 4360만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>61조 8207억 5987만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>59조 7773억 9141만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>55조 7049억 3694만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>53조 811억 6540만</t>
-  </si>
-  <si>
     <t>포뇨야</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
   </si>
   <si>
-    <t>46조 6729억 2879만</t>
+    <t>46조 8132억 192만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -666,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>42조 8377억 6291만</t>
+    <t>43조 5213억 2613만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -687,7 +687,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>2경 2100조 9597억 1931만</t>
+    <t>2경 2256조 6472억 4538만</t>
   </si>
   <si>
     <t>실민</t>
@@ -708,7 +708,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>2522조 3017억 1179만</t>
+    <t>2538조 1629억 9171만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -726,7 +726,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>759조 7355억 439만</t>
+    <t>888조 8863억 1085만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>821조 6016억 2180만</t>
   </si>
   <si>
     <t>앨삐</t>
@@ -735,16 +744,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
   </si>
   <si>
-    <t>733조 6203억 8517만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>721조 6837억 3333만</t>
+    <t>735조 1810억 6085만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>680조 5687억 5789만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -753,16 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>676조 3860억 485만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>595조 3193억 1491만</t>
+    <t>677조 6328억 4114만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -771,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
   </si>
   <si>
-    <t>231조 2571억 7985만</t>
+    <t>237조 5153억 3073만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -783,6 +783,15 @@
     <t>180조 1511억 6313만</t>
   </si>
   <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>123조 3664억 3446만</t>
+  </si>
+  <si>
     <t>은달총</t>
   </si>
   <si>
@@ -792,16 +801,25 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>103조 7256억 5191만</t>
-  </si>
-  <si>
-    <t>낭만탕슉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%83%95%EC%8A%89</t>
-  </si>
-  <si>
-    <t>102조 8045억 7118만</t>
+    <t>122조 7081억 6117만</t>
+  </si>
+  <si>
+    <t>런닝쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>122조 668억 9161만</t>
+  </si>
+  <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>119조 7499억 1993만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -810,25 +828,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>97조 7761억 4970만</t>
-  </si>
-  <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>95조 9087억 8563만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>93조 9222억 9452만</t>
+    <t>98조 8208억 4140만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>78조 546억 8943만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -840,15 +849,6 @@
     <t>76조 9522억 1152만</t>
   </si>
   <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>76조 984억 802만</t>
-  </si>
-  <si>
     <t>벨히</t>
   </si>
   <si>
@@ -864,13 +864,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>54조 2197억 8399만</t>
-  </si>
-  <si>
-    <t>낭만만듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
+    <t>59조 697억 5052만</t>
+  </si>
+  <si>
+    <t>만듀쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
   </si>
   <si>
     <t>48조 6128억 1055만</t>
@@ -885,24 +885,24 @@
     <t>35조 7282억 8133만</t>
   </si>
   <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>30조 8752억 547만</t>
+  </si>
+  <si>
+    <t>빠나쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
   </si>
   <si>
     <t>30조 3332억 8831만</t>
   </si>
   <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>30조 1377억 9123만</t>
-  </si>
-  <si>
     <t>강한고등어</t>
   </si>
   <si>
@@ -912,7 +912,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>13조 9027억 593만</t>
+    <t>14조 3369억 9211만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -924,7 +924,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 1441억 2224만</t>
+    <t>7조 1824억 9202만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -933,19 +933,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>4조 9121억 1951만</t>
+    <t>5조 247억 5988만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>1조 3833억 9331만</t>
+    <t>1조 3870억 7073만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
   </si>
   <si>
-    <t>3경 8288조 8596억 2121만</t>
+    <t>3경 8659조 7409억 1602만</t>
   </si>
   <si>
     <t>쥬정뱅이</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%84%AC</t>
   </si>
   <si>
-    <t>2368조 2326억 1555만</t>
+    <t>2375조 8543억 1894만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -972,7 +972,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>2164조 6361억 9806만</t>
+    <t>2267조 6858억 4448만</t>
   </si>
   <si>
     <t>귀여워서미안</t>
@@ -981,7 +981,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
   </si>
   <si>
-    <t>2040조 2096억 9819만</t>
+    <t>2046조 964억 4708만</t>
   </si>
   <si>
     <t>밀프푸씨</t>
@@ -990,7 +990,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
   </si>
   <si>
-    <t>1768조 6189억 4009만</t>
+    <t>1775조 5915억 3045만</t>
   </si>
   <si>
     <t>쑥국</t>
@@ -1017,7 +1017,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
   </si>
   <si>
-    <t>506조 4480억 7633만</t>
+    <t>539조 6044억 1771만</t>
   </si>
   <si>
     <t>엔젤가든</t>
@@ -1035,7 +1035,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
   </si>
   <si>
-    <t>357조 3874억 6906만</t>
+    <t>376조 5549억 45만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -1053,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
   </si>
   <si>
-    <t>348조 712억 4764만</t>
+    <t>348조 9207억 6037만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -1080,7 +1080,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
   </si>
   <si>
-    <t>198조 2897억 5440만</t>
+    <t>200조 4625억 6046만</t>
+  </si>
+  <si>
+    <t>헛점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
+  </si>
+  <si>
+    <t>196조 6153억 456만</t>
+  </si>
+  <si>
+    <t>개점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
+  </si>
+  <si>
+    <t>190조 2848억 2308만</t>
   </si>
   <si>
     <t>키은</t>
@@ -1092,24 +1110,6 @@
     <t>187조 7068억 1178만</t>
   </si>
   <si>
-    <t>개점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
-  </si>
-  <si>
-    <t>184조 8328억 9468만</t>
-  </si>
-  <si>
-    <t>헛점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
-  </si>
-  <si>
-    <t>182조 1231억 889만</t>
-  </si>
-  <si>
     <t>사마련</t>
   </si>
   <si>
@@ -1134,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>123조 3182억 1974만</t>
+    <t>129조 5826억 618만</t>
   </si>
   <si>
     <t>81학찬</t>
@@ -1152,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
   </si>
   <si>
-    <t>100조 4428억 3022만</t>
+    <t>104조 8738억 3465만</t>
   </si>
   <si>
     <t>핫딜만삼</t>
@@ -1161,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>83조 9600억 7589만</t>
+    <t>84조 768억 468만</t>
   </si>
   <si>
     <t>샤갈츄</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>66조 3220억 6577만</t>
+    <t>66조 3840억 5859만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
   </si>
   <si>
-    <t>57조 1080억 8059만</t>
+    <t>59조 2713억 6623만</t>
   </si>
   <si>
     <t>까사PC</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>16조 5600억 6366만</t>
+    <t>17조 7436억 7619만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>4411조 1890억 4667만</t>
+    <t>4443조 6113억 6153만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1242,7 +1242,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
   </si>
   <si>
-    <t>1910조 6530억 8185만</t>
+    <t>1976조 4062억 1908만</t>
   </si>
   <si>
     <t>중탸치</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1785조 9877억 5238만</t>
+    <t>1786조 4744억 96만</t>
   </si>
   <si>
     <t>김우이</t>
@@ -1278,7 +1278,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>1165조 48억 3022만</t>
+    <t>1166조 4276억 622만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1290,7 +1290,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>912조 2420억 8820만</t>
+    <t>967조 6736억 462만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>676조 3856억 4619만</t>
+    <t>681조 1534억 9210만</t>
   </si>
   <si>
     <t>임승민</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>491조 9049억 1230만</t>
+    <t>493조 625억 5862만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>373조 8415억 2368만</t>
+    <t>377조 597억 9715만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1353,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>142조 427억 623만</t>
+    <t>144조 7563억 2315만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1362,7 +1362,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
   </si>
   <si>
-    <t>91조 5258억 8878만</t>
+    <t>93조 3399억 7742만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>66조 5106억 606만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1389,16 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>61조 7138억 9820만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>61조 6600억 8872만</t>
+    <t>61조 9101억 5469만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1407,7 +1407,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>42조 7545억 8140만</t>
+    <t>45조 7219억 3707만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>39조 9013억 8175만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1428,15 +1437,6 @@
     <t>33조 3361억 4093만</t>
   </si>
   <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>30조 6216억 8106만</t>
-  </si>
-  <si>
     <t>크앙레몬</t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
   </si>
   <si>
-    <t>25조 6546억 6954만</t>
+    <t>26조 5379억 1952만</t>
   </si>
   <si>
     <t>라흐S2</t>
@@ -1461,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
   </si>
   <si>
-    <t>21조 5556억 5967만</t>
+    <t>22조 2168억 4393만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1470,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>17조 3788억 1099만</t>
+    <t>18조 849억 4416만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1506,7 +1506,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>1경 729조 2871억 9338만</t>
+    <t>1경 3332조 5483억 2852만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -1524,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
   </si>
   <si>
-    <t>1122조 5711억 445만</t>
+    <t>1154조 1568억 8093만</t>
   </si>
   <si>
     <t>픠즈</t>
@@ -1533,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>1101조 7618억 8922만</t>
+    <t>1104조 8278억 4301만</t>
   </si>
   <si>
     <t>환불한너잉</t>
@@ -1554,6 +1554,12 @@
     <t>897조 9270억 5416만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
+  </si>
+  <si>
+    <t>827조 2597억 8821만</t>
+  </si>
+  <si>
     <t>아투피</t>
   </si>
   <si>
@@ -1563,19 +1569,13 @@
     <t>817조 5160억 1169만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
-  </si>
-  <si>
-    <t>754조 7329억 996만</t>
-  </si>
-  <si>
     <t>널비</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
   </si>
   <si>
-    <t>740조 2648억 1193만</t>
+    <t>808조 2793억 4877만</t>
   </si>
   <si>
     <t>뷰질</t>
@@ -1584,7 +1584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
   </si>
   <si>
-    <t>363조 4035억 3744만</t>
+    <t>384조 152억 919만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1593,7 +1593,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
   </si>
   <si>
-    <t>292조 3059억 2299만</t>
+    <t>295조 2246억 5581만</t>
   </si>
   <si>
     <t>순서교체</t>
@@ -1620,7 +1620,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
   </si>
   <si>
-    <t>133조 1855억 4352만</t>
+    <t>136조 6011억 3021만</t>
   </si>
   <si>
     <t>약할뻔</t>
@@ -1629,7 +1629,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
   </si>
   <si>
-    <t>118조 9378억 4192만</t>
+    <t>119조 3285억 9293만</t>
   </si>
   <si>
     <t>맥맥</t>
@@ -1638,7 +1638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
   </si>
   <si>
-    <t>102조 3828억 5629만</t>
+    <t>112조 7713억 330만</t>
   </si>
   <si>
     <t>성칙이</t>
@@ -1647,7 +1647,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>99조 2930억 183만</t>
+    <t>104조 7639억 4878만</t>
   </si>
   <si>
     <t>돌아온홍굴이</t>
@@ -1665,7 +1665,16 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>55조 5203억 2746만</t>
+    <t>58조 1255억 6692만</t>
+  </si>
+  <si>
+    <t>숔숔숔숔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
+  </si>
+  <si>
+    <t>57조 8031억 3763만</t>
   </si>
   <si>
     <t>안재똥</t>
@@ -1677,15 +1686,6 @@
     <t>53조 316억 6109만</t>
   </si>
   <si>
-    <t>숔숔숔숔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
-  </si>
-  <si>
-    <t>50조 2478억 3457만</t>
-  </si>
-  <si>
     <t>순샷</t>
   </si>
   <si>
@@ -1704,6 +1704,15 @@
     <t>22조 2876억 1489만</t>
   </si>
   <si>
+    <t>보마가될인재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>21조 9996억 1996만</t>
+  </si>
+  <si>
     <t>기차아저씨</t>
   </si>
   <si>
@@ -1713,15 +1722,6 @@
     <t>21조 5370억 1579만</t>
   </si>
   <si>
-    <t>보마가될인재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>20조 7031억 8531만</t>
-  </si>
-  <si>
     <t>이서지용</t>
   </si>
   <si>
@@ -1737,7 +1737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>14조 5182억 6768만</t>
+    <t>14조 5766억 2012만</t>
   </si>
   <si>
     <t>힐줄까</t>
@@ -1746,7 +1746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
   </si>
   <si>
-    <t>3경 8920조 1864억 1544만</t>
+    <t>3경 9082조 7801억 1837만</t>
   </si>
   <si>
     <t>키노눙</t>
@@ -1755,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
   </si>
   <si>
-    <t>1경 6707조 9046억 3656만</t>
+    <t>1경 6717조 711억 4758만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1782,13 +1782,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>1593조 2425억 1661만</t>
+    <t>1611조 3444억 7846만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
   </si>
   <si>
-    <t>1173조 2300억 690만</t>
+    <t>1190조 6095억 7843만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1797,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>1049조 6039억 2329만</t>
+    <t>1099조 3935억 1589만</t>
   </si>
   <si>
     <t>윤돌이굴돌이</t>
@@ -1827,22 +1827,22 @@
     <t>264조 7186억 3340만</t>
   </si>
   <si>
+    <t>퀸돈대통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
+  </si>
+  <si>
+    <t>231조 4022억 5454만</t>
+  </si>
+  <si>
     <t>갓쿠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
   </si>
   <si>
-    <t>208조 4588억 4458만</t>
-  </si>
-  <si>
-    <t>퀸돈대통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
-  </si>
-  <si>
-    <t>192조 6574억 726만</t>
+    <t>210조 7742억 6605만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1851,7 +1851,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>130조 5809억 799만</t>
+    <t>132조 4633억 9157만</t>
   </si>
   <si>
     <t>김컁구</t>
@@ -1860,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>112조 8623억 7315만</t>
+    <t>114조 3776억 2024만</t>
   </si>
   <si>
     <t>킴술하</t>
@@ -1878,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
   </si>
   <si>
-    <t>94조 6162억 350만</t>
+    <t>95조 2702억 7914만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1887,7 +1887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>75조 9369억 9337만</t>
+    <t>76조 7654억 4288만</t>
   </si>
   <si>
     <t>잼이유</t>
@@ -1899,22 +1899,22 @@
     <t>51조 3598억 1393만</t>
   </si>
   <si>
+    <t>사철화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>39조 9532억 706만</t>
+  </si>
+  <si>
     <t>붕붕월드</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
   </si>
   <si>
-    <t>38조 2956억 4793만</t>
-  </si>
-  <si>
-    <t>사철화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>35조 6128억 8346만</t>
+    <t>38조 3557억 5010만</t>
   </si>
   <si>
     <t>얼음조아</t>
@@ -1923,7 +1923,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>29조 9650억 2208만</t>
+    <t>31조 710억 771만</t>
   </si>
   <si>
     <t>커피숍</t>
@@ -1950,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=Subaru</t>
   </si>
   <si>
-    <t>18조 3365억 7780만</t>
+    <t>18조 7319억 7969만</t>
   </si>
   <si>
     <t>도시리</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>14조 1113억 6643만</t>
+    <t>15조 5318억 9821만</t>
   </si>
   <si>
     <t>킴밍끼</t>
@@ -1989,7 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
   </si>
   <si>
-    <t>11조 52억 3281만</t>
+    <t>11조 4148억 5544만</t>
   </si>
   <si>
     <t>메린이이</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>9조 8298억 4972만</t>
+    <t>10조 2452억 7329만</t>
   </si>
   <si>
     <t>먕겜</t>
@@ -2007,7 +2007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%95%EA%B2%9C</t>
   </si>
   <si>
-    <t>4경 993조 8187억 6351만</t>
+    <t>4경 2259조 5810억 45만</t>
   </si>
   <si>
     <t>용려니</t>
@@ -2025,7 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
   </si>
   <si>
-    <t>2267조 5866억 9886만</t>
+    <t>2416조 5150억 6445만</t>
   </si>
   <si>
     <t>켘켘3</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>1461조 8726억 7625만</t>
+    <t>1561조 2331억 3123만</t>
   </si>
   <si>
     <t>샤프리</t>
@@ -2043,7 +2043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>634조 4715억 6984만</t>
+    <t>779조 5240억 1382만</t>
   </si>
   <si>
     <t>참달</t>
@@ -2052,7 +2052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
   </si>
   <si>
-    <t>595조 2826억 5325만</t>
+    <t>599조 494억 3324만</t>
   </si>
   <si>
     <t>인두겁</t>
@@ -2061,7 +2061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>308조 5022억 7425만</t>
+    <t>342조 1801억 3259만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2070,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>169조 2665억 763만</t>
+    <t>170조 4718억 6262만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2094,7 +2094,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>63조 4078억 7837만</t>
+    <t>68조 7812억 4342만</t>
+  </si>
+  <si>
+    <t>포근한소리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>63조 1483억 5627만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2106,13 +2115,13 @@
     <t>58조 3600억 2129만</t>
   </si>
   <si>
-    <t>포근한소리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>54조 9966억 3279만</t>
+    <t>잘스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>32조 6623억 7594만</t>
   </si>
   <si>
     <t>본분</t>
@@ -2142,22 +2151,13 @@
     <t>30조 191억 6568만</t>
   </si>
   <si>
-    <t>잘스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>28조 8997억 4964만</t>
-  </si>
-  <si>
     <t>로넌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
   </si>
   <si>
-    <t>22조 9580억 1744만</t>
+    <t>23조 326억 7042만</t>
   </si>
   <si>
     <t>하이요하임</t>
@@ -2166,7 +2166,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%EC%9A%94%ED%95%98%EC%9E%84</t>
   </si>
   <si>
-    <t>19조 7941억 7292만</t>
+    <t>22조 5566억 2690만</t>
+  </si>
+  <si>
+    <t>외단</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
+  </si>
+  <si>
+    <t>20조 902억 1568만</t>
   </si>
   <si>
     <t>개도둑놈</t>
@@ -2175,7 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>15조 8287억 2821만</t>
+    <t>16조 698억 3425만</t>
   </si>
   <si>
     <t>1조투력찍었던</t>
@@ -2184,7 +2193,7 @@
     <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
   </si>
   <si>
-    <t>15조 1689억 1238만</t>
+    <t>15조 7646억 700만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2214,22 +2223,13 @@
     <t>10조 4824억 8636만</t>
   </si>
   <si>
-    <t>외단</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
-  </si>
-  <si>
-    <t>10조 3730억 6086만</t>
-  </si>
-  <si>
     <t>콩새우</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%A9%EC%83%88%EC%9A%B0</t>
   </si>
   <si>
-    <t>8조 2239억 4862만</t>
+    <t>8조 8508억 9461만</t>
   </si>
   <si>
     <t>진우정</t>
@@ -2238,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>7조 5107억 5140만</t>
+    <t>8조 5602억 354만</t>
   </si>
   <si>
     <t>BudriQ</t>
@@ -2247,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
   </si>
   <si>
-    <t>6조 7907억 4297만</t>
+    <t>7조 585억 8416만</t>
   </si>
   <si>
     <t>가겠네</t>
@@ -2256,7 +2256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
   </si>
   <si>
-    <t>5조 3289억 8433만</t>
+    <t>5조 8108억 4605만</t>
   </si>
   <si>
     <t>킴카</t>
@@ -2265,7 +2265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
   </si>
   <si>
-    <t>4조 7892억 8086만</t>
+    <t>5조 2900억 2276만</t>
   </si>
 </sst>
 </file>
@@ -2998,7 +2998,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3438,13 +3438,13 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3455,28 +3455,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3487,25 +3487,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>153</v>
@@ -3534,13 +3534,13 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3554,25 +3554,25 @@
         <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3583,28 +3583,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3615,16 +3615,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
@@ -3636,7 +3636,7 @@
         <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3647,28 +3647,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3679,16 +3679,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
@@ -3697,10 +3697,10 @@
         <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3711,16 +3711,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
@@ -3732,7 +3732,7 @@
         <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3746,13 +3746,13 @@
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -3761,10 +3761,10 @@
         <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3778,25 +3778,25 @@
         <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3807,28 +3807,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3839,7 +3839,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>23</v>
@@ -3848,16 +3848,16 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>195</v>
@@ -3871,16 +3871,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -3889,10 +3889,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3903,16 +3903,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
@@ -3921,10 +3921,10 @@
         <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3935,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>206</v>
@@ -3950,10 +3950,10 @@
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>208</v>
@@ -3985,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>211</v>
@@ -4291,7 +4291,7 @@
         <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>116</v>
@@ -4323,10 +4323,10 @@
         <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>237</v>
@@ -4358,7 +4358,7 @@
         <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>240</v>
@@ -4390,7 +4390,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>243</v>
@@ -4454,7 +4454,7 @@
         <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>249</v>
@@ -4483,13 +4483,13 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4500,25 +4500,25 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>256</v>
@@ -4532,7 +4532,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>257</v>
@@ -4547,10 +4547,10 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>259</v>
@@ -4582,7 +4582,7 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>262</v>
@@ -4611,10 +4611,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>265</v>
@@ -4628,7 +4628,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>266</v>
@@ -4643,10 +4643,10 @@
         <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>268</v>
@@ -4660,7 +4660,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>269</v>
@@ -4675,10 +4675,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>271</v>
@@ -4692,7 +4692,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>272</v>
@@ -4710,7 +4710,7 @@
         <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>274</v>
@@ -4724,7 +4724,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>275</v>
@@ -4742,7 +4742,7 @@
         <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>277</v>
@@ -4756,7 +4756,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>278</v>
@@ -4774,7 +4774,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>280</v>
@@ -4806,7 +4806,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>283</v>
@@ -4835,10 +4835,10 @@
         <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>286</v>
@@ -4852,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>287</v>
@@ -4867,10 +4867,10 @@
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>289</v>
@@ -4884,7 +4884,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>290</v>
@@ -4899,7 +4899,7 @@
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>292</v>
@@ -4916,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>294</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>298</v>
@@ -4980,7 +4980,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>33</v>
@@ -4992,7 +4992,7 @@
         <v>301</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>90</v>
@@ -5108,7 +5108,7 @@
         <v>303</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>106</v>
@@ -5338,7 +5338,7 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>325</v>
@@ -5434,7 +5434,7 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>334</v>
@@ -5498,7 +5498,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>340</v>
@@ -5512,7 +5512,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>341</v>
@@ -5544,7 +5544,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>344</v>
@@ -5594,7 +5594,7 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>349</v>
@@ -5623,10 +5623,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>352</v>
@@ -5640,7 +5640,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>353</v>
@@ -5658,7 +5658,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>355</v>
@@ -5672,7 +5672,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>356</v>
@@ -5687,10 +5687,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>358</v>
@@ -5704,7 +5704,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>359</v>
@@ -5722,7 +5722,7 @@
         <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5736,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>362</v>
@@ -5751,10 +5751,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5768,7 +5768,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>365</v>
@@ -5786,7 +5786,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5815,10 +5815,10 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5850,7 +5850,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>373</v>
@@ -5864,7 +5864,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>374</v>
@@ -5882,7 +5882,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -5896,7 +5896,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>377</v>
@@ -5914,7 +5914,7 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>379</v>
@@ -5928,7 +5928,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>380</v>
@@ -5946,7 +5946,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>382</v>
@@ -5960,7 +5960,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>383</v>
@@ -5978,7 +5978,7 @@
         <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>385</v>
@@ -5992,7 +5992,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>386</v>
@@ -6010,7 +6010,7 @@
         <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>388</v>
@@ -6042,7 +6042,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>391</v>
@@ -6185,7 +6185,7 @@
         <v>395</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>90</v>
@@ -6511,7 +6511,7 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>428</v>
@@ -6557,7 +6557,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>432</v>
@@ -6575,7 +6575,7 @@
         <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>434</v>
@@ -6589,7 +6589,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>435</v>
@@ -6607,7 +6607,7 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>437</v>
@@ -6639,7 +6639,7 @@
         <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>440</v>
@@ -6668,10 +6668,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
@@ -6685,7 +6685,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>444</v>
@@ -6700,10 +6700,10 @@
         <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>418</v>
+        <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>446</v>
@@ -6717,7 +6717,7 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>447</v>
@@ -6732,10 +6732,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>449</v>
@@ -6749,7 +6749,7 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>450</v>
@@ -6764,10 +6764,10 @@
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>452</v>
@@ -6781,7 +6781,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>453</v>
@@ -6796,10 +6796,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>455</v>
@@ -6813,7 +6813,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>456</v>
@@ -6831,7 +6831,7 @@
         <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>458</v>
@@ -6860,10 +6860,10 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>461</v>
@@ -6895,7 +6895,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>464</v>
@@ -6909,7 +6909,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>465</v>
@@ -6924,10 +6924,10 @@
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>467</v>
@@ -6941,7 +6941,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>468</v>
@@ -6956,10 +6956,10 @@
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>470</v>
@@ -6973,7 +6973,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>471</v>
@@ -6991,7 +6991,7 @@
         <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>473</v>
@@ -7005,7 +7005,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>474</v>
@@ -7037,7 +7037,7 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>477</v>
@@ -7052,10 +7052,10 @@
         <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>479</v>
@@ -7084,10 +7084,10 @@
         <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>482</v>
@@ -7265,7 +7265,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>91</v>
@@ -7445,25 +7445,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7477,19 +7477,19 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>509</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>510</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>121</v>
@@ -7524,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>514</v>
@@ -7602,7 +7602,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>521</v>
@@ -7620,7 +7620,7 @@
         <v>418</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>523</v>
@@ -7634,7 +7634,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>524</v>
@@ -7649,10 +7649,10 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>526</v>
@@ -7684,7 +7684,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>529</v>
@@ -7716,7 +7716,7 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>532</v>
@@ -7730,7 +7730,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>533</v>
@@ -7748,7 +7748,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>535</v>
@@ -7762,7 +7762,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>536</v>
@@ -7780,7 +7780,7 @@
         <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>538</v>
@@ -7794,7 +7794,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>539</v>
@@ -7812,7 +7812,7 @@
         <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>541</v>
@@ -7826,7 +7826,7 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>542</v>
@@ -7844,7 +7844,7 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>544</v>
@@ -7858,7 +7858,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>545</v>
@@ -7873,10 +7873,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>157</v>
+        <v>255</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>547</v>
@@ -7905,10 +7905,10 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>550</v>
@@ -7940,7 +7940,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>553</v>
@@ -7954,7 +7954,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>554</v>
@@ -7972,7 +7972,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>556</v>
@@ -7986,7 +7986,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>557</v>
@@ -8001,10 +8001,10 @@
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>559</v>
@@ -8018,7 +8018,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>560</v>
@@ -8033,10 +8033,10 @@
         <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>562</v>
@@ -8050,7 +8050,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>563</v>
@@ -8065,10 +8065,10 @@
         <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>565</v>
@@ -8082,7 +8082,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>566</v>
@@ -8100,7 +8100,7 @@
         <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>568</v>
@@ -8370,7 +8370,7 @@
         <v>584</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>106</v>
@@ -8408,7 +8408,7 @@
         <v>106</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>588</v>
@@ -8501,10 +8501,10 @@
         <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>597</v>
@@ -8533,10 +8533,10 @@
         <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>600</v>
@@ -8565,10 +8565,10 @@
         <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>603</v>
@@ -8597,7 +8597,7 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>126</v>
@@ -8614,7 +8614,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>607</v>
@@ -8632,7 +8632,7 @@
         <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>609</v>
@@ -8646,7 +8646,7 @@
         <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>610</v>
@@ -8664,7 +8664,7 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>612</v>
@@ -8693,10 +8693,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>615</v>
@@ -8725,10 +8725,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>618</v>
@@ -8742,7 +8742,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>619</v>
@@ -8760,7 +8760,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>621</v>
@@ -8774,7 +8774,7 @@
         <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>622</v>
@@ -8789,10 +8789,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>292</v>
+        <v>198</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>624</v>
@@ -8806,7 +8806,7 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>625</v>
@@ -8821,10 +8821,10 @@
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>627</v>
@@ -8838,7 +8838,7 @@
         <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>628</v>
@@ -8853,10 +8853,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>630</v>
@@ -8870,7 +8870,7 @@
         <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>631</v>
@@ -8885,7 +8885,7 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>292</v>
@@ -8920,7 +8920,7 @@
         <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>636</v>
@@ -8952,7 +8952,7 @@
         <v>106</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>639</v>
@@ -8966,7 +8966,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>640</v>
@@ -8998,7 +8998,7 @@
         <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>643</v>
@@ -9030,7 +9030,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>646</v>
@@ -9062,7 +9062,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>650</v>
@@ -9094,7 +9094,7 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>653</v>
@@ -9112,7 +9112,7 @@
         <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>655</v>
@@ -9356,7 +9356,7 @@
         <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>670</v>
@@ -9420,7 +9420,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>676</v>
@@ -9452,7 +9452,7 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>679</v>
@@ -9481,10 +9481,10 @@
         <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>682</v>
@@ -9516,7 +9516,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>685</v>
@@ -9542,13 +9542,13 @@
         <v>686</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>687</v>
@@ -9577,10 +9577,10 @@
         <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>690</v>
@@ -9609,10 +9609,10 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>693</v>
@@ -9626,7 +9626,7 @@
         <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>694</v>
@@ -9641,10 +9641,10 @@
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>696</v>
@@ -9658,7 +9658,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>697</v>
@@ -9673,10 +9673,10 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>699</v>
@@ -9705,10 +9705,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>702</v>
@@ -9737,10 +9737,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>705</v>
@@ -9754,7 +9754,7 @@
         <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>706</v>
@@ -9772,7 +9772,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>708</v>
@@ -9786,7 +9786,7 @@
         <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>709</v>
@@ -9818,7 +9818,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>712</v>
@@ -9833,10 +9833,10 @@
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>714</v>
@@ -9850,7 +9850,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>715</v>
@@ -9865,10 +9865,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>717</v>
@@ -9882,7 +9882,7 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>718</v>
@@ -9897,10 +9897,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>648</v>
+        <v>292</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>720</v>
@@ -9929,7 +9929,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>292</v>
@@ -9964,7 +9964,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>648</v>
+        <v>292</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>726</v>
@@ -9978,7 +9978,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>727</v>
@@ -9996,7 +9996,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>292</v>
+        <v>648</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>729</v>
@@ -10010,7 +10010,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>730</v>
@@ -10042,7 +10042,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>733</v>
@@ -10060,7 +10060,7 @@
         <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>296</v>
+        <v>648</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>735</v>
@@ -10074,7 +10074,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>736</v>
@@ -10106,7 +10106,7 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>739</v>
@@ -10124,7 +10124,7 @@
         <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>296</v>
+        <v>648</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>741</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -84,501 +84,504 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 6578조 3092억 4574만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>12경 997조 5244억 3604만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>5경 9020조 1939억 6317만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>7경 895조 6692억 2510만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>7경 5026조 3174억 3719만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>6경 9299조 7115억 6231만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>6경 6578조 3092억 4574만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.07</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>6경 9232조 7667억 1784만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3경 27조 8635억 7445만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6493조 5045억 7772만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5860조 1812억 2503만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3106조 9258억 9914만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2011조 4544억 3476만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1007조 3178억 5658만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>874조 5211억 9379만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>869조 5677억 141만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>684조 4401억 9646만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>481조 5847억 7403만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>379조 5440억 9162만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>366조 6787억 5438만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>334조 4614억 9803만</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>275조 8357억 446만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>11경 9267조 3727억 8819만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 8868조 2988억 6543만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>7경 895조 6692억 2510만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>273조 8981억 703만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>266조 8078억 6673만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>254조 2629억 9000만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>239조 5598억 9073만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>186조 7933억 7887만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>143조 3408억 6701만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>7경 5026조 3174억 3719만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>6경 9162조 9519억 932만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>6경 9232조 7667억 1784만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>3경 27조 8635억 7445만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6493조 5045억 7772만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5860조 1812억 2503만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3106조 9258억 9914만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2011조 4544억 3476만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1007조 3178억 5658만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>874조 5211억 9379만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>869조 5677억 141만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>684조 4401억 9646만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>481조 5847억 7403만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>379조 5440억 9162만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>366조 6787억 5438만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>334조 4614억 9803만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>275조 8357억 446만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>273조 8981억 703만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>266조 8078억 6673만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>254조 2629억 9000만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>239조 5598억 9073만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>186조 7933억 7887만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>143조 3408억 6701만</t>
-  </si>
-  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -633,9 +636,6 @@
     <t>55조 7049억 3694만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>8경 4605조 5179억 3801만</t>
+    <t>8경 6327조 6013억 9186만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -783,6 +783,15 @@
     <t>180조 1511억 6313만</t>
   </si>
   <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>125조 4342억 3651만</t>
+  </si>
+  <si>
     <t>땩콩</t>
   </si>
   <si>
@@ -813,15 +822,6 @@
     <t>122조 668억 9161만</t>
   </si>
   <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>119조 7499억 1993만</t>
-  </si>
-  <si>
     <t>봄녘</t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>30조 8752억 547만</t>
+    <t>33조 3902억 7692만</t>
   </si>
   <si>
     <t>빠나쨩</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%84%AC</t>
   </si>
   <si>
-    <t>2375조 8543억 1894만</t>
+    <t>2507조 4446억 8062만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -990,7 +990,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
   </si>
   <si>
-    <t>1775조 5915억 3045만</t>
+    <t>1791조 9945억 7647만</t>
   </si>
   <si>
     <t>쑥국</t>
@@ -1053,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
   </si>
   <si>
-    <t>348조 9207억 6037만</t>
+    <t>349조 435억 3882만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -1062,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
   </si>
   <si>
-    <t>254조 3992억 7562만</t>
+    <t>254조 6182억 4665만</t>
   </si>
   <si>
     <t>겸찰</t>
@@ -1098,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
   </si>
   <si>
-    <t>190조 2848억 2308만</t>
+    <t>191조 6596억 3475만</t>
   </si>
   <si>
     <t>키은</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>66조 3840억 5859만</t>
+    <t>68조 277억 3204만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
   </si>
   <si>
-    <t>59조 2713억 6623만</t>
+    <t>59조 8128억 2165만</t>
   </si>
   <si>
     <t>까사PC</t>
@@ -1788,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
   </si>
   <si>
-    <t>1190조 6095억 7843만</t>
+    <t>1220조 1789억 2840만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>15조 5318억 9821만</t>
+    <t>15조 5820억 6189만</t>
   </si>
   <si>
     <t>킴밍끼</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>10조 2452억 7329만</t>
+    <t>10조 3519억 8814만</t>
   </si>
   <si>
     <t>먕겜</t>
@@ -2638,7 +2638,7 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="50.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -3519,16 +3519,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -3540,7 +3540,7 @@
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3551,7 +3551,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>158</v>
@@ -3743,16 +3743,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -3764,7 +3764,7 @@
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3775,16 +3775,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -3796,7 +3796,7 @@
         <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3807,28 +3807,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3848,19 +3848,19 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3871,16 +3871,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -3889,10 +3889,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3903,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>201</v>
@@ -3953,7 +3953,7 @@
         <v>160</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>208</v>
@@ -3985,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>211</v>
@@ -4483,10 +4483,10 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>252</v>
@@ -4515,13 +4515,13 @@
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4535,22 +4535,22 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>259</v>
@@ -4564,7 +4564,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>260</v>
@@ -4579,10 +4579,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>262</v>
@@ -4596,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>263</v>
@@ -4614,7 +4614,7 @@
         <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>265</v>
@@ -4646,7 +4646,7 @@
         <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>268</v>
@@ -4710,7 +4710,7 @@
         <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>274</v>
@@ -4774,7 +4774,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>280</v>
@@ -4788,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>281</v>
@@ -4820,7 +4820,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>284</v>
@@ -4852,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>287</v>
@@ -4899,7 +4899,7 @@
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>292</v>
@@ -4916,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>294</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>298</v>
@@ -4992,7 +4992,7 @@
         <v>301</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>90</v>
@@ -5108,7 +5108,7 @@
         <v>303</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>106</v>
@@ -5576,7 +5576,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>347</v>
@@ -5608,7 +5608,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>350</v>
@@ -5754,7 +5754,7 @@
         <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5800,7 +5800,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>368</v>
@@ -5818,7 +5818,7 @@
         <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5832,7 +5832,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>371</v>
@@ -5864,7 +5864,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>374</v>
@@ -5882,7 +5882,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -5914,7 +5914,7 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>379</v>
@@ -5928,7 +5928,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>380</v>
@@ -5946,7 +5946,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>382</v>
@@ -5960,7 +5960,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>383</v>
@@ -6185,7 +6185,7 @@
         <v>395</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>90</v>
@@ -6621,7 +6621,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>438</v>
@@ -6653,7 +6653,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>441</v>
@@ -6668,10 +6668,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
@@ -6703,7 +6703,7 @@
         <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>446</v>
@@ -6767,7 +6767,7 @@
         <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>452</v>
@@ -6799,7 +6799,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>455</v>
@@ -6831,7 +6831,7 @@
         <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>458</v>
@@ -6845,7 +6845,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>459</v>
@@ -6863,7 +6863,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>461</v>
@@ -6877,7 +6877,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>462</v>
@@ -6895,7 +6895,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>464</v>
@@ -6909,7 +6909,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>465</v>
@@ -6927,7 +6927,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>467</v>
@@ -6973,7 +6973,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>471</v>
@@ -6991,7 +6991,7 @@
         <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>473</v>
@@ -7005,7 +7005,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>474</v>
@@ -7265,7 +7265,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>91</v>
@@ -7454,7 +7454,7 @@
         <v>507</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>84</v>
@@ -7649,7 +7649,7 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -7666,7 +7666,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>527</v>
@@ -7698,7 +7698,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>530</v>
@@ -7812,7 +7812,7 @@
         <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>541</v>
@@ -7844,7 +7844,7 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>544</v>
@@ -7873,10 +7873,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>547</v>
@@ -7890,7 +7890,7 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>548</v>
@@ -7908,7 +7908,7 @@
         <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>550</v>
@@ -7922,7 +7922,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>551</v>
@@ -7940,7 +7940,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>553</v>
@@ -7954,7 +7954,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>554</v>
@@ -8018,7 +8018,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>560</v>
@@ -8050,7 +8050,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>563</v>
@@ -8370,7 +8370,7 @@
         <v>584</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>106</v>
@@ -8536,7 +8536,7 @@
         <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>600</v>
@@ -8664,7 +8664,7 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>612</v>
@@ -8678,7 +8678,7 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>613</v>
@@ -8693,10 +8693,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>615</v>
@@ -8710,7 +8710,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>616</v>
@@ -8725,10 +8725,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>618</v>
@@ -8760,7 +8760,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>621</v>
@@ -8792,7 +8792,7 @@
         <v>160</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>624</v>
@@ -8856,7 +8856,7 @@
         <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>630</v>
@@ -8885,7 +8885,7 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>292</v>
@@ -8902,7 +8902,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>634</v>
@@ -8934,7 +8934,7 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>637</v>
@@ -8966,7 +8966,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>640</v>
@@ -9030,7 +9030,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>646</v>
@@ -9062,7 +9062,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>650</v>
@@ -9452,7 +9452,7 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>679</v>
@@ -9484,7 +9484,7 @@
         <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>682</v>
@@ -9516,7 +9516,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>685</v>
@@ -9542,13 +9542,13 @@
         <v>686</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>687</v>
@@ -9580,7 +9580,7 @@
         <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>690</v>
@@ -9612,7 +9612,7 @@
         <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>693</v>
@@ -9690,7 +9690,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>700</v>
@@ -9722,7 +9722,7 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>703</v>
@@ -9740,7 +9740,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>705</v>
@@ -9914,7 +9914,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>721</v>
@@ -9929,7 +9929,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>292</v>
@@ -9946,7 +9946,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>724</v>
@@ -9978,7 +9978,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>727</v>
@@ -10042,7 +10042,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>733</v>
@@ -10074,7 +10074,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>736</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -84,159 +84,159 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 9526조 6385억 8996만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>12경 997조 5244억 3604만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>5경 9020조 1939억 6317만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>7경 895조 6692억 2510만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>7경 5026조 3174억 3719만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>6경 9299조 7115억 6231만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>6경 6578조 3092억 4574만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.07</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>12경 997조 5244억 3604만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 9020조 1939억 6317만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>7경 895조 6692억 2510만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>7경 5026조 3174억 3719만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>6경 9299조 7115억 6231만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>Lv.7</t>
   </si>
   <si>
@@ -633,7 +633,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>55조 7049억 3694만</t>
+    <t>55조 8372억 8110만</t>
   </si>
   <si>
     <t>악의꽃</t>
@@ -3839,7 +3839,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>23</v>
@@ -3871,7 +3871,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>197</v>
@@ -3903,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>201</v>
@@ -4884,7 +4884,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>290</v>
@@ -4916,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>294</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>298</v>
@@ -5896,7 +5896,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>377</v>
@@ -5928,7 +5928,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>380</v>
@@ -5960,7 +5960,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>383</v>
@@ -6941,7 +6941,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>468</v>
@@ -6973,7 +6973,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>471</v>
@@ -7005,7 +7005,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>474</v>
@@ -7986,7 +7986,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>557</v>
@@ -8018,7 +8018,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>560</v>
@@ -8050,7 +8050,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>563</v>
@@ -8998,7 +8998,7 @@
         <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>643</v>
@@ -9030,7 +9030,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>646</v>
@@ -9062,7 +9062,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>650</v>
@@ -10010,7 +10010,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>730</v>
@@ -10042,7 +10042,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>733</v>
@@ -10074,7 +10074,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>736</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -10,8 +10,8 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
     <sheet name="이콩" sheetId="3" r:id="rId3"/>
-    <sheet name="고점" sheetId="4" r:id="rId4"/>
-    <sheet name="딸기키우기" sheetId="5" r:id="rId5"/>
+    <sheet name="딸기키우기" sheetId="4" r:id="rId4"/>
+    <sheet name="고점" sheetId="5" r:id="rId5"/>
     <sheet name="LUXURY" sheetId="6" r:id="rId6"/>
     <sheet name="싸이월드" sheetId="7" r:id="rId7"/>
     <sheet name="라때는말이야" sheetId="8" r:id="rId8"/>
@@ -19,10 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">고점!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">딸기키우기!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">딸기키우기!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">이콩!$A$1:$J$31</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="752">
   <si>
     <t>guild_name</t>
   </si>
@@ -93,64 +93,85 @@
     <t>Lv.9</t>
   </si>
   <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 8783조 8206억 2005만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.10</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>14경 2496조 8142억 9932만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>6경 1458조 5611억 4628만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>29명</t>
   </si>
   <si>
-    <t>6경 8421조 8622억 5527만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.09</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>13경 8257조 8135억 3849만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>7경 9666조 6535억 6776만</t>
+    <t>8경 764조 1355억 1620만</t>
   </si>
   <si>
     <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
@@ -159,27 +180,6 @@
     <t>루팡잉</t>
   </si>
   <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 9741조 7729억 2375만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
     <t>LUXURY</t>
   </si>
   <si>
@@ -192,7 +192,7 @@
     <t>26</t>
   </si>
   <si>
-    <t>7경 1399조 3163억 8270만</t>
+    <t>7경 1608조 4818억 5870만</t>
   </si>
   <si>
     <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
@@ -216,7 +216,7 @@
     <t>Lv.11</t>
   </si>
   <si>
-    <t>7경 703조 3254억 5852만</t>
+    <t>7경 1108조 4008억 3062만</t>
   </si>
   <si>
     <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
@@ -237,7 +237,7 @@
     <t>25</t>
   </si>
   <si>
-    <t>7경 6683조 3585억 8001만</t>
+    <t>7경 6902조 3808억 4436만</t>
   </si>
   <si>
     <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
@@ -336,7 +336,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>6968조 104억 2396만</t>
+    <t>7134조 202억 6943만</t>
   </si>
   <si>
     <t>5</t>
@@ -465,6 +465,18 @@
     <t>13</t>
   </si>
   <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>376조 4639억 8378만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>프리프리</t>
   </si>
   <si>
@@ -474,18 +486,6 @@
     <t>366조 6787억 5438만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>341조 7670억 4182만</t>
-  </si>
-  <si>
     <t>뽀삐스</t>
   </si>
   <si>
@@ -504,7 +504,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>292조 5070억 9227만</t>
+    <t>306조 242억 4016만</t>
   </si>
   <si>
     <t>17</t>
@@ -519,7 +519,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>281조 4414억 8910만</t>
+    <t>283조 2299억 3363만</t>
   </si>
   <si>
     <t>18</t>
@@ -531,7 +531,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>267조 6625억 7984만</t>
+    <t>268조 6339억 8298만</t>
   </si>
   <si>
     <t>19</t>
@@ -573,13 +573,28 @@
     <t>22</t>
   </si>
   <si>
+    <t>트라이던트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>120조 4334억 1795만</t>
+  </si>
+  <si>
     <t>루넨</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>104조 1545억 8903만</t>
+    <t>111조 7258억 7736만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -588,10 +603,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>77조 3430억 5082만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>79조 4152억 1967만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -603,7 +615,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>77조 668억 4804만</t>
+    <t>78조 6990억 3251만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -612,10 +624,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>72조 3341억 9706만</t>
+    <t>74조 115억 3375만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -624,7 +633,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>59조 7773억 9141만</t>
+    <t>65조 6418억 239만</t>
   </si>
   <si>
     <t>악의꽃</t>
@@ -639,16 +648,16 @@
     <t>53조 811억 6540만</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>포뇨야</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
   </si>
   <si>
-    <t>47조 2211억 9311만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>48조 9494억 4507만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -657,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>43조 5213억 2613만</t>
+    <t>47조 5168억 4869만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -669,7 +678,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>9경 9698조 8347억 5091만</t>
+    <t>10경 1168조 1030억 2275만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -681,7 +690,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>2경 4945조 3179억 1766만</t>
+    <t>2경 7463조 6748억 47만</t>
   </si>
   <si>
     <t>실민</t>
@@ -690,7 +699,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>2779조 4631억 118만</t>
+    <t>3014조 9142억 183만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -699,7 +708,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>2744조 8360억 6186만</t>
+    <t>2758조 7891억 2624만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -744,7 +753,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>726조 4509억 8439만</t>
+    <t>744조 1717억 9089만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -753,7 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>680조 1657억 2733만</t>
+    <t>681조 4769억 8567만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -762,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
   </si>
   <si>
-    <t>237조 5153억 3073만</t>
+    <t>238조 299억 1925만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -771,7 +780,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>198조 6656억 3811만</t>
+    <t>203조 3134억 1121만</t>
   </si>
   <si>
     <t>런닝쨩</t>
@@ -780,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
   </si>
   <si>
-    <t>170조 5890억 1489만</t>
+    <t>170조 8260억 4954만</t>
   </si>
   <si>
     <t>경특</t>
@@ -789,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
   </si>
   <si>
-    <t>141조 8303억 9284만</t>
+    <t>142조 1893억 9084만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -801,7 +810,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>133조 7889억 4681만</t>
+    <t>136조 4796억 3878만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -810,7 +819,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>129조 4764억 6219만</t>
+    <t>130조 1969억 7479만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -822,22 +831,31 @@
     <t>123조 1135억 2578만</t>
   </si>
   <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>109조 9622억 713만</t>
+  </si>
+  <si>
     <t>봄녘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>103조 2402억 1093만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>89조 663억 7122만</t>
+    <t>105조 9342억 1993만</t>
+  </si>
+  <si>
+    <t>벨히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
+  </si>
+  <si>
+    <t>83조 6675억 1656만</t>
   </si>
   <si>
     <t>에망</t>
@@ -849,16 +867,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>76조 4776억 4320만</t>
-  </si>
-  <si>
-    <t>벨히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
-  </si>
-  <si>
-    <t>75조 6326억 6046만</t>
+    <t>78조 3833억 5577만</t>
   </si>
   <si>
     <t>만듀쨩</t>
@@ -867,7 +876,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
   </si>
   <si>
-    <t>50조 5104억 822만</t>
+    <t>52조 4392억 439만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>38조 6842억 289만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -879,15 +897,6 @@
     <t>37조 7184억 1518만</t>
   </si>
   <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>35조 7282억 8133만</t>
-  </si>
-  <si>
     <t>빠나쨩</t>
   </si>
   <si>
@@ -906,7 +915,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>14조 8268억 8011만</t>
+    <t>15조 3154억 124만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -918,7 +927,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>7조 3810억 465만</t>
+    <t>7조 6323억 7685만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -927,25 +936,292 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
+    <t>5조 1906억 6537만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
-    <t>5조 989억 2129만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>2조 3473억 2545만</t>
+    <t>2조 8174억 6097만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>1조 3870억 7073만</t>
+    <t>1조 3930억 395만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
+  </si>
+  <si>
+    <t>4경 1795조 7320억 7609만</t>
+  </si>
+  <si>
+    <t>쥬정뱅이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5603조 1838억 5505만</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2379조 1030억 8187만</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>2276조 6706억 764만</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>2043조 9070억 2827만</t>
+  </si>
+  <si>
+    <t>쑥국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>1446조 6204억 9719만</t>
+  </si>
+  <si>
+    <t>냉도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
+  </si>
+  <si>
+    <t>656조 9558억 6537만</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>572조 672억 5261만</t>
+  </si>
+  <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>469조 1275억 6045만</t>
+  </si>
+  <si>
+    <t>엔젤가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>450조 8886억 9927만</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>418조 8762억 484만</t>
+  </si>
+  <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>390조 249억 8316만</t>
+  </si>
+  <si>
+    <t>피치에이드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>385조 3263억 5548만</t>
+  </si>
+  <si>
+    <t>핫장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>349조 7498억 7099만</t>
+  </si>
+  <si>
+    <t>키은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>252조 8340억 5412만</t>
+  </si>
+  <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>222조 1786억 5343만</t>
+  </si>
+  <si>
+    <t>헛점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
+  </si>
+  <si>
+    <t>208조 2578억 2132만</t>
+  </si>
+  <si>
+    <t>개점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
+  </si>
+  <si>
+    <t>202조 9796억 3764만</t>
+  </si>
+  <si>
+    <t>쵸꼬님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>201조 7265억 7269만</t>
+  </si>
+  <si>
+    <t>사마련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>169조 6095억 1023만</t>
+  </si>
+  <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>155조 4791억 1909만</t>
+  </si>
+  <si>
+    <t>앨리스빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>135조 9349억 5864만</t>
+  </si>
+  <si>
+    <t>챠재범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
+  </si>
+  <si>
+    <t>123조 642억 8896만</t>
+  </si>
+  <si>
+    <t>81학찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>122조 3620억 6338만</t>
+  </si>
+  <si>
+    <t>머쓰윽타드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
+  </si>
+  <si>
+    <t>116조 2310억 4300만</t>
+  </si>
+  <si>
+    <t>핫딜만삼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
+  </si>
+  <si>
+    <t>94조 8416억 4398만</t>
+  </si>
+  <si>
+    <t>핫두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
+  </si>
+  <si>
+    <t>84조 5926억 3781만</t>
+  </si>
+  <si>
+    <t>샤갈츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
+  </si>
+  <si>
+    <t>79조 7546억 4080만</t>
+  </si>
+  <si>
+    <t>까사PC</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%82%ACPC</t>
+  </si>
+  <si>
+    <t>35조 6114억 3084만</t>
+  </si>
+  <si>
+    <t>딸기비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>19조 3261억 8612만</t>
   </si>
   <si>
     <t>THE끌림</t>
@@ -972,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>1경 4038조 7073억 2011만</t>
+    <t>1경 4141조 129억 8162만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -981,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>4536조 29억 3617만</t>
+    <t>4926조 4952억 4658만</t>
   </si>
   <si>
     <t>픠즈</t>
@@ -993,6 +1269,15 @@
     <t>1334조 8600억 794만</t>
   </si>
   <si>
+    <t>환불한너잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1241조 5819억 5194만</t>
+  </si>
+  <si>
     <t>S2베코</t>
   </si>
   <si>
@@ -1002,13 +1287,22 @@
     <t>1240조 2038억 950만</t>
   </si>
   <si>
-    <t>환불한너잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
-  </si>
-  <si>
-    <t>994조 1109억 7955만</t>
+    <t>널비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
+  </si>
+  <si>
+    <t>999조 3355억 8864만</t>
+  </si>
+  <si>
+    <t>아투피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
+  </si>
+  <si>
+    <t>965조 5660억 7598만</t>
   </si>
   <si>
     <t>똔똔잉</t>
@@ -1017,16 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>898조 3976억 4843만</t>
-  </si>
-  <si>
-    <t>아투피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
-  </si>
-  <si>
-    <t>842조 9789억 1242만</t>
+    <t>910조 1406억 1458만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
@@ -1035,22 +1320,13 @@
     <t>834조 3899억 7972만</t>
   </si>
   <si>
-    <t>널비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
-  </si>
-  <si>
-    <t>808조 2793억 4877만</t>
-  </si>
-  <si>
     <t>뷰질</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
   </si>
   <si>
-    <t>402조 4984억 6025만</t>
+    <t>404조 1071억 5892만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1059,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
   </si>
   <si>
-    <t>299조 4880억 1566만</t>
+    <t>302조 4915억 5376만</t>
   </si>
   <si>
     <t>순서교체</t>
@@ -1071,7 +1347,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>295조 9억 3640만</t>
+    <t>295조 2263억 5709만</t>
   </si>
   <si>
     <t>김천아재</t>
@@ -1080,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>151조 7185억 7427만</t>
+    <t>152조 1542억 3220만</t>
   </si>
   <si>
     <t>무썬</t>
@@ -1089,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
   </si>
   <si>
-    <t>136조 6011억 3021만</t>
+    <t>137조 5795억 3096만</t>
   </si>
   <si>
     <t>약할뻔</t>
@@ -1098,7 +1374,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
   </si>
   <si>
-    <t>119조 3807억 5743만</t>
+    <t>124조 879억 9510만</t>
+  </si>
+  <si>
+    <t>성칙이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>117조 3939억 6205만</t>
   </si>
   <si>
     <t>맥맥</t>
@@ -1110,22 +1395,13 @@
     <t>116조 5913억 6566만</t>
   </si>
   <si>
-    <t>성칙이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>107조 7661억 6692만</t>
-  </si>
-  <si>
     <t>kiaer</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>73조 3391억 7529만</t>
+    <t>75조 7068억 4710만</t>
   </si>
   <si>
     <t>돌아온홍굴이</t>
@@ -1134,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>63조 2574억 2846만</t>
+    <t>67조 267억 1700만</t>
   </si>
   <si>
     <t>숔숔숔숔</t>
@@ -1143,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>57조 8869억 2917만</t>
+    <t>62조 6511억 3357만</t>
   </si>
   <si>
     <t>안재똥</t>
@@ -1197,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>15조 8463억 7569만</t>
+    <t>16조 1850억 9656만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1209,264 +1485,6 @@
     <t>14조 7080억 4787만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
-  </si>
-  <si>
-    <t>4경 620조 8178억 2657만</t>
-  </si>
-  <si>
-    <t>쥬정뱅이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5602조 2913억 7655만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2379조 1030억 8187만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>2272조 2135억 5342만</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>1974조 1472억 8009만</t>
-  </si>
-  <si>
-    <t>쑥국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>1443조 6813억 5226만</t>
-  </si>
-  <si>
-    <t>냉도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
-  </si>
-  <si>
-    <t>656조 9558억 6537만</t>
-  </si>
-  <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>558조 1671억 2929만</t>
-  </si>
-  <si>
-    <t>엔젤가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>450조 8886억 9927만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>445조 1430억 4567만</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>410조 4353억 8122만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>389조 8924억 3403만</t>
-  </si>
-  <si>
-    <t>핫장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>348조 4135억 7489만</t>
-  </si>
-  <si>
-    <t>키은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>252조 4323억 5228만</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>220조 5596억 5079만</t>
-  </si>
-  <si>
-    <t>개점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
-  </si>
-  <si>
-    <t>202조 8194억 2263만</t>
-  </si>
-  <si>
-    <t>쵸꼬님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>200조 6649억 52만</t>
-  </si>
-  <si>
-    <t>헛점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
-  </si>
-  <si>
-    <t>196조 6153억 456만</t>
-  </si>
-  <si>
-    <t>사마련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>169조 6095억 1023만</t>
-  </si>
-  <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>155조 4791억 1909만</t>
-  </si>
-  <si>
-    <t>앨리스빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>135조 9349억 5864만</t>
-  </si>
-  <si>
-    <t>챠재범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
-  </si>
-  <si>
-    <t>123조 642억 8896만</t>
-  </si>
-  <si>
-    <t>81학찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>122조 3620억 6338만</t>
-  </si>
-  <si>
-    <t>머쓰윽타드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
-  </si>
-  <si>
-    <t>112조 4402억 4369만</t>
-  </si>
-  <si>
-    <t>핫딜만삼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
-  </si>
-  <si>
-    <t>94조 2534억 2073만</t>
-  </si>
-  <si>
-    <t>샤갈츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
-  </si>
-  <si>
-    <t>79조 7546억 4080만</t>
-  </si>
-  <si>
-    <t>핫두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
-  </si>
-  <si>
-    <t>68조 8958억 4155만</t>
-  </si>
-  <si>
-    <t>까사PC</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%82%ACPC</t>
-  </si>
-  <si>
-    <t>35조 6114억 3084만</t>
-  </si>
-  <si>
-    <t>딸기비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>19조 1251억 7441만</t>
-  </si>
-  <si>
     <t>가숭혁</t>
   </si>
   <si>
@@ -1488,7 +1506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>4532조 8060억 8665만</t>
+    <t>4563조 183억 1982만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1515,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>1516조 4618억 7308만</t>
+    <t>1543조 6108억 6622만</t>
   </si>
   <si>
     <t>26길초</t>
@@ -1524,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>1306조 2157억 7265만</t>
+    <t>1329조 3467억 5056만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1542,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>1046조 8702억 9456만</t>
+    <t>1048조 7771억 8533만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1569,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>721조 2407억 8538만</t>
+    <t>747조 4600억 3160만</t>
   </si>
   <si>
     <t>임승민</t>
@@ -1578,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>505조 5101억 2486만</t>
+    <t>512조 7605억 5869만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1587,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>377조 597억 9715만</t>
+    <t>387조 1028억 3085만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1605,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>147조 4284억 2581만</t>
+    <t>181조 3451억 8305만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1614,7 +1632,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
   </si>
   <si>
-    <t>93조 3399억 7742만</t>
+    <t>97조 9418억 9550만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>79조 5854억 7226만</t>
   </si>
   <si>
     <t>26퐝바</t>
@@ -1623,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>72조 9068억 5514만</t>
+    <t>78조 6332억 1246만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1635,22 +1662,13 @@
     <t>71조 9870억 7033만</t>
   </si>
   <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>65조 5798억 3189만</t>
-  </si>
-  <si>
     <t>아모르파티퀘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>64조 5735억 8175만</t>
+    <t>66조 1962억 7097만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1659,7 +1677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>47조 2350억 5392만</t>
+    <t>47조 7632억 1862만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1668,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>40조 3196억 2618만</t>
+    <t>43조 8601억 7965만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1680,6 +1698,15 @@
     <t>38조 9035억 6838만</t>
   </si>
   <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>38조 8993억 8861만</t>
+  </si>
+  <si>
     <t>최씨용</t>
   </si>
   <si>
@@ -1695,16 +1722,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>28조 5477억 2207만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>27조 6163억 4636만</t>
+    <t>29조 2909억 3365만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>25조 3702억 7718만</t>
   </si>
   <si>
     <t>라흐S2</t>
@@ -1716,15 +1743,6 @@
     <t>22조 7225억 1066만</t>
   </si>
   <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>18조 849억 4416만</t>
-  </si>
-  <si>
     <t>귬스파파</t>
   </si>
   <si>
@@ -1776,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>1611조 3444억 7846만</t>
+    <t>1959조 5150억 4135만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
@@ -1791,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>1200조 3517억 6107만</t>
+    <t>1202조 1417억 6795만</t>
   </si>
   <si>
     <t>윤돌이굴돌이</t>
@@ -1836,7 +1854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
   </si>
   <si>
-    <t>231조 4022억 5454만</t>
+    <t>256조 2963억 2403만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1845,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>134조 9581억 8389만</t>
+    <t>135조 5031억 6663만</t>
   </si>
   <si>
     <t>김컁구</t>
@@ -1854,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>121조 1466억 9264만</t>
+    <t>121조 4076억 2356만</t>
   </si>
   <si>
     <t>킴술하</t>
@@ -1863,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%88%A0%ED%95%98</t>
   </si>
   <si>
-    <t>107조 4309억 5168만</t>
+    <t>109조 901억 6154만</t>
   </si>
   <si>
     <t>우당탕탼</t>
@@ -1890,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
   </si>
   <si>
-    <t>56조 5335억 6102만</t>
+    <t>62조 9785억 2925만</t>
   </si>
   <si>
     <t>사철화</t>
@@ -1899,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
   </si>
   <si>
-    <t>39조 9532억 706만</t>
+    <t>57조 9163억 4863만</t>
   </si>
   <si>
     <t>붕붕월드</t>
@@ -1908,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
   </si>
   <si>
-    <t>39조 3243억 1890만</t>
+    <t>39조 4507억 2328만</t>
   </si>
   <si>
     <t>얼음조아</t>
@@ -1920,13 +1938,22 @@
     <t>31조 1704억 5827만</t>
   </si>
   <si>
+    <t>커피숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
+  </si>
+  <si>
+    <t>23조 8781억 4901만</t>
+  </si>
+  <si>
     <t>Subaru</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Subaru</t>
   </si>
   <si>
-    <t>22조 8861억 4764만</t>
+    <t>22조 9229억 3625만</t>
   </si>
   <si>
     <t>뵤으</t>
@@ -1935,16 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
   </si>
   <si>
-    <t>21조 6737억 3130만</t>
-  </si>
-  <si>
-    <t>커피숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
-  </si>
-  <si>
-    <t>20조 7109억 6991만</t>
+    <t>22조 2555억 6247만</t>
   </si>
   <si>
     <t>도시리</t>
@@ -1953,7 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>20조 6586억 1157만</t>
+    <t>21조 9701억 9383만</t>
   </si>
   <si>
     <t>57년김춘배</t>
@@ -1962,7 +1980,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>16조 7877억 8967만</t>
+    <t>18조 586억 1754만</t>
   </si>
   <si>
     <t>킴밍끼</t>
@@ -2019,7 +2037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 425조 7486억 8504만</t>
+    <t>2경 1290조 7233억 4187만</t>
   </si>
   <si>
     <t>메키멍</t>
@@ -2028,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
   </si>
   <si>
-    <t>2644조 848억 4344만</t>
+    <t>2663조 8506억 3319만</t>
   </si>
   <si>
     <t>켘켘3</t>
@@ -2055,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
   </si>
   <si>
-    <t>659조 3993억 1261만</t>
+    <t>687조 4283억 4886만</t>
   </si>
   <si>
     <t>인두겁</t>
@@ -2064,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>420조 7791억 5709만</t>
+    <t>433조 1261억 7818만</t>
   </si>
   <si>
     <t>소잦ol</t>
@@ -2073,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>199조 1074억 9721만</t>
+    <t>202조 2047억 3526만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2082,7 +2100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>189조 9325억 5363만</t>
+    <t>191조 452억 8026만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2091,13 +2109,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%9D%98%EA%B8%B0%EC%9A%B4</t>
   </si>
   <si>
-    <t>150조 6746억 98만</t>
+    <t>151조 6081억 6191만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>119조 7863억 975만</t>
+    <t>120조 3286억 9597만</t>
   </si>
   <si>
     <t>포근한소리</t>
@@ -2106,7 +2124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
   </si>
   <si>
-    <t>67조 5855억 2149만</t>
+    <t>69조 2045억 3518만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2115,7 +2133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
   </si>
   <si>
-    <t>65조 9488억 2923만</t>
+    <t>67조 7484억 4106만</t>
   </si>
   <si>
     <t>본분</t>
@@ -2124,7 +2142,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%B6%84</t>
   </si>
   <si>
-    <t>37조 4562억 1350만</t>
+    <t>41조 1436억 8059만</t>
+  </si>
+  <si>
+    <t>잘스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>39조 4627억 4626만</t>
   </si>
   <si>
     <t>머수킹</t>
@@ -2133,16 +2160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>34조 180억 3529만</t>
-  </si>
-  <si>
-    <t>잘스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>32조 6623억 7594만</t>
+    <t>34조 6113억 3761만</t>
   </si>
   <si>
     <t>못스제</t>
@@ -2187,7 +2205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>17조 8503억 879만</t>
+    <t>19조 561억 9267만</t>
   </si>
   <si>
     <t>1조투력찍었던</t>
@@ -2196,7 +2214,16 @@
     <t>https://mgf.gg/contents/character.php?n=1%EC%A1%B0%ED%88%AC%EB%A0%A5%EC%B0%8D%EC%97%88%EB%8D%98</t>
   </si>
   <si>
-    <t>16조 8516억 4673만</t>
+    <t>17조 2502억 868만</t>
+  </si>
+  <si>
+    <t>탕화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
+  </si>
+  <si>
+    <t>16조 2456억 440만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2217,15 +2244,6 @@
     <t>14조 2938억 3283만</t>
   </si>
   <si>
-    <t>탕화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
-  </si>
-  <si>
-    <t>12조 626억 7380만</t>
-  </si>
-  <si>
     <t>진우정</t>
   </si>
   <si>
@@ -2250,7 +2268,16 @@
     <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
   </si>
   <si>
-    <t>7조 585억 8416만</t>
+    <t>7조 686억 9139만</t>
+  </si>
+  <si>
+    <t>킴카</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
+  </si>
+  <si>
+    <t>6조 5435억 1670만</t>
   </si>
   <si>
     <t>가겠네</t>
@@ -2260,15 +2287,6 @@
   </si>
   <si>
     <t>6조 3980억 9233만</t>
-  </si>
-  <si>
-    <t>킴카</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
-  </si>
-  <si>
-    <t>5조 7917억 9534만</t>
   </si>
 </sst>
 </file>
@@ -2755,16 +2773,16 @@
         <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2772,40 +2790,40 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2813,31 +2831,31 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>46</v>
@@ -2878,7 +2896,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>53</v>
@@ -2919,7 +2937,7 @@
         <v>60</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>61</v>
@@ -2960,7 +2978,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>68</v>
@@ -2992,7 +3010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3156,7 +3174,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>101</v>
@@ -3441,10 +3459,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>146</v>
@@ -3473,7 +3491,7 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>111</v>
@@ -3729,13 +3747,13 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3746,28 +3764,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3778,22 +3796,22 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>141</v>
@@ -3825,10 +3843,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>194</v>
@@ -3845,22 +3863,22 @@
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>197</v>
@@ -3877,25 +3895,25 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3909,22 +3927,22 @@
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>204</v>
@@ -3953,10 +3971,10 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>208</v>
@@ -3965,8 +3983,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3997,6 +4047,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4013,7 +4064,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4057,13 +4108,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -4072,10 +4123,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4089,13 +4140,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -4104,10 +4155,10 @@
         <v>116</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4121,13 +4172,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -4139,7 +4190,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4153,25 +4204,25 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4185,13 +4236,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -4203,7 +4254,7 @@
         <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4217,13 +4268,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -4232,10 +4283,10 @@
         <v>131</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4249,13 +4300,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -4267,7 +4318,7 @@
         <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4281,13 +4332,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -4299,7 +4350,7 @@
         <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4313,13 +4364,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -4331,7 +4382,7 @@
         <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4345,13 +4396,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -4363,7 +4414,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4377,13 +4428,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -4395,7 +4446,7 @@
         <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4409,13 +4460,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -4427,7 +4478,7 @@
         <v>132</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4441,25 +4492,25 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4473,13 +4524,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -4488,10 +4539,10 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4505,25 +4556,25 @@
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4537,13 +4588,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -4552,10 +4603,10 @@
         <v>161</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4569,13 +4620,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -4587,7 +4638,7 @@
         <v>141</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4601,25 +4652,25 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4633,25 +4684,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4665,13 +4716,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -4680,10 +4731,10 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4697,13 +4748,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -4712,10 +4763,10 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4729,13 +4780,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -4744,10 +4795,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4758,28 +4809,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4790,28 +4841,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4825,13 +4876,13 @@
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -4840,10 +4891,10 @@
         <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4857,25 +4908,25 @@
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4889,13 +4940,13 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -4904,10 +4955,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4921,13 +4972,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -4936,10 +4987,10 @@
         <v>116</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4953,13 +5004,13 @@
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -4968,10 +5019,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4982,28 +5033,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5049,7 +5100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5096,31 +5147,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5128,19 +5179,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -5149,10 +5200,10 @@
         <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>215</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5160,31 +5211,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5192,19 +5243,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -5213,10 +5264,10 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5224,31 +5275,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5256,31 +5307,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5288,31 +5339,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5320,31 +5371,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5352,31 +5403,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5384,31 +5435,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>334</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>334</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5416,31 +5467,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5448,31 +5499,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5480,31 +5531,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>132</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5512,31 +5563,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5544,31 +5595,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5576,19 +5627,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -5600,7 +5651,7 @@
         <v>132</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5608,31 +5659,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5640,31 +5691,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5672,31 +5723,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>141</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5704,19 +5755,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -5725,10 +5776,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5736,31 +5787,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>271</v>
+        <v>132</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5768,31 +5819,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5800,31 +5851,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5832,31 +5883,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5864,19 +5915,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -5885,10 +5936,10 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5896,31 +5947,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5928,31 +5979,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5960,19 +6011,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -5981,10 +6032,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5992,38 +6043,70 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6054,6 +6137,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6070,7 +6154,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6108,31 +6192,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>397</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>397</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6140,19 +6224,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -6161,10 +6245,10 @@
         <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>218</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6172,31 +6256,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6204,19 +6288,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -6225,10 +6309,10 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6236,31 +6320,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6268,31 +6352,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6300,31 +6384,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6332,31 +6416,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6364,31 +6448,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6396,31 +6480,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6428,31 +6512,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>421</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6460,31 +6544,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6492,31 +6576,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>132</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6524,31 +6608,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>437</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6556,31 +6640,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>132</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6588,31 +6672,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6620,19 +6704,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -6644,7 +6728,7 @@
         <v>141</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6652,19 +6736,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -6673,10 +6757,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6684,31 +6768,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>141</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6716,31 +6800,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>132</v>
+        <v>277</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6748,31 +6832,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6780,31 +6864,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6812,19 +6896,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -6833,10 +6917,10 @@
         <v>161</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6844,31 +6928,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6876,19 +6960,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -6897,10 +6981,10 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6908,31 +6992,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6940,31 +7024,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6972,31 +7056,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7004,31 +7088,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7126,13 +7210,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -7141,10 +7225,10 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7164,10 +7248,10 @@
         <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>89</v>
@@ -7176,7 +7260,7 @@
         <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7190,13 +7274,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -7208,7 +7292,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7222,13 +7306,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7240,7 +7324,7 @@
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7254,13 +7338,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -7272,7 +7356,7 @@
         <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7286,13 +7370,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -7304,7 +7388,7 @@
         <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7318,13 +7402,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -7336,7 +7420,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7350,13 +7434,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -7368,7 +7452,7 @@
         <v>117</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7382,25 +7466,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>345</v>
+        <v>437</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7414,13 +7498,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -7432,7 +7516,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7446,13 +7530,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -7464,7 +7548,7 @@
         <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7478,13 +7562,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -7496,7 +7580,7 @@
         <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7510,13 +7594,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -7525,10 +7609,10 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7542,13 +7626,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -7560,7 +7644,7 @@
         <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7574,13 +7658,13 @@
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -7592,7 +7676,7 @@
         <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7606,13 +7690,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -7621,10 +7705,10 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7638,25 +7722,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7670,25 +7754,25 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7702,25 +7786,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>345</v>
+        <v>161</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7734,25 +7818,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7766,13 +7850,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -7781,10 +7865,10 @@
         <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7798,13 +7882,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -7813,10 +7897,10 @@
         <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7827,16 +7911,16 @@
         <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -7845,10 +7929,10 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7859,16 +7943,16 @@
         <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -7877,10 +7961,10 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7894,25 +7978,25 @@
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7926,25 +8010,25 @@
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7958,25 +8042,25 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7990,25 +8074,25 @@
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8022,25 +8106,25 @@
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8051,16 +8135,16 @@
         <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -8069,10 +8153,10 @@
         <v>161</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8171,13 +8255,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -8189,7 +8273,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8203,13 +8287,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -8221,7 +8305,7 @@
         <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8235,13 +8319,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8253,7 +8337,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8267,25 +8351,25 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>345</v>
+        <v>437</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8299,13 +8383,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8317,7 +8401,7 @@
         <v>117</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8337,10 +8421,10 @@
         <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>105</v>
@@ -8349,7 +8433,7 @@
         <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8363,13 +8447,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -8381,7 +8465,7 @@
         <v>117</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8395,13 +8479,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -8413,7 +8497,7 @@
         <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8427,13 +8511,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -8445,7 +8529,7 @@
         <v>132</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8459,13 +8543,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8477,7 +8561,7 @@
         <v>132</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8491,13 +8575,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8509,7 +8593,7 @@
         <v>141</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8523,13 +8607,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -8538,10 +8622,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8555,13 +8639,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -8570,10 +8654,10 @@
         <v>161</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8587,13 +8671,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -8605,7 +8689,7 @@
         <v>141</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8619,13 +8703,13 @@
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -8634,10 +8718,10 @@
         <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8651,25 +8735,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8683,25 +8767,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8715,13 +8799,13 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8730,10 +8814,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8747,13 +8831,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8762,10 +8846,10 @@
         <v>161</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8779,13 +8863,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -8794,10 +8878,10 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8811,13 +8895,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8826,10 +8910,10 @@
         <v>161</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8843,25 +8927,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8872,28 +8956,28 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8904,28 +8988,28 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8939,13 +9023,13 @@
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -8954,10 +9038,10 @@
         <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8971,13 +9055,13 @@
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -8986,10 +9070,10 @@
         <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9003,13 +9087,13 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9018,10 +9102,10 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9035,13 +9119,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -9050,10 +9134,10 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9067,13 +9151,13 @@
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -9082,10 +9166,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9096,16 +9180,16 @@
         <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -9114,10 +9198,10 @@
         <v>105</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -9216,25 +9300,25 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9248,13 +9332,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -9266,7 +9350,7 @@
         <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9280,13 +9364,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -9295,10 +9379,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9312,13 +9396,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9330,7 +9414,7 @@
         <v>117</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9344,13 +9428,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -9359,10 +9443,10 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9376,13 +9460,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9394,7 +9478,7 @@
         <v>132</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9408,13 +9492,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9426,7 +9510,7 @@
         <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9440,13 +9524,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9458,7 +9542,7 @@
         <v>141</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9472,13 +9556,13 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -9487,10 +9571,10 @@
         <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9504,13 +9588,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9519,10 +9603,10 @@
         <v>161</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9542,19 +9626,19 @@
         <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9568,13 +9652,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -9583,10 +9667,10 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9600,13 +9684,13 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -9615,10 +9699,10 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9632,13 +9716,13 @@
         <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -9647,10 +9731,10 @@
         <v>116</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9664,25 +9748,25 @@
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9696,25 +9780,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9728,13 +9812,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -9743,10 +9827,10 @@
         <v>116</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9760,13 +9844,13 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9775,10 +9859,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9792,13 +9876,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -9807,10 +9891,10 @@
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9824,13 +9908,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -9839,10 +9923,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9856,13 +9940,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -9871,10 +9955,10 @@
         <v>116</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9888,13 +9972,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9903,10 +9987,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9917,28 +10001,28 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>255</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9949,28 +10033,28 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9984,13 +10068,13 @@
         <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -9999,10 +10083,10 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10016,13 +10100,13 @@
         <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -10031,10 +10115,10 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10048,13 +10132,13 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -10063,10 +10147,10 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10080,13 +10164,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -10095,10 +10179,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10112,25 +10196,25 @@
         <v>205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10141,28 +10225,28 @@
         <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -10,8 +10,8 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
     <sheet name="딸기키우기" sheetId="3" r:id="rId3"/>
-    <sheet name="고점" sheetId="4" r:id="rId4"/>
-    <sheet name="이콩" sheetId="5" r:id="rId5"/>
+    <sheet name="이콩" sheetId="4" r:id="rId4"/>
+    <sheet name="고점" sheetId="5" r:id="rId5"/>
     <sheet name="LUXURY" sheetId="6" r:id="rId6"/>
     <sheet name="싸이월드" sheetId="7" r:id="rId7"/>
     <sheet name="라때는말이야" sheetId="8" r:id="rId8"/>
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">고점!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">딸기키우기!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이콩!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">이콩!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,586 +84,586 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>7경 7887조 9045억 2325만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.13</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>6경 8830조 4685억 5100만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>14경 9846조 303억 4362만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>9경 363조 7887억 7202만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>7경 4188조 4823억 5035만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>8경 4279조 8653억 3737만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>9경 9215조 3855억 1288만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>3경 4551조 729억 9907만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 914조 5474억 2169만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7420조 1976억 5060만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3873조 4462억 5106만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>오리부엉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1162조 5985억 5436만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1074조 896억 9253만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>907조 6750억 5110만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>811조 9295억 7976만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>694조 653억 200만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>558조 6279억 6089만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>453조 8899억 9995만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>424조 8134억 6221만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>411조 6165억 8335만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>394조 6570억 9129만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>344조 8231억 8195만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>308조 4617억 340만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>302조 2014억 7259만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>278조 7113억 5832만</t>
+  </si>
+  <si>
+    <t>트라이던트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>277조 5717억 4284만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>156조 2682억 1016만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>146조 8630억 5381만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>85조 9182억 4297만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>84조 963억 6746만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>83조 1051억 2122만</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>7경 6404조 4281억 3644만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.12</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>65조 6418억 239만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>53조 4730억 7686만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>53조 811억 6540만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>6경 7916조 2333억 8468만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>8경 9627조 5939억 9026만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>14경 9205조 3977억 8568만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>7경 3265조 2241억 3321만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>8경 202조 24억 5927만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>9경 1041조 4061억 5015만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3경 3545조 6796억 1930만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 914조 5474억 2169만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7417조 7397억 4975만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3871조 8969억 9688만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1119조 3342억 4814만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1074조 896억 9253만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>907조 6750억 5110만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>811조 9295억 7976만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>557조 2451억 6845만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>528조 9527억 5536만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>453조 8899억 9995만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>424조 8134억 6221만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>358조 3273억 4642만</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>332조 3362억 821만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>320조 777억 809만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>302조 2014억 7259만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>278조 7113억 5832만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>트라이던트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>251조 6569억 9612만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>237조 5337억 5992만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>146조 8630억 5381만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>138조 3313억 6702만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>82조 4181억 4388만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>81조 3271억 4694만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>80조 5043억 1725만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>65조 6418억 239만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>53조 4501억 5112만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>53조 811억 6540만</t>
-  </si>
-  <si>
     <t>몽호</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>47조 9296억 7008만</t>
+    <t>48조 301억 8971만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
@@ -672,7 +672,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>4경 5836조 2273억 9254만</t>
+    <t>4경 6246조 5329억 6651만</t>
   </si>
   <si>
     <t>쥬정뱅이</t>
@@ -681,27 +681,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
   </si>
   <si>
+    <t>5817조 6630억 8889만</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3125조 3955억 7391만</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>5634조 3435억 169만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3064조 7528억 5873만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
     <t>2385조 2517억 7689만</t>
   </si>
   <si>
@@ -711,7 +711,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
   </si>
   <si>
-    <t>2117조 4235억 7945만</t>
+    <t>2166조 5658억 5341만</t>
   </si>
   <si>
     <t>쑥국</t>
@@ -720,7 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
   </si>
   <si>
-    <t>1481조 6288억 2666만</t>
+    <t>1503조 5221억 7270만</t>
   </si>
   <si>
     <t>린뜌</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
   </si>
   <si>
-    <t>987조 9048억 8766만</t>
+    <t>1035조 3864억 4951만</t>
   </si>
   <si>
     <t>냉도</t>
@@ -741,22 +741,22 @@
     <t>656조 9558억 6537만</t>
   </si>
   <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>617조 2885억 7558만</t>
+  </si>
+  <si>
     <t>베티베디베</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
   </si>
   <si>
-    <t>590조 3712억 1131만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>581조 6068억 8335만</t>
+    <t>608조 9234억 8526만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -774,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>463조 4721억 7396만</t>
+    <t>468조 8913억 3536만</t>
   </si>
   <si>
     <t>노득</t>
@@ -792,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>418조 6530억 8907만</t>
+    <t>434조 7240억 1391만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -801,7 +801,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
   </si>
   <si>
-    <t>375조 5411억 7808만</t>
+    <t>415조 9967억 3924만</t>
   </si>
   <si>
     <t>키은</t>
@@ -837,7 +837,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
   </si>
   <si>
-    <t>214조 8139억 9587만</t>
+    <t>220조 4844억 2901만</t>
   </si>
   <si>
     <t>개점</t>
@@ -855,7 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
   </si>
   <si>
-    <t>204조 8543억 3970만</t>
+    <t>205조 6769억 6188만</t>
   </si>
   <si>
     <t>연지임당</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>129조 483억 298만</t>
+    <t>133조 5410억 7173만</t>
   </si>
   <si>
     <t>머쓰윽타드</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
   </si>
   <si>
-    <t>116조 3405억 2955만</t>
+    <t>126조 4923억 4416만</t>
   </si>
   <si>
     <t>핫딜만삼</t>
@@ -909,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>102조 3716억 6465만</t>
+    <t>106조 5028억 4206만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -942,6 +942,285 @@
     <t>20조 8249억 9066만</t>
   </si>
   <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>10경 4231조 6630억 7867만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>3경 165조 4505억 8118만</t>
+  </si>
+  <si>
+    <t>실민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>3203조 6647억 1152만</t>
+  </si>
+  <si>
+    <t>설즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>3092조 6447억 2797만</t>
+  </si>
+  <si>
+    <t>항상밝은하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>2520조 6545억 4022만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1052조 4313억 7363만</t>
+  </si>
+  <si>
+    <t>문디르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1002조 2239억 1309만</t>
+  </si>
+  <si>
+    <t>약한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>888조 8863억 1085만</t>
+  </si>
+  <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>846조 4505억 4261만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>837조 2181억 3685만</t>
+  </si>
+  <si>
+    <t>봉튜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
+  </si>
+  <si>
+    <t>329조 6872억 1096만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>226조 711억 8057만</t>
+  </si>
+  <si>
+    <t>런닝쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>213조 5974억 3169만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>162조 9128억 357만</t>
+  </si>
+  <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>152조 840억 4467만</t>
+  </si>
+  <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>151조 4096억 8600만</t>
+  </si>
+  <si>
+    <t>김대협</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
+  </si>
+  <si>
+    <t>123조 1135억 2578만</t>
+  </si>
+  <si>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>116조 2059억 335만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>114조 1301억 6006만</t>
+  </si>
+  <si>
+    <t>봄녘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
+  </si>
+  <si>
+    <t>108조 3712억 1332만</t>
+  </si>
+  <si>
+    <t>벨히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
+  </si>
+  <si>
+    <t>89조 9680억 4504만</t>
+  </si>
+  <si>
+    <t>만듀쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>53조 2608억 9403만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>49조 6658억 3233만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>39조 3228억 7888만</t>
+  </si>
+  <si>
+    <t>빠나쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>34조 6247억 9291만</t>
+  </si>
+  <si>
+    <t>강한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>18조 5796억 3291만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>11조 7843억 4694만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>5조 3137억 5771만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2조 8174억 6097만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>1조 6968억 1763만</t>
+  </si>
+  <si>
     <t>THE끌림</t>
   </si>
   <si>
@@ -957,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
   </si>
   <si>
-    <t>2경 3044조 8342억 6085만</t>
+    <t>2경 3057조 438억 9472만</t>
   </si>
   <si>
     <t>NUKE</t>
@@ -966,7 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>1경 5311조 6854억 2248만</t>
+    <t>1경 5902조 2270억 8478만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -975,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>6074조 8745억 5744만</t>
+    <t>6082조 5899억 9532만</t>
   </si>
   <si>
     <t>픠즈</t>
@@ -984,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>1495조 6456억 5700만</t>
+    <t>1522조 6363억 6055만</t>
   </si>
   <si>
     <t>환불한너잉</t>
@@ -1002,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
   </si>
   <si>
-    <t>1313조 2405억 3880만</t>
+    <t>1332조 7011억 8804만</t>
   </si>
   <si>
     <t>아투피</t>
@@ -1011,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
   </si>
   <si>
-    <t>1067조 4927억 8729만</t>
+    <t>1069조 5001억 3952만</t>
   </si>
   <si>
     <t>널비</t>
@@ -1029,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>924조 7588억 4221만</t>
+    <t>963조 767억 5617만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
@@ -1053,7 +1332,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>406조 9335억 7306만</t>
+    <t>407조 7854억 1028만</t>
   </si>
   <si>
     <t>순서교체</t>
@@ -1083,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>165조 1224억 4723만</t>
+    <t>172조 7216억 3475만</t>
   </si>
   <si>
     <t>무썬</t>
@@ -1092,7 +1371,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
   </si>
   <si>
-    <t>160조 1550억 360만</t>
+    <t>162조 2040억 1021만</t>
+  </si>
+  <si>
+    <t>맥맥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
+  </si>
+  <si>
+    <t>142조 3917억 4769만</t>
   </si>
   <si>
     <t>약할뻔</t>
@@ -1104,22 +1392,13 @@
     <t>132조 345억 3112만</t>
   </si>
   <si>
-    <t>맥맥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
-  </si>
-  <si>
-    <t>126조 4623억 1042만</t>
-  </si>
-  <si>
     <t>성칙이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>124조 9039억 8234만</t>
+    <t>131조 2262억 136만</t>
   </si>
   <si>
     <t>돌아온홍굴이</t>
@@ -1128,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>87조 7748억 6264만</t>
+    <t>88조 6014억 4228만</t>
   </si>
   <si>
     <t>kiaer</t>
@@ -1137,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>81조 2308억 8654만</t>
+    <t>83조 2714억 6448만</t>
   </si>
   <si>
     <t>숔숔숔숔</t>
@@ -1146,9 +1425,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
     <t>65조 4491억 2144만</t>
   </si>
   <si>
@@ -1176,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
   </si>
   <si>
-    <t>25조 3991억 7965만</t>
+    <t>26조 6757억 2478만</t>
   </si>
   <si>
     <t>탱탱볼탱탱볼</t>
@@ -1185,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
   </si>
   <si>
-    <t>23조 8712억 3299만</t>
+    <t>25조 2007억 355만</t>
   </si>
   <si>
     <t>기차아저씨</t>
@@ -1203,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>17조 8169억 9750만</t>
+    <t>18조 5435억 6534만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1215,282 +1491,6 @@
     <t>14조 7080억 4787만</t>
   </si>
   <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>10경 4213조 3341억 2919만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>3경 165조 4505억 8118만</t>
-  </si>
-  <si>
-    <t>실민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>3203조 6647억 1152만</t>
-  </si>
-  <si>
-    <t>설즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>3090조 2807억 3244만</t>
-  </si>
-  <si>
-    <t>항상밝은하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>2520조 6545억 4022만</t>
-  </si>
-  <si>
-    <t>약한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>888조 8863억 1085만</t>
-  </si>
-  <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>846조 4505억 4261만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>821조 6016억 2180만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>803조 1823억 5135만</t>
-  </si>
-  <si>
-    <t>문디르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>789조 8923억 5688만</t>
-  </si>
-  <si>
-    <t>봉튜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
-  </si>
-  <si>
-    <t>245조 9122억 6145만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>226조 711억 8057만</t>
-  </si>
-  <si>
-    <t>런닝쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>188조 2054억 3275만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>157조 9720억 5805만</t>
-  </si>
-  <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>149조 3493억 6774만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>149조 1499억 4051만</t>
-  </si>
-  <si>
-    <t>김대협</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
-  </si>
-  <si>
-    <t>123조 1135억 2578만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>114조 1301억 6006만</t>
-  </si>
-  <si>
-    <t>봄녘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
-  </si>
-  <si>
-    <t>106조 6997억 8584만</t>
-  </si>
-  <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>97조 6481억 4334만</t>
-  </si>
-  <si>
-    <t>벨히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
-  </si>
-  <si>
-    <t>89조 9680억 4504만</t>
-  </si>
-  <si>
-    <t>만듀쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>53조 2608억 9403만</t>
-  </si>
-  <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>49조 6658억 3233만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>37조 7184억 1518만</t>
-  </si>
-  <si>
-    <t>빠나쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>34조 1773억 5718만</t>
-  </si>
-  <si>
-    <t>강한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>18조 4864억 6131만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>11조 1291억 995만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>5조 3041억 5693만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>2조 8174억 6097만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>1조 6968억 1763만</t>
-  </si>
-  <si>
     <t>가숭혁</t>
   </si>
   <si>
@@ -1515,7 +1515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>4751조 9234억 1540만</t>
+    <t>5117조 5958억 6146만</t>
   </si>
   <si>
     <t>중탸치</t>
@@ -1524,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>2281조 47억 5976만</t>
+    <t>2532조 2373억 4043만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1542,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>1741조 8789억 9098만</t>
+    <t>1775조 9991억 8579만</t>
   </si>
   <si>
     <t>김우이</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>1648조 8352억 8620만</t>
+    <t>1745조 689억 2967만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>1187조 7661억 6858만</t>
+    <t>1226조 1409억 3217만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>1068조 7284억 7122만</t>
+    <t>1100조 7691억 366만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1596,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>787조 7117억 9579만</t>
+    <t>796조 7562억 1221만</t>
   </si>
   <si>
     <t>임승민</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>546조 7348억 2757만</t>
+    <t>576조 3578억 3259만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1614,7 +1614,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>457조 7924억 3618만</t>
+    <t>478조 7718억 6899만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>199조 9367억 4325만</t>
   </si>
   <si>
     <t>륵스리</t>
@@ -1626,22 +1635,13 @@
     <t>188조 934억 8649만</t>
   </si>
   <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>186조 7057억 5557만</t>
-  </si>
-  <si>
     <t>쑤삔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
   </si>
   <si>
-    <t>116조 1528억 5232만</t>
+    <t>122조 6504억 8335만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1659,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>83조 1338억 573만</t>
+    <t>86조 918억 7363만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1686,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>68조 5037억 3487만</t>
+    <t>68조 8334억 3382만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1698,13 +1698,22 @@
     <t>59조 629억 3728만</t>
   </si>
   <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>58조 5741억 7634만</t>
+  </si>
+  <si>
     <t>뻐늬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>54조 9340억 4419만</t>
+    <t>55조 5842억 8873만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1713,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>44조 4515억 9974만</t>
+    <t>45조 7141억 4410만</t>
   </si>
   <si>
     <t>브깃</t>
@@ -1725,15 +1734,6 @@
     <t>38조 8993억 8861만</t>
   </si>
   <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>37조 5662억 4896만</t>
-  </si>
-  <si>
     <t>크앙레몬</t>
   </si>
   <si>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
   </si>
   <si>
-    <t>4경 5922조 7614억 9890만</t>
+    <t>4경 9204조 937억 4909만</t>
   </si>
   <si>
     <t>키노눙</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
   </si>
   <si>
-    <t>1경 8320조 3642억 9923만</t>
+    <t>1경 8332조 6943억 3224만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1794,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
   </si>
   <si>
-    <t>2703조 8629억 5803만</t>
+    <t>3322조 9648억 9158만</t>
   </si>
   <si>
     <t>냠규리</t>
@@ -1806,28 +1806,28 @@
     <t>2100조 9602억 4443만</t>
   </si>
   <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>1512조 5812억 3348만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
   </si>
   <si>
     <t>1490조 8551억 4351만</t>
   </si>
   <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>1465조 2366억 9652만</t>
-  </si>
-  <si>
     <t>윤돌이굴돌이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1056조 4271억 956만</t>
+    <t>1096조 8111억 4520만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1836,7 +1836,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>437조 4163억 6568만</t>
+    <t>444조 1910억 2693만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>331조 4025억 9550만</t>
   </si>
   <si>
     <t>쏘세용</t>
@@ -1848,15 +1857,6 @@
     <t>310조 9348억 7972만</t>
   </si>
   <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>308조 1656억 8294만</t>
-  </si>
-  <si>
     <t>갓쿠</t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>173조 4056억 2251만</t>
+    <t>198조 959억 2783만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1890,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>141조 6353억 6830만</t>
+    <t>143조 9499억 1569만</t>
   </si>
   <si>
     <t>우당탕탼</t>
@@ -1899,7 +1899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
   </si>
   <si>
-    <t>99조 8418억 6218만</t>
+    <t>109조 8721억 2888만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1908,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>93조 48억 7302만</t>
+    <t>95조 5430억 1232만</t>
   </si>
   <si>
     <t>잼이유</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
   </si>
   <si>
-    <t>57조 9163억 4863만</t>
+    <t>63조 5113억 4896만</t>
   </si>
   <si>
     <t>붕붕월드</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
   </si>
   <si>
-    <t>48조 8338억 9181만</t>
+    <t>51조 2209억 5329만</t>
   </si>
   <si>
     <t>얼음조아</t>
@@ -1953,7 +1953,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
   </si>
   <si>
-    <t>25조 374억 7712만</t>
+    <t>26조 1892억 2065만</t>
+  </si>
+  <si>
+    <t>Subaru</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
+  </si>
+  <si>
+    <t>25조 542억 916만</t>
   </si>
   <si>
     <t>커피숍</t>
@@ -1965,15 +1974,6 @@
     <t>24조 2630억 1451만</t>
   </si>
   <si>
-    <t>Subaru</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
-  </si>
-  <si>
-    <t>23조 2544억 9932만</t>
-  </si>
-  <si>
     <t>도시리</t>
   </si>
   <si>
@@ -1989,7 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
   </si>
   <si>
-    <t>19조 1117억 6275만</t>
+    <t>20조 6286억 190만</t>
   </si>
   <si>
     <t>57년김춘배</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>18조 5426억 385만</t>
+    <t>18조 6341억 167만</t>
   </si>
   <si>
     <t>시네루최</t>
@@ -2007,7 +2007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
   </si>
   <si>
-    <t>13조 3782억 3228만</t>
+    <t>14조 3488억 8737만</t>
   </si>
   <si>
     <t>메린이이</t>
@@ -2019,13 +2019,13 @@
     <t>12조 5504억 8355만</t>
   </si>
   <si>
-    <t>먕겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%95%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>6경 829조 8758억 921만</t>
+    <t>길원구함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%9B%90%EA%B5%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>6경 4418조 6995억 1326만</t>
   </si>
   <si>
     <t>용려니</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 1952조 4453억 7020만</t>
+    <t>2경 6353조 7834억 9002만</t>
   </si>
   <si>
     <t>메키멍</t>
@@ -2052,7 +2052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>1992조 8499억 1675만</t>
+    <t>2036조 611억 2978만</t>
   </si>
   <si>
     <t>샤프리</t>
@@ -2061,7 +2061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>1058조 25억 9444만</t>
+    <t>1079조 3591억 1373만</t>
   </si>
   <si>
     <t>참달</t>
@@ -2070,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
   </si>
   <si>
-    <t>740조 4131억 765만</t>
+    <t>779조 1618억 552만</t>
   </si>
   <si>
     <t>인두겁</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>240조 1878억 9765만</t>
+    <t>263조 4489억 2859만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2097,7 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>222조 7450억 8175만</t>
+    <t>224조 574억 5850만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2106,13 +2106,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%9D%98%EA%B8%B0%EC%9A%B4</t>
   </si>
   <si>
-    <t>156조 2456억 4605만</t>
+    <t>189조 9265억 2860만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>120조 9493억 256만</t>
+    <t>131조 8995억 3827만</t>
   </si>
   <si>
     <t>포근한소리</t>
@@ -2121,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
   </si>
   <si>
-    <t>83조 927억 4662만</t>
+    <t>83조 6965억 8694만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2139,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%B6%84</t>
   </si>
   <si>
-    <t>43조 1382억 108만</t>
+    <t>43조 3917억 7045만</t>
   </si>
   <si>
     <t>잘스제</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>39조 4627억 4626만</t>
+    <t>40조 339억 9271만</t>
   </si>
   <si>
     <t>머수킹</t>
@@ -2175,7 +2175,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
   </si>
   <si>
-    <t>26조 9950억 7463만</t>
+    <t>27조 1641억 7545만</t>
   </si>
   <si>
     <t>외단</t>
@@ -2202,7 +2202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>21조 1650억 3027만</t>
+    <t>21조 3040억 3330만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2214,6 +2214,15 @@
     <t>20조 8826억 9850만</t>
   </si>
   <si>
+    <t>훈이ing</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EC%9D%B4ing</t>
+  </si>
+  <si>
+    <t>19조 3817억 1577만</t>
+  </si>
+  <si>
     <t>탕화</t>
   </si>
   <si>
@@ -2223,22 +2232,13 @@
     <t>16조 2456억 440만</t>
   </si>
   <si>
-    <t>훈이ing</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EC%9D%B4ing</t>
-  </si>
-  <si>
-    <t>14조 3307억 621만</t>
-  </si>
-  <si>
     <t>진우정</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>13조 228억 7708만</t>
+    <t>13조 8549억 3735만</t>
   </si>
   <si>
     <t>BudriQ</t>
@@ -2247,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
   </si>
   <si>
-    <t>9조 5421억 8713만</t>
+    <t>10조 1299억 3132만</t>
   </si>
   <si>
     <t>콩새우</t>
@@ -2256,7 +2256,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%A9%EC%83%88%EC%9A%B0</t>
   </si>
   <si>
-    <t>8조 8508억 9461만</t>
+    <t>10조 377억 3373만</t>
+  </si>
+  <si>
+    <t>가겠네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
+  </si>
+  <si>
+    <t>7조 7937억 6259만</t>
   </si>
   <si>
     <t>킴카</t>
@@ -2265,16 +2274,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
   </si>
   <si>
-    <t>7조 291억 6921만</t>
-  </si>
-  <si>
-    <t>가겠네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
-  </si>
-  <si>
-    <t>6조 3980억 9233만</t>
+    <t>7조 5356억 6853만</t>
   </si>
 </sst>
 </file>
@@ -2647,7 +2647,7 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="50.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -2790,16 +2790,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
@@ -2831,16 +2831,16 @@
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -3007,7 +3007,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3290,10 +3290,10 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3304,16 +3304,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -3325,7 +3325,7 @@
         <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3336,28 +3336,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3368,16 +3368,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -3386,10 +3386,10 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3400,16 +3400,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -3418,10 +3418,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3432,16 +3432,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -3450,7 +3450,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3511,13 +3511,13 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3528,7 +3528,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>153</v>
@@ -3543,13 +3543,13 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3560,7 +3560,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>157</v>
@@ -3607,10 +3607,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>163</v>
@@ -3639,10 +3639,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>167</v>
@@ -3671,13 +3671,13 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3688,16 +3688,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -3706,10 +3706,10 @@
         <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3720,28 +3720,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3752,28 +3752,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3784,16 +3784,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -3802,10 +3802,10 @@
         <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3816,28 +3816,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3848,28 +3848,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3880,7 +3880,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
@@ -3889,19 +3889,19 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3912,7 +3912,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>200</v>
@@ -3927,10 +3927,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>202</v>
@@ -3944,16 +3944,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -3962,10 +3962,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3976,7 +3976,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>208</v>
@@ -3994,7 +3994,7 @@
         <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>210</v>
@@ -4105,7 +4105,7 @@
         <v>211</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>105</v>
@@ -4143,10 +4143,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4160,13 +4160,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -4178,7 +4178,7 @@
         <v>115</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4192,13 +4192,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -4207,7 +4207,7 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>223</v>
@@ -4268,7 +4268,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>115</v>
@@ -4303,7 +4303,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>232</v>
@@ -4349,7 +4349,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>236</v>
@@ -4367,7 +4367,7 @@
         <v>95</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>238</v>
@@ -4381,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>239</v>
@@ -4399,7 +4399,7 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>241</v>
@@ -4413,7 +4413,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>242</v>
@@ -4431,7 +4431,7 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>244</v>
@@ -4445,7 +4445,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>245</v>
@@ -4463,7 +4463,7 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>247</v>
@@ -4477,7 +4477,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>248</v>
@@ -4492,10 +4492,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>250</v>
@@ -4527,7 +4527,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>253</v>
@@ -4573,7 +4573,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>257</v>
@@ -4591,7 +4591,7 @@
         <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>259</v>
@@ -4605,7 +4605,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>260</v>
@@ -4623,7 +4623,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>262</v>
@@ -4655,7 +4655,7 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>265</v>
@@ -4687,7 +4687,7 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>268</v>
@@ -4716,10 +4716,10 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>271</v>
@@ -4733,7 +4733,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>272</v>
@@ -4751,7 +4751,7 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>274</v>
@@ -4765,7 +4765,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>275</v>
@@ -4783,7 +4783,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>277</v>
@@ -4797,7 +4797,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>278</v>
@@ -4812,10 +4812,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>280</v>
@@ -4829,7 +4829,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>281</v>
@@ -4847,7 +4847,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>283</v>
@@ -4861,7 +4861,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>284</v>
@@ -4876,10 +4876,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>286</v>
@@ -4893,7 +4893,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>287</v>
@@ -4911,7 +4911,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>289</v>
@@ -4925,7 +4925,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>290</v>
@@ -4943,7 +4943,7 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>292</v>
@@ -4957,7 +4957,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>293</v>
@@ -4989,7 +4989,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>297</v>
@@ -5007,7 +5007,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
@@ -5021,7 +5021,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>300</v>
@@ -5039,7 +5039,7 @@
         <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>302</v>
@@ -5097,7 +5097,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5156,7 +5156,7 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>305</v>
@@ -5185,7 +5185,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>212</v>
@@ -5220,7 +5220,7 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>311</v>
@@ -5249,10 +5249,10 @@
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>314</v>
@@ -5281,10 +5281,10 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>317</v>
@@ -5313,10 +5313,10 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>320</v>
@@ -5348,7 +5348,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5377,10 +5377,10 @@
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>326</v>
@@ -5394,7 +5394,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>327</v>
@@ -5409,10 +5409,10 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>329</v>
@@ -5426,7 +5426,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>330</v>
@@ -5441,10 +5441,10 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -5458,28 +5458,28 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>333</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>333</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5490,28 +5490,28 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5522,28 +5522,28 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5557,25 +5557,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5589,13 +5589,13 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -5604,10 +5604,10 @@
         <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5618,28 +5618,28 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5650,28 +5650,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5685,13 +5685,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -5700,10 +5700,10 @@
         <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5717,25 +5717,25 @@
         <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5749,25 +5749,25 @@
         <v>168</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5778,28 +5778,28 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5810,28 +5810,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5842,25 +5842,25 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>371</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>372</v>
@@ -5874,7 +5874,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>373</v>
@@ -5889,7 +5889,7 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>295</v>
@@ -5906,7 +5906,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>376</v>
@@ -5921,10 +5921,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>378</v>
@@ -5938,7 +5938,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>379</v>
@@ -5953,13 +5953,13 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>295</v>
+        <v>381</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5970,28 +5970,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6002,28 +6002,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6034,28 +6034,28 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>392</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6066,28 +6066,28 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6142,7 +6142,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6186,13 +6186,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -6201,10 +6201,10 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6218,25 +6218,25 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>212</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6250,13 +6250,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -6265,10 +6265,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>216</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6282,25 +6282,25 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>216</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6314,25 +6314,25 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6346,25 +6346,25 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6378,25 +6378,25 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6410,25 +6410,25 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6439,28 +6439,28 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6471,28 +6471,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6503,28 +6503,28 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>424</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>424</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6535,28 +6535,28 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6567,28 +6567,28 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6602,25 +6602,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6634,13 +6634,13 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -6649,10 +6649,10 @@
         <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6663,28 +6663,28 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6695,28 +6695,28 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6730,25 +6730,25 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6762,25 +6762,25 @@
         <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6794,25 +6794,25 @@
         <v>168</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>295</v>
+        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6823,28 +6823,28 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6855,28 +6855,28 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6887,28 +6887,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>344</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6919,28 +6919,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6951,28 +6951,28 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6983,28 +6983,28 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>371</v>
+        <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>471</v>
+        <v>295</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7015,25 +7015,25 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>475</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>476</v>
@@ -7047,7 +7047,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>477</v>
@@ -7062,10 +7062,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>475</v>
+        <v>295</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>479</v>
@@ -7079,7 +7079,7 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>480</v>
@@ -7094,13 +7094,13 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7111,25 +7111,25 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>47</v>
+        <v>483</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>483</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>484</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>482</v>
+        <v>295</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>485</v>
@@ -7272,7 +7272,7 @@
         <v>490</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>95</v>
@@ -7342,7 +7342,7 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>497</v>
@@ -7374,7 +7374,7 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>500</v>
@@ -7484,7 +7484,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>510</v>
@@ -7499,7 +7499,7 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>115</v>
@@ -7516,7 +7516,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>513</v>
@@ -7534,7 +7534,7 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>515</v>
@@ -7548,7 +7548,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>516</v>
@@ -7563,10 +7563,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>518</v>
@@ -7580,7 +7580,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>519</v>
@@ -7598,7 +7598,7 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>521</v>
@@ -7612,7 +7612,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>522</v>
@@ -7630,7 +7630,7 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>524</v>
@@ -7662,7 +7662,7 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>527</v>
@@ -7691,10 +7691,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>530</v>
@@ -7708,7 +7708,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>531</v>
@@ -7723,10 +7723,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>533</v>
@@ -7740,7 +7740,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>534</v>
@@ -7755,10 +7755,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>536</v>
@@ -7790,7 +7790,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>539</v>
@@ -7819,10 +7819,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>542</v>
@@ -7851,7 +7851,7 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>295</v>
@@ -7868,7 +7868,7 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>546</v>
@@ -7886,7 +7886,7 @@
         <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>548</v>
@@ -7900,7 +7900,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>549</v>
@@ -7918,7 +7918,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>551</v>
@@ -7932,7 +7932,7 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>552</v>
@@ -7950,7 +7950,7 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>554</v>
@@ -7964,7 +7964,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>555</v>
@@ -7979,10 +7979,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>557</v>
@@ -7996,7 +7996,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>558</v>
@@ -8011,10 +8011,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>295</v>
+        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>560</v>
@@ -8028,7 +8028,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>561</v>
@@ -8043,7 +8043,7 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>295</v>
@@ -8060,7 +8060,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>564</v>
@@ -8075,10 +8075,10 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>566</v>
@@ -8092,7 +8092,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>567</v>
@@ -8107,7 +8107,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>295</v>
@@ -8124,7 +8124,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>570</v>
@@ -8139,10 +8139,10 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>206</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>572</v>
@@ -8156,7 +8156,7 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>573</v>
@@ -8171,10 +8171,10 @@
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>575</v>
@@ -8384,7 +8384,7 @@
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>115</v>
@@ -8436,16 +8436,16 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>591</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>591</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>105</v>
@@ -8454,7 +8454,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8468,16 +8468,16 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>593</v>
+        <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>593</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>594</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>105</v>
@@ -8515,7 +8515,7 @@
         <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>598</v>
@@ -8529,7 +8529,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>599</v>
@@ -8547,7 +8547,7 @@
         <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>601</v>
@@ -8561,7 +8561,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>602</v>
@@ -8576,10 +8576,10 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>604</v>
@@ -8593,7 +8593,7 @@
         <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>605</v>
@@ -8608,10 +8608,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>607</v>
@@ -8625,7 +8625,7 @@
         <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>608</v>
@@ -8640,10 +8640,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>610</v>
@@ -8657,7 +8657,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>611</v>
@@ -8675,7 +8675,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>613</v>
@@ -8707,7 +8707,7 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>616</v>
@@ -8736,7 +8736,7 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>110</v>
@@ -8753,7 +8753,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>620</v>
@@ -8768,10 +8768,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>622</v>
@@ -8785,7 +8785,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>623</v>
@@ -8800,10 +8800,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>625</v>
@@ -8835,7 +8835,7 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>628</v>
@@ -8864,10 +8864,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>631</v>
@@ -8899,7 +8899,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>634</v>
@@ -8913,7 +8913,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>635</v>
@@ -8928,10 +8928,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>637</v>
@@ -8945,7 +8945,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>638</v>
@@ -8977,7 +8977,7 @@
         <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>641</v>
@@ -8992,10 +8992,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>371</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>206</v>
+        <v>295</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>643</v>
@@ -9009,7 +9009,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>644</v>
@@ -9024,10 +9024,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>344</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>646</v>
@@ -9041,7 +9041,7 @@
         <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>647</v>
@@ -9059,7 +9059,7 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>649</v>
@@ -9073,7 +9073,7 @@
         <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>650</v>
@@ -9091,7 +9091,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>652</v>
@@ -9105,7 +9105,7 @@
         <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>653</v>
@@ -9123,7 +9123,7 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>655</v>
@@ -9137,7 +9137,7 @@
         <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>656</v>
@@ -9155,7 +9155,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>658</v>
@@ -9169,7 +9169,7 @@
         <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>659</v>
@@ -9367,7 +9367,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>670</v>
@@ -9399,7 +9399,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>673</v>
@@ -9431,7 +9431,7 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>676</v>
@@ -9463,7 +9463,7 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>679</v>
@@ -9495,7 +9495,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>682</v>
@@ -9527,7 +9527,7 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>685</v>
@@ -9541,7 +9541,7 @@
         <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>686</v>
@@ -9559,7 +9559,7 @@
         <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>688</v>
@@ -9573,7 +9573,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>689</v>
@@ -9588,10 +9588,10 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>691</v>
@@ -9605,7 +9605,7 @@
         <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>70</v>
@@ -9617,13 +9617,13 @@
         <v>692</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>693</v>
@@ -9637,7 +9637,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>694</v>
@@ -9655,7 +9655,7 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>696</v>
@@ -9669,7 +9669,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>697</v>
@@ -9716,10 +9716,10 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>702</v>
@@ -9765,7 +9765,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>706</v>
@@ -9783,7 +9783,7 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>708</v>
@@ -9797,7 +9797,7 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>709</v>
@@ -9812,7 +9812,7 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>295</v>
@@ -9879,7 +9879,7 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>717</v>
@@ -9911,7 +9911,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>471</v>
+        <v>205</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>720</v>
@@ -9925,7 +9925,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>721</v>
@@ -9940,10 +9940,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>723</v>
@@ -9957,7 +9957,7 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>724</v>
@@ -9972,10 +9972,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>726</v>
@@ -9989,7 +9989,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>727</v>
@@ -10007,7 +10007,7 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>729</v>
@@ -10021,7 +10021,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>730</v>
@@ -10039,7 +10039,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>732</v>
@@ -10053,7 +10053,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>733</v>
@@ -10071,7 +10071,7 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>735</v>
@@ -10085,7 +10085,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>736</v>
@@ -10103,7 +10103,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>738</v>
@@ -10117,7 +10117,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>739</v>
@@ -10135,7 +10135,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>741</v>
@@ -10149,7 +10149,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>742</v>
@@ -10164,10 +10164,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>744</v>
@@ -10181,7 +10181,7 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>745</v>
@@ -10196,10 +10196,10 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>747</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>7경 7887조 9045억 2325만</t>
+    <t>7경 9248조 6141억 4724만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -105,7 +105,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.05.13</t>
+    <t>2026.05.14</t>
   </si>
   <si>
     <t>딸기키우기</t>
@@ -117,531 +117,531 @@
     <t>Scania 28</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>6경 9604조 5236억 1538만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>15경 2785조 7641억 3752만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>9경 3474조 4154억 7447만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>7경 5173조 8231억 3465만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>9경 3541조 1252억 8295만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>9경 9291조 7559억 1810만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>3경 5513조 6807억 1084만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 914조 5474억 2169만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7420조 1976억 5060만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3963조 8600억 6259만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>오리부엉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1194조 1815억 1689만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1074조 896억 9253만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>954조 3229억 9711만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>811조 9295억 7976만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>694조 653억 200만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>646조 2693억 6314만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>453조 8899억 9995만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>438조 2316억 8493만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>424조 8134억 6221만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>411조 6165억 8335만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>346조 718억 3269만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>트라이던트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>319조 6566억 3917만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>308조 4617억 340만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>306조 4721억 6101만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>296조 8012억 4137만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>156조 2682억 1016만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>146조 8630억 5381만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>90조 3578억 9631만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>88조 1693억 8227만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>87조 5947억 8692만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>68조 9582억 9227만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>65조 6418억 239만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>6경 8830조 4685억 5100만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>14경 9846조 303억 4362만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>9경 363조 7887억 7202만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>7경 4188조 4823억 5035만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>8경 4279조 8653억 3737만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>9경 9215조 3855억 1288만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3경 4551조 729억 9907만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 914조 5474억 2169만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7420조 1976억 5060만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3873조 4462억 5106만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>오리부엉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1162조 5985억 5436만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1074조 896억 9253만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>907조 6750억 5110만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>811조 9295억 7976만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>694조 653억 200만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>558조 6279억 6089만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>453조 8899억 9995만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>424조 8134억 6221만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>411조 6165억 8335만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>394조 6570억 9129만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>344조 8231억 8195만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>308조 4617억 340만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>302조 2014억 7259만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>278조 7113억 5832만</t>
-  </si>
-  <si>
-    <t>트라이던트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>277조 5717억 4284만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>156조 2682억 1016만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>146조 8630억 5381만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>85조 9182억 4297만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>84조 963억 6746만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>83조 1051억 2122만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>65조 6418억 239만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>53조 4730억 7686만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -663,7 +663,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>48조 301억 8971만</t>
+    <t>52조 897억 1819만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
   </si>
   <si>
-    <t>5817조 6630억 8889만</t>
+    <t>5918조 8920억 9178만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -690,7 +690,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>3125조 3955억 7391만</t>
+    <t>3181조 2698억 4745만</t>
   </si>
   <si>
     <t>귀여워서미안</t>
@@ -711,7 +711,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
   </si>
   <si>
-    <t>2166조 5658억 5341만</t>
+    <t>2287조 9054억 1438만</t>
   </si>
   <si>
     <t>쑥국</t>
@@ -720,7 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
   </si>
   <si>
-    <t>1503조 5221억 7270만</t>
+    <t>1506조 4854억 4672만</t>
   </si>
   <si>
     <t>린뜌</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
   </si>
   <si>
-    <t>1035조 3864억 4951만</t>
+    <t>1150조 3685억 8626만</t>
   </si>
   <si>
     <t>냉도</t>
@@ -741,6 +741,15 @@
     <t>656조 9558억 6537만</t>
   </si>
   <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>621조 3825억 5983만</t>
+  </si>
+  <si>
     <t>약해진쭌석</t>
   </si>
   <si>
@@ -750,13 +759,13 @@
     <t>617조 2885억 7558만</t>
   </si>
   <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>608조 9234억 8526만</t>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>496조 154억 9234만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -765,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
   </si>
   <si>
-    <t>484조 8916억 8904만</t>
+    <t>491조 3307억 6609만</t>
   </si>
   <si>
     <t>엔젤가든</t>
@@ -774,16 +783,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>468조 8913억 3536만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>448조 5015억 6405만</t>
+    <t>478조 3554억 6735만</t>
   </si>
   <si>
     <t>피치에이드</t>
@@ -792,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>434조 7240억 1391만</t>
+    <t>454조 9016억 8346만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -810,7 +810,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
   </si>
   <si>
-    <t>267조 6907억 4148만</t>
+    <t>274조 4068억 5151만</t>
+  </si>
+  <si>
+    <t>잉잉기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>251조 2235억 1539만</t>
   </si>
   <si>
     <t>사마련</t>
@@ -846,7 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
   </si>
   <si>
-    <t>206조 3148억 8046만</t>
+    <t>214조 79억 4060만</t>
   </si>
   <si>
     <t>쵸꼬님</t>
@@ -864,7 +873,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
   </si>
   <si>
-    <t>191조 2956억 2387만</t>
+    <t>195조 4146억 3879만</t>
   </si>
   <si>
     <t>81학찬</t>
@@ -876,22 +885,22 @@
     <t>167조 6436억 2625만</t>
   </si>
   <si>
+    <t>챠재범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
+  </si>
+  <si>
+    <t>137조 9092억 3023만</t>
+  </si>
+  <si>
     <t>앨리스빌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
   </si>
   <si>
-    <t>135조 9349억 5864만</t>
-  </si>
-  <si>
-    <t>챠재범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
-  </si>
-  <si>
-    <t>133조 5410억 7173만</t>
+    <t>136조 5819억 1543만</t>
   </si>
   <si>
     <t>머쓰윽타드</t>
@@ -909,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>106조 5028억 4206만</t>
+    <t>106조 8596억 2319만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -921,7 +930,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>84조 5926억 3781만</t>
+    <t>100조 1050억 8254만</t>
   </si>
   <si>
     <t>샤갈츄</t>
@@ -930,16 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
   </si>
   <si>
-    <t>79조 7546억 4080만</t>
-  </si>
-  <si>
-    <t>딸기비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>20조 8249억 9066만</t>
+    <t>91조 5565억 2461만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>10경 4231조 6630억 7867만</t>
+    <t>10경 4463조 7733억 6212만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
   </si>
   <si>
-    <t>3경 165조 4505억 8118만</t>
+    <t>3경 2586조 7910억 130만</t>
   </si>
   <si>
     <t>실민</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1052조 4313억 7363만</t>
+    <t>1220조 4703억 6798만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -1041,22 +1041,40 @@
     <t>329조 6872억 1096만</t>
   </si>
   <si>
+    <t>런닝쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>267조 7968억 6997만</t>
+  </si>
+  <si>
     <t>꽃나래</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>226조 711억 8057만</t>
-  </si>
-  <si>
-    <t>런닝쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>213조 5974억 3169만</t>
+    <t>233조 5011억 2014만</t>
+  </si>
+  <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>166조 292억 7674만</t>
+  </si>
+  <si>
+    <t>땩콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>164조 9595억 1451만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1071,22 +1089,13 @@
     <t>162조 9128억 357만</t>
   </si>
   <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>152조 840억 4467만</t>
-  </si>
-  <si>
-    <t>땩콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>151조 4096억 8600만</t>
+    <t>에망</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
+  </si>
+  <si>
+    <t>125조 9683억 8296만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1095,16 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>123조 1135억 2578만</t>
-  </si>
-  <si>
-    <t>에망</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
-  </si>
-  <si>
-    <t>116조 2059억 335만</t>
+    <t>123조 2333억 2843만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>114조 1301억 6006만</t>
+    <t>116조 8434억 4188만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1131,7 +1131,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
   </si>
   <si>
-    <t>89조 9680억 4504만</t>
+    <t>97조 5908억 118만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>54조 5956억 72만</t>
   </si>
   <si>
     <t>만듀쨩</t>
@@ -1143,15 +1152,6 @@
     <t>53조 2608억 9403만</t>
   </si>
   <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>49조 6658억 3233만</t>
-  </si>
-  <si>
     <t>다송이</t>
   </si>
   <si>
@@ -1167,7 +1167,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
   </si>
   <si>
-    <t>34조 6247억 9291만</t>
+    <t>36조 9918억 3341만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1176,526 +1176,526 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
+    <t>18조 7042억 6495만</t>
+  </si>
+  <si>
+    <t>양카오너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 6867억 401만</t>
+  </si>
+  <si>
+    <t>돌쇠영만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>5조 5199억 3952만</t>
+  </si>
+  <si>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>3조 1427억 9822만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
+  </si>
+  <si>
+    <t>1조 8676억 4550만</t>
+  </si>
+  <si>
+    <t>THE끌림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>3경 4504조 1799억 176만</t>
+  </si>
+  <si>
+    <t>멸국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>2경 5450조 3097억 9239만</t>
+  </si>
+  <si>
+    <t>NUKE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
+  </si>
+  <si>
+    <t>1경 6113조 5145억 6321만</t>
+  </si>
+  <si>
+    <t>쌔주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>6301조 7323억 1594만</t>
+  </si>
+  <si>
+    <t>픠즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1526조 7136억 7184만</t>
+  </si>
+  <si>
+    <t>환불한너잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1387조 5965억 1147만</t>
+  </si>
+  <si>
+    <t>S2베코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
+  </si>
+  <si>
+    <t>1335조 1649억 624만</t>
+  </si>
+  <si>
+    <t>아투피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
+  </si>
+  <si>
+    <t>1148조 8112억 6056만</t>
+  </si>
+  <si>
+    <t>널비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1117조 5002억 9858만</t>
+  </si>
+  <si>
+    <t>똔똔잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
+  </si>
+  <si>
+    <t>968조 4710억 3658만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
+  </si>
+  <si>
+    <t>862조 7784억 6240만</t>
+  </si>
+  <si>
+    <t>백히로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>449조 5247억 8928만</t>
+  </si>
+  <si>
+    <t>뷰질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
+  </si>
+  <si>
+    <t>428조 4895억 1975만</t>
+  </si>
+  <si>
+    <t>순서교체</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>348조 615억 5196만</t>
+  </si>
+  <si>
+    <t>근접맞나이거</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
+  </si>
+  <si>
+    <t>325조 1782억 3169만</t>
+  </si>
+  <si>
+    <t>김천아재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>174조 2413억 9336만</t>
+  </si>
+  <si>
+    <t>무썬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
+  </si>
+  <si>
+    <t>167조 1050억 94만</t>
+  </si>
+  <si>
+    <t>맥맥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
+  </si>
+  <si>
+    <t>142조 3917억 4769만</t>
+  </si>
+  <si>
+    <t>성칙이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>137조 3352억 2088만</t>
+  </si>
+  <si>
+    <t>약할뻔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
+  </si>
+  <si>
+    <t>132조 345억 3112만</t>
+  </si>
+  <si>
+    <t>돌아온홍굴이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>92조 31억 6115만</t>
+  </si>
+  <si>
+    <t>kiaer</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
+  </si>
+  <si>
+    <t>84조 2647억 3492만</t>
+  </si>
+  <si>
+    <t>숔숔숔숔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
+  </si>
+  <si>
+    <t>70조 3988억 5686만</t>
+  </si>
+  <si>
+    <t>안재똥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
+  </si>
+  <si>
+    <t>60조 7527억 4015만</t>
+  </si>
+  <si>
+    <t>순샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
+  </si>
+  <si>
+    <t>37조 6312억 4077만</t>
+  </si>
+  <si>
+    <t>보마가될인재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>27조 3546억 3878만</t>
+  </si>
+  <si>
+    <t>탱탱볼탱탱볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>25조 3530억 1424만</t>
+  </si>
+  <si>
+    <t>기차아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>21조 5370억 1579만</t>
+  </si>
+  <si>
+    <t>구뺑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
+  </si>
+  <si>
+    <t>19조 9877억 2122만</t>
+  </si>
+  <si>
+    <t>이서지용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>14조 7080억 4787만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>4경 3707조 2620억 9240만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 51조 1568억 2849만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>5907조 2293억 8649만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>2532조 2373억 4043만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>2030조 6297억 4815만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>1806조 8755억 3068만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1784조 9224억 69만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>1228조 3761억 3124만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1129조 3231억 8018만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>1009조 7065억 2372만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>837조 3638억 1007만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>805조 3347억 6173만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>594조 6433억 402만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>481조 1302억 1440만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>199조 9367억 4325만</t>
+  </si>
+  <si>
+    <t>륵스리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B5%EC%8A%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>188조 934억 8649만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>122조 6863억 1126만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>91조 768억 8769만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>88조 5930억 3627만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>78조 9603억 8863만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>75조 1071억 9773만</t>
+  </si>
+  <si>
+    <t>라흐S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>18조 5796억 3291만</t>
-  </si>
-  <si>
-    <t>양카오너</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B9%B4%EC%98%A4%EB%84%88</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>11조 7843억 4694만</t>
-  </si>
-  <si>
-    <t>돌쇠영만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>5조 3137억 5771만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>2조 8174억 6097만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
-  </si>
-  <si>
-    <t>1조 6968억 1763만</t>
-  </si>
-  <si>
-    <t>THE끌림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>3경 4504조 1799억 176만</t>
-  </si>
-  <si>
-    <t>멸국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>2경 3057조 438억 9472만</t>
-  </si>
-  <si>
-    <t>NUKE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=NUKE</t>
-  </si>
-  <si>
-    <t>1경 5902조 2270억 8478만</t>
-  </si>
-  <si>
-    <t>쌔주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>6082조 5899억 9532만</t>
-  </si>
-  <si>
-    <t>픠즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1522조 6363억 6055만</t>
-  </si>
-  <si>
-    <t>환불한너잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1387조 5965억 1147만</t>
-  </si>
-  <si>
-    <t>S2베코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
-  </si>
-  <si>
-    <t>1332조 7011억 8804만</t>
-  </si>
-  <si>
-    <t>아투피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
-  </si>
-  <si>
-    <t>1069조 5001억 3952만</t>
-  </si>
-  <si>
-    <t>널비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EB%B9%84</t>
-  </si>
-  <si>
-    <t>999조 3355억 8864만</t>
-  </si>
-  <si>
-    <t>똔똔잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
-  </si>
-  <si>
-    <t>963조 767억 5617만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
-  </si>
-  <si>
-    <t>855조 2917억 2909만</t>
-  </si>
-  <si>
-    <t>뷰질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
-  </si>
-  <si>
-    <t>428조 4895억 1975만</t>
-  </si>
-  <si>
-    <t>백히로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>407조 7854억 1028만</t>
-  </si>
-  <si>
-    <t>순서교체</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%84%9C%EA%B5%90%EC%B2%B4</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>343조 2072억 6852만</t>
-  </si>
-  <si>
-    <t>근접맞나이거</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
-  </si>
-  <si>
-    <t>325조 1782억 3169만</t>
-  </si>
-  <si>
-    <t>김천아재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>172조 7216억 3475만</t>
-  </si>
-  <si>
-    <t>무썬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
-  </si>
-  <si>
-    <t>162조 2040억 1021만</t>
-  </si>
-  <si>
-    <t>맥맥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
-  </si>
-  <si>
-    <t>142조 3917억 4769만</t>
-  </si>
-  <si>
-    <t>약할뻔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%A0%EB%BB%94</t>
-  </si>
-  <si>
-    <t>132조 345억 3112만</t>
-  </si>
-  <si>
-    <t>성칙이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%B9%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>131조 2262억 136만</t>
-  </si>
-  <si>
-    <t>돌아온홍굴이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>88조 6014억 4228만</t>
-  </si>
-  <si>
-    <t>kiaer</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=kiaer</t>
-  </si>
-  <si>
-    <t>83조 2714억 6448만</t>
-  </si>
-  <si>
-    <t>숔숔숔숔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
-  </si>
-  <si>
-    <t>65조 4491억 2144만</t>
-  </si>
-  <si>
-    <t>안재똥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%9E%AC%EB%98%A5</t>
-  </si>
-  <si>
-    <t>60조 7527억 4015만</t>
-  </si>
-  <si>
-    <t>순샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
-  </si>
-  <si>
-    <t>37조 6312억 4077만</t>
-  </si>
-  <si>
-    <t>보마가될인재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>26조 6757억 2478만</t>
-  </si>
-  <si>
-    <t>탱탱볼탱탱볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>25조 2007억 355만</t>
-  </si>
-  <si>
-    <t>기차아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B0%A8%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>21조 5370억 1579만</t>
-  </si>
-  <si>
-    <t>구뺑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
-  </si>
-  <si>
-    <t>18조 5435억 6534만</t>
-  </si>
-  <si>
-    <t>이서지용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%9C%EC%A7%80%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>14조 7080억 4787만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>4경 3707조 2620억 9240만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>1경 51조 1568억 2849만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>5117조 5958억 6146만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>2532조 2373억 4043만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>2030조 6297억 4815만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>1775조 9991억 8579만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1745조 689억 2967만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>1226조 1409억 3217만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1100조 7691억 366만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>1009조 7065억 2372만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>805조 3347억 6173만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>796조 7562억 1221만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>576조 3578억 3259만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>478조 7718억 6899만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>199조 9367억 4325만</t>
-  </si>
-  <si>
-    <t>륵스리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B5%EC%8A%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>188조 934억 8649만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>122조 6504억 8335만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>91조 768억 8769만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>86조 918억 7363만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>78조 9603억 8863만</t>
-  </si>
-  <si>
-    <t>라흐S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
-  </si>
-  <si>
     <t>70조 1472억 8337만</t>
   </si>
   <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>68조 8334억 3382만</t>
-  </si>
-  <si>
     <t>26조선</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
   </si>
   <si>
-    <t>59조 629억 3728만</t>
+    <t>65조 5913억 2358만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>55조 5842억 8873만</t>
+    <t>58조 1801억 5553만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>45조 7141억 4410만</t>
+    <t>57조 7610억 8802만</t>
   </si>
   <si>
     <t>브깃</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>29조 3438억 1686만</t>
+    <t>32조 2986억 1846만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
   </si>
   <si>
-    <t>4경 9204조 937억 4909만</t>
+    <t>5경 8186조 6798억 750만</t>
   </si>
   <si>
     <t>키노눙</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
   </si>
   <si>
-    <t>1경 8332조 6943억 3224만</t>
+    <t>1경 8334조 3386억 5885만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>1512조 5812억 3348만</t>
+    <t>1660조 4260억 845만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
@@ -1827,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1096조 8111억 4520만</t>
+    <t>1101조 2050억 1239만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1836,7 +1836,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>444조 1910억 2693만</t>
+    <t>497조 8703억 1088만</t>
+  </si>
+  <si>
+    <t>갓쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>344조 3485억 1584만</t>
   </si>
   <si>
     <t>김모나</t>
@@ -1845,7 +1854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
   </si>
   <si>
-    <t>331조 4025억 9550만</t>
+    <t>332조 2079억 8779만</t>
   </si>
   <si>
     <t>쏘세용</t>
@@ -1857,15 +1866,6 @@
     <t>310조 9348억 7972만</t>
   </si>
   <si>
-    <t>갓쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>300조 8636억 9018만</t>
-  </si>
-  <si>
     <t>퀸돈대통</t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>198조 959억 2783만</t>
+    <t>205조 9666억 8724만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1890,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>143조 9499억 1569만</t>
+    <t>144조 1504억 3072만</t>
   </si>
   <si>
     <t>우당탕탼</t>
@@ -1908,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>95조 5430억 1232만</t>
+    <t>96조 8340억 2822만</t>
   </si>
   <si>
     <t>잼이유</t>
@@ -1917,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
   </si>
   <si>
-    <t>67조 7486억 5797만</t>
+    <t>68조 6204억 7258만</t>
   </si>
   <si>
     <t>사철화</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
   </si>
   <si>
-    <t>51조 2209억 5329만</t>
+    <t>56조 239억 7473만</t>
   </si>
   <si>
     <t>얼음조아</t>
@@ -1944,7 +1944,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>45조 5820억 9822만</t>
+    <t>45조 8311억 1027만</t>
+  </si>
+  <si>
+    <t>커피숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
+  </si>
+  <si>
+    <t>27조 8048억 345만</t>
   </si>
   <si>
     <t>뵤으</t>
@@ -1953,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
   </si>
   <si>
-    <t>26조 1892억 2065만</t>
+    <t>26조 2248억 5501만</t>
   </si>
   <si>
     <t>Subaru</t>
@@ -1962,16 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=Subaru</t>
   </si>
   <si>
-    <t>25조 542억 916만</t>
-  </si>
-  <si>
-    <t>커피숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
-  </si>
-  <si>
-    <t>24조 2630억 1451만</t>
+    <t>25조 1401억 1826만</t>
   </si>
   <si>
     <t>도시리</t>
@@ -1989,7 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
   </si>
   <si>
-    <t>20조 6286억 190만</t>
+    <t>21조 3195억 6464만</t>
   </si>
   <si>
     <t>57년김춘배</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>18조 6341억 167만</t>
+    <t>18조 7798억 9957만</t>
   </si>
   <si>
     <t>시네루최</t>
@@ -2016,7 +2016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>12조 5504억 8355만</t>
+    <t>13조 8584억 1758만</t>
   </si>
   <si>
     <t>길원구함</t>
@@ -2052,7 +2052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>2036조 611억 2978만</t>
+    <t>2049조 5018억 5626만</t>
   </si>
   <si>
     <t>샤프리</t>
@@ -2079,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>455조 4744억 1423만</t>
+    <t>462조 9927억 5773만</t>
   </si>
   <si>
     <t>소잦ol</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>263조 4489억 2859만</t>
+    <t>268조 2011억 5138만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2097,7 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>224조 574억 5850만</t>
+    <t>235조 372억 7611만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2112,7 +2112,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>131조 8995억 3827만</t>
+    <t>133조 2933억 4161만</t>
+  </si>
+  <si>
+    <t>마리아네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
+  </si>
+  <si>
+    <t>86조 8622억 2854만</t>
   </si>
   <si>
     <t>포근한소리</t>
@@ -2121,16 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EA%B7%BC%ED%95%9C%EC%86%8C%EB%A6%AC</t>
   </si>
   <si>
-    <t>83조 6965억 8694만</t>
-  </si>
-  <si>
-    <t>마리아네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
-  </si>
-  <si>
-    <t>71조 1056억 4208만</t>
+    <t>85조 1243억 6551만</t>
   </si>
   <si>
     <t>본분</t>
@@ -2139,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B8%EB%B6%84</t>
   </si>
   <si>
-    <t>43조 3917억 7045만</t>
+    <t>50조 7961억 3821만</t>
   </si>
   <si>
     <t>잘스제</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>40조 339억 9271만</t>
+    <t>42조 7618억 2795만</t>
   </si>
   <si>
     <t>머수킹</t>
@@ -2160,6 +2160,15 @@
     <t>36조 9465억 8391만</t>
   </si>
   <si>
+    <t>외단</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
+  </si>
+  <si>
+    <t>33조 1898억 1686만</t>
+  </si>
+  <si>
     <t>못스제</t>
   </si>
   <si>
@@ -2175,16 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
   </si>
   <si>
-    <t>27조 1641억 7545만</t>
-  </si>
-  <si>
-    <t>외단</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%B8%EB%8B%A8</t>
-  </si>
-  <si>
-    <t>25조 4538억 9449만</t>
+    <t>28조 6143억 9548만</t>
   </si>
   <si>
     <t>1조투력찍었던</t>
@@ -2202,7 +2202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>21조 3040억 3330만</t>
+    <t>21조 6060억 2226만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2247,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
   </si>
   <si>
-    <t>10조 1299억 3132만</t>
+    <t>11조 5549억 7981만</t>
   </si>
   <si>
     <t>콩새우</t>
@@ -2265,7 +2265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
   </si>
   <si>
-    <t>7조 7937억 6259만</t>
+    <t>7조 8495억 621만</t>
   </si>
   <si>
     <t>킴카</t>
@@ -2647,7 +2647,7 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" customWidth="1"/>
     <col min="11" max="11" width="50.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -3007,7 +3007,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3290,10 +3290,10 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3304,16 +3304,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -3325,7 +3325,7 @@
         <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3336,25 +3336,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>130</v>
@@ -3418,7 +3418,7 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>139</v>
@@ -3450,7 +3450,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3479,13 +3479,13 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3496,28 +3496,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3528,25 +3528,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>156</v>
@@ -3578,7 +3578,7 @@
         <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>159</v>
@@ -3610,10 +3610,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3624,28 +3624,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3656,28 +3656,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3688,28 +3688,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3720,16 +3720,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -3741,7 +3741,7 @@
         <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3755,25 +3755,25 @@
         <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3784,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>184</v>
@@ -3802,7 +3802,7 @@
         <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>186</v>
@@ -3831,10 +3831,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>190</v>
@@ -3863,10 +3863,10 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>194</v>
@@ -3883,22 +3883,22 @@
         <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>198</v>
@@ -3912,28 +3912,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="G29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3944,7 +3944,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>203</v>
@@ -3994,7 +3994,7 @@
         <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>210</v>
@@ -4105,7 +4105,7 @@
         <v>211</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>105</v>
@@ -4268,7 +4268,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>115</v>
@@ -4335,7 +4335,7 @@
         <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>235</v>
@@ -4349,7 +4349,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>236</v>
@@ -4367,7 +4367,7 @@
         <v>95</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>238</v>
@@ -4381,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>239</v>
@@ -4399,7 +4399,7 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>241</v>
@@ -4428,10 +4428,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>244</v>
@@ -4460,10 +4460,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>247</v>
@@ -4492,10 +4492,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>250</v>
@@ -4541,7 +4541,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>254</v>
@@ -4559,7 +4559,7 @@
         <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>256</v>
@@ -4573,7 +4573,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>257</v>
@@ -4623,7 +4623,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>262</v>
@@ -4652,7 +4652,7 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>134</v>
@@ -4669,7 +4669,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>266</v>
@@ -4684,7 +4684,7 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>134</v>
@@ -4701,7 +4701,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>269</v>
@@ -4716,7 +4716,7 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>134</v>
@@ -4733,7 +4733,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>272</v>
@@ -4748,10 +4748,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>274</v>
@@ -4765,7 +4765,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>275</v>
@@ -4780,10 +4780,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>277</v>
@@ -4812,10 +4812,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>280</v>
@@ -4829,7 +4829,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>281</v>
@@ -4844,10 +4844,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>283</v>
@@ -4876,10 +4876,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>286</v>
@@ -4911,7 +4911,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>289</v>
@@ -4943,7 +4943,7 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>292</v>
@@ -4957,7 +4957,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>293</v>
@@ -4975,10 +4975,10 @@
         <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4989,25 +4989,25 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
@@ -5036,10 +5036,10 @@
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>302</v>
@@ -5185,7 +5185,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>212</v>
@@ -5249,7 +5249,7 @@
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>222</v>
@@ -5284,7 +5284,7 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>317</v>
@@ -5316,7 +5316,7 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>320</v>
@@ -5348,7 +5348,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5377,7 +5377,7 @@
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>90</v>
@@ -5394,7 +5394,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>327</v>
@@ -5412,7 +5412,7 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>329</v>
@@ -5426,7 +5426,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>330</v>
@@ -5444,7 +5444,7 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -5476,7 +5476,7 @@
         <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>335</v>
@@ -5505,10 +5505,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>338</v>
@@ -5537,10 +5537,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -5569,13 +5569,13 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5586,28 +5586,28 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5618,25 +5618,25 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>351</v>
@@ -5665,10 +5665,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>298</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>354</v>
@@ -5697,10 +5697,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>295</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>357</v>
@@ -5714,7 +5714,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>358</v>
@@ -5729,10 +5729,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>360</v>
@@ -5746,7 +5746,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>361</v>
@@ -5764,7 +5764,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>363</v>
@@ -5778,7 +5778,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>364</v>
@@ -5796,7 +5796,7 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>366</v>
@@ -5810,7 +5810,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>367</v>
@@ -5825,10 +5825,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>369</v>
@@ -5857,10 +5857,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>372</v>
@@ -5874,7 +5874,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>373</v>
@@ -5892,7 +5892,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>375</v>
@@ -5921,7 +5921,7 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>205</v>
@@ -5953,13 +5953,13 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5973,13 +5973,13 @@
         <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -5988,10 +5988,10 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6002,28 +6002,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6034,16 +6034,16 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -6052,10 +6052,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6075,19 +6075,19 @@
         <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6186,13 +6186,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -6204,7 +6204,7 @@
         <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6218,13 +6218,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -6236,7 +6236,7 @@
         <v>212</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6250,13 +6250,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -6268,7 +6268,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6282,13 +6282,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -6300,7 +6300,7 @@
         <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6314,13 +6314,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -6332,7 +6332,7 @@
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6346,13 +6346,13 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -6364,7 +6364,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6378,13 +6378,13 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -6393,10 +6393,10 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6410,13 +6410,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -6425,10 +6425,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6439,16 +6439,16 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -6457,10 +6457,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6471,28 +6471,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>424</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6512,19 +6512,19 @@
         <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6538,25 +6538,25 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6570,25 +6570,25 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>432</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6602,25 +6602,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6631,16 +6631,16 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -6652,7 +6652,7 @@
         <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6663,28 +6663,28 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6698,13 +6698,13 @@
         <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -6716,7 +6716,7 @@
         <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6730,13 +6730,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -6745,10 +6745,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6759,28 +6759,28 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6791,28 +6791,28 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6823,16 +6823,16 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -6841,10 +6841,10 @@
         <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6855,16 +6855,16 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -6873,10 +6873,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6890,25 +6890,25 @@
         <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6919,28 +6919,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6954,25 +6954,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6986,25 +6986,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7018,13 +7018,13 @@
         <v>195</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -7033,10 +7033,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7047,16 +7047,16 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -7065,10 +7065,10 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7079,16 +7079,16 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -7097,10 +7097,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7114,25 +7114,25 @@
         <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7231,13 +7231,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -7246,10 +7246,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>488</v>
+        <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7269,19 +7269,19 @@
         <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7295,13 +7295,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -7313,7 +7313,7 @@
         <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7327,13 +7327,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7345,7 +7345,7 @@
         <v>115</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7359,13 +7359,13 @@
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -7377,7 +7377,7 @@
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7391,13 +7391,13 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -7409,7 +7409,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7423,13 +7423,13 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -7441,7 +7441,7 @@
         <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7455,13 +7455,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -7473,7 +7473,7 @@
         <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7484,28 +7484,28 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7516,16 +7516,16 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -7534,10 +7534,10 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7551,25 +7551,25 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7583,25 +7583,25 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7615,13 +7615,13 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -7630,10 +7630,10 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7647,13 +7647,13 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -7665,7 +7665,7 @@
         <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7676,16 +7676,16 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -7697,7 +7697,7 @@
         <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7708,16 +7708,16 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -7729,7 +7729,7 @@
         <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7743,25 +7743,25 @@
         <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7775,13 +7775,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -7790,10 +7790,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7804,28 +7804,28 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7836,28 +7836,28 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7868,16 +7868,16 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -7886,10 +7886,10 @@
         <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>381</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7900,16 +7900,16 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -7918,7 +7918,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>550</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>551</v>
@@ -7950,7 +7950,7 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>554</v>
@@ -7964,7 +7964,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>555</v>
@@ -7982,7 +7982,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>557</v>
@@ -8014,7 +8014,7 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>560</v>
@@ -8046,7 +8046,7 @@
         <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>295</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>563</v>
@@ -8075,10 +8075,10 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>566</v>
@@ -8092,7 +8092,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>567</v>
@@ -8107,10 +8107,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>569</v>
@@ -8124,7 +8124,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>570</v>
@@ -8139,10 +8139,10 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>572</v>
@@ -8171,7 +8171,7 @@
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>205</v>
@@ -8291,7 +8291,7 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>578</v>
@@ -8320,10 +8320,10 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>581</v>
@@ -8355,7 +8355,7 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>584</v>
@@ -8384,7 +8384,7 @@
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>115</v>
@@ -8451,7 +8451,7 @@
         <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>593</v>
@@ -8477,7 +8477,7 @@
         <v>594</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>105</v>
@@ -8515,7 +8515,7 @@
         <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>598</v>
@@ -8529,7 +8529,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>599</v>
@@ -8561,7 +8561,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>602</v>
@@ -8576,10 +8576,10 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>604</v>
@@ -8608,10 +8608,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>607</v>
@@ -8640,7 +8640,7 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>134</v>
@@ -8675,7 +8675,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>613</v>
@@ -8721,7 +8721,7 @@
         <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>617</v>
@@ -8736,10 +8736,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>619</v>
@@ -8753,7 +8753,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>620</v>
@@ -8768,10 +8768,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>622</v>
@@ -8800,10 +8800,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>625</v>
@@ -8835,7 +8835,7 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>628</v>
@@ -8849,7 +8849,7 @@
         <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>629</v>
@@ -8864,10 +8864,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>631</v>
@@ -8881,7 +8881,7 @@
         <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>632</v>
@@ -8899,7 +8899,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>205</v>
+        <v>298</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>634</v>
@@ -8913,7 +8913,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>635</v>
@@ -8928,10 +8928,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>637</v>
@@ -8945,7 +8945,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>638</v>
@@ -8960,10 +8960,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>350</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>640</v>
@@ -8992,10 +8992,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>643</v>
@@ -9009,7 +9009,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>644</v>
@@ -9024,10 +9024,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>205</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>646</v>
@@ -9091,7 +9091,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>652</v>
@@ -9137,7 +9137,7 @@
         <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>656</v>
@@ -9155,7 +9155,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>658</v>
@@ -9169,7 +9169,7 @@
         <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>659</v>
@@ -9187,7 +9187,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>661</v>
@@ -9367,7 +9367,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>670</v>
@@ -9463,7 +9463,7 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>679</v>
@@ -9495,7 +9495,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>682</v>
@@ -9541,7 +9541,7 @@
         <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>686</v>
@@ -9559,7 +9559,7 @@
         <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>688</v>
@@ -9573,7 +9573,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>689</v>
@@ -9588,10 +9588,10 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>691</v>
@@ -9617,13 +9617,13 @@
         <v>692</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>693</v>
@@ -9652,10 +9652,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>696</v>
@@ -9684,10 +9684,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>295</v>
+        <v>193</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>699</v>
@@ -9716,7 +9716,7 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>205</v>
@@ -9733,7 +9733,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>703</v>
@@ -9751,7 +9751,7 @@
         <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>705</v>
@@ -9765,7 +9765,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>706</v>
@@ -9812,10 +9812,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>711</v>
@@ -9844,10 +9844,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>714</v>
@@ -9861,7 +9861,7 @@
         <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>715</v>
@@ -9879,7 +9879,7 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>381</v>
+        <v>298</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>717</v>
@@ -9893,7 +9893,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>718</v>
@@ -9925,7 +9925,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>721</v>
@@ -9940,7 +9940,7 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>205</v>
@@ -9957,7 +9957,7 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>724</v>
@@ -9972,10 +9972,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>726</v>
@@ -10007,7 +10007,7 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>381</v>
+        <v>205</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>729</v>
@@ -10021,7 +10021,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>730</v>
@@ -10039,7 +10039,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>732</v>
@@ -10071,7 +10071,7 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>735</v>
@@ -10103,7 +10103,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>738</v>
@@ -10135,7 +10135,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>741</v>
@@ -10149,7 +10149,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>742</v>
@@ -10167,7 +10167,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>744</v>
@@ -10181,7 +10181,7 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>745</v>
@@ -10199,7 +10199,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>747</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>7경 9248조 6141억 4724만</t>
+    <t>7경 9712조 2552억 8223만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -105,7 +105,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.05.14</t>
+    <t>2026.05.15</t>
   </si>
   <si>
     <t>딸기키우기</t>
@@ -117,519 +117,519 @@
     <t>Scania 28</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>7경 3399조 9144억 8922만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>15경 3119조 3206억 9546만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>9경 6986조 2207억 6649만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>7경 5259조 7373억 6323만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>9경 4159조 6712억 3350만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10경 3091조 3069억 1729만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>3경 5513조 6807억 1084만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 914조 5474억 2169만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7431조 8591억 9954만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>4127조 8803억 2415만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>오리부엉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1223조 9852억 5985만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1074조 896억 9253만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>954조 3229억 9711만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>811조 9295억 7976만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>792조 7888억 2988만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>707조 263억 9474만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>476조 8196억 1413만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>453조 8899억 9995만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>438조 2316억 8493만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>411조 6165억 8335만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>362조 9074억 865만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>트라이던트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>330조 8081억 5518만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>308조 4617억 340만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>307조 6736억 3797만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>305조 2441억 9600만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>156조 2682억 1016만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>147조 1131억 168만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>92조 2004억 2098만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>90조 1641억 8803만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>87조 5947억 8692만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>69조 8370억 2136만</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>6경 9604조 5236억 1538만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>15경 2785조 7641억 3752만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>9경 3474조 4154억 7447만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>7경 5173조 8231억 3465만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>9경 3541조 1252억 8295만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>9경 9291조 7559억 1810만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3경 5513조 6807억 1084만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 914조 5474억 2169만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7420조 1976억 5060만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3963조 8600억 6259만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>오리부엉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1194조 1815억 1689만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1074조 896억 9253만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>954조 3229억 9711만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>811조 9295억 7976만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>694조 653억 200만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>646조 2693억 6314만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>453조 8899억 9995만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>438조 2316억 8493만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>424조 8134억 6221만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>411조 6165억 8335만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>346조 718억 3269만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>트라이던트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>319조 6566억 3917만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>308조 4617억 340만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>306조 4721억 6101만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>296조 8012억 4137만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>156조 2682억 1016만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>146조 8630억 5381만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>90조 3578억 9631만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>88조 1693억 8227만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>87조 5947억 8692만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>68조 9582억 9227만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
@@ -642,6 +642,18 @@
     <t>29</t>
   </si>
   <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>56조 1609억 5738만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -654,310 +666,298 @@
     <t>53조 811억 6540만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>52조 897억 1819만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
   </si>
   <si>
+    <t>4경 9475조 1314억 7511만</t>
+  </si>
+  <si>
+    <t>쥬정뱅이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6169조 4931억 150만</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3208조 3176억 9005만</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>2483조 9523억 830만</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>2287조 9054억 1438만</t>
+  </si>
+  <si>
+    <t>쑥국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>1510조 3216억 6613만</t>
+  </si>
+  <si>
+    <t>린뜌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1156조 9억 4305만</t>
+  </si>
+  <si>
+    <t>냉도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
+  </si>
+  <si>
+    <t>656조 9558억 6537만</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>637조 576억 6413만</t>
+  </si>
+  <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>617조 2885억 7558만</t>
+  </si>
+  <si>
+    <t>엔젤가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>521조 2139억 1621만</t>
+  </si>
+  <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>496조 8224억 519만</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>491조 3307억 6609만</t>
+  </si>
+  <si>
+    <t>피치에이드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>459조 5824억 6646만</t>
+  </si>
+  <si>
+    <t>핫장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>415조 9967억 3924만</t>
+  </si>
+  <si>
+    <t>키은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>289조 5814억 5826만</t>
+  </si>
+  <si>
+    <t>잉잉기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>263조 4954억 803만</t>
+  </si>
+  <si>
+    <t>사마련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>233조 7154억 7456만</t>
+  </si>
+  <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>233조 5121억 7783만</t>
+  </si>
+  <si>
+    <t>헛점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
+  </si>
+  <si>
+    <t>220조 4844억 2901만</t>
+  </si>
+  <si>
+    <t>개점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
+  </si>
+  <si>
+    <t>214조 79억 4060만</t>
+  </si>
+  <si>
+    <t>앨리스빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>212조 5875억 9857만</t>
+  </si>
+  <si>
+    <t>쵸꼬님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>205조 8807억 5331만</t>
+  </si>
+  <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>199조 9599억 432만</t>
+  </si>
+  <si>
+    <t>81학찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>167조 6436억 2625만</t>
+  </si>
+  <si>
+    <t>챠재범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
+  </si>
+  <si>
+    <t>140조 4932억 7375만</t>
+  </si>
+  <si>
+    <t>머쓰윽타드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
+  </si>
+  <si>
+    <t>132조 6602억 1746만</t>
+  </si>
+  <si>
+    <t>핫딜만삼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
+  </si>
+  <si>
+    <t>106조 8596억 2319만</t>
+  </si>
+  <si>
+    <t>핫두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>100조 1050억 8254만</t>
+  </si>
+  <si>
+    <t>샤갈츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
+  </si>
+  <si>
+    <t>91조 5565억 2461만</t>
+  </si>
+  <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>10경 4463조 7733억 6212만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>4경 6246조 5329억 6651만</t>
-  </si>
-  <si>
-    <t>쥬정뱅이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5918조 8920억 9178만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3181조 2698억 4745만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2385조 2517억 7689만</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>2287조 9054억 1438만</t>
-  </si>
-  <si>
-    <t>쑥국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>1506조 4854억 4672만</t>
-  </si>
-  <si>
-    <t>린뜌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
-  </si>
-  <si>
-    <t>1150조 3685억 8626만</t>
-  </si>
-  <si>
-    <t>냉도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
-  </si>
-  <si>
-    <t>656조 9558억 6537만</t>
-  </si>
-  <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>621조 3825억 5983만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>617조 2885억 7558만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>496조 154억 9234만</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>491조 3307억 6609만</t>
-  </si>
-  <si>
-    <t>엔젤가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>478조 3554억 6735만</t>
-  </si>
-  <si>
-    <t>피치에이드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>454조 9016억 8346만</t>
-  </si>
-  <si>
-    <t>핫장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>415조 9967억 3924만</t>
-  </si>
-  <si>
-    <t>키은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>274조 4068억 5151만</t>
-  </si>
-  <si>
-    <t>잉잉기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>251조 2235억 1539만</t>
-  </si>
-  <si>
-    <t>사마련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>233조 7154억 7456만</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>233조 5121억 7783만</t>
-  </si>
-  <si>
-    <t>헛점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
-  </si>
-  <si>
-    <t>220조 4844억 2901만</t>
-  </si>
-  <si>
-    <t>개점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
-  </si>
-  <si>
-    <t>214조 79억 4060만</t>
-  </si>
-  <si>
-    <t>쵸꼬님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>205조 6769억 6188만</t>
-  </si>
-  <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>195조 4146억 3879만</t>
-  </si>
-  <si>
-    <t>81학찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>167조 6436억 2625만</t>
-  </si>
-  <si>
-    <t>챠재범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
-  </si>
-  <si>
-    <t>137조 9092억 3023만</t>
-  </si>
-  <si>
-    <t>앨리스빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>136조 5819억 1543만</t>
-  </si>
-  <si>
-    <t>머쓰윽타드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
-  </si>
-  <si>
-    <t>126조 4923억 4416만</t>
-  </si>
-  <si>
-    <t>핫딜만삼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
-  </si>
-  <si>
-    <t>106조 8596억 2319만</t>
-  </si>
-  <si>
-    <t>핫두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>100조 1050억 8254만</t>
-  </si>
-  <si>
-    <t>샤갈츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
-  </si>
-  <si>
-    <t>91조 5565억 2461만</t>
-  </si>
-  <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>10경 4463조 7733억 6212만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>3경 2586조 7910억 130만</t>
+    <t>3경 2880조 6230억 615만</t>
   </si>
   <si>
     <t>실민</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
   </si>
   <si>
-    <t>267조 7968억 6997만</t>
+    <t>268조 8777억 5698만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1056,7 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>233조 5011억 2014만</t>
+    <t>234조 3201억 854만</t>
   </si>
   <si>
     <t>경특</t>
@@ -1095,7 +1095,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>125조 9683억 8296만</t>
+    <t>132조 4026억 7303만</t>
+  </si>
+  <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>129조 83억 2195만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1104,16 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>123조 2333억 2843만</t>
-  </si>
-  <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>116조 8434억 4188만</t>
+    <t>125조 603억 5184만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>108조 3712억 1332만</t>
+    <t>119조 4338억 7232만</t>
   </si>
   <si>
     <t>벨히</t>
@@ -1149,7 +1149,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
   </si>
   <si>
-    <t>53조 2608억 9403만</t>
+    <t>53조 9165억 7906만</t>
+  </si>
+  <si>
+    <t>빠나쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>40조 3575억 5906만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1161,22 +1170,13 @@
     <t>39조 3228억 7888만</t>
   </si>
   <si>
-    <t>빠나쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>36조 9918억 3341만</t>
-  </si>
-  <si>
     <t>강한고등어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>18조 7042억 6495만</t>
+    <t>20조 545억 1474만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1188,7 +1188,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>12조 6867억 401만</t>
+    <t>13조 2272억 3403만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>5조 5199억 3952만</t>
+    <t>5조 5278억 4929만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1224,7 +1224,7 @@
     <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
   </si>
   <si>
-    <t>3경 4504조 1799억 176만</t>
+    <t>3경 5820조 227억 1154만</t>
   </si>
   <si>
     <t>멸국</t>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
   </si>
   <si>
-    <t>2경 5450조 3097억 9239만</t>
+    <t>2경 5463조 8075억 3440만</t>
   </si>
   <si>
     <t>NUKE</t>
@@ -1242,7 +1242,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>1경 6113조 5145억 6321만</t>
+    <t>1경 6949조 3854억 3582만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>6301조 7323억 1594만</t>
+    <t>7141조 7308억 6306만</t>
   </si>
   <si>
     <t>픠즈</t>
@@ -1260,7 +1260,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>1526조 7136억 7184만</t>
+    <t>1543조 7551억 8482만</t>
+  </si>
+  <si>
+    <t>S2베코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
+  </si>
+  <si>
+    <t>1449조 9818억 5066만</t>
   </si>
   <si>
     <t>환불한너잉</t>
@@ -1269,16 +1278,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%ED%95%9C%EB%84%88%EC%9E%89</t>
   </si>
   <si>
-    <t>1387조 5965억 1147만</t>
-  </si>
-  <si>
-    <t>S2베코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
-  </si>
-  <si>
-    <t>1335조 1649억 624만</t>
+    <t>1442조 628억 5329만</t>
   </si>
   <si>
     <t>아투피</t>
@@ -1287,7 +1287,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
   </si>
   <si>
-    <t>1148조 8112억 6056만</t>
+    <t>1402조 2407억 157만</t>
   </si>
   <si>
     <t>널비</t>
@@ -1305,13 +1305,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>968조 4710억 3658만</t>
+    <t>970조 1753억 4722만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
   </si>
   <si>
-    <t>862조 7784억 6240만</t>
+    <t>864조 4216억 9237만</t>
   </si>
   <si>
     <t>백히로</t>
@@ -1320,7 +1320,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>449조 5247억 8928만</t>
+    <t>459조 2880억 546만</t>
   </si>
   <si>
     <t>뷰질</t>
@@ -1341,7 +1341,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>348조 615억 5196만</t>
+    <t>350조 8823억 93만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1359,7 +1359,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>174조 2413억 9336만</t>
+    <t>189조 7900억 1786만</t>
   </si>
   <si>
     <t>무썬</t>
@@ -1368,7 +1368,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
   </si>
   <si>
-    <t>167조 1050억 94만</t>
+    <t>179조 6205억 5618만</t>
   </si>
   <si>
     <t>맥맥</t>
@@ -1377,7 +1377,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
   </si>
   <si>
-    <t>142조 3917억 4769만</t>
+    <t>143조 4785억 4970만</t>
   </si>
   <si>
     <t>성칙이</t>
@@ -1404,7 +1404,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>92조 31억 6115만</t>
+    <t>103조 430억 9139만</t>
   </si>
   <si>
     <t>kiaer</t>
@@ -1413,7 +1413,7 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>84조 2647억 3492만</t>
+    <t>87조 9127억 8755만</t>
   </si>
   <si>
     <t>숔숔숔숔</t>
@@ -1422,7 +1422,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>70조 3988억 5686만</t>
+    <t>74조 1321억 5923만</t>
   </si>
   <si>
     <t>안재똥</t>
@@ -1440,7 +1440,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
   </si>
   <si>
-    <t>37조 6312억 4077만</t>
+    <t>39조 835억 6119만</t>
   </si>
   <si>
     <t>보마가될인재</t>
@@ -1449,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
   </si>
   <si>
-    <t>27조 3546억 3878만</t>
+    <t>27조 8516억 579만</t>
   </si>
   <si>
     <t>탱탱볼탱탱볼</t>
@@ -1458,7 +1458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
   </si>
   <si>
-    <t>25조 3530억 1424만</t>
+    <t>25조 8247억 7168만</t>
   </si>
   <si>
     <t>기차아저씨</t>
@@ -1476,7 +1476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>19조 9877억 2122만</t>
+    <t>20조 1935억 7880만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1521,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>2532조 2373억 4043만</t>
+    <t>2535조 1401억 3160만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1533,22 +1533,22 @@
     <t>2030조 6297억 4815만</t>
   </si>
   <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1841조 1563억 9683만</t>
+  </si>
+  <si>
     <t>26길초</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>1806조 8755억 3068만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1784조 9224억 69만</t>
+    <t>1814조 2840억 9265만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1557,7 +1557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>1228조 3761억 3124만</t>
+    <t>1230조 4957억 4952만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1566,7 +1566,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>1129조 3231억 8018만</t>
+    <t>1133조 6489억 3302만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1611,7 +1611,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>481조 1302억 1440만</t>
+    <t>481조 7818억 7594만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1638,7 +1638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
   </si>
   <si>
-    <t>122조 6863억 1126만</t>
+    <t>123조 5969억 2392만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1656,7 +1656,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>88조 5930억 3627만</t>
+    <t>88조 8146억 7801만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1665,7 +1665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
   </si>
   <si>
-    <t>78조 9603억 8863만</t>
+    <t>84조 3496억 599만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1674,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>75조 1071억 9773만</t>
+    <t>78조 8845억 758만</t>
   </si>
   <si>
     <t>라흐S2</t>
@@ -1683,313 +1683,313 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%9D%90S2</t>
   </si>
   <si>
+    <t>70조 1472억 8337만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>65조 5913억 2358만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>59조 9574억 1766만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>58조 5741억 7634만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>57조 9078억 5041만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>38조 8993억 8861만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>32조 3476억 5895만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>25조 3702억 7718만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>16조 3555억 1942만</t>
+  </si>
+  <si>
+    <t>힐줄까</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
+  </si>
+  <si>
+    <t>5경 8640조 6567억 4680만</t>
+  </si>
+  <si>
+    <t>키노눙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
+  </si>
+  <si>
+    <t>1경 8334조 3386억 5885만</t>
+  </si>
+  <si>
+    <t>Rahee</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
+  </si>
+  <si>
+    <t>4608조 9514억 3015만</t>
+  </si>
+  <si>
+    <t>한마드릴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
+  </si>
+  <si>
+    <t>3422조 1776억 1291만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2100조 9602억 4443만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>1688조 2047억 3073만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>1490조 8551억 4351만</t>
+  </si>
+  <si>
+    <t>윤돌이굴돌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1102조 8075억 3116만</t>
+  </si>
+  <si>
+    <t>다끝남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>497조 8703억 1088만</t>
+  </si>
+  <si>
+    <t>갓쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>344조 3485억 1584만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>337조 176억 7846만</t>
+  </si>
+  <si>
+    <t>쏘세용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>310조 9348억 7972만</t>
+  </si>
+  <si>
+    <t>퀸돈대통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
+  </si>
+  <si>
+    <t>288조 5253억 3633만</t>
+  </si>
+  <si>
+    <t>김컁구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>219조 1882억 4687만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>144조 7934억 6306만</t>
+  </si>
+  <si>
+    <t>우당탕탼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
+  </si>
+  <si>
+    <t>118조 2427억 4076만</t>
+  </si>
+  <si>
+    <t>표창빌런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
+  </si>
+  <si>
+    <t>97조 306억 5919만</t>
+  </si>
+  <si>
+    <t>잼이유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>68조 9635억 2408만</t>
+  </si>
+  <si>
+    <t>사철화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>63조 5113억 4896만</t>
+  </si>
+  <si>
+    <t>붕붕월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>56조 239억 7473만</t>
+  </si>
+  <si>
+    <t>얼음조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>51조 2885억 1759만</t>
+  </si>
+  <si>
+    <t>커피숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
+  </si>
+  <si>
+    <t>27조 8048억 345만</t>
+  </si>
+  <si>
+    <t>뵤으</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
+  </si>
+  <si>
+    <t>26조 2248억 5501만</t>
+  </si>
+  <si>
+    <t>Subaru</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
+  </si>
+  <si>
+    <t>25조 2117억 1423만</t>
+  </si>
+  <si>
+    <t>도시리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>22조 9492억 5119만</t>
+  </si>
+  <si>
+    <t>킴밍끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>70조 1472억 8337만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>65조 5913억 2358만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>58조 5741억 7634만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>58조 1801억 5553만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>57조 7610억 8802만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>38조 8993억 8861만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>32조 2986억 1846만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>25조 3702억 7718만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>16조 3555억 1942만</t>
-  </si>
-  <si>
-    <t>힐줄까</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
-  </si>
-  <si>
-    <t>5경 8186조 6798억 750만</t>
-  </si>
-  <si>
-    <t>키노눙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%85%B8%EB%88%99</t>
-  </si>
-  <si>
-    <t>1경 8334조 3386억 5885만</t>
-  </si>
-  <si>
-    <t>Rahee</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
-  </si>
-  <si>
-    <t>4608조 9514억 3015만</t>
-  </si>
-  <si>
-    <t>한마드릴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%88%EB%93%9C%EB%A6%B4</t>
-  </si>
-  <si>
-    <t>3322조 9648억 9158만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2100조 9602억 4443만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>1660조 4260억 845만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1490조 8551억 4351만</t>
-  </si>
-  <si>
-    <t>윤돌이굴돌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1101조 2050억 1239만</t>
-  </si>
-  <si>
-    <t>다끝남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>497조 8703억 1088만</t>
-  </si>
-  <si>
-    <t>갓쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>344조 3485억 1584만</t>
-  </si>
-  <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>332조 2079억 8779만</t>
-  </si>
-  <si>
-    <t>쏘세용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%84%B8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>310조 9348억 7972만</t>
-  </si>
-  <si>
-    <t>퀸돈대통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8F%88%EB%8C%80%ED%86%B5</t>
-  </si>
-  <si>
-    <t>288조 5253억 3633만</t>
-  </si>
-  <si>
-    <t>김컁구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>205조 9666억 8724만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>144조 1504억 3072만</t>
-  </si>
-  <si>
-    <t>우당탕탼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
-  </si>
-  <si>
-    <t>109조 8721억 2888만</t>
-  </si>
-  <si>
-    <t>표창빌런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>96조 8340억 2822만</t>
-  </si>
-  <si>
-    <t>잼이유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>68조 6204억 7258만</t>
-  </si>
-  <si>
-    <t>사철화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>63조 5113억 4896만</t>
-  </si>
-  <si>
-    <t>붕붕월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>56조 239억 7473만</t>
-  </si>
-  <si>
-    <t>얼음조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>45조 8311억 1027만</t>
-  </si>
-  <si>
-    <t>커피숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EC%88%8D</t>
-  </si>
-  <si>
-    <t>27조 8048억 345만</t>
-  </si>
-  <si>
-    <t>뵤으</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B5%A4%EC%9C%BC</t>
-  </si>
-  <si>
-    <t>26조 2248억 5501만</t>
-  </si>
-  <si>
-    <t>Subaru</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
-  </si>
-  <si>
-    <t>25조 1401억 1826만</t>
-  </si>
-  <si>
-    <t>도시리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>22조 5703억 2791만</t>
-  </si>
-  <si>
-    <t>킴밍끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
-  </si>
-  <si>
-    <t>21조 3195억 6464만</t>
+    <t>22조 7916억 1972만</t>
   </si>
   <si>
     <t>57년김춘배</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>18조 7798억 9957만</t>
+    <t>19조 7903억 8984만</t>
   </si>
   <si>
     <t>시네루최</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%A0%A4%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 6353조 7834억 9002만</t>
+    <t>2경 9912조 2643억 881만</t>
   </si>
   <si>
     <t>메키멍</t>
@@ -2052,7 +2052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>2049조 5018억 5626만</t>
+    <t>2193조 2531억 2214만</t>
   </si>
   <si>
     <t>샤프리</t>
@@ -2079,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>462조 9927억 5773만</t>
+    <t>505조 2960억 1220만</t>
   </si>
   <si>
     <t>소잦ol</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>268조 2011억 5138만</t>
+    <t>289조 5792억 7570만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2112,7 +2112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>133조 2933억 4161만</t>
+    <t>138조 3174억 7293만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2121,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
   </si>
   <si>
-    <t>86조 8622억 2854만</t>
+    <t>87조 2035억 4809만</t>
   </si>
   <si>
     <t>포근한소리</t>
@@ -2133,6 +2133,15 @@
     <t>85조 1243억 6551만</t>
   </si>
   <si>
+    <t>잘스제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>51조 6548억 8869만</t>
+  </si>
+  <si>
     <t>본분</t>
   </si>
   <si>
@@ -2142,15 +2151,6 @@
     <t>50조 7961억 3821만</t>
   </si>
   <si>
-    <t>잘스제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>42조 7618억 2795만</t>
-  </si>
-  <si>
     <t>머수킹</t>
   </si>
   <si>
@@ -2169,6 +2169,15 @@
     <t>33조 1898억 1686만</t>
   </si>
   <si>
+    <t>로넌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
+  </si>
+  <si>
+    <t>32조 4393억 9810만</t>
+  </si>
+  <si>
     <t>못스제</t>
   </si>
   <si>
@@ -2178,15 +2187,6 @@
     <t>30조 191억 6568만</t>
   </si>
   <si>
-    <t>로넌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%84%8C</t>
-  </si>
-  <si>
-    <t>28조 6143억 9548만</t>
-  </si>
-  <si>
     <t>1조투력찍었던</t>
   </si>
   <si>
@@ -2202,7 +2202,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
   </si>
   <si>
-    <t>21조 6060억 2226만</t>
+    <t>22조 5268억 9024만</t>
+  </si>
+  <si>
+    <t>BudriQ</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
+  </si>
+  <si>
+    <t>22조 5189억 8076만</t>
   </si>
   <si>
     <t>겁재이</t>
@@ -2229,7 +2238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
   </si>
   <si>
-    <t>16조 2456억 440만</t>
+    <t>16조 2730억 1760만</t>
   </si>
   <si>
     <t>진우정</t>
@@ -2241,22 +2250,13 @@
     <t>13조 8549억 3735만</t>
   </si>
   <si>
-    <t>BudriQ</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=BudriQ</t>
-  </si>
-  <si>
-    <t>11조 5549억 7981만</t>
-  </si>
-  <si>
     <t>콩새우</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%A9%EC%83%88%EC%9A%B0</t>
   </si>
   <si>
-    <t>10조 377억 3373만</t>
+    <t>12조 6597억 2246만</t>
   </si>
   <si>
     <t>가겠네</t>
@@ -2265,7 +2265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
   </si>
   <si>
-    <t>7조 8495억 621만</t>
+    <t>8조 8078억 8915만</t>
   </si>
   <si>
     <t>킴카</t>
@@ -2274,7 +2274,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
   </si>
   <si>
-    <t>7조 5356억 6853만</t>
+    <t>7조 5970억 3624만</t>
   </si>
 </sst>
 </file>
@@ -3130,10 +3130,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3144,16 +3144,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -3162,10 +3162,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3176,25 +3176,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>106</v>
@@ -3223,7 +3223,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>110</v>
@@ -3386,10 +3386,10 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3400,16 +3400,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -3418,7 +3418,7 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>139</v>
@@ -3447,10 +3447,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3479,13 +3479,13 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3496,25 +3496,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>152</v>
@@ -3575,7 +3575,7 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>129</v>
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>168</v>
@@ -3656,28 +3656,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3688,28 +3688,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3720,7 +3720,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>177</v>
@@ -3738,7 +3738,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>179</v>
@@ -3752,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>180</v>
@@ -3784,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>184</v>
@@ -3799,7 +3799,7 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>163</v>
@@ -3880,28 +3880,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3912,7 +3912,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>23</v>
@@ -3959,13 +3959,13 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3976,25 +3976,25 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>210</v>
@@ -4108,13 +4108,13 @@
         <v>200</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4128,13 +4128,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -4143,10 +4143,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4160,13 +4160,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -4178,7 +4178,7 @@
         <v>115</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4189,16 +4189,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -4207,10 +4207,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4221,16 +4221,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -4242,7 +4242,7 @@
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4256,13 +4256,13 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -4274,7 +4274,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4288,13 +4288,13 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -4303,10 +4303,10 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4320,25 +4320,25 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4352,13 +4352,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -4370,7 +4370,7 @@
         <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4384,13 +4384,13 @@
         <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -4399,10 +4399,10 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4416,25 +4416,25 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4445,28 +4445,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4480,25 +4480,25 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4512,13 +4512,13 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -4527,10 +4527,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4541,16 +4541,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -4562,7 +4562,7 @@
         <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4576,13 +4576,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -4591,10 +4591,10 @@
         <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4608,13 +4608,13 @@
         <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -4623,10 +4623,10 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4640,13 +4640,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -4655,10 +4655,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4672,13 +4672,13 @@
         <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -4687,10 +4687,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4701,16 +4701,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -4719,10 +4719,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4733,16 +4733,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -4751,10 +4751,10 @@
         <v>182</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4765,28 +4765,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4797,28 +4797,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4829,28 +4829,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4864,25 +4864,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>285</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4896,25 +4896,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4925,16 +4925,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -4943,10 +4943,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4957,16 +4957,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -4978,7 +4978,7 @@
         <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4992,13 +4992,13 @@
         <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -5007,10 +5007,10 @@
         <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5021,16 +5021,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -5042,7 +5042,7 @@
         <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5141,13 +5141,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -5159,7 +5159,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5173,13 +5173,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -5188,7 +5188,7 @@
         <v>182</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>308</v>
@@ -5220,7 +5220,7 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>311</v>
@@ -5234,7 +5234,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>312</v>
@@ -5252,7 +5252,7 @@
         <v>182</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>314</v>
@@ -5266,7 +5266,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>315</v>
@@ -5348,7 +5348,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5380,7 +5380,7 @@
         <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>326</v>
@@ -5473,10 +5473,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>335</v>
@@ -5490,7 +5490,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>336</v>
@@ -5540,7 +5540,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -5569,7 +5569,7 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>163</v>
@@ -5586,7 +5586,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>345</v>
@@ -5601,7 +5601,7 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>163</v>
@@ -5665,10 +5665,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>298</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>354</v>
@@ -5697,10 +5697,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>357</v>
@@ -5729,10 +5729,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>360</v>
@@ -5746,7 +5746,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>361</v>
@@ -5778,7 +5778,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>364</v>
@@ -5793,7 +5793,7 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>193</v>
@@ -5810,7 +5810,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>367</v>
@@ -5828,7 +5828,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>369</v>
@@ -5842,7 +5842,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>370</v>
@@ -5874,7 +5874,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>373</v>
@@ -5889,10 +5889,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>375</v>
@@ -5921,10 +5921,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>205</v>
+        <v>297</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>378</v>
@@ -5956,7 +5956,7 @@
         <v>350</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>381</v>
@@ -5970,7 +5970,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>382</v>
@@ -6002,7 +6002,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>386</v>
@@ -6049,7 +6049,7 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>391</v>
@@ -6066,7 +6066,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>40</v>
@@ -6201,7 +6201,7 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>397</v>
@@ -6233,7 +6233,7 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>400</v>
@@ -6265,7 +6265,7 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>403</v>
@@ -6279,7 +6279,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>404</v>
@@ -6297,7 +6297,7 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>406</v>
@@ -6311,7 +6311,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>407</v>
@@ -6358,7 +6358,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>115</v>
@@ -6390,10 +6390,10 @@
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>415</v>
@@ -6457,7 +6457,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>421</v>
@@ -6535,7 +6535,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>427</v>
@@ -6582,7 +6582,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>110</v>
@@ -6617,7 +6617,7 @@
         <v>435</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>436</v>
@@ -6631,7 +6631,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>437</v>
@@ -6646,10 +6646,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>439</v>
@@ -6681,7 +6681,7 @@
         <v>189</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>442</v>
@@ -6713,7 +6713,7 @@
         <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>445</v>
@@ -6777,7 +6777,7 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>451</v>
@@ -6791,7 +6791,7 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>452</v>
@@ -6806,10 +6806,10 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>454</v>
@@ -6823,7 +6823,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>455</v>
@@ -6855,7 +6855,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>458</v>
@@ -6873,7 +6873,7 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>298</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>460</v>
@@ -6887,7 +6887,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>461</v>
@@ -6919,7 +6919,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>464</v>
@@ -6934,10 +6934,10 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>466</v>
@@ -7001,7 +7001,7 @@
         <v>128</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>472</v>
@@ -7015,7 +7015,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>473</v>
@@ -7033,7 +7033,7 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>475</v>
@@ -7047,7 +7047,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>476</v>
@@ -7062,10 +7062,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>478</v>
@@ -7097,7 +7097,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>481</v>
@@ -7111,7 +7111,7 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>482</v>
@@ -7126,10 +7126,10 @@
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>484</v>
@@ -7246,7 +7246,7 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>487</v>
@@ -7307,10 +7307,10 @@
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>493</v>
@@ -7324,7 +7324,7 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>494</v>
@@ -7356,7 +7356,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>497</v>
@@ -7371,7 +7371,7 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>115</v>
@@ -7403,7 +7403,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>115</v>
@@ -7435,7 +7435,7 @@
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>115</v>
@@ -7580,7 +7580,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>518</v>
@@ -7627,7 +7627,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>110</v>
@@ -7659,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>526</v>
@@ -7676,7 +7676,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>527</v>
@@ -7691,10 +7691,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>529</v>
@@ -7726,7 +7726,7 @@
         <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>532</v>
@@ -7819,7 +7819,7 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>163</v>
@@ -7836,7 +7836,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>542</v>
@@ -7854,7 +7854,7 @@
         <v>435</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>544</v>
@@ -7868,7 +7868,7 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>545</v>
@@ -7900,7 +7900,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>548</v>
@@ -7918,10 +7918,10 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7932,16 +7932,16 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -7953,7 +7953,7 @@
         <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7964,28 +7964,28 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7999,25 +7999,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8031,13 +8031,13 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -8049,7 +8049,7 @@
         <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8060,16 +8060,16 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -8078,10 +8078,10 @@
         <v>128</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8092,28 +8092,28 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8127,25 +8127,25 @@
         <v>202</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8156,28 +8156,28 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8276,13 +8276,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -8294,7 +8294,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8308,13 +8308,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -8326,7 +8326,7 @@
         <v>489</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8340,13 +8340,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8355,10 +8355,10 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8369,16 +8369,16 @@
         <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -8390,7 +8390,7 @@
         <v>115</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8401,16 +8401,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8422,7 +8422,7 @@
         <v>115</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8436,25 +8436,25 @@
         <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8474,19 +8474,19 @@
         <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8500,25 +8500,25 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8532,25 +8532,25 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8564,13 +8564,13 @@
         <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>603</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8579,10 +8579,10 @@
         <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8596,13 +8596,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8614,7 +8614,7 @@
         <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8625,28 +8625,28 @@
         <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8660,13 +8660,13 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -8678,7 +8678,7 @@
         <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8692,25 +8692,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8721,28 +8721,28 @@
         <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>618</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8756,13 +8756,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -8774,7 +8774,7 @@
         <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8788,13 +8788,13 @@
         <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -8806,7 +8806,7 @@
         <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8820,13 +8820,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8838,7 +8838,7 @@
         <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8852,25 +8852,25 @@
         <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>630</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>193</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8881,28 +8881,28 @@
         <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8913,28 +8913,28 @@
         <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>636</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8945,16 +8945,16 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -8963,10 +8963,10 @@
         <v>350</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8977,16 +8977,16 @@
         <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -8995,10 +8995,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9009,28 +9009,28 @@
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9044,13 +9044,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -9059,10 +9059,10 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9076,13 +9076,13 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -9091,7 +9091,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>652</v>
@@ -9105,7 +9105,7 @@
         <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>653</v>
@@ -9123,7 +9123,7 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>655</v>
@@ -9137,7 +9137,7 @@
         <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>656</v>
@@ -9152,10 +9152,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>658</v>
@@ -9187,7 +9187,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>661</v>
@@ -9303,7 +9303,7 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>664</v>
@@ -9335,7 +9335,7 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>667</v>
@@ -9381,7 +9381,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>671</v>
@@ -9399,7 +9399,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>673</v>
@@ -9413,7 +9413,7 @@
         <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>674</v>
@@ -9428,10 +9428,10 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>676</v>
@@ -9527,7 +9527,7 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>685</v>
@@ -9556,7 +9556,7 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>163</v>
@@ -9588,7 +9588,7 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>163</v>
@@ -9637,7 +9637,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>694</v>
@@ -9655,7 +9655,7 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>696</v>
@@ -9684,7 +9684,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>193</v>
@@ -9716,10 +9716,10 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>205</v>
+        <v>297</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>702</v>
@@ -9733,7 +9733,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>703</v>
@@ -9748,10 +9748,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>705</v>
@@ -9780,10 +9780,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>708</v>
@@ -9815,7 +9815,7 @@
         <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>711</v>
@@ -9844,10 +9844,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>714</v>
@@ -9876,10 +9876,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>717</v>
@@ -9893,7 +9893,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>718</v>
@@ -9911,7 +9911,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>720</v>
@@ -9925,7 +9925,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>721</v>
@@ -9943,7 +9943,7 @@
         <v>182</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>723</v>
@@ -9957,7 +9957,7 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>724</v>
@@ -9972,10 +9972,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>726</v>
@@ -9989,7 +9989,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>727</v>
@@ -10004,10 +10004,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>350</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>729</v>
@@ -10021,7 +10021,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>730</v>
@@ -10039,7 +10039,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>550</v>
+        <v>209</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>732</v>
@@ -10068,10 +10068,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>384</v>
+        <v>209</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>735</v>
@@ -10100,10 +10100,10 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>550</v>
+        <v>384</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>738</v>
@@ -10117,7 +10117,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>739</v>
@@ -10132,7 +10132,7 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>384</v>
@@ -10149,7 +10149,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>742</v>
@@ -10164,7 +10164,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>384</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="749">
   <si>
     <t>guild_name</t>
   </si>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>7경 9712조 2552억 8223만</t>
+    <t>7경 9850조 1886억 4529만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -105,7 +105,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.05.15</t>
+    <t>2026.05.16</t>
   </si>
   <si>
     <t>딸기키우기</t>
@@ -126,7 +126,7 @@
     <t>Lv.8</t>
   </si>
   <si>
-    <t>7경 3399조 9144억 8922만</t>
+    <t>7경 5060조 7518억 9559만</t>
   </si>
   <si>
     <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
@@ -141,438 +141,441 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>17경 241조 1254억 3924만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>10경 1292조 4019억 2755만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>7경 5666조 9054억 7698만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>9경 4191조 7738억 2037만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10경 4130조 1715억 1958만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>3경 5592조 7889억 7365만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 914조 5474억 2169만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7442조 8929억 4568만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>4129조 2553억 9084만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>오리부엉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1233조 1346억 5863만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1074조 896억 9253만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>954조 3229억 9711만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>811조 9295억 7976만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>795조 9442억 9462만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>711조 3418억 6684만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>476조 8196억 1413만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>453조 8899억 9995만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>438조 5517억 9938만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>411조 6165억 8335만</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>15경 3119조 3206억 9546만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>362조 9074억 865만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>트라이던트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>332조 1973억 1171만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>320조 9854억 4596만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>308조 4617억 340만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>305조 7514억 5636만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>156조 2682억 1016만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>9경 6986조 2207억 6649만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>7경 5259조 7373억 6323만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>9경 4159조 6712억 3350만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10경 3091조 3069억 1729만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3경 5513조 6807억 1084만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 914조 5474억 2169만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7431조 8591억 9954만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>4127조 8803억 2415만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>오리부엉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1223조 9852억 5985만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1074조 896억 9253만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>954조 3229억 9711만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>811조 9295억 7976만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>792조 7888억 2988만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>707조 263억 9474만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>476조 8196억 1413만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>453조 8899억 9995만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>438조 2316억 8493만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>411조 6165억 8335만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>362조 9074억 865만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>트라이던트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>330조 8081억 5518만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>308조 4617억 340만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>307조 6736억 3797만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>305조 2441억 9600만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>156조 2682억 1016만</t>
-  </si>
-  <si>
     <t>POSCO</t>
   </si>
   <si>
@@ -582,7 +585,19 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>147조 1131억 168만</t>
+    <t>149조 8311억 7292만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>96조 8587억 9464만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -591,7 +606,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>92조 2004억 2098만</t>
+    <t>92조 4757억 3454만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -603,19 +618,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>90조 1641억 8803만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>87조 5947억 8692만</t>
+    <t>90조 3499억 3851만</t>
   </si>
   <si>
     <t>포뇨야</t>
@@ -624,7 +627,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
   </si>
   <si>
-    <t>69조 8370억 2136만</t>
+    <t>71조 5603억 8398만</t>
   </si>
   <si>
     <t>28</t>
@@ -648,7 +651,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>56조 1609억 5738만</t>
+    <t>56조 2620억 6423만</t>
   </si>
   <si>
     <t>30</t>
@@ -669,7 +672,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
   </si>
   <si>
-    <t>4경 9475조 1314억 7511만</t>
+    <t>5경 55조 1425억 7737만</t>
   </si>
   <si>
     <t>쥬정뱅이</t>
@@ -678,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
   </si>
   <si>
-    <t>6169조 4931억 150만</t>
+    <t>6739조 8118억 4479만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -687,7 +690,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>3208조 3176억 9005만</t>
+    <t>3228조 4676억 3560만</t>
   </si>
   <si>
     <t>귀여워서미안</t>
@@ -696,7 +699,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
   </si>
   <si>
-    <t>2483조 9523억 830만</t>
+    <t>2799조 6857억 5214만</t>
   </si>
   <si>
     <t>밀프푸씨</t>
@@ -714,7 +717,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
   </si>
   <si>
-    <t>1510조 3216억 6613만</t>
+    <t>1513조 579억 3563만</t>
   </si>
   <si>
     <t>린뜌</t>
@@ -726,7 +729,16 @@
     <t>111</t>
   </si>
   <si>
-    <t>1156조 9억 4305만</t>
+    <t>1161조 8119억 5088만</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>671조 5924억 6971만</t>
   </si>
   <si>
     <t>냉도</t>
@@ -738,15 +750,6 @@
     <t>656조 9558억 6537만</t>
   </si>
   <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>637조 576억 6413만</t>
-  </si>
-  <si>
     <t>약해진쭌석</t>
   </si>
   <si>
@@ -762,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>521조 2139억 1621만</t>
+    <t>523조 901억 2403만</t>
   </si>
   <si>
     <t>노득</t>
@@ -771,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
   </si>
   <si>
-    <t>496조 8224억 519만</t>
+    <t>502조 5881억 8650만</t>
   </si>
   <si>
     <t>섴히</t>
@@ -789,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>459조 5824억 6646만</t>
+    <t>462조 7270억 1897만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -801,22 +804,22 @@
     <t>415조 9967억 3924만</t>
   </si>
   <si>
+    <t>잉잉기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>309조 7179억 7806만</t>
+  </si>
+  <si>
     <t>키은</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
   </si>
   <si>
-    <t>289조 5814억 5826만</t>
-  </si>
-  <si>
-    <t>잉잉기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>263조 4954억 803만</t>
+    <t>299조 431억 7332만</t>
   </si>
   <si>
     <t>사마련</t>
@@ -843,7 +846,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
   </si>
   <si>
-    <t>220조 4844억 2901만</t>
+    <t>221조 2769억 8033만</t>
   </si>
   <si>
     <t>개점</t>
@@ -852,7 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
   </si>
   <si>
-    <t>214조 79억 4060만</t>
+    <t>220조 9095억 1753만</t>
   </si>
   <si>
     <t>앨리스빌</t>
@@ -888,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
   </si>
   <si>
-    <t>167조 6436억 2625만</t>
+    <t>196조 4973억 8641만</t>
   </si>
   <si>
     <t>챠재범</t>
@@ -897,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>140조 4932억 7375만</t>
+    <t>149조 4516억 7157만</t>
   </si>
   <si>
     <t>머쓰윽타드</t>
@@ -906,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
   </si>
   <si>
-    <t>132조 6602억 1746만</t>
+    <t>146조 135억 7414만</t>
   </si>
   <si>
     <t>핫딜만삼</t>
@@ -915,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
   </si>
   <si>
-    <t>106조 8596억 2319만</t>
+    <t>107조 1900억 4990만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -936,16 +939,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
   </si>
   <si>
-    <t>91조 5565억 2461만</t>
-  </si>
-  <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>10경 4463조 7733억 6212만</t>
+    <t>97조 4377억 1675만</t>
+  </si>
+  <si>
+    <t>데카짱3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EC%B9%B4%EC%A7%B13</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>12경 970조 733억 4979만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -957,7 +963,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>3경 2880조 6230억 615만</t>
+    <t>3경 2947조 6339억 8616만</t>
   </si>
   <si>
     <t>실민</t>
@@ -984,7 +990,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>2520조 6545억 4022만</t>
+    <t>2908조 2716억 750만</t>
   </si>
   <si>
     <t>비트츄</t>
@@ -1047,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
   </si>
   <si>
-    <t>268조 8777억 5698만</t>
+    <t>311조 6199억 9097만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1056,7 +1062,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>234조 3201억 854만</t>
+    <t>246조 8973억 3128만</t>
+  </si>
+  <si>
+    <t>김대협</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
+  </si>
+  <si>
+    <t>195조 3747억 726만</t>
   </si>
   <si>
     <t>경특</t>
@@ -1065,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
   </si>
   <si>
-    <t>166조 292억 7674만</t>
+    <t>177조 5144억 4620만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -1074,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>164조 9595억 1451만</t>
+    <t>165조 4011억 665만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1089,6 +1104,15 @@
     <t>162조 9128억 357만</t>
   </si>
   <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>137조 6461억 9485만</t>
+  </si>
+  <si>
     <t>에망</t>
   </si>
   <si>
@@ -1098,24 +1122,6 @@
     <t>132조 4026억 7303만</t>
   </si>
   <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>129조 83억 2195만</t>
-  </si>
-  <si>
-    <t>김대협</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
-  </si>
-  <si>
-    <t>125조 603억 5184만</t>
-  </si>
-  <si>
     <t>봄녘</t>
   </si>
   <si>
@@ -1131,7 +1137,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%ED%9E%88</t>
   </si>
   <si>
-    <t>97조 5908억 118만</t>
+    <t>100조 9733억 9173만</t>
+  </si>
+  <si>
+    <t>만듀쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>59조 9083억 4710만</t>
   </si>
   <si>
     <t>봉합불가</t>
@@ -1140,16 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>54조 5956억 72만</t>
-  </si>
-  <si>
-    <t>만듀쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%93%80%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>53조 9165억 7906만</t>
+    <t>56조 5366억 4222만</t>
   </si>
   <si>
     <t>빠나쨩</t>
@@ -1158,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
   </si>
   <si>
-    <t>40조 3575억 5906만</t>
+    <t>43조 4744억 1835만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1176,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>20조 545억 1474만</t>
+    <t>20조 895억 5165만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1188,7 +1194,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>13조 2272억 3403만</t>
+    <t>13조 2668억 876만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1197,7 +1203,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>5조 5278억 4929만</t>
+    <t>5조 6796억 7614만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1209,13 +1215,13 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 1427억 9822만</t>
+    <t>3조 5466억 4961만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>1조 8676억 4550만</t>
+    <t>1조 8931억 2634만</t>
   </si>
   <si>
     <t>THE끌림</t>
@@ -1224,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=THE%EB%81%8C%EB%A6%BC</t>
   </si>
   <si>
-    <t>3경 5820조 227억 1154만</t>
+    <t>3경 9484조 987억 7273만</t>
   </si>
   <si>
     <t>멸국</t>
@@ -1233,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%B8%EA%B5%AD</t>
   </si>
   <si>
-    <t>2경 5463조 8075억 3440만</t>
+    <t>2경 5757조 9226억 3373만</t>
   </si>
   <si>
     <t>NUKE</t>
@@ -1242,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=NUKE</t>
   </si>
   <si>
-    <t>1경 6949조 3854억 3582만</t>
+    <t>1경 7084조 6002억 3706만</t>
   </si>
   <si>
     <t>쌔주</t>
@@ -1260,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>1543조 7551억 8482만</t>
+    <t>1547조 6184억 2408만</t>
   </si>
   <si>
     <t>S2베코</t>
@@ -1269,7 +1275,16 @@
     <t>https://mgf.gg/contents/character.php?n=S2%EB%B2%A0%EC%BD%94</t>
   </si>
   <si>
-    <t>1449조 9818억 5066만</t>
+    <t>1502조 4629억 2988만</t>
+  </si>
+  <si>
+    <t>아투피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
+  </si>
+  <si>
+    <t>1452조 4584억 7027만</t>
   </si>
   <si>
     <t>환불한너잉</t>
@@ -1281,15 +1296,6 @@
     <t>1442조 628억 5329만</t>
   </si>
   <si>
-    <t>아투피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%88%AC%ED%94%BC</t>
-  </si>
-  <si>
-    <t>1402조 2407억 157만</t>
-  </si>
-  <si>
     <t>널비</t>
   </si>
   <si>
@@ -1305,13 +1311,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>970조 1753억 4722만</t>
+    <t>970조 2810억 789만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
   </si>
   <si>
-    <t>864조 4216억 9237만</t>
+    <t>870조 1219억 8420만</t>
   </si>
   <si>
     <t>백히로</t>
@@ -1320,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>459조 2880억 546만</t>
+    <t>475조 3937억 7377만</t>
   </si>
   <si>
     <t>뷰질</t>
@@ -1329,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
   </si>
   <si>
-    <t>428조 4895억 1975만</t>
+    <t>442조 5355억 7171만</t>
   </si>
   <si>
     <t>순서교체</t>
@@ -1341,7 +1347,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>350조 8823억 93만</t>
+    <t>388조 6571억 5768만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1350,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
   </si>
   <si>
-    <t>325조 1782억 3169만</t>
+    <t>328조 4011억 7299만</t>
   </si>
   <si>
     <t>김천아재</t>
@@ -1359,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>189조 7900억 1786만</t>
+    <t>191조 9759억 7320만</t>
   </si>
   <si>
     <t>무썬</t>
@@ -1377,7 +1383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A5%EB%A7%A5</t>
   </si>
   <si>
-    <t>143조 4785억 4970만</t>
+    <t>154조 6437억 2145만</t>
   </si>
   <si>
     <t>성칙이</t>
@@ -1404,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>103조 430억 9139만</t>
+    <t>103조 2703억 3445만</t>
   </si>
   <si>
     <t>kiaer</t>
@@ -1413,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>87조 9127억 8755만</t>
+    <t>95조 3142억 5013만</t>
   </si>
   <si>
     <t>숔숔숔숔</t>
@@ -1422,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>74조 1321억 5923만</t>
+    <t>74조 3806억 7160만</t>
   </si>
   <si>
     <t>안재똥</t>
@@ -1440,7 +1446,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
   </si>
   <si>
-    <t>39조 835억 6119만</t>
+    <t>46조 5516억 6298만</t>
   </si>
   <si>
     <t>보마가될인재</t>
@@ -1458,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
   </si>
   <si>
-    <t>25조 8247억 7168만</t>
+    <t>25조 8446억 3279만</t>
   </si>
   <si>
     <t>기차아저씨</t>
@@ -1476,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>20조 1935억 7880만</t>
+    <t>20조 2491억 561만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1500,9 +1506,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>1경 51조 1568억 2849만</t>
   </si>
   <si>
@@ -1524,6 +1527,15 @@
     <t>2535조 1401억 3160만</t>
   </si>
   <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2123조 2935억 5845만</t>
+  </si>
+  <si>
     <t>달싹</t>
   </si>
   <si>
@@ -1533,22 +1545,13 @@
     <t>2030조 6297억 4815만</t>
   </si>
   <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1841조 1563억 9683만</t>
-  </si>
-  <si>
     <t>26길초</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>1814조 2840억 9265만</t>
+    <t>1815조 2685억 5588만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1557,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>1230조 4957억 4952만</t>
+    <t>1239조 2708억 8326만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1566,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>1133조 6489억 3302만</t>
+    <t>1183조 9034억 3517만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1584,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>837조 3638억 1007만</t>
+    <t>851조 6682억 5370만</t>
   </si>
   <si>
     <t>덜박</t>
@@ -1602,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>594조 6433억 402만</t>
+    <t>599조 1848억 7795만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1611,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>481조 7818억 7594만</t>
+    <t>496조 3223억 8174만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1650,13 +1653,22 @@
     <t>91조 768억 8769만</t>
   </si>
   <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>90조 501억 9749만</t>
+  </si>
+  <si>
     <t>26퐝바</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>88조 8146억 7801만</t>
+    <t>89조 2177억 3532만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1668,13 +1680,13 @@
     <t>84조 3496억 599만</t>
   </si>
   <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>78조 8845억 758만</t>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>72조 6635억 3759만</t>
   </si>
   <si>
     <t>라흐S2</t>
@@ -1701,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>59조 9574억 1766만</t>
+    <t>65조 2633억 1293만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1713,15 +1725,6 @@
     <t>58조 5741억 7634만</t>
   </si>
   <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>57조 9078억 5041만</t>
-  </si>
-  <si>
     <t>브깃</t>
   </si>
   <si>
@@ -1824,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%8F%8C%EC%9D%B4%EA%B5%B4%EB%8F%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1102조 8075억 3116만</t>
+    <t>1117조 8051억 3408만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1833,7 +1836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>497조 8703억 1088만</t>
+    <t>504조 4717억 3522만</t>
   </si>
   <si>
     <t>갓쿠</t>
@@ -1851,7 +1854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
   </si>
   <si>
-    <t>337조 176억 7846만</t>
+    <t>338조 2772억 7034만</t>
   </si>
   <si>
     <t>쏘세용</t>
@@ -1878,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>219조 1882억 4687만</t>
+    <t>220조 457억 6174만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1887,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>144조 7934억 6306만</t>
+    <t>144조 8742억 6883만</t>
   </si>
   <si>
     <t>우당탕탼</t>
@@ -1896,7 +1899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
   </si>
   <si>
-    <t>118조 2427억 4076만</t>
+    <t>118조 4473억 2355만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1905,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>97조 306억 5919만</t>
+    <t>98조 2803억 696만</t>
   </si>
   <si>
     <t>잼이유</t>
@@ -1914,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
   </si>
   <si>
-    <t>68조 9635억 2408만</t>
+    <t>69조 1464억 1630만</t>
   </si>
   <si>
     <t>사철화</t>
@@ -1923,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%B2%A0%ED%99%94</t>
   </si>
   <si>
-    <t>63조 5113억 4896만</t>
+    <t>67조 6464억 6921만</t>
   </si>
   <si>
     <t>붕붕월드</t>
@@ -1941,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>51조 2885억 1759만</t>
+    <t>51조 6258억 9026만</t>
   </si>
   <si>
     <t>커피숍</t>
@@ -1953,6 +1956,15 @@
     <t>27조 8048억 345만</t>
   </si>
   <si>
+    <t>Subaru</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
+  </si>
+  <si>
+    <t>26조 4424억 4277만</t>
+  </si>
+  <si>
     <t>뵤으</t>
   </si>
   <si>
@@ -1962,13 +1974,16 @@
     <t>26조 2248억 5501만</t>
   </si>
   <si>
-    <t>Subaru</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Subaru</t>
-  </si>
-  <si>
-    <t>25조 2117억 1423만</t>
+    <t>킴밍끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>22조 9554억 7970만</t>
   </si>
   <si>
     <t>도시리</t>
@@ -1980,25 +1995,13 @@
     <t>22조 9492억 5119만</t>
   </si>
   <si>
-    <t>킴밍끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>22조 7916억 1972만</t>
-  </si>
-  <si>
     <t>57년김춘배</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>19조 7903억 8984만</t>
+    <t>20조 5918억 3269만</t>
   </si>
   <si>
     <t>시네루최</t>
@@ -2043,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%8D</t>
   </si>
   <si>
-    <t>2775조 8545억 4823만</t>
+    <t>3273조 3182억 5815만</t>
   </si>
   <si>
     <t>켘켘3</t>
@@ -2052,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%98%EC%BC%983</t>
   </si>
   <si>
-    <t>2193조 2531억 2214만</t>
+    <t>2642조 4976억 5721만</t>
   </si>
   <si>
     <t>샤프리</t>
@@ -2070,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8%EB%8B%AC</t>
   </si>
   <si>
-    <t>779조 1618억 552만</t>
+    <t>820조 905억 5122만</t>
   </si>
   <si>
     <t>인두겁</t>
@@ -2079,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>505조 2960억 1220만</t>
+    <t>519조 7203억 1399만</t>
   </si>
   <si>
     <t>소잦ol</t>
@@ -2097,7 +2100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>235조 372억 7611만</t>
+    <t>238조 1928억 7003만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2106,13 +2109,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%9D%98%EA%B8%B0%EC%9A%B4</t>
   </si>
   <si>
-    <t>189조 9265억 2860만</t>
+    <t>190조 2229억 7658만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>138조 3174억 7293만</t>
+    <t>148조 5490억 4644만</t>
   </si>
   <si>
     <t>마리아네</t>
@@ -2121,7 +2124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A6%AC%EC%95%84%EB%84%A4</t>
   </si>
   <si>
-    <t>87조 2035억 4809만</t>
+    <t>94조 6247억 2112만</t>
   </si>
   <si>
     <t>포근한소리</t>
@@ -2139,7 +2142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%8A%A4%EC%A0%9C</t>
   </si>
   <si>
-    <t>51조 6548억 8869만</t>
+    <t>52조 5842억 5531만</t>
   </si>
   <si>
     <t>본분</t>
@@ -2187,6 +2190,15 @@
     <t>30조 191억 6568만</t>
   </si>
   <si>
+    <t>개도둑놈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
+  </si>
+  <si>
+    <t>23조 9483억 620만</t>
+  </si>
+  <si>
     <t>1조투력찍었던</t>
   </si>
   <si>
@@ -2196,15 +2208,6 @@
     <t>22조 6811억 4682만</t>
   </si>
   <si>
-    <t>개도둑놈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%8F%84%EB%91%91%EB%86%88</t>
-  </si>
-  <si>
-    <t>22조 5268억 9024만</t>
-  </si>
-  <si>
     <t>BudriQ</t>
   </si>
   <si>
@@ -2238,7 +2241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%95%ED%99%94</t>
   </si>
   <si>
-    <t>16조 2730억 1760만</t>
+    <t>16조 4689억 7874만</t>
   </si>
   <si>
     <t>진우정</t>
@@ -2265,7 +2268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EB%84%A4</t>
   </si>
   <si>
-    <t>8조 8078억 8915만</t>
+    <t>9조 3912억 7089만</t>
   </si>
   <si>
     <t>킴카</t>
@@ -2274,7 +2277,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EC%B9%B4</t>
   </si>
   <si>
-    <t>7조 5970억 3624만</t>
+    <t>7조 7132억 9972만</t>
   </si>
 </sst>
 </file>
@@ -3130,10 +3133,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3144,16 +3147,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -3165,7 +3168,7 @@
         <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3176,28 +3179,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3208,28 +3211,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3240,16 +3243,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -3258,10 +3261,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3272,16 +3275,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -3290,10 +3293,10 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3304,16 +3307,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -3322,10 +3325,10 @@
         <v>95</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3336,28 +3339,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3368,16 +3371,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -3386,10 +3389,10 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3400,16 +3403,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -3418,10 +3421,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3432,28 +3435,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3464,16 +3467,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -3482,10 +3485,10 @@
         <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3496,7 +3499,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>149</v>
@@ -3514,7 +3517,7 @@
         <v>151</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>152</v>
@@ -3546,7 +3549,7 @@
         <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>156</v>
@@ -3560,28 +3563,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3592,16 +3595,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -3610,10 +3613,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3624,28 +3627,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3659,25 +3662,25 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3688,16 +3691,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -3706,10 +3709,10 @@
         <v>151</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3720,7 +3723,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>177</v>
@@ -3738,7 +3741,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>179</v>
@@ -3752,28 +3755,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3787,25 +3790,25 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3819,25 +3822,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3851,25 +3854,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3883,13 +3886,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -3898,10 +3901,10 @@
         <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3912,7 +3915,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>23</v>
@@ -3921,19 +3924,19 @@
         <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3944,16 +3947,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -3962,10 +3965,10 @@
         <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3976,16 +3979,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -3994,10 +3997,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4052,7 +4055,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4102,19 +4105,19 @@
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4128,13 +4131,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -4143,10 +4146,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4160,13 +4163,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -4175,10 +4178,10 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4189,16 +4192,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -4207,10 +4210,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4221,16 +4224,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -4239,10 +4242,10 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4253,28 +4256,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4285,16 +4288,16 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -4303,10 +4306,10 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4317,28 +4320,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4349,28 +4352,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4381,16 +4384,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -4399,10 +4402,10 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4413,28 +4416,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4445,28 +4448,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4477,16 +4480,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -4495,10 +4498,10 @@
         <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4509,16 +4512,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -4527,10 +4530,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4541,16 +4544,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -4559,10 +4562,10 @@
         <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4576,25 +4579,25 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4605,28 +4608,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4637,16 +4640,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -4655,10 +4658,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4669,16 +4672,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -4687,10 +4690,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4704,13 +4707,13 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -4719,10 +4722,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4733,28 +4736,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4765,16 +4768,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -4783,10 +4786,10 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4797,28 +4800,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4832,13 +4835,13 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -4847,10 +4850,10 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4864,13 +4867,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -4879,10 +4882,10 @@
         <v>151</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4896,25 +4899,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4928,13 +4931,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -4943,10 +4946,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4957,16 +4960,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -4975,10 +4978,10 @@
         <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4989,16 +4992,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -5007,10 +5010,10 @@
         <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5021,16 +5024,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -5039,10 +5042,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5097,7 +5100,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5141,13 +5144,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -5156,10 +5159,10 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5173,25 +5176,25 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5205,13 +5208,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -5220,10 +5223,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5234,28 +5237,28 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5266,16 +5269,16 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -5284,10 +5287,10 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5298,16 +5301,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -5316,10 +5319,10 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5330,16 +5333,16 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -5348,10 +5351,10 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5362,28 +5365,28 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5394,16 +5397,16 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -5412,10 +5415,10 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5426,16 +5429,16 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -5444,10 +5447,10 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5458,28 +5461,28 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5490,28 +5493,28 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5522,16 +5525,16 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -5540,10 +5543,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5554,28 +5557,28 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5586,28 +5589,28 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5621,25 +5624,25 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>350</v>
+        <v>151</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5650,28 +5653,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5682,16 +5685,16 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -5700,10 +5703,10 @@
         <v>151</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5714,28 +5717,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5749,13 +5752,13 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -5764,10 +5767,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5778,28 +5781,28 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5810,28 +5813,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5842,28 +5845,28 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5877,25 +5880,25 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5909,13 +5912,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -5924,10 +5927,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5941,25 +5944,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5973,13 +5976,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -5988,10 +5991,10 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6002,28 +6005,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6034,28 +6037,28 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6066,7 +6069,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>40</v>
@@ -6075,19 +6078,19 @@
         <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6186,13 +6189,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -6201,10 +6204,10 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6218,13 +6221,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -6233,10 +6236,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6250,13 +6253,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -6265,10 +6268,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6279,16 +6282,16 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -6297,10 +6300,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6311,16 +6314,16 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -6329,10 +6332,10 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6343,16 +6346,16 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -6361,10 +6364,10 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6375,16 +6378,16 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -6393,10 +6396,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6407,16 +6410,16 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -6425,10 +6428,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6439,16 +6442,16 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -6457,10 +6460,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6471,28 +6474,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6503,7 +6506,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>47</v>
@@ -6512,19 +6515,19 @@
         <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6535,16 +6538,16 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -6553,10 +6556,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6567,28 +6570,28 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6599,28 +6602,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6631,28 +6634,28 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6666,25 +6669,25 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6695,16 +6698,16 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -6713,10 +6716,10 @@
         <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6727,16 +6730,16 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -6745,10 +6748,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6759,16 +6762,16 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -6777,10 +6780,10 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6794,25 +6797,25 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6823,16 +6826,16 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -6841,10 +6844,10 @@
         <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6855,16 +6858,16 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -6873,10 +6876,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6887,28 +6890,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6922,13 +6925,13 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -6937,10 +6940,10 @@
         <v>151</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6954,25 +6957,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6986,25 +6989,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7018,13 +7021,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -7033,10 +7036,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7047,28 +7050,28 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7079,16 +7082,16 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -7097,10 +7100,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7111,16 +7114,16 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -7129,10 +7132,10 @@
         <v>151</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7231,13 +7234,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -7246,10 +7249,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7269,19 +7272,19 @@
         <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>489</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7295,25 +7298,25 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7324,16 +7327,16 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7342,10 +7345,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7356,28 +7359,28 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7388,28 +7391,28 @@
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7420,16 +7423,16 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -7438,10 +7441,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7452,16 +7455,16 @@
         <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -7470,10 +7473,10 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7484,28 +7487,28 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7516,16 +7519,16 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -7534,10 +7537,10 @@
         <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7548,16 +7551,16 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -7566,10 +7569,10 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7580,28 +7583,28 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7612,28 +7615,28 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7644,28 +7647,28 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7676,28 +7679,28 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7711,13 +7714,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -7726,10 +7729,10 @@
         <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7740,28 +7743,28 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7772,16 +7775,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -7790,10 +7793,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7804,28 +7807,28 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7839,25 +7842,25 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>435</v>
+        <v>151</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>297</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7868,28 +7871,28 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>437</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>298</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7900,28 +7903,28 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7932,16 +7935,16 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -7950,10 +7953,10 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7967,25 +7970,25 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7999,25 +8002,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8031,25 +8034,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8063,25 +8066,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8092,16 +8095,16 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -8110,10 +8113,10 @@
         <v>151</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8124,16 +8127,16 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -8142,10 +8145,10 @@
         <v>151</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8156,16 +8159,16 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -8174,10 +8177,10 @@
         <v>151</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8276,13 +8279,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -8294,7 +8297,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8308,13 +8311,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -8323,10 +8326,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>489</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8340,13 +8343,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8358,7 +8361,7 @@
         <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8369,28 +8372,28 @@
         <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8401,16 +8404,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8419,10 +8422,10 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8433,28 +8436,28 @@
         <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8465,7 +8468,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>63</v>
@@ -8474,19 +8477,19 @@
         <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8497,28 +8500,28 @@
         <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8529,28 +8532,28 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8561,28 +8564,28 @@
         <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8593,16 +8596,16 @@
         <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8611,10 +8614,10 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8625,16 +8628,16 @@
         <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -8643,10 +8646,10 @@
         <v>151</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8657,16 +8660,16 @@
         <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -8675,10 +8678,10 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8689,28 +8692,28 @@
         <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8721,16 +8724,16 @@
         <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -8739,10 +8742,10 @@
         <v>151</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8756,25 +8759,25 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8785,28 +8788,28 @@
         <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8817,16 +8820,16 @@
         <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8835,10 +8838,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8849,16 +8852,16 @@
         <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8867,10 +8870,10 @@
         <v>151</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8884,25 +8887,25 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8913,16 +8916,16 @@
         <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8931,10 +8934,10 @@
         <v>151</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8945,28 +8948,28 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8977,28 +8980,28 @@
         <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9012,25 +9015,25 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9044,25 +9047,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
+        <v>649</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9076,25 +9079,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>651</v>
+        <v>210</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9108,13 +9111,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9123,10 +9126,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9137,28 +9140,28 @@
         <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9169,16 +9172,16 @@
         <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -9187,10 +9190,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9288,13 +9291,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -9303,10 +9306,10 @@
         <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9320,13 +9323,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -9338,7 +9341,7 @@
         <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9352,13 +9355,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -9367,10 +9370,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9381,16 +9384,16 @@
         <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9399,10 +9402,10 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9413,28 +9416,28 @@
         <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9445,16 +9448,16 @@
         <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9463,10 +9466,10 @@
         <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9477,16 +9480,16 @@
         <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9495,10 +9498,10 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9509,16 +9512,16 @@
         <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9527,10 +9530,10 @@
         <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9541,28 +9544,28 @@
         <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9573,16 +9576,16 @@
         <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9591,10 +9594,10 @@
         <v>151</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9605,7 +9608,7 @@
         <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>70</v>
@@ -9614,19 +9617,19 @@
         <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9637,16 +9640,16 @@
         <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -9655,10 +9658,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9669,28 +9672,28 @@
         <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9701,16 +9704,16 @@
         <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -9719,10 +9722,10 @@
         <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9733,28 +9736,28 @@
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9768,25 +9771,25 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9797,16 +9800,16 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -9815,10 +9818,10 @@
         <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9829,16 +9832,16 @@
         <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9847,10 +9850,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9861,28 +9864,28 @@
         <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9896,25 +9899,25 @@
         <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>209</v>
+        <v>298</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9925,28 +9928,28 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9957,16 +9960,16 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9975,10 +9978,10 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9989,28 +9992,28 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10024,13 +10027,13 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -10039,10 +10042,10 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10056,13 +10059,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -10071,10 +10074,10 @@
         <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10088,25 +10091,25 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>384</v>
+        <v>649</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10120,25 +10123,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10149,28 +10152,28 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10181,16 +10184,16 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -10199,10 +10202,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="셀린느" sheetId="2" r:id="rId2"/>
-    <sheet name="딸기키우기" sheetId="3" r:id="rId3"/>
+    <sheet name="딸기키우기" sheetId="2" r:id="rId2"/>
+    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
     <sheet name="이콩" sheetId="4" r:id="rId4"/>
     <sheet name="고점" sheetId="5" r:id="rId5"/>
     <sheet name="LUXURY" sheetId="6" r:id="rId6"/>
@@ -19,10 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">딸기키우기!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">고점!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">딸기키우기!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">라때는말이야!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">싸이월드!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">이콩!$A$1:$J$31</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="746">
   <si>
     <t>guild_name</t>
   </si>
@@ -72,15 +72,48 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>7경 5604조 5340억 916만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>2026.05.17</t>
+  </si>
+  <si>
     <t>셀린느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 2</t>
   </si>
   <si>
@@ -93,10 +126,7 @@
     <t>Lv.9</t>
   </si>
   <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>7경 9850조 1886억 4529만</t>
+    <t>8경 126조 4950억 5703만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -105,172 +135,529 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.05.16</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>7경 5060조 7518억 9559만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
     <t>이콩</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>17경 2039조 2785억 6387만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>10경 1382조 1405억 2872만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>7경 5907조 4239억 562만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>9경 4604조 6161억 2005만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10경 4179조 4394억 5432만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>5경 55조 1425억 7737만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>쥬정뱅이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>6977조 1367억 2816만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>임순이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3228조 4676억 3560만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>귀여워서미안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>2805조 3689억 2360만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>밀프푸씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
+  </si>
+  <si>
+    <t>2287조 9054억 1438만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>쑥국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1531조 7565억 775만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>린뜌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1164조 8251억 2253만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>베티베디베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>672조 6620억 6812만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>냉도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>656조 9558억 6537만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>약해진쭌석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>617조 2885억 7558만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>엔젤가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>536조 902억 315만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>노득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
+  </si>
+  <si>
+    <t>514조 7171억 2153만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>섴히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
+  </si>
+  <si>
+    <t>491조 3307억 6609만</t>
+  </si>
+  <si>
+    <t>피치에이드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>479조 7718억 7122만</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>17경 241조 1254억 3924만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>10경 1292조 4019억 2755만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>7경 5666조 9054억 7698만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>9경 4191조 7738억 2037만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10경 4130조 1715억 1958만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>핫장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>440조 5363억 8975만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>겸찰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
+  </si>
+  <si>
+    <t>377조 1931억 6904만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잉잉기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>334조 5787억 6657만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>키은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>299조 431억 7332만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>사마련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>233조 7154억 7456만</t>
+  </si>
+  <si>
+    <t>헛점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
+  </si>
+  <si>
+    <t>224조 7612억 8658만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>개점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
+  </si>
+  <si>
+    <t>220조 9095억 1753만</t>
+  </si>
+  <si>
+    <t>쵸꼬님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>217조 4543억 8993만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>앨리스빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>212조 5875억 9857만</t>
+  </si>
+  <si>
+    <t>연지임당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>206조 9514억 9821만</t>
+  </si>
+  <si>
+    <t>81학찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>196조 4973억 8641만</t>
+  </si>
+  <si>
+    <t>챠재범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
+  </si>
+  <si>
+    <t>163조 9080억 9320만</t>
+  </si>
+  <si>
+    <t>머쓰윽타드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
+  </si>
+  <si>
+    <t>150조 2180억 3272만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>핫딜만삼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
+  </si>
+  <si>
+    <t>109조 1177억 2813만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>핫두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>100조 1050억 8254만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>샤갈츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
+  </si>
+  <si>
+    <t>97조 5370억 4151만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -279,19 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3경 5592조 7889억 7365만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>3경 5617조 4307억 5046만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -300,46 +675,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
     <t>113</t>
   </si>
   <si>
     <t>1경 914조 5474억 2169만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>돈스</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
     <t>1경 904조 1185억 7211만</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>진자이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>7442조 8929억 4568만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>7585조 4905억 7193만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -348,16 +708,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>4129조 2553억 9084만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>4156조 3230억 1076만</t>
   </si>
   <si>
     <t>오리부엉이</t>
@@ -366,13 +717,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B6%80%EC%97%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1233조 1346억 5863만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>1245조 5490억 7311만</t>
   </si>
   <si>
     <t>여사</t>
@@ -381,15 +726,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>1074조 896억 9253만</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>니달리신</t>
   </si>
   <si>
@@ -399,9 +738,6 @@
     <t>1042조 3116억 6204만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>단풍노비</t>
   </si>
   <si>
@@ -411,9 +747,6 @@
     <t>954조 3229억 9711만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>약어</t>
   </si>
   <si>
@@ -423,25 +756,16 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>811조 9295억 7976만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>소소채2</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>795조 9442억 9462만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>799조 1528억 3322만</t>
   </si>
   <si>
     <t>닼나짱2</t>
@@ -450,13 +774,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
   </si>
   <si>
-    <t>107</t>
-  </si>
-  <si>
     <t>711조 3418억 6684만</t>
   </si>
   <si>
-    <t>13</t>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>477조 7372억 5581만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -468,31 +795,13 @@
     <t>476조 8196억 1413만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>453조 8899억 9995만</t>
-  </si>
-  <si>
     <t>잼포즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>438조 5517억 9938만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>450조 1604억 495만</t>
   </si>
   <si>
     <t>뽀삐스</t>
@@ -504,19 +813,13 @@
     <t>411조 6165억 8335만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>하후돈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>362조 9074억 865만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>375조 4927억 454만</t>
   </si>
   <si>
     <t>트라이던트</t>
@@ -525,13 +828,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8A%B8%EB%9D%BC%EC%9D%B4%EB%8D%98%ED%8A%B8</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>332조 1973억 1171만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>333조 552억 8499만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -543,6 +840,15 @@
     <t>320조 9854억 4596만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>311조 9481억 8445만</t>
+  </si>
+  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
@@ -552,18 +858,6 @@
     <t>308조 4617억 340만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>305조 7514억 5636만</t>
-  </si>
-  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -573,19 +867,13 @@
     <t>156조 2682억 1016만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>POSCO</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=POSCO</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>149조 8311억 7292만</t>
+    <t>149조 8439억 4629만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -594,9 +882,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
     <t>96조 8587억 9464만</t>
   </si>
   <si>
@@ -606,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>92조 4757억 3454만</t>
+    <t>92조 9258억 4088만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -621,6 +906,12 @@
     <t>90조 3499억 3851만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>76조 4594억 9964만</t>
+  </si>
+  <si>
     <t>포뇨야</t>
   </si>
   <si>
@@ -630,21 +921,6 @@
     <t>71조 5603억 8398만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>65조 6418억 239만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>몽호</t>
   </si>
   <si>
@@ -654,9 +930,6 @@
     <t>56조 2620억 6423만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -669,279 +942,6 @@
     <t>53조 811억 6540만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%98z</t>
-  </si>
-  <si>
-    <t>5경 55조 1425억 7737만</t>
-  </si>
-  <si>
-    <t>쥬정뱅이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%EC%A0%95%EB%B1%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6739조 8118억 4479만</t>
-  </si>
-  <si>
-    <t>임순이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%88%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3228조 4676억 3560만</t>
-  </si>
-  <si>
-    <t>귀여워서미안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%AC%EC%9B%8C%EC%84%9C%EB%AF%B8%EC%95%88</t>
-  </si>
-  <si>
-    <t>2799조 6857억 5214만</t>
-  </si>
-  <si>
-    <t>밀프푸씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
-  </si>
-  <si>
-    <t>2287조 9054억 1438만</t>
-  </si>
-  <si>
-    <t>쑥국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A5%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>1513조 579억 3563만</t>
-  </si>
-  <si>
-    <t>린뜌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EB%9C%8C</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1161조 8119억 5088만</t>
-  </si>
-  <si>
-    <t>베티베디베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%ED%8B%B0%EB%B2%A0%EB%94%94%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>671조 5924억 6971만</t>
-  </si>
-  <si>
-    <t>냉도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%84</t>
-  </si>
-  <si>
-    <t>656조 9558억 6537만</t>
-  </si>
-  <si>
-    <t>약해진쭌석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%B4%EC%A7%84%EC%AD%8C%EC%84%9D</t>
-  </si>
-  <si>
-    <t>617조 2885억 7558만</t>
-  </si>
-  <si>
-    <t>엔젤가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EC%A0%A4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>523조 901억 2403만</t>
-  </si>
-  <si>
-    <t>노득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
-  </si>
-  <si>
-    <t>502조 5881억 8650만</t>
-  </si>
-  <si>
-    <t>섴히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B4%ED%9E%88</t>
-  </si>
-  <si>
-    <t>491조 3307억 6609만</t>
-  </si>
-  <si>
-    <t>피치에이드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%98%EC%97%90%EC%9D%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>462조 7270억 1897만</t>
-  </si>
-  <si>
-    <t>핫장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>415조 9967억 3924만</t>
-  </si>
-  <si>
-    <t>잉잉기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>309조 7179억 7806만</t>
-  </si>
-  <si>
-    <t>키은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>299조 431억 7332만</t>
-  </si>
-  <si>
-    <t>사마련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%88%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>233조 7154억 7456만</t>
-  </si>
-  <si>
-    <t>겸찰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B8%EC%B0%B0</t>
-  </si>
-  <si>
-    <t>233조 5121억 7783만</t>
-  </si>
-  <si>
-    <t>헛점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%9B%EC%A0%90</t>
-  </si>
-  <si>
-    <t>221조 2769억 8033만</t>
-  </si>
-  <si>
-    <t>개점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
-  </si>
-  <si>
-    <t>220조 9095억 1753만</t>
-  </si>
-  <si>
-    <t>앨리스빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EB%A6%AC%EC%8A%A4%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>212조 5875억 9857만</t>
-  </si>
-  <si>
-    <t>쵸꼬님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EA%BC%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>205조 8807억 5331만</t>
-  </si>
-  <si>
-    <t>연지임당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%A7%80%EC%9E%84%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>199조 9599억 432만</t>
-  </si>
-  <si>
-    <t>81학찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=81%ED%95%99%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>196조 4973억 8641만</t>
-  </si>
-  <si>
-    <t>챠재범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
-  </si>
-  <si>
-    <t>149조 4516억 7157만</t>
-  </si>
-  <si>
-    <t>머쓰윽타드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%93%B0%EC%9C%BD%ED%83%80%EB%93%9C</t>
-  </si>
-  <si>
-    <t>146조 135억 7414만</t>
-  </si>
-  <si>
-    <t>핫딜만삼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%EB%A7%8C%EC%82%BC</t>
-  </si>
-  <si>
-    <t>107조 1900억 4990만</t>
-  </si>
-  <si>
-    <t>핫두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>100조 1050억 8254만</t>
-  </si>
-  <si>
-    <t>샤갈츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EA%B0%88%EC%B8%84</t>
-  </si>
-  <si>
-    <t>97조 4377억 1675만</t>
-  </si>
-  <si>
     <t>데카짱3</t>
   </si>
   <si>
@@ -951,7 +951,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>12경 970조 733억 4979만</t>
+    <t>12경 1135조 3832억 8320만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -963,7 +963,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>3경 2947조 6339억 8616만</t>
+    <t>3경 4546조 9540억 5262만</t>
   </si>
   <si>
     <t>실민</t>
@@ -1053,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EC%A8%A9</t>
   </si>
   <si>
-    <t>311조 6199억 9097만</t>
+    <t>312조 1928억 7516만</t>
   </si>
   <si>
     <t>꽃나래</t>
@@ -1062,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>246조 8973억 3128만</t>
+    <t>256조 480억 4967만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1080,7 +1080,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
   </si>
   <si>
-    <t>177조 5144억 4620만</t>
+    <t>184조 4930억 1588만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>168조 1664억 9280만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -1089,19 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>165조 4011억 665만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>162조 9128억 357만</t>
+    <t>167조 9719억 4194만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1110,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>137조 6461억 9485만</t>
+    <t>142조 5277억 2792만</t>
   </si>
   <si>
     <t>에망</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>132조 4026억 7303만</t>
+    <t>135조 89억 6129만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>56조 5366억 4222만</t>
+    <t>56조 7492억 87만</t>
   </si>
   <si>
     <t>빠나쨩</t>
@@ -1164,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EC%A8%A9</t>
   </si>
   <si>
-    <t>43조 4744억 1835만</t>
+    <t>44조 4589억 5495만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>20조 895억 5165만</t>
+    <t>20조 2441억 6010만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1194,7 +1194,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>13조 2668억 876만</t>
+    <t>13조 3810억 3630만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1203,7 +1203,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>5조 6796억 7614만</t>
+    <t>5조 6897억 7385만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1221,7 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>1조 8931억 2634만</t>
+    <t>1조 9316억 6094만</t>
   </si>
   <si>
     <t>THE끌림</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>7141조 7308억 6306만</t>
+    <t>7171조 8465억 7184만</t>
   </si>
   <si>
     <t>픠즈</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%A0%EC%A6%88</t>
   </si>
   <si>
-    <t>1547조 6184억 2408만</t>
+    <t>1552조 2240억 708만</t>
   </si>
   <si>
     <t>S2베코</t>
@@ -1311,13 +1311,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%94%EB%98%94%EC%9E%89</t>
   </si>
   <si>
-    <t>970조 2810억 789만</t>
+    <t>974조 1882억 3306만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%8C%A1%EC%9E%89</t>
   </si>
   <si>
-    <t>870조 1219억 8420만</t>
+    <t>871조 315억 3631만</t>
   </si>
   <si>
     <t>백히로</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%ED%9E%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>475조 3937억 7377만</t>
+    <t>486조 7715억 6413만</t>
   </si>
   <si>
     <t>뷰질</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B7%B0%EC%A7%88</t>
   </si>
   <si>
-    <t>442조 5355억 7171만</t>
+    <t>452조 4213억 7610만</t>
   </si>
   <si>
     <t>순서교체</t>
@@ -1347,7 +1347,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>388조 6571억 5768만</t>
+    <t>398조 2051억 9418만</t>
   </si>
   <si>
     <t>근접맞나이거</t>
@@ -1356,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%A0%91%EB%A7%9E%EB%82%98%EC%9D%B4%EA%B1%B0</t>
   </si>
   <si>
-    <t>328조 4011억 7299만</t>
+    <t>336조 5240억 7414만</t>
   </si>
   <si>
     <t>김천아재</t>
@@ -1365,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B2%9C%EC%95%84%EC%9E%AC</t>
   </si>
   <si>
-    <t>191조 9759억 7320만</t>
+    <t>192조 3230억 3221만</t>
   </si>
   <si>
     <t>무썬</t>
@@ -1374,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8D%AC</t>
   </si>
   <si>
-    <t>179조 6205억 5618만</t>
+    <t>180조 9990억 3661만</t>
   </si>
   <si>
     <t>맥맥</t>
@@ -1410,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%95%84%EC%98%A8%ED%99%8D%EA%B5%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>103조 2703억 3445만</t>
+    <t>113조 2027억 527만</t>
   </si>
   <si>
     <t>kiaer</t>
@@ -1419,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=kiaer</t>
   </si>
   <si>
-    <t>95조 3142억 5013만</t>
+    <t>96조 730억 156만</t>
   </si>
   <si>
     <t>숔숔숔숔</t>
@@ -1428,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%94%EC%88%94%EC%88%94%EC%88%94</t>
   </si>
   <si>
-    <t>74조 3806억 7160만</t>
+    <t>74조 4610억 6912만</t>
   </si>
   <si>
     <t>안재똥</t>
@@ -1446,16 +1446,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%83%B7</t>
   </si>
   <si>
-    <t>46조 5516억 6298만</t>
-  </si>
-  <si>
-    <t>보마가될인재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EA%B0%80%EB%90%A0%EC%9D%B8%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>27조 8516억 579만</t>
+    <t>47조 102억 9559만</t>
   </si>
   <si>
     <t>탱탱볼탱탱볼</t>
@@ -1464,7 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%83%B1%EB%B3%BC%ED%83%B1%ED%83%B1%EB%B3%BC</t>
   </si>
   <si>
-    <t>25조 8446억 3279만</t>
+    <t>26조 1887억 9875만</t>
   </si>
   <si>
     <t>기차아저씨</t>
@@ -1482,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%BA%91</t>
   </si>
   <si>
-    <t>20조 2491억 561만</t>
+    <t>20조 2635억 4690만</t>
   </si>
   <si>
     <t>이서지용</t>
@@ -1533,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>2123조 2935억 5845만</t>
+    <t>2266조 6350억 3805만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1560,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>1239조 2708억 8326만</t>
+    <t>1256조 9257억 8837만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -1569,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>1183조 9034억 3517만</t>
+    <t>1188조 4141억 330만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1587,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>851조 6682억 5370만</t>
+    <t>853조 789억 9482만</t>
   </si>
   <si>
     <t>덜박</t>
@@ -1605,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>599조 1848억 7795만</t>
+    <t>630조 2500억 1893만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1614,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>496조 3223억 8174만</t>
+    <t>500조 4911억 2907만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1623,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>199조 9367억 4325만</t>
+    <t>218조 7034억 357만</t>
   </si>
   <si>
     <t>륵스리</t>
@@ -1650,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
   </si>
   <si>
-    <t>91조 768억 8769만</t>
+    <t>103조 2432억 3632만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1659,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>90조 501억 9749만</t>
+    <t>96조 1498억 4307만</t>
   </si>
   <si>
     <t>26퐝바</t>
@@ -1668,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>89조 2177억 3532만</t>
+    <t>89조 4719억 8812만</t>
   </si>
   <si>
     <t>메키무라딘</t>
@@ -1686,7 +1677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>72조 6635억 3759만</t>
+    <t>73조 3278억 4723만</t>
   </si>
   <si>
     <t>라흐S2</t>
@@ -1740,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>32조 3476억 5895만</t>
+    <t>32조 7631억 8835만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1767,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%A4%84%EA%B9%8C</t>
   </si>
   <si>
-    <t>5경 8640조 6567억 4680만</t>
+    <t>5경 9021조 4247억 8690만</t>
   </si>
   <si>
     <t>키노눙</t>
@@ -1836,7 +1827,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>504조 4717억 3522만</t>
+    <t>507조 3974억 6617만</t>
+  </si>
+  <si>
+    <t>김모나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
+  </si>
+  <si>
+    <t>347조 2766억 5611만</t>
   </si>
   <si>
     <t>갓쿠</t>
@@ -1848,15 +1848,6 @@
     <t>344조 3485억 1584만</t>
   </si>
   <si>
-    <t>김모나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%AA%A8%EB%82%98</t>
-  </si>
-  <si>
-    <t>338조 2772억 7034만</t>
-  </si>
-  <si>
     <t>쏘세용</t>
   </si>
   <si>
@@ -1881,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%BB%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>220조 457억 6174만</t>
+    <t>220조 4953억 3321만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1890,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>144조 8742억 6883만</t>
+    <t>144조 9660억 8774만</t>
   </si>
   <si>
     <t>우당탕탼</t>
@@ -1899,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%B9%ED%83%95%ED%83%BC</t>
   </si>
   <si>
-    <t>118조 4473억 2355만</t>
+    <t>118조 9077억 2827만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1917,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%EC%9D%B4%EC%9C%A0</t>
   </si>
   <si>
-    <t>69조 1464억 1630만</t>
+    <t>78조 5150억 3287만</t>
   </si>
   <si>
     <t>사철화</t>
@@ -1935,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EB%B6%95%EC%9B%94%EB%93%9C</t>
   </si>
   <si>
-    <t>56조 239억 7473만</t>
+    <t>64조 3078억 4122만</t>
   </si>
   <si>
     <t>얼음조아</t>
@@ -1944,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>51조 6258억 9026만</t>
+    <t>52조 7819억 3957만</t>
   </si>
   <si>
     <t>커피숍</t>
@@ -1962,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=Subaru</t>
   </si>
   <si>
-    <t>26조 4424억 4277만</t>
+    <t>26조 5509억 2316만</t>
   </si>
   <si>
     <t>뵤으</t>
@@ -1980,36 +1971,36 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B0%8D%EB%81%BC</t>
   </si>
   <si>
+    <t>23조 1858억 1469만</t>
+  </si>
+  <si>
+    <t>도시리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>22조 9492억 5119만</t>
+  </si>
+  <si>
+    <t>57년김춘배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>20조 5918억 3269만</t>
+  </si>
+  <si>
+    <t>시네루최</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>22조 9554억 7970만</t>
-  </si>
-  <si>
-    <t>도시리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%8B%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>22조 9492억 5119만</t>
-  </si>
-  <si>
-    <t>57년김춘배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>20조 5918억 3269만</t>
-  </si>
-  <si>
-    <t>시네루최</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%84%A4%EB%A3%A8%EC%B5%9C</t>
-  </si>
-  <si>
     <t>14조 3488억 8737만</t>
   </si>
   <si>
@@ -2082,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EB%91%90%EA%B2%81</t>
   </si>
   <si>
-    <t>519조 7203억 1399만</t>
+    <t>525조 1527억 7498만</t>
   </si>
   <si>
     <t>소잦ol</t>
@@ -2091,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%9E%A6ol</t>
   </si>
   <si>
-    <t>289조 5792억 7570만</t>
+    <t>299조 3420억 2509만</t>
   </si>
   <si>
     <t>랏해</t>
@@ -2100,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%ED%95%B4</t>
   </si>
   <si>
-    <t>238조 1928억 7003만</t>
+    <t>262조 5771억 6097만</t>
   </si>
   <si>
     <t>아빠의기운</t>
@@ -2109,13 +2100,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%